--- a/GICS_SubIndustry_Leaderboard.xlsx
+++ b/GICS_SubIndustry_Leaderboard.xlsx
@@ -483,7 +483,7 @@
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
@@ -613,19 +613,19 @@
         <v>0.08663249041434457</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>1.244677861413887</v>
+        <v>1.244677842958211</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>1.792525286794282</v>
+        <v>1.792525328888184</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>4.16361532964973</v>
+        <v>4.163615367838757</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>4.979059402321011</v>
+        <v>4.979059309050459</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.6478409427172583</v>
+        <v>0.6478409376740997</v>
       </c>
     </row>
     <row r="3">
@@ -672,16 +672,16 @@
         <v>0.7032021173523821</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>1.087554450760204</v>
+        <v>1.087554521803245</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>1.255210183550469</v>
+        <v>1.255210352159859</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>1.661466236717235</v>
+        <v>1.661465914727214</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>0.3845145587613037</v>
+        <v>0.3845145055231329</v>
       </c>
     </row>
     <row r="4">
@@ -725,19 +725,19 @@
         <v>0.4034679045372773</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0.3191086466698497</v>
+        <v>0.3191086461533874</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.6822238415383096</v>
+        <v>0.6822238416394506</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0.9189945435862914</v>
+        <v>0.9189945839445026</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0.5292787950829703</v>
+        <v>0.5292788272931989</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.1406180207398831</v>
+        <v>0.1406180294968576</v>
       </c>
     </row>
     <row r="5">
@@ -787,13 +787,13 @@
         <v>0.700234671603098</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>1.445044275661495</v>
+        <v>1.445044318518835</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>5.159482394549803</v>
+        <v>5.159482419869979</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0.6695978285496773</v>
+        <v>0.6695978337208821</v>
       </c>
     </row>
     <row r="6">
@@ -837,19 +837,19 @@
         <v>-0.06104460085121235</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.3922115354298273</v>
+        <v>0.39221147588384</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>0.7182142874199335</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>1.806413131255643</v>
+        <v>1.806412911350844</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>2.965586040809177</v>
+        <v>2.965585747412105</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.5790007504110437</v>
+        <v>0.5790007134828588</v>
       </c>
     </row>
     <row r="7">
@@ -899,13 +899,13 @@
         <v>0.7148199980944048</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.6597446028585605</v>
+        <v>0.6597444657071088</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>1.027456268139173</v>
+        <v>1.027455858830626</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0.2656603213379691</v>
+        <v>0.2656602361662805</v>
       </c>
     </row>
     <row r="8">
@@ -952,16 +952,16 @@
         <v>0.5783249968015878</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.5904258217059926</v>
+        <v>0.5904258085861832</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>1.14665316150183</v>
+        <v>1.146653129684827</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>2.230727581484355</v>
+        <v>2.230727550770774</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.3644079996347145</v>
+        <v>0.3644079861621557</v>
       </c>
     </row>
     <row r="9">
@@ -1005,19 +1005,19 @@
         <v>-0.07396321785908144</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.2919009569227647</v>
+        <v>0.2919009087610203</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>0.5627178490526396</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>1.289708597515559</v>
+        <v>1.289708515017932</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>5.208997071469394</v>
+        <v>5.20899694990361</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.8135719676834237</v>
+        <v>0.8135719548840679</v>
       </c>
     </row>
     <row r="10">
@@ -1070,10 +1070,10 @@
         <v>0.6934919068830254</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>2.476652362834999</v>
+        <v>2.4766512744254</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.5149108949739487</v>
+        <v>0.5149107368866508</v>
       </c>
     </row>
     <row r="11">
@@ -1120,16 +1120,16 @@
         <v>0.5842401546507788</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.361149683654181</v>
+        <v>0.3611496942071956</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.3933190697000969</v>
+        <v>0.3933190594106613</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>1.396180925288069</v>
+        <v>1.396180948838349</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0.3007040138910977</v>
+        <v>0.300704019849293</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         <v>0.5414897085509536</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.8058447739907552</v>
+        <v>0.8058449745721032</v>
       </c>
       <c r="O12" s="5" t="n">
         <v>1.028501610606008</v>
@@ -1229,7 +1229,7 @@
         <v>0.021193317170832</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.6415881827754055</v>
+        <v>0.6415881341486216</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>0.4444417632736972</v>
@@ -1238,10 +1238,10 @@
         <v>0.543394809259925</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>-0.07474526550900951</v>
+        <v>-0.07474526364045544</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-0.02577702665555009</v>
+        <v>-0.02577702621849115</v>
       </c>
     </row>
     <row r="14">
@@ -1294,10 +1294,10 @@
         <v>0.4314490291712281</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>0.7749698736315818</v>
+        <v>0.7749697323917717</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2107756049202796</v>
+        <v>0.210775572805233</v>
       </c>
     </row>
     <row r="15">
@@ -1341,19 +1341,19 @@
         <v>0.2204228106932928</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.3781793853064817</v>
+        <v>0.3781792230865633</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>0.2832214797464565</v>
+        <v>0.2832213391106446</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.2155286108543433</v>
+        <v>0.2155284846648906</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>0.4149829496823025</v>
+        <v>0.4149831206819428</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>0.1226655657773561</v>
+        <v>0.1226656110017881</v>
       </c>
     </row>
     <row r="16">
@@ -1453,19 +1453,19 @@
         <v>0.2599329763440218</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.3009506800869595</v>
+        <v>0.3009506681437875</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.1088139061630743</v>
+        <v>0.1088138965952475</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.2757501332203308</v>
+        <v>0.2757501418882448</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>0.2230142037484998</v>
+        <v>0.2230142738724509</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.06684909802562307</v>
+        <v>0.0668491199706507</v>
       </c>
     </row>
     <row r="18">
@@ -1509,19 +1509,19 @@
         <v>0.09194539781393063</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.10051908555523</v>
+        <v>0.1005190395794113</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.4316115207896773</v>
+        <v>0.4316113969032783</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.4604743245333124</v>
+        <v>0.4604741978417656</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>0.4780163433567304</v>
+        <v>0.4780161226233791</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.1389153687425875</v>
+        <v>0.13891531056898</v>
       </c>
     </row>
     <row r="19">
@@ -1565,19 +1565,19 @@
         <v>0.2030947134664058</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.1064268815653523</v>
+        <v>0.1064268556069772</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>0.4119706339126221</v>
+        <v>0.4119705749930277</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.2161039363598886</v>
+        <v>0.2161039781847318</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.4246980909811748</v>
+        <v>0.4246979967587478</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>0.1090153473896869</v>
+        <v>0.1090153354099656</v>
       </c>
     </row>
     <row r="20">
@@ -1621,19 +1621,19 @@
         <v>0.08435639219375579</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.1019838320237772</v>
+        <v>0.1019838600905013</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.3689701034657987</v>
+        <v>0.3689700477056893</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.48645781444299</v>
+        <v>0.4864577668070321</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>1.531225843508527</v>
+        <v>1.531225639631062</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0.3514984750998527</v>
+        <v>0.3514984307804296</v>
       </c>
     </row>
     <row r="21">
@@ -1683,13 +1683,13 @@
         <v>0.430459225443603</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.4512921149325702</v>
+        <v>0.4512920269583951</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.1940888300747472</v>
+        <v>0.1940887666460341</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0.06090448515140112</v>
+        <v>0.0609044662742203</v>
       </c>
     </row>
     <row r="22">
@@ -1739,13 +1739,13 @@
         <v>0.4032555284041406</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0.5939768980865894</v>
+        <v>0.5939769383361339</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0.2740681693484774</v>
+        <v>0.2740682161494903</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.07295412830619408</v>
+        <v>0.07295414365094421</v>
       </c>
     </row>
     <row r="23">
@@ -1798,10 +1798,10 @@
         <v>0.1698878415471274</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>1.831945702775993</v>
+        <v>1.831945480826255</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0.4147997490387982</v>
+        <v>0.4147997120778211</v>
       </c>
     </row>
     <row r="24">
@@ -1845,19 +1845,19 @@
         <v>0.1736991728724348</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.211304162046761</v>
+        <v>0.2113041846241446</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.2484309781909822</v>
+        <v>0.2484309935341293</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>0.2407745912046626</v>
+        <v>0.2407746360533602</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>0.5479253755656133</v>
+        <v>0.5479253885754578</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.1369283060715659</v>
+        <v>0.1369283110160364</v>
       </c>
     </row>
     <row r="25">
@@ -1901,19 +1901,19 @@
         <v>0.3918158291051093</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.1822674072213568</v>
+        <v>0.1822673276746378</v>
       </c>
       <c r="M25" s="5" t="n">
         <v>0.07366655763910956</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>-0.006617832123474998</v>
+        <v>-0.006617944442553703</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>-0.01672982295609038</v>
+        <v>-0.01672960286792557</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>-0.005607998509453815</v>
+        <v>-0.005607924316927804</v>
       </c>
     </row>
     <row r="26">
@@ -1957,7 +1957,7 @@
         <v>-0.01090676745725661</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.1576443504521307</v>
+        <v>0.1576443801954869</v>
       </c>
       <c r="M26" s="5" t="n">
         <v>0.3296137739389521</v>
@@ -1966,10 +1966,10 @@
         <v>0.5660516009301498</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>3.220079057077904</v>
+        <v>3.220078670442756</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.5401822772898037</v>
+        <v>0.5401822298625055</v>
       </c>
     </row>
     <row r="27">
@@ -2016,16 +2016,16 @@
         <v>0.3042270159797207</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>0.1557673813988754</v>
+        <v>0.1557673643849343</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>0.2740346598953544</v>
+        <v>0.2740346883434491</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>3.107443615388398</v>
+        <v>3.107443671597667</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>0.5236447107738047</v>
+        <v>0.5236447187460306</v>
       </c>
     </row>
     <row r="28">
@@ -2075,13 +2075,13 @@
         <v>0.3215667590125882</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0.512958713140267</v>
+        <v>0.5129586884831961</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>2.461256786273177</v>
+        <v>2.461256995443425</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.4710058662282565</v>
+        <v>0.4710059105266797</v>
       </c>
     </row>
     <row r="29">
@@ -2125,19 +2125,19 @@
         <v>0.1335305474991672</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.3028437168712624</v>
+        <v>0.3028437014853571</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>0.1788405471094643</v>
+        <v>0.1788405196967776</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>0.2023151141723626</v>
+        <v>0.2023150926115641</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>1.00604198388663</v>
+        <v>1.00604198101479</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>0.242580975967461</v>
+        <v>0.2425809826499563</v>
       </c>
     </row>
     <row r="30">
@@ -2178,22 +2178,22 @@
         <v>-0.02317408370763607</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.1261851568280095</v>
+        <v>0.126185122490367</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.155530689360389</v>
+        <v>0.1555307358735154</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.2038977968369416</v>
+        <v>0.2038977502665122</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>0.3245106444453261</v>
+        <v>0.3245106901289797</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>1.203921322020677</v>
+        <v>1.203921545649172</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.2828800225939143</v>
+        <v>0.2828800666556932</v>
       </c>
     </row>
     <row r="31">
@@ -2237,19 +2237,19 @@
         <v>0.02442621596945416</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.1554423641520849</v>
+        <v>0.155442385815536</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>0.2426573482961469</v>
+        <v>0.2426573225941508</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>0.4610912929528785</v>
+        <v>0.4610912856248852</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>1.803283634869916</v>
+        <v>1.803283563787194</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>0.3338429438851662</v>
+        <v>0.3338429258604537</v>
       </c>
     </row>
     <row r="32">
@@ -2302,10 +2302,10 @@
         <v>0.1366640768107714</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>2.326183255813332</v>
+        <v>2.326183626299121</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>0.4927327378778639</v>
+        <v>0.4927327933003709</v>
       </c>
     </row>
     <row r="33">
@@ -2349,19 +2349,19 @@
         <v>0.09985297474397888</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.2274026064453174</v>
+        <v>0.2274026267484262</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0.2187334562812843</v>
+        <v>0.2187333865362002</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>0.2492046302530503</v>
+        <v>0.2492046619429529</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>0.6088356066620146</v>
+        <v>0.608835698120114</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>0.1713971945694266</v>
+        <v>0.1713972152349236</v>
       </c>
     </row>
     <row r="34">
@@ -2411,13 +2411,13 @@
         <v>0.2458202592809221</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>0.3656261920815619</v>
+        <v>0.3656261313051978</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>0.6490695290561063</v>
+        <v>0.6490696163065709</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.1804541112253973</v>
+        <v>0.1804541312470984</v>
       </c>
     </row>
     <row r="35">
@@ -2461,19 +2461,19 @@
         <v>0.06763436725383359</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.06087973316052805</v>
+        <v>0.06087971098132841</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.2986614754012067</v>
+        <v>0.2986615165568531</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>0.3937437490925703</v>
+        <v>0.3937437342163484</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>0.2703101329122802</v>
+        <v>0.2703101609498064</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>0.07826136891117087</v>
+        <v>0.07826137924773888</v>
       </c>
     </row>
     <row r="36">
@@ -2517,19 +2517,19 @@
         <v>0.09523350704233645</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.07757953125676323</v>
+        <v>0.0775795416261575</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>0.231095892681363</v>
+        <v>0.2310958793278077</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>0.3854544184188505</v>
+        <v>0.3854544045641122</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>0.3942562820718071</v>
+        <v>0.3942563432084448</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>0.09362591871340291</v>
+        <v>0.09362593525318179</v>
       </c>
     </row>
     <row r="37">
@@ -2573,19 +2573,19 @@
         <v>-0.03210705718557921</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.1123078178326336</v>
+        <v>0.1123077879574017</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>0.2474900246478346</v>
+        <v>0.2474900206232788</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>0.5427434382754457</v>
+        <v>0.5427434004169769</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>1.476753518708922</v>
+        <v>1.476753567929687</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>0.345262966128231</v>
+        <v>0.3452629745703673</v>
       </c>
     </row>
     <row r="38">
@@ -2629,19 +2629,19 @@
         <v>0.066479962402341</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.1751061690172872</v>
+        <v>0.1751061674820718</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.2917049064248446</v>
+        <v>0.2917049028558264</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0.2366926795640515</v>
+        <v>0.236692653237132</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>0.6360334305380627</v>
+        <v>0.6360333044584519</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.1723623571999199</v>
+        <v>0.1723623257366306</v>
       </c>
     </row>
     <row r="39">
@@ -2685,19 +2685,19 @@
         <v>0.09952236791925818</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.2077191565697032</v>
+        <v>0.2077191694276469</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>0.1687937874866665</v>
+        <v>0.1687938004313692</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>0.260454387141293</v>
+        <v>0.2604543857908975</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>1.465035925264494</v>
+        <v>1.465036023877349</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>0.3444199174885215</v>
+        <v>0.3444199365732987</v>
       </c>
     </row>
     <row r="40">
@@ -2741,19 +2741,19 @@
         <v>0.166278134734991</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.03335470412567351</v>
+        <v>0.03335468468288477</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.1304788575839449</v>
+        <v>0.1304788570543013</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>0.3269457797714518</v>
+        <v>0.3269457514230463</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>1.013738541389392</v>
+        <v>1.013738543288461</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.2502194172424015</v>
+        <v>0.2502194183939072</v>
       </c>
     </row>
     <row r="41">
@@ -2800,16 +2800,16 @@
         <v>-0.01744462815968473</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>0.2916113793709598</v>
+        <v>0.2916114836631125</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>0.2141409841796846</v>
+        <v>0.2141408920231624</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>0.2208464444739047</v>
+        <v>0.2208466308284625</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>0.0687767908030823</v>
+        <v>0.06877684518377225</v>
       </c>
     </row>
     <row r="42">
@@ -2856,16 +2856,16 @@
         <v>0.1059477285230108</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>0.3053532938854738</v>
+        <v>0.3053532376294944</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0.2993394199204109</v>
+        <v>0.2993394176000879</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>0.5192584394290196</v>
+        <v>0.5192583788026871</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>0.1492285759075186</v>
+        <v>0.1492285600467756</v>
       </c>
     </row>
     <row r="43">
@@ -2918,10 +2918,10 @@
         <v>0.2986602020042002</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>1.043550862897364</v>
+        <v>1.043551137372892</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>0.2690005700370139</v>
+        <v>0.2690006268514527</v>
       </c>
     </row>
     <row r="44">
@@ -2974,10 +2974,10 @@
         <v>0.1024373616220888</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>0.05144151890255588</v>
+        <v>0.05144170135440063</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.01686127255464154</v>
+        <v>0.01686133137173562</v>
       </c>
     </row>
     <row r="45">
@@ -3021,19 +3021,19 @@
         <v>0.09998480472191509</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.02016357344099427</v>
+        <v>0.02016358413408299</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0.1685539881982587</v>
+        <v>0.1685540184678741</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0.2571539083259939</v>
+        <v>0.2571538925958808</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.4665675434600599</v>
+        <v>0.4665675327786942</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>0.1282701527028302</v>
+        <v>0.1282701495644201</v>
       </c>
     </row>
     <row r="46">
@@ -3080,16 +3080,16 @@
         <v>0.140320071199596</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>0.1847921444585202</v>
+        <v>0.1847921259586965</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>0.1978371220719151</v>
+        <v>0.1978371047254206</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>1.208166657274482</v>
+        <v>1.208166592649423</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>0.2985502986812404</v>
+        <v>0.2985502878309826</v>
       </c>
     </row>
     <row r="47">
@@ -3133,19 +3133,19 @@
         <v>-0.03956946689176888</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.05574546840419087</v>
+        <v>0.05574545038469492</v>
       </c>
       <c r="M47" s="5" t="n">
         <v>0.1952306062257987</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>0.4447896617890589</v>
+        <v>0.4447896311760025</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>0.4769474405158803</v>
+        <v>0.476947400257379</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>0.1248906542272003</v>
+        <v>0.124890648135438</v>
       </c>
     </row>
     <row r="48">
@@ -3189,19 +3189,19 @@
         <v>0.03856755184676611</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>0.09031217515260004</v>
+        <v>0.09031219522906897</v>
       </c>
       <c r="M48" s="5" t="n">
         <v>0.142813242614231</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>0.2378053784352271</v>
+        <v>0.2378053392396853</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>0.281325400823793</v>
+        <v>0.2813252618015255</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>0.07822612911576765</v>
+        <v>0.07822608665809244</v>
       </c>
     </row>
     <row r="49">
@@ -3251,13 +3251,13 @@
         <v>0.06718279231575708</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>-0.08786118698041778</v>
+        <v>-0.08786129301665385</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>0.1107799530206475</v>
+        <v>0.1107799904953525</v>
       </c>
       <c r="P49" s="5" t="n">
-        <v>0.03551714669766448</v>
+        <v>0.03551715809607425</v>
       </c>
     </row>
     <row r="50">
@@ -3307,13 +3307,13 @@
         <v>0.1525511246341834</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>-0.004158319894498164</v>
+        <v>-0.004158264036900283</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>0.511616286174954</v>
+        <v>0.5116163533989129</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.1474484019844169</v>
+        <v>0.1474484194772017</v>
       </c>
     </row>
     <row r="51">
@@ -3413,19 +3413,19 @@
         <v>0.0978330121925908</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0.05888069819995938</v>
+        <v>0.05888068611780699</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>0.1275343155989436</v>
+        <v>0.1275343279318245</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>0.1276796481582697</v>
+        <v>0.1276796681950005</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>0.9046585896258088</v>
+        <v>0.9046585474138147</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>0.2342697964921735</v>
+        <v>0.2342697902237137</v>
       </c>
     </row>
     <row r="53">
@@ -3475,13 +3475,13 @@
         <v>0.1748102163820486</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>0.08536906357319768</v>
+        <v>0.08536908999447385</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0.9627319377158012</v>
+        <v>0.9627321635296782</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>0.2515275320733558</v>
+        <v>0.2515275793453835</v>
       </c>
     </row>
     <row r="54">
@@ -3528,16 +3528,16 @@
         <v>0.08164247799871627</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>0.2558021762747522</v>
+        <v>0.2558021337539758</v>
       </c>
       <c r="N54" s="5" t="n">
-        <v>0.1415871849492057</v>
+        <v>0.1415872534983892</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>1.093106788609147</v>
+        <v>1.093106892456555</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.2784508500750714</v>
+        <v>0.2784508702796629</v>
       </c>
     </row>
     <row r="55">
@@ -3590,10 +3590,10 @@
         <v>0.4554877527998453</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>1.242944831345113</v>
+        <v>1.242944924290823</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>0.3081621938100984</v>
+        <v>0.3081622125770158</v>
       </c>
     </row>
     <row r="56">
@@ -3643,13 +3643,13 @@
         <v>0.1956884226718441</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>0.1141528359609871</v>
+        <v>0.1141528832540025</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>1.19499658228</v>
+        <v>1.194996465459046</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.2961914952340335</v>
+        <v>0.2961914742668922</v>
       </c>
     </row>
     <row r="57">
@@ -3693,7 +3693,7 @@
         <v>0.1536758216416354</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>0.03516336327524083</v>
+        <v>0.03516347975022249</v>
       </c>
       <c r="M57" s="5" t="n">
         <v>0.1154412994533758</v>
@@ -3755,13 +3755,13 @@
         <v>0.1384849973295821</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>0.1746908663067173</v>
+        <v>0.174690982880656</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>0.4620644371908027</v>
+        <v>0.4620647983655464</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>0.1349816442633731</v>
+        <v>0.1349817377217872</v>
       </c>
     </row>
     <row r="59">
@@ -3805,19 +3805,19 @@
         <v>0.03631070494710912</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.002906769335800733</v>
+        <v>-0.002906766834220068</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0.1910061958493235</v>
+        <v>0.1910061912121664</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>0.1818617487933157</v>
+        <v>0.1818618022355778</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>0.09065066615993793</v>
+        <v>0.09065064057537438</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>0.01999128990618724</v>
+        <v>0.01999128739470107</v>
       </c>
     </row>
     <row r="60">
@@ -3864,16 +3864,16 @@
         <v>0.07258671922883293</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>0.1153562848023902</v>
+        <v>0.1153563413481097</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0.1490148705389207</v>
+        <v>0.1490149026269424</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>0.7375410285330611</v>
+        <v>0.7375410480440555</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>0.1974950254964335</v>
+        <v>0.1974950340851071</v>
       </c>
     </row>
     <row r="61">
@@ -3973,13 +3973,13 @@
         <v>-0.002976792869941088</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>0.1545086708920145</v>
+        <v>0.1545087001301226</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.08560993970771628</v>
+        <v>0.08560997507927819</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>0.1793661725881055</v>
+        <v>0.1793661456862526</v>
       </c>
       <c r="O62" s="5" t="n">
         <v>0.8924790678061418</v>
@@ -4029,19 +4029,19 @@
         <v>0.002466861965037093</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.04313794278532592</v>
+        <v>0.04313797760904323</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>0.1974675945488942</v>
+        <v>0.1974675678087305</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>0.138786197475739</v>
+        <v>0.1387862282612196</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>0.5198251142169985</v>
+        <v>0.5198252312367526</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>0.1451960521867616</v>
+        <v>0.1451960820886935</v>
       </c>
     </row>
     <row r="64">
@@ -4085,19 +4085,19 @@
         <v>0.1202980879019061</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0.01515826756477323</v>
+        <v>0.01515825290605131</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>0.112140815047663</v>
+        <v>0.112140841147869</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>0.009779867792167062</v>
+        <v>0.009779849069227686</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>0.2595258606919307</v>
+        <v>0.2595258324603201</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.07569398378473417</v>
+        <v>0.07569397174894088</v>
       </c>
     </row>
     <row r="65">
@@ -4147,7 +4147,7 @@
         <v>0.1186750823250835</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>0.2589487819113832</v>
+        <v>0.2589486945902977</v>
       </c>
       <c r="O65" s="5" t="n">
         <v>0.2441556554336897</v>
@@ -4200,16 +4200,16 @@
         <v>0.1425685421850817</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>-0.05200983253282013</v>
+        <v>-0.05200986473626601</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>0.02126557672852318</v>
+        <v>0.02126556329404046</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>1.353176479684714</v>
+        <v>1.353176477604264</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>0.3287443078636159</v>
+        <v>0.3287443062233597</v>
       </c>
     </row>
     <row r="67">
@@ -4253,19 +4253,19 @@
         <v>0.1745408281103143</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>0.06748496722830108</v>
+        <v>0.06748495689293027</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0.01859811487641574</v>
+        <v>0.01859811638321045</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>-0.0872502179752592</v>
+        <v>-0.08725021364104774</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>0.09218856407596833</v>
+        <v>0.09218857691068345</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>0.01289019454452352</v>
+        <v>0.01289019806150497</v>
       </c>
     </row>
     <row r="68">
@@ -4318,10 +4318,10 @@
         <v>0.02906989704851481</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>0.1679997088572087</v>
+        <v>0.1679996493245731</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>0.05242707632848087</v>
+        <v>0.05242705745040599</v>
       </c>
     </row>
     <row r="69">
@@ -4365,7 +4365,7 @@
         <v>0.09195448720583703</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>0.02997256188346516</v>
+        <v>0.02997253136254981</v>
       </c>
       <c r="M69" s="5" t="n">
         <v>0.07040953365445475</v>
@@ -4374,10 +4374,10 @@
         <v>0.04970122095006146</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>-0.0980429174344692</v>
+        <v>-0.098042991589541</v>
       </c>
       <c r="P69" s="5" t="n">
-        <v>-0.03683277438391316</v>
+        <v>-0.03683279861735019</v>
       </c>
     </row>
     <row r="70">
@@ -4424,16 +4424,16 @@
         <v>0.1078014079850389</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.155339009409664</v>
+        <v>0.1553390486950595</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>0.02407379972069697</v>
+        <v>0.02407374919481934</v>
       </c>
       <c r="O70" s="5" t="n">
-        <v>0.9156521625101485</v>
+        <v>0.9156522165280684</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.2387878853827904</v>
+        <v>0.2387878988251467</v>
       </c>
     </row>
     <row r="71">
@@ -4483,13 +4483,13 @@
         <v>0.02684674765269328</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>0.2676770297353217</v>
+        <v>0.2676770654098996</v>
       </c>
       <c r="O71" s="5" t="n">
-        <v>0.8464194947536088</v>
+        <v>0.8464195481078779</v>
       </c>
       <c r="P71" s="5" t="n">
-        <v>0.2138148691265422</v>
+        <v>0.2138148783370218</v>
       </c>
     </row>
     <row r="72">
@@ -4533,13 +4533,13 @@
         <v>-0.1253464324537674</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.09202741863314456</v>
+        <v>-0.09202752498722955</v>
       </c>
       <c r="M72" s="5" t="n">
         <v>0.3374990283562946</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>0.2939717603393948</v>
+        <v>0.2939718683405486</v>
       </c>
       <c r="O72" s="5" t="n">
         <v>-0.3455796985458148</v>
@@ -4598,10 +4598,10 @@
         <v>-0.1217041088998335</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>-0.2894574495395481</v>
+        <v>-0.2894572895786319</v>
       </c>
       <c r="P73" s="5" t="n">
-        <v>-0.1076606799219325</v>
+        <v>-0.1076606129592975</v>
       </c>
     </row>
     <row r="74">
@@ -4654,10 +4654,10 @@
         <v>0.1479572711738253</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>-0.2993415880423304</v>
+        <v>-0.2993416106528338</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>-0.1185476286296178</v>
+        <v>-0.1185476369223323</v>
       </c>
     </row>
     <row r="75">
@@ -4701,10 +4701,10 @@
         <v>0.05085223683927764</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-0.04992303902957096</v>
+        <v>-0.04992295277399517</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>0.121893009012312</v>
+        <v>0.1218928887381328</v>
       </c>
       <c r="N75" s="5" t="n">
         <v>0.006809014610812181</v>
@@ -4757,19 +4757,19 @@
         <v>0.01161765299109786</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.005776444505673447</v>
+        <v>-0.005776439592030923</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0.06664914517184042</v>
+        <v>0.06664914687992797</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>0.09317918279520811</v>
+        <v>0.09317917292225822</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>0.3361700903115287</v>
+        <v>0.3361700374189094</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>0.09154233138972163</v>
+        <v>0.09154231864539265</v>
       </c>
     </row>
     <row r="77">
@@ -4813,19 +4813,19 @@
         <v>-0.01015012411891817</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.02374805264026925</v>
+        <v>-0.02374801573972744</v>
       </c>
       <c r="M77" s="5" t="n">
         <v>0.0588031849254255</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>0.1591687242163161</v>
+        <v>0.1591686506333059</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>0.5775997646089071</v>
+        <v>0.5775999145971988</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>0.1579896526238561</v>
+        <v>0.1579896950740956</v>
       </c>
     </row>
     <row r="78">
@@ -4872,16 +4872,16 @@
         <v>0.04224650623510917</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>0.1656038332861666</v>
+        <v>0.1656037991991886</v>
       </c>
       <c r="N78" s="5" t="n">
         <v>0.09065373081364564</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>0.3119840474070418</v>
+        <v>0.3119838931831398</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.08588490337068033</v>
+        <v>0.08588486307352178</v>
       </c>
     </row>
     <row r="79">
@@ -4981,19 +4981,19 @@
         <v>0.07637034787635782</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.04797397621340044</v>
+        <v>-0.04797398974912512</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>0.04515864083225531</v>
+        <v>0.04515861247317996</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>-0.03096438283148802</v>
+        <v>-0.03096439004599115</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>0.1355451694741966</v>
+        <v>0.1355451259825815</v>
       </c>
       <c r="P80" s="5" t="n">
-        <v>0.0389269908760444</v>
+        <v>0.03892698168991948</v>
       </c>
     </row>
     <row r="81">
@@ -5040,16 +5040,16 @@
         <v>0.01387222163721072</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>-0.005964295429485672</v>
+        <v>-0.005964264255908692</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>-0.06246056142271187</v>
+        <v>-0.06246056260138138</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>0.4944273293599099</v>
+        <v>0.4944273846295957</v>
       </c>
       <c r="P81" s="5" t="n">
-        <v>0.130721717170279</v>
+        <v>0.1307217331534305</v>
       </c>
     </row>
     <row r="82">
@@ -5093,7 +5093,7 @@
         <v>-0.02966137654831813</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>0.1009674331704362</v>
+        <v>0.10096735124439</v>
       </c>
       <c r="M82" s="5" t="n">
         <v>0.09439255191490492</v>
@@ -5102,10 +5102,10 @@
         <v>-0.02096091812613043</v>
       </c>
       <c r="O82" s="5" t="n">
-        <v>-0.07016804702639501</v>
+        <v>-0.07016816389879355</v>
       </c>
       <c r="P82" s="5" t="n">
-        <v>-0.02395878823996089</v>
+        <v>-0.02395882913347291</v>
       </c>
     </row>
     <row r="83">
@@ -5149,19 +5149,19 @@
         <v>-0.02565389057936807</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.0157403229994631</v>
+        <v>-0.01574037464383804</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>0.1369764932633029</v>
+        <v>0.1369764588418053</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>0.02822078536244421</v>
+        <v>0.02822084283353032</v>
       </c>
       <c r="O83" s="5" t="n">
-        <v>0.2457680972610836</v>
+        <v>0.2457681790683123</v>
       </c>
       <c r="P83" s="5" t="n">
-        <v>0.07600020629894988</v>
+        <v>0.07600022985127619</v>
       </c>
     </row>
     <row r="84">
@@ -5205,19 +5205,19 @@
         <v>0.003231385781948052</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.05420185532420241</v>
+        <v>-0.05420184999105634</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>0.05518035424980792</v>
+        <v>0.05518035540142665</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>0.08039841167936398</v>
+        <v>0.08039841283434232</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>0.8108060093992341</v>
+        <v>0.8108060564446674</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>0.1962119248083078</v>
+        <v>0.1962119329587291</v>
       </c>
     </row>
     <row r="85">
@@ -5261,19 +5261,19 @@
         <v>-0.02035500618629195</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.05710070148116837</v>
+        <v>-0.05710069998697857</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>0.07239240897598251</v>
+        <v>0.07239239923937923</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>0.109632464881924</v>
+        <v>0.1096324632285698</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>0.4197395579525056</v>
+        <v>0.4197395263787876</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>0.1212357389549963</v>
+        <v>0.1212357319461709</v>
       </c>
     </row>
     <row r="86">
@@ -5317,19 +5317,19 @@
         <v>0.1353062324132862</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.0002495400329916205</v>
+        <v>-0.000249552468389036</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>-0.0346240494541221</v>
+        <v>-0.03462407533271322</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>-0.1556412825139368</v>
+        <v>-0.1556412767323837</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>0.1032522036517298</v>
+        <v>0.1032522843955551</v>
       </c>
       <c r="P86" s="5" t="n">
-        <v>0.02782946163101004</v>
+        <v>0.02782949024132901</v>
       </c>
     </row>
     <row r="87">
@@ -5376,16 +5376,16 @@
         <v>-0.05676731018273573</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>0.1079311024465786</v>
+        <v>0.1079311305506833</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>0.1358207517794911</v>
+        <v>0.1358207024272309</v>
       </c>
       <c r="O87" s="5" t="n">
-        <v>1.188982987830415</v>
+        <v>1.188982791125987</v>
       </c>
       <c r="P87" s="5" t="n">
-        <v>0.2731963117792972</v>
+        <v>0.2731962807720321</v>
       </c>
     </row>
     <row r="88">
@@ -5435,13 +5435,13 @@
         <v>0.07202526207641019</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>0.2280544600332723</v>
+        <v>0.2280543313888945</v>
       </c>
       <c r="O88" s="5" t="n">
-        <v>0.7221647404000319</v>
+        <v>0.7221646132543217</v>
       </c>
       <c r="P88" s="5" t="n">
-        <v>0.1956711804928749</v>
+        <v>0.1956711476478334</v>
       </c>
     </row>
     <row r="89">
@@ -5491,13 +5491,13 @@
         <v>0.05037132447369702</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>-0.004469907540662496</v>
+        <v>-0.004469898911142647</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>0.763928586869836</v>
+        <v>0.7639285923235524</v>
       </c>
       <c r="P89" s="5" t="n">
-        <v>0.1929868601295628</v>
+        <v>0.1929868589940521</v>
       </c>
     </row>
     <row r="90">
@@ -5550,10 +5550,10 @@
         <v>-0.2322172128631561</v>
       </c>
       <c r="O90" s="5" t="n">
-        <v>-0.1611979732024529</v>
+        <v>-0.1611978762709849</v>
       </c>
       <c r="P90" s="5" t="n">
-        <v>-0.07316400550551122</v>
+        <v>-0.07316398056605905</v>
       </c>
     </row>
     <row r="91">
@@ -5603,7 +5603,7 @@
         <v>0.346612874229051</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>0.591333790482401</v>
+        <v>0.5913337495271249</v>
       </c>
       <c r="O91" s="5" t="n">
         <v>0.2177836089824027</v>
@@ -5650,22 +5650,22 @@
         <v>-0.04467795098273104</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.0387195086750626</v>
+        <v>-0.03871948991847311</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>0.03315990803956533</v>
+        <v>0.03315988737974383</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>0.07840791946598595</v>
+        <v>0.0784079698844526</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>0.001908366836997177</v>
+        <v>0.001908352322244533</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>0.1670274965219889</v>
+        <v>0.1670274076335067</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>0.05168547364537641</v>
+        <v>0.05168544728457327</v>
       </c>
     </row>
     <row r="93">
@@ -5712,16 +5712,16 @@
         <v>0.06998723509477693</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>0.03415347454176365</v>
+        <v>0.03415349776165307</v>
       </c>
       <c r="N93" s="5" t="n">
         <v>-0.007977921556034273</v>
       </c>
       <c r="O93" s="5" t="n">
-        <v>0.2150813332736366</v>
+        <v>0.2150814030193</v>
       </c>
       <c r="P93" s="5" t="n">
-        <v>0.06504077325224793</v>
+        <v>0.06504079190949137</v>
       </c>
     </row>
     <row r="94">
@@ -5768,16 +5768,16 @@
         <v>-0.08106516201652747</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>0.02343031356748293</v>
+        <v>0.02343040866002188</v>
       </c>
       <c r="N94" s="5" t="n">
         <v>0.04940682974438304</v>
       </c>
       <c r="O94" s="5" t="n">
-        <v>0.5831118424631649</v>
+        <v>0.5831119562319396</v>
       </c>
       <c r="P94" s="5" t="n">
-        <v>0.1654774253155658</v>
+        <v>0.1654774532341945</v>
       </c>
     </row>
     <row r="95">
@@ -5827,13 +5827,13 @@
         <v>0.09164820702790685</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>-0.07357682784219519</v>
+        <v>-0.07357680364727173</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>-0.02008781408610028</v>
+        <v>-0.02008780186774525</v>
       </c>
       <c r="P95" s="5" t="n">
-        <v>-0.01295828451637185</v>
+        <v>-0.01295827798960281</v>
       </c>
     </row>
     <row r="96">
@@ -5880,16 +5880,16 @@
         <v>-0.06226329264427977</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>0.006920044251899848</v>
+        <v>0.006920055183645413</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>-0.0575522422929609</v>
+        <v>-0.0575522327030147</v>
       </c>
       <c r="O96" s="5" t="n">
-        <v>-0.1422302956075828</v>
+        <v>-0.1422303128396976</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>-0.05373000907197173</v>
+        <v>-0.05373001634488192</v>
       </c>
     </row>
     <row r="97">
@@ -5933,19 +5933,19 @@
         <v>-0.05425489439957368</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>0.07171811346721477</v>
+        <v>0.07171814254827505</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>-0.07446394884875945</v>
+        <v>-0.07446394849640853</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>0.0882957927681326</v>
+        <v>0.08829579957447389</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>1.349911166358886</v>
+        <v>1.349911401838036</v>
       </c>
       <c r="P97" s="5" t="n">
-        <v>0.328452080845878</v>
+        <v>0.3284521270066699</v>
       </c>
     </row>
     <row r="98">
@@ -5989,19 +5989,19 @@
         <v>0.06611945029503159</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>-0.03117706378232912</v>
+        <v>-0.03117705865487067</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>-0.08364622746524759</v>
+        <v>-0.08364623827154558</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>-0.1089357674822451</v>
+        <v>-0.1089357585832487</v>
       </c>
       <c r="O98" s="5" t="n">
-        <v>0.02965684472973047</v>
+        <v>0.02965684001137874</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>0.005081208409682104</v>
+        <v>0.005081209019705858</v>
       </c>
     </row>
     <row r="99">
@@ -6045,19 +6045,19 @@
         <v>-0.01196558282146271</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.1411659941772012</v>
+        <v>-0.1411659939663122</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>0.02546305759126147</v>
+        <v>0.0254630615857533</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>0.0436666288829069</v>
+        <v>0.04366660948949295</v>
       </c>
       <c r="O99" s="5" t="n">
-        <v>1.054364074815623</v>
+        <v>1.054364059651788</v>
       </c>
       <c r="P99" s="5" t="n">
-        <v>0.2359989427641671</v>
+        <v>0.2359989449290831</v>
       </c>
     </row>
     <row r="100">
@@ -6101,19 +6101,19 @@
         <v>0.1597042336816761</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>-0.174157155348022</v>
+        <v>-0.1741571118286115</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>-0.2021973738624304</v>
+        <v>-0.2021973996901199</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>-0.05128588077490942</v>
+        <v>-0.05128588354150865</v>
       </c>
       <c r="O100" s="5" t="n">
-        <v>0.4143582449869427</v>
+        <v>0.4143582529847809</v>
       </c>
       <c r="P100" s="5" t="n">
-        <v>0.121996972229909</v>
+        <v>0.1219969725117269</v>
       </c>
     </row>
     <row r="101">
@@ -6157,19 +6157,19 @@
         <v>-0.01980756132547801</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>-0.07294433448048382</v>
+        <v>-0.07294437331837594</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>-0.07735399006925781</v>
+        <v>-0.07735395551215124</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>0.02180800059059351</v>
+        <v>0.02180804875590214</v>
       </c>
       <c r="O101" s="5" t="n">
-        <v>1.097504408755027</v>
+        <v>1.097504667478765</v>
       </c>
       <c r="P101" s="5" t="n">
-        <v>0.2359462551626035</v>
+        <v>0.2359463121518943</v>
       </c>
     </row>
     <row r="102">
@@ -6213,19 +6213,19 @@
         <v>-0.04866173141222541</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>-0.04917757234337328</v>
+        <v>-0.04917764834001059</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>0.04556319907088358</v>
+        <v>0.04556310717498779</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>-0.09375693713011812</v>
+        <v>-0.09375700616759863</v>
       </c>
       <c r="O102" s="5" t="n">
-        <v>-0.2230180374504144</v>
+        <v>-0.223018138946055</v>
       </c>
       <c r="P102" s="5" t="n">
-        <v>-0.08067237117813886</v>
+        <v>-0.08067241120813318</v>
       </c>
     </row>
     <row r="103">
@@ -6272,16 +6272,16 @@
         <v>-0.04185960770262389</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>-0.05221881771391219</v>
+        <v>-0.05221882242623668</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>-0.1535968749226637</v>
+        <v>-0.153596884148628</v>
       </c>
       <c r="O103" s="5" t="n">
-        <v>0.6220521239073676</v>
+        <v>0.6220520848681527</v>
       </c>
       <c r="P103" s="5" t="n">
-        <v>0.1610920385176</v>
+        <v>0.1610920289827123</v>
       </c>
     </row>
     <row r="104">
@@ -6334,10 +6334,10 @@
         <v>-0.1709887608965278</v>
       </c>
       <c r="O104" s="5" t="n">
-        <v>0.09379384579402461</v>
+        <v>0.09379388576923564</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.02501456016469067</v>
+        <v>0.02501457489907727</v>
       </c>
     </row>
     <row r="105">
@@ -6381,19 +6381,19 @@
         <v>-0.02816261931186692</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>-0.04748619200046876</v>
+        <v>-0.04748618702515113</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>-0.009526203238050729</v>
+        <v>-0.009526222397947898</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>-0.1075540110283731</v>
+        <v>-0.107554054074342</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>0.3924168507159148</v>
+        <v>0.3924169192416649</v>
       </c>
       <c r="P105" s="5" t="n">
-        <v>0.08596701699117949</v>
+        <v>0.08596703902630412</v>
       </c>
     </row>
     <row r="106">
@@ -6499,13 +6499,13 @@
         <v>-0.1150343871074165</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>-0.2001919611333431</v>
+        <v>-0.2001920075231385</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>0.2627600945119619</v>
+        <v>0.2627601295886035</v>
       </c>
       <c r="P107" s="5" t="n">
-        <v>0.06750912797160635</v>
+        <v>0.06750913630155315</v>
       </c>
     </row>
     <row r="108">
@@ -6549,19 +6549,19 @@
         <v>-0.00676341574420658</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>-0.1305860364141379</v>
+        <v>-0.1305860524345072</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>-0.08779867724936183</v>
+        <v>-0.08779869649248148</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>-0.1220269125558185</v>
+        <v>-0.1220269465440862</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>0.342613726948845</v>
+        <v>0.3426136456915745</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.09891057795904934</v>
+        <v>0.09891055228677341</v>
       </c>
     </row>
     <row r="109">
@@ -6605,19 +6605,19 @@
         <v>-0.05946397188873093</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>-0.04467401459868015</v>
+        <v>-0.04467405888810555</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>-0.1156236560639213</v>
+        <v>-0.1156236083201516</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>-0.0790031275161957</v>
+        <v>-0.07900309211678813</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>-0.5287266517027218</v>
+        <v>-0.5287266346067148</v>
       </c>
       <c r="P109" s="5" t="n">
-        <v>-0.2220899195707481</v>
+        <v>-0.222089911112999</v>
       </c>
     </row>
     <row r="110">
@@ -6667,13 +6667,13 @@
         <v>-0.04593656066894732</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>-0.06600198593206386</v>
+        <v>-0.06600201001308885</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>-0.03128450569032304</v>
+        <v>-0.03128459378686229</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>-0.0112467051675923</v>
+        <v>-0.01124673527686563</v>
       </c>
     </row>
     <row r="111">
@@ -6894,10 +6894,10 @@
         <v>-0.3167791799257963</v>
       </c>
       <c r="O114" s="5" t="n">
-        <v>-0.0477492892812208</v>
+        <v>-0.04774937133783064</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>-0.01617670445637098</v>
+        <v>-0.01617673271545783</v>
       </c>
     </row>
     <row r="115">
@@ -6947,13 +6947,13 @@
         <v>-0.1956835911805617</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>-0.2164688712391434</v>
+        <v>-0.2164688743907062</v>
       </c>
       <c r="O115" s="5" t="n">
-        <v>0.7632179873024504</v>
+        <v>0.7632179928997349</v>
       </c>
       <c r="P115" s="5" t="n">
-        <v>0.08477465620131386</v>
+        <v>0.08477465832789721</v>
       </c>
     </row>
     <row r="116">
@@ -7006,10 +7006,10 @@
         <v>-0.2906884956561359</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>-0.4792775253024119</v>
+        <v>-0.4792774901675869</v>
       </c>
       <c r="P116" s="5" t="n">
-        <v>-0.2061203490381073</v>
+        <v>-0.2061203341320192</v>
       </c>
     </row>
     <row r="117">
@@ -7115,13 +7115,13 @@
         <v>-0.2582978451902048</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>-0.1984201001772415</v>
+        <v>-0.1984201143881997</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>-0.08030176047573528</v>
+        <v>-0.08030181052651714</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>-0.05472712663930943</v>
+        <v>-0.05472714471585408</v>
       </c>
     </row>
     <row r="119">
@@ -7165,19 +7165,19 @@
         <v>-0.004080899369296787</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>-0.149284307094314</v>
+        <v>-0.1492843460991432</v>
       </c>
       <c r="M119" s="5" t="n">
         <v>-0.12553554744848</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>-0.2406236737753953</v>
+        <v>-0.2406237593979195</v>
       </c>
       <c r="O119" s="5" t="n">
-        <v>-0.0237231516187299</v>
+        <v>-0.02372303536830861</v>
       </c>
       <c r="P119" s="5" t="n">
-        <v>-0.008314245235521656</v>
+        <v>-0.008314205629156135</v>
       </c>
     </row>
     <row r="120">
@@ -7221,7 +7221,7 @@
         <v>-0.1282162139982877</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>-0.03729548325777587</v>
+        <v>-0.03729546031090173</v>
       </c>
       <c r="M120" s="5" t="n">
         <v>-0.1495822868267143</v>
@@ -7230,10 +7230,10 @@
         <v>-0.09327253859608597</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>-0.0362509114960002</v>
+        <v>-0.03625082947909356</v>
       </c>
       <c r="P120" s="5" t="n">
-        <v>-0.0123399083224589</v>
+        <v>-0.0123398807643138</v>
       </c>
     </row>
     <row r="121">
@@ -7277,19 +7277,19 @@
         <v>-0.03401270592833727</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>-0.1070727482868547</v>
+        <v>-0.1070727729425837</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>-0.1542842754070115</v>
+        <v>-0.1542842631197825</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>-0.2727250715049876</v>
+        <v>-0.2727250642105972</v>
       </c>
       <c r="O121" s="5" t="n">
-        <v>0.1111149893916434</v>
+        <v>0.1111150190594919</v>
       </c>
       <c r="P121" s="5" t="n">
-        <v>0.02759100438816448</v>
+        <v>0.0275910175454529</v>
       </c>
     </row>
     <row r="122">
@@ -7339,13 +7339,13 @@
         <v>-0.1904093325924132</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>-0.1635757911903977</v>
+        <v>-0.1635757456394104</v>
       </c>
       <c r="O122" s="5" t="n">
-        <v>0.386493517527296</v>
+        <v>0.3864935885509022</v>
       </c>
       <c r="P122" s="5" t="n">
-        <v>0.1110594798214342</v>
+        <v>0.1110594980216694</v>
       </c>
     </row>
     <row r="123">
@@ -7389,19 +7389,19 @@
         <v>0.004200514805582256</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>-0.1728012122795241</v>
+        <v>-0.1728012431454147</v>
       </c>
       <c r="M123" s="5" t="n">
-        <v>-0.1845638205868632</v>
+        <v>-0.1845638489253458</v>
       </c>
       <c r="N123" s="5" t="n">
-        <v>-0.3326179095873146</v>
+        <v>-0.3326179305183918</v>
       </c>
       <c r="O123" s="5" t="n">
-        <v>-0.1859330630364712</v>
+        <v>-0.1859329328451698</v>
       </c>
       <c r="P123" s="5" t="n">
-        <v>-0.06730123927908355</v>
+        <v>-0.06730119135727536</v>
       </c>
     </row>
     <row r="124">
@@ -7445,7 +7445,7 @@
         <v>-0.1150652072756954</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>-0.2148431701842643</v>
+        <v>-0.2148431920582364</v>
       </c>
       <c r="M124" s="5" t="n">
         <v>-0.2067635150544242</v>
@@ -7454,10 +7454,10 @@
         <v>-0.1458291825204074</v>
       </c>
       <c r="O124" s="5" t="n">
-        <v>0.9312047838242187</v>
+        <v>0.9312047297066077</v>
       </c>
       <c r="P124" s="5" t="n">
-        <v>0.1062317715743426</v>
+        <v>0.1062317683885599</v>
       </c>
     </row>
     <row r="125">
@@ -7616,16 +7616,16 @@
         <v>-0.3082371740210899</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>-0.3493437353066631</v>
+        <v>-0.3493437762829898</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>-0.366902042130179</v>
+        <v>-0.3669020773159793</v>
       </c>
       <c r="O127" s="5" t="n">
-        <v>1.905563698459998</v>
+        <v>1.905563657584753</v>
       </c>
       <c r="P127" s="5" t="n">
-        <v>0.1818068197880137</v>
+        <v>0.1818068073166262</v>
       </c>
     </row>
     <row r="128">
@@ -7942,10 +7942,10 @@
         <v>6.621066744079008</v>
       </c>
       <c r="O4" t="n">
-        <v>13.41205869514149</v>
+        <v>13.41206027941172</v>
       </c>
       <c r="P4" t="n">
-        <v>1.433559714491861</v>
+        <v>1.433559803662931</v>
       </c>
     </row>
     <row r="5">
@@ -8052,10 +8052,10 @@
         <v>0.9473096472107514</v>
       </c>
       <c r="M6" t="n">
-        <v>1.814266922287201</v>
+        <v>1.81426717548461</v>
       </c>
       <c r="N6" t="n">
-        <v>4.12584857047205</v>
+        <v>4.125848990453617</v>
       </c>
       <c r="O6" t="n">
         <v>13.59771234155111</v>
@@ -8232,10 +8232,10 @@
         <v>3.395798731076073</v>
       </c>
       <c r="O9" t="n">
-        <v>6.946002801784267</v>
+        <v>6.946001899499144</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9954900713981498</v>
+        <v>0.9954899958674661</v>
       </c>
     </row>
     <row r="10">
@@ -8287,13 +8287,13 @@
         <v>1.121627621193379</v>
       </c>
       <c r="N10" t="n">
-        <v>1.231987820595752</v>
+        <v>1.231988202805507</v>
       </c>
       <c r="O10" t="n">
-        <v>1.717235651393779</v>
+        <v>1.717235368161583</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3954333603738072</v>
+        <v>0.3954333118892785</v>
       </c>
     </row>
     <row r="11">
@@ -8342,16 +8342,16 @@
         <v>1.518460150071377</v>
       </c>
       <c r="M11" t="n">
-        <v>1.453704249679884</v>
+        <v>1.453704045900014</v>
       </c>
       <c r="N11" t="n">
-        <v>2.422579688520868</v>
+        <v>2.422579292038412</v>
       </c>
       <c r="O11" t="n">
-        <v>3.081627465395376</v>
+        <v>3.081627183457392</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5981263830544785</v>
+        <v>0.5981263462576742</v>
       </c>
     </row>
     <row r="12">
@@ -8406,10 +8406,10 @@
         <v>1.484539790233016</v>
       </c>
       <c r="O12" t="n">
-        <v>1.926620045336704</v>
+        <v>1.926619362598837</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4303932355119755</v>
+        <v>0.4303931242819916</v>
       </c>
     </row>
     <row r="13">
@@ -8577,13 +8577,13 @@
         <v>0.9726551274876898</v>
       </c>
       <c r="N15" t="n">
-        <v>2.066464251361024</v>
+        <v>2.066464027465083</v>
       </c>
       <c r="O15" t="n">
-        <v>3.920907695629906</v>
+        <v>3.920907119048244</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7009115867153004</v>
+        <v>0.7009115202834868</v>
       </c>
     </row>
     <row r="16">
@@ -8635,13 +8635,13 @@
         <v>0.8350615907363548</v>
       </c>
       <c r="N16" t="n">
-        <v>2.135245409446063</v>
+        <v>2.135245207878731</v>
       </c>
       <c r="O16" t="n">
-        <v>2.772375156896572</v>
+        <v>2.772374865082109</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5567001193452694</v>
+        <v>0.556700079205428</v>
       </c>
     </row>
     <row r="17">
@@ -8745,13 +8745,13 @@
         <v>-0.03834943079539666</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4592719927396136</v>
+        <v>0.459271855286612</v>
       </c>
       <c r="M18" t="n">
         <v>0.7693724764766192</v>
       </c>
       <c r="N18" t="n">
-        <v>1.933693667046309</v>
+        <v>1.933693389278915</v>
       </c>
       <c r="O18" t="n">
         <v>2.280718199478279</v>
@@ -8806,10 +8806,10 @@
         <v>0.5811444681729387</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9025171411943749</v>
+        <v>0.9025173543234968</v>
       </c>
       <c r="N19" t="n">
-        <v>1.049102939822638</v>
+        <v>1.049103063441054</v>
       </c>
       <c r="O19" t="n">
         <v>1.340543013421222</v>
@@ -8977,7 +8977,7 @@
         <v>0.1350103894400907</v>
       </c>
       <c r="L22" t="n">
-        <v>1.266776821011175</v>
+        <v>1.266776626504039</v>
       </c>
       <c r="M22" t="n">
         <v>0.5893131979102355</v>
@@ -9038,7 +9038,7 @@
         <v>0.3702125948100741</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7965964224130706</v>
+        <v>0.7965965737611478</v>
       </c>
       <c r="N23" t="n">
         <v>0.8502590500059604</v>
@@ -9215,13 +9215,13 @@
         <v>0.7050461587862247</v>
       </c>
       <c r="N26" t="n">
-        <v>1.024658496293005</v>
+        <v>1.024658316759524</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1030357037266632</v>
+        <v>0.1030358103006246</v>
       </c>
       <c r="P26" t="n">
-        <v>0.03322884827017059</v>
+        <v>0.03322888154660575</v>
       </c>
     </row>
     <row r="27">
@@ -9331,13 +9331,13 @@
         <v>0.5748832195675018</v>
       </c>
       <c r="N28" t="n">
-        <v>0.7628383734313864</v>
+        <v>0.7628382498692772</v>
       </c>
       <c r="O28" t="n">
-        <v>2.007476510233244</v>
+        <v>2.007475970777251</v>
       </c>
       <c r="P28" t="n">
-        <v>0.4434466867927711</v>
+        <v>0.4434466004882995</v>
       </c>
     </row>
     <row r="29">
@@ -9389,13 +9389,13 @@
         <v>0.8900890690172796</v>
       </c>
       <c r="N29" t="n">
-        <v>1.320267534583946</v>
+        <v>1.320267287091065</v>
       </c>
       <c r="O29" t="n">
-        <v>4.633171856243308</v>
+        <v>4.633171491545954</v>
       </c>
       <c r="P29" t="n">
-        <v>0.7793074628066736</v>
+        <v>0.7793074244086062</v>
       </c>
     </row>
     <row r="30">
@@ -9563,7 +9563,7 @@
         <v>0.5675864707062335</v>
       </c>
       <c r="N32" t="n">
-        <v>1.390004627696169</v>
+        <v>1.390004477849068</v>
       </c>
       <c r="O32" t="n">
         <v>6.446047524636436</v>
@@ -9621,13 +9621,13 @@
         <v>0.5356575889095865</v>
       </c>
       <c r="N33" t="n">
-        <v>0.8245132360763423</v>
+        <v>0.8245130650060515</v>
       </c>
       <c r="O33" t="n">
-        <v>0.4931626953762251</v>
+        <v>0.4931628099525516</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1429723131806682</v>
+        <v>0.1429723424156082</v>
       </c>
     </row>
     <row r="34">
@@ -9795,7 +9795,7 @@
         <v>0.6245179042853479</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8041652033185138</v>
+        <v>0.8041653970297045</v>
       </c>
       <c r="O36" t="n">
         <v>0.6227741146194077</v>
@@ -9850,16 +9850,16 @@
         <v>0.2527497652708715</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6674156522364612</v>
+        <v>0.6674155080806141</v>
       </c>
       <c r="N37" t="n">
         <v>0.8727768373936435</v>
       </c>
       <c r="O37" t="n">
-        <v>2.679941156324026</v>
+        <v>2.679941507396149</v>
       </c>
       <c r="P37" t="n">
-        <v>0.5438802968360614</v>
+        <v>0.5438803459322556</v>
       </c>
     </row>
     <row r="38">
@@ -9914,10 +9914,10 @@
         <v>1.307466010869858</v>
       </c>
       <c r="O38" t="n">
-        <v>7.906652890998293</v>
+        <v>7.906652156707558</v>
       </c>
       <c r="P38" t="n">
-        <v>1.072867341206321</v>
+        <v>1.072867284241887</v>
       </c>
     </row>
     <row r="39">
@@ -9963,19 +9963,19 @@
         <v>0.2336421344488935</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1709567848235387</v>
+        <v>0.1709567069484135</v>
       </c>
       <c r="M39" t="n">
-        <v>0.764135733501101</v>
+        <v>0.7641355567423178</v>
       </c>
       <c r="N39" t="n">
         <v>0.6226043022338741</v>
       </c>
       <c r="O39" t="n">
-        <v>0.7182467559336299</v>
+        <v>0.7182465882510003</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1977380435875664</v>
+        <v>0.1977380046253956</v>
       </c>
     </row>
     <row r="40">
@@ -10027,13 +10027,13 @@
         <v>0.7148199980944048</v>
       </c>
       <c r="N40" t="n">
-        <v>0.6597446028585605</v>
+        <v>0.6597444657071088</v>
       </c>
       <c r="O40" t="n">
-        <v>1.027456268139173</v>
+        <v>1.027455858830626</v>
       </c>
       <c r="P40" t="n">
-        <v>0.2656603213379691</v>
+        <v>0.2656602361662805</v>
       </c>
     </row>
     <row r="41">
@@ -10088,10 +10088,10 @@
         <v>0.6934919068830254</v>
       </c>
       <c r="O41" t="n">
-        <v>2.476652362834999</v>
+        <v>2.4766512744254</v>
       </c>
       <c r="P41" t="n">
-        <v>0.5149108949739487</v>
+        <v>0.5149107368866508</v>
       </c>
     </row>
     <row r="42">
@@ -10137,19 +10137,19 @@
         <v>-0.1025227566951225</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4089105537527835</v>
+        <v>0.4089103934758482</v>
       </c>
       <c r="M42" t="n">
         <v>0.5489365422163925</v>
       </c>
       <c r="N42" t="n">
-        <v>1.090249197169175</v>
+        <v>1.090249020780648</v>
       </c>
       <c r="O42" t="n">
-        <v>2.888343111231949</v>
+        <v>2.888342806039791</v>
       </c>
       <c r="P42" t="n">
-        <v>0.5724910906075609</v>
+        <v>0.5724910494664759</v>
       </c>
     </row>
     <row r="43">
@@ -10372,16 +10372,16 @@
         <v>0.3932471057297879</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2760444058302054</v>
+        <v>0.2760445035864412</v>
       </c>
       <c r="N46" t="n">
-        <v>0.4769515687982373</v>
+        <v>0.4769514378362274</v>
       </c>
       <c r="O46" t="n">
-        <v>0.1992278750609635</v>
+        <v>0.1992280477426769</v>
       </c>
       <c r="P46" t="n">
-        <v>0.06243060217507357</v>
+        <v>0.06243065316964325</v>
       </c>
     </row>
     <row r="47">
@@ -10433,13 +10433,13 @@
         <v>0.5569413447118006</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4668899687583246</v>
+        <v>0.4668898503119241</v>
       </c>
       <c r="O47" t="n">
-        <v>0.5701785880667818</v>
+        <v>0.5701784523527076</v>
       </c>
       <c r="P47" t="n">
-        <v>0.1622949483644349</v>
+        <v>0.1622949148778434</v>
       </c>
     </row>
     <row r="48">
@@ -10491,13 +10491,13 @@
         <v>0.4407050891570201</v>
       </c>
       <c r="N48" t="n">
-        <v>0.5928423018604885</v>
+        <v>0.5928424207238172</v>
       </c>
       <c r="O48" t="n">
-        <v>2.91211491258255</v>
+        <v>2.912114195572206</v>
       </c>
       <c r="P48" t="n">
-        <v>0.575689113088059</v>
+        <v>0.5756890168242317</v>
       </c>
     </row>
     <row r="49">
@@ -10601,19 +10601,19 @@
         <v>0.3749302040370464</v>
       </c>
       <c r="L50" t="n">
-        <v>0.3457797420718609</v>
+        <v>0.3457796465264849</v>
       </c>
       <c r="M50" t="n">
-        <v>0.204538802521828</v>
+        <v>0.2045387259792135</v>
       </c>
       <c r="N50" t="n">
         <v>0.3439219460844007</v>
       </c>
       <c r="O50" t="n">
-        <v>0.02269183370436045</v>
+        <v>0.02269216476130165</v>
       </c>
       <c r="P50" t="n">
-        <v>0.007507441841103635</v>
+        <v>0.007507550554952225</v>
       </c>
     </row>
     <row r="51">
@@ -10659,13 +10659,13 @@
         <v>0.2430853145142446</v>
       </c>
       <c r="L51" t="n">
-        <v>0.6475538517964847</v>
+        <v>0.6475536856953985</v>
       </c>
       <c r="M51" t="n">
         <v>0.2941056709378393</v>
       </c>
       <c r="N51" t="n">
-        <v>0.1165023278261308</v>
+        <v>0.1165022515458092</v>
       </c>
       <c r="O51" t="n">
         <v>0.196719774857534</v>
@@ -10775,13 +10775,13 @@
         <v>0.2814995188559202</v>
       </c>
       <c r="N53" t="n">
-        <v>0.5167142063441161</v>
+        <v>0.516714070669833</v>
       </c>
       <c r="O53" t="n">
-        <v>1.386536286090338</v>
+        <v>1.386535950177898</v>
       </c>
       <c r="P53" t="n">
-        <v>0.336357577803633</v>
+        <v>0.3363575151047951</v>
       </c>
     </row>
     <row r="54">
@@ -10891,7 +10891,7 @@
         <v>0.455094281444669</v>
       </c>
       <c r="N55" t="n">
-        <v>0.9374010547915597</v>
+        <v>0.9374008463549652</v>
       </c>
       <c r="O55" t="n">
         <v>0.5319391946796537</v>
@@ -10946,16 +10946,16 @@
         <v>0.2006747882910678</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5330527274572519</v>
+        <v>0.5330525925160468</v>
       </c>
       <c r="N56" t="n">
         <v>0.6411131210480601</v>
       </c>
       <c r="O56" t="n">
-        <v>0.8635671213687435</v>
+        <v>0.8635673207666361</v>
       </c>
       <c r="P56" t="n">
-        <v>0.2305946232313556</v>
+        <v>0.230594667121728</v>
       </c>
     </row>
     <row r="57">
@@ -11184,10 +11184,10 @@
         <v>0.4314490291712281</v>
       </c>
       <c r="O60" t="n">
-        <v>0.7749698736315818</v>
+        <v>0.7749697323917717</v>
       </c>
       <c r="P60" t="n">
-        <v>0.2107756049202796</v>
+        <v>0.210775572805233</v>
       </c>
     </row>
     <row r="61">
@@ -11236,16 +11236,16 @@
         <v>0.3465235181323922</v>
       </c>
       <c r="M61" t="n">
-        <v>0.4058048482838774</v>
+        <v>0.4058046851740424</v>
       </c>
       <c r="N61" t="n">
-        <v>0.4815561706817151</v>
+        <v>0.4815562612625666</v>
       </c>
       <c r="O61" t="n">
-        <v>1.63496664943556</v>
+        <v>1.634967222469658</v>
       </c>
       <c r="P61" t="n">
-        <v>0.3812057391518016</v>
+        <v>0.381205839276779</v>
       </c>
     </row>
     <row r="62">
@@ -11300,10 +11300,10 @@
         <v>0.6348785966478943</v>
       </c>
       <c r="O62" t="n">
-        <v>0.02508820317541027</v>
+        <v>0.02508834357844902</v>
       </c>
       <c r="P62" t="n">
-        <v>0.008293757807272373</v>
+        <v>0.008293803841522784</v>
       </c>
     </row>
     <row r="63">
@@ -11355,7 +11355,7 @@
         <v>0.4584615128165592</v>
       </c>
       <c r="N63" t="n">
-        <v>0.8075243446629965</v>
+        <v>0.807524552114502</v>
       </c>
       <c r="O63" t="n">
         <v>1.434229106592608</v>
@@ -11413,7 +11413,7 @@
         <v>0.3872692742288826</v>
       </c>
       <c r="N64" t="n">
-        <v>0.9629207792361025</v>
+        <v>0.9629206362709333</v>
       </c>
       <c r="O64" t="n">
         <v>2.039127705383382</v>
@@ -11468,16 +11468,16 @@
         <v>0.4065866041776069</v>
       </c>
       <c r="M65" t="n">
-        <v>0.3708559998535936</v>
+        <v>0.3708558556710855</v>
       </c>
       <c r="N65" t="n">
-        <v>0.03395246093822513</v>
+        <v>0.03395254296018169</v>
       </c>
       <c r="O65" t="n">
-        <v>-0.3202428262978377</v>
+        <v>-0.3202427553945151</v>
       </c>
       <c r="P65" t="n">
-        <v>-0.1207387511549983</v>
+        <v>-0.1207387205840119</v>
       </c>
     </row>
     <row r="66">
@@ -11590,10 +11590,10 @@
         <v>0.5437333860786051</v>
       </c>
       <c r="O67" t="n">
-        <v>0.6787762021334942</v>
+        <v>0.6787760865073351</v>
       </c>
       <c r="P67" t="n">
-        <v>0.1884956633300323</v>
+        <v>0.1884956360440462</v>
       </c>
     </row>
     <row r="68">
@@ -11648,10 +11648,10 @@
         <v>0.3533861346773128</v>
       </c>
       <c r="O68" t="n">
-        <v>1.398165001367012</v>
+        <v>1.398164761372844</v>
       </c>
       <c r="P68" t="n">
-        <v>0.3385245885658212</v>
+        <v>0.3385245439152789</v>
       </c>
     </row>
     <row r="69">
@@ -11700,16 +11700,16 @@
         <v>0.2778064964011986</v>
       </c>
       <c r="M69" t="n">
-        <v>0.3569342125712471</v>
+        <v>0.3569340904591349</v>
       </c>
       <c r="N69" t="n">
         <v>0.4929796842791168</v>
       </c>
       <c r="O69" t="n">
-        <v>0.6973376429820597</v>
+        <v>0.6973380251091053</v>
       </c>
       <c r="P69" t="n">
-        <v>0.1928598314296806</v>
+        <v>0.192859920947122</v>
       </c>
     </row>
     <row r="70">
@@ -11755,7 +11755,7 @@
         <v>0.3270130190245142</v>
       </c>
       <c r="L70" t="n">
-        <v>0.06923362585582815</v>
+        <v>0.06923371196989803</v>
       </c>
       <c r="M70" t="n">
         <v>0.1566777195949434</v>
@@ -11764,10 +11764,10 @@
         <v>0.4584647763480352</v>
       </c>
       <c r="O70" t="n">
-        <v>-0.01532865003034978</v>
+        <v>-0.01532857699863477</v>
       </c>
       <c r="P70" t="n">
-        <v>-0.005135882138581738</v>
+        <v>-0.005135857542682865</v>
       </c>
     </row>
     <row r="71">
@@ -11813,7 +11813,7 @@
         <v>0.1649175887612344</v>
       </c>
       <c r="L71" t="n">
-        <v>0.1314585485511923</v>
+        <v>0.1314586211369522</v>
       </c>
       <c r="M71" t="n">
         <v>0.3562575115137776</v>
@@ -11822,10 +11822,10 @@
         <v>0.5448538515474555</v>
       </c>
       <c r="O71" t="n">
-        <v>0.8252957546491255</v>
+        <v>0.8252959435528999</v>
       </c>
       <c r="P71" t="n">
-        <v>0.2221122047096982</v>
+        <v>0.2221122468693681</v>
       </c>
     </row>
     <row r="72">
@@ -11929,19 +11929,19 @@
         <v>0.2204228106932928</v>
       </c>
       <c r="L73" t="n">
-        <v>0.3781793853064817</v>
+        <v>0.3781792230865633</v>
       </c>
       <c r="M73" t="n">
-        <v>0.2832214797464565</v>
+        <v>0.2832213391106446</v>
       </c>
       <c r="N73" t="n">
-        <v>0.2155286108543433</v>
+        <v>0.2155284846648906</v>
       </c>
       <c r="O73" t="n">
-        <v>0.4149829496823025</v>
+        <v>0.4149831206819428</v>
       </c>
       <c r="P73" t="n">
-        <v>0.1226655657773561</v>
+        <v>0.1226656110017881</v>
       </c>
     </row>
     <row r="74">
@@ -12051,13 +12051,13 @@
         <v>0.4884732060391868</v>
       </c>
       <c r="N75" t="n">
-        <v>0.3959695474114637</v>
+        <v>0.3959693714631136</v>
       </c>
       <c r="O75" t="n">
-        <v>0.1853354921890242</v>
+        <v>0.1853353653315981</v>
       </c>
       <c r="P75" t="n">
-        <v>0.05831210311822899</v>
+        <v>0.05831206536386735</v>
       </c>
     </row>
     <row r="76">
@@ -12109,7 +12109,7 @@
         <v>0.3864532548969266</v>
       </c>
       <c r="N76" t="n">
-        <v>0.4949252228338925</v>
+        <v>0.494925316547109</v>
       </c>
       <c r="O76" t="n">
         <v>2.913248099434589</v>
@@ -12167,13 +12167,13 @@
         <v>0.360304774717779</v>
       </c>
       <c r="N77" t="n">
-        <v>0.5303684782401494</v>
+        <v>0.5303682959110572</v>
       </c>
       <c r="O77" t="n">
-        <v>0.7062689135830036</v>
+        <v>0.7062690269088545</v>
       </c>
       <c r="P77" t="n">
-        <v>0.1949484203813898</v>
+        <v>0.1949484468364897</v>
       </c>
     </row>
     <row r="78">
@@ -12225,13 +12225,13 @@
         <v>0.3363631522260104</v>
       </c>
       <c r="N78" t="n">
-        <v>0.2475725283844661</v>
+        <v>0.2475724018023036</v>
       </c>
       <c r="O78" t="n">
-        <v>0.1629646885549711</v>
+        <v>0.1629645785597127</v>
       </c>
       <c r="P78" t="n">
-        <v>0.05161194241504652</v>
+        <v>0.05161190926060599</v>
       </c>
     </row>
     <row r="79">
@@ -12286,10 +12286,10 @@
         <v>0.3128422889996696</v>
       </c>
       <c r="O79" t="n">
-        <v>0.9662915328916595</v>
+        <v>0.9662914076366937</v>
       </c>
       <c r="P79" t="n">
-        <v>0.2528025721257934</v>
+        <v>0.252802545524152</v>
       </c>
     </row>
     <row r="80">
@@ -12341,13 +12341,13 @@
         <v>0.4045358173501639</v>
       </c>
       <c r="N80" t="n">
-        <v>0.6661260063733485</v>
+        <v>0.6661262003736961</v>
       </c>
       <c r="O80" t="n">
-        <v>1.085117758392727</v>
+        <v>1.085117910313786</v>
       </c>
       <c r="P80" t="n">
-        <v>0.27754692906398</v>
+        <v>0.277546960091209</v>
       </c>
     </row>
     <row r="81">
@@ -12393,19 +12393,19 @@
         <v>0.1183204030017726</v>
       </c>
       <c r="L81" t="n">
-        <v>0.1244042056189409</v>
+        <v>0.1244041136673035</v>
       </c>
       <c r="M81" t="n">
-        <v>0.4501953569964003</v>
+        <v>0.4501952040400354</v>
       </c>
       <c r="N81" t="n">
-        <v>0.4160203692592508</v>
+        <v>0.4160202234270145</v>
       </c>
       <c r="O81" t="n">
-        <v>0.4224307318505878</v>
+        <v>0.4224302903838852</v>
       </c>
       <c r="P81" t="n">
-        <v>0.1246318418308507</v>
+        <v>0.1246317254836358</v>
       </c>
     </row>
     <row r="82">
@@ -12454,16 +12454,16 @@
         <v>0.1651544387547697</v>
       </c>
       <c r="M82" t="n">
-        <v>0.3451250883649237</v>
+        <v>0.3451249913051158</v>
       </c>
       <c r="N82" t="n">
-        <v>0.496774402824725</v>
+        <v>0.4967742826462267</v>
       </c>
       <c r="O82" t="n">
-        <v>1.709331217226505</v>
+        <v>1.709331414109565</v>
       </c>
       <c r="P82" t="n">
-        <v>0.3940789417179467</v>
+        <v>0.3940789754864917</v>
       </c>
     </row>
     <row r="83">
@@ -12512,7 +12512,7 @@
         <v>0.1679896919801747</v>
       </c>
       <c r="M83" t="n">
-        <v>0.3639738276428508</v>
+        <v>0.3639739172508984</v>
       </c>
       <c r="N83" t="n">
         <v>0.4193609164938652</v>
@@ -12567,7 +12567,7 @@
         <v>0.1404366362013083</v>
       </c>
       <c r="L84" t="n">
-        <v>0.2443345717715735</v>
+        <v>0.2443344272863401</v>
       </c>
       <c r="M84" t="n">
         <v>0.1738311633259442</v>
@@ -12628,16 +12628,16 @@
         <v>0.1736620324886784</v>
       </c>
       <c r="M85" t="n">
-        <v>0.3328302038274265</v>
+        <v>0.3328300455334325</v>
       </c>
       <c r="N85" t="n">
-        <v>0.3252447993424781</v>
+        <v>0.3252449558398702</v>
       </c>
       <c r="O85" t="n">
-        <v>0.3405400117218569</v>
+        <v>0.3405399316565492</v>
       </c>
       <c r="P85" t="n">
-        <v>0.1026218482665406</v>
+        <v>0.1026218263147503</v>
       </c>
     </row>
     <row r="86">
@@ -12689,7 +12689,7 @@
         <v>0.2942883496008892</v>
       </c>
       <c r="N86" t="n">
-        <v>0.4510921892696798</v>
+        <v>0.4510923134386149</v>
       </c>
       <c r="O86" t="n">
         <v>0.2248960039709578</v>
@@ -12750,10 +12750,10 @@
         <v>0.4406276805711637</v>
       </c>
       <c r="O87" t="n">
-        <v>0.752508543266458</v>
+        <v>0.7525084231144121</v>
       </c>
       <c r="P87" t="n">
-        <v>0.2056466615719876</v>
+        <v>0.205646634018928</v>
       </c>
     </row>
     <row r="88">
@@ -12802,16 +12802,16 @@
         <v>0.1787645220226246</v>
       </c>
       <c r="M88" t="n">
-        <v>0.159456880969189</v>
+        <v>0.1594567662688824</v>
       </c>
       <c r="N88" t="n">
-        <v>0.03631395761323231</v>
+        <v>0.03631404924333026</v>
       </c>
       <c r="O88" t="n">
-        <v>-0.2668037998597723</v>
+        <v>-0.2668038457262935</v>
       </c>
       <c r="P88" t="n">
-        <v>-0.0982764713855927</v>
+        <v>-0.09827649018861895</v>
       </c>
     </row>
     <row r="89">
@@ -12860,16 +12860,16 @@
         <v>0.2050473737654177</v>
       </c>
       <c r="M89" t="n">
-        <v>0.2801826331427688</v>
+        <v>0.2801827318058157</v>
       </c>
       <c r="N89" t="n">
         <v>0.2898177207774832</v>
       </c>
       <c r="O89" t="n">
-        <v>1.537098026277856</v>
+        <v>1.537097832521886</v>
       </c>
       <c r="P89" t="n">
-        <v>0.3638891750767186</v>
+        <v>0.3638891403570408</v>
       </c>
     </row>
     <row r="90">
@@ -12924,10 +12924,10 @@
         <v>0.7551066862830169</v>
       </c>
       <c r="O90" t="n">
-        <v>0.6279594843625353</v>
+        <v>0.6279593556271912</v>
       </c>
       <c r="P90" t="n">
-        <v>0.1763806277620616</v>
+        <v>0.1763805967535568</v>
       </c>
     </row>
     <row r="91">
@@ -12976,16 +12976,16 @@
         <v>0.1697031517570995</v>
       </c>
       <c r="M91" t="n">
-        <v>0.193779705013472</v>
+        <v>0.1937797966697599</v>
       </c>
       <c r="N91" t="n">
-        <v>0.4214862856024881</v>
+        <v>0.421486155645644</v>
       </c>
       <c r="O91" t="n">
-        <v>2.045487073430452</v>
+        <v>2.045487371692102</v>
       </c>
       <c r="P91" t="n">
-        <v>0.4495023378834282</v>
+        <v>0.4495023852027278</v>
       </c>
     </row>
     <row r="92">
@@ -13034,16 +13034,16 @@
         <v>0.2105575051694557</v>
       </c>
       <c r="M92" t="n">
-        <v>0.2590225808904834</v>
+        <v>0.2590224319815229</v>
       </c>
       <c r="N92" t="n">
-        <v>0.1837449154348931</v>
+        <v>0.1837447838002957</v>
       </c>
       <c r="O92" t="n">
-        <v>0.6546573188348521</v>
+        <v>0.6546569330358218</v>
       </c>
       <c r="P92" t="n">
-        <v>0.1827765028449655</v>
+        <v>0.182776410919776</v>
       </c>
     </row>
     <row r="93">
@@ -13092,10 +13092,10 @@
         <v>0.07663396549151913</v>
       </c>
       <c r="M93" t="n">
-        <v>0.4130276845829544</v>
+        <v>0.4130275897665212</v>
       </c>
       <c r="N93" t="n">
-        <v>0.504928279807374</v>
+        <v>0.5049281722565166</v>
       </c>
       <c r="O93" t="n">
         <v>0.533601954862873</v>
@@ -13150,7 +13150,7 @@
         <v>0.2688778272524419</v>
       </c>
       <c r="M94" t="n">
-        <v>0.2806398431656594</v>
+        <v>0.2806399322194333</v>
       </c>
       <c r="N94" t="n">
         <v>0.3463720502671284</v>
@@ -13388,10 +13388,10 @@
         <v>0.7031773425999421</v>
       </c>
       <c r="O98" t="n">
-        <v>2.105981870243868</v>
+        <v>2.105981639896615</v>
       </c>
       <c r="P98" t="n">
-        <v>0.459037000260039</v>
+        <v>0.4590369641914473</v>
       </c>
     </row>
     <row r="99">
@@ -13446,10 +13446,10 @@
         <v>0.2883118478995923</v>
       </c>
       <c r="O99" t="n">
-        <v>1.363891546523861</v>
+        <v>1.363891717356255</v>
       </c>
       <c r="P99" t="n">
-        <v>0.3321174454115743</v>
+        <v>0.3321174775011468</v>
       </c>
     </row>
     <row r="100">
@@ -13501,7 +13501,7 @@
         <v>0.2489992939479486</v>
       </c>
       <c r="N100" t="n">
-        <v>0.2339977714375903</v>
+        <v>0.2339978930885378</v>
       </c>
       <c r="O100" t="n">
         <v>0.6487116772815948</v>
@@ -13556,16 +13556,16 @@
         <v>0.1297184598969634</v>
       </c>
       <c r="M101" t="n">
-        <v>0.488759742839052</v>
+        <v>0.4887598822441113</v>
       </c>
       <c r="N101" t="n">
         <v>0.3641304054055794</v>
       </c>
       <c r="O101" t="n">
-        <v>-0.02291483810558836</v>
+        <v>-0.02291471801080391</v>
       </c>
       <c r="P101" t="n">
-        <v>-0.00769737695836914</v>
+        <v>-0.007697336303310154</v>
       </c>
     </row>
     <row r="102">
@@ -13614,16 +13614,16 @@
         <v>0.2224536211128001</v>
       </c>
       <c r="M102" t="n">
-        <v>0.2813740411846677</v>
+        <v>0.2813739516943787</v>
       </c>
       <c r="N102" t="n">
         <v>0.394497288562071</v>
       </c>
       <c r="O102" t="n">
-        <v>1.884856954557365</v>
+        <v>1.884856727757582</v>
       </c>
       <c r="P102" t="n">
-        <v>0.4235566721089581</v>
+        <v>0.4235566348035438</v>
       </c>
     </row>
     <row r="103">
@@ -13672,10 +13672,10 @@
         <v>0.2962109081757076</v>
       </c>
       <c r="M103" t="n">
-        <v>0.2743766461842938</v>
+        <v>0.2743767367972125</v>
       </c>
       <c r="N103" t="n">
-        <v>0.456479762669709</v>
+        <v>0.4564796443101455</v>
       </c>
       <c r="O103" t="n">
         <v>2.692738180644901</v>
@@ -13736,10 +13736,10 @@
         <v>0.3383514191409882</v>
       </c>
       <c r="O104" t="n">
-        <v>-0.133560174334013</v>
+        <v>-0.1335602421655232</v>
       </c>
       <c r="P104" t="n">
-        <v>-0.0466636878155352</v>
+        <v>-0.04666371269367897</v>
       </c>
     </row>
     <row r="105">
@@ -13852,10 +13852,10 @@
         <v>0.2410917921633398</v>
       </c>
       <c r="O106" t="n">
-        <v>0.1747456579363058</v>
+        <v>0.1747457976169018</v>
       </c>
       <c r="P106" t="n">
-        <v>0.05515100312652721</v>
+        <v>0.05515104494667633</v>
       </c>
     </row>
     <row r="107">
@@ -13907,13 +13907,13 @@
         <v>0.2505571114104495</v>
       </c>
       <c r="N107" t="n">
-        <v>0.335680851658873</v>
+        <v>0.3356809605656679</v>
       </c>
       <c r="O107" t="n">
-        <v>0.9772632658911571</v>
+        <v>0.9772633852208625</v>
       </c>
       <c r="P107" t="n">
-        <v>0.2551284273351657</v>
+        <v>0.2551284525845605</v>
       </c>
     </row>
     <row r="108">
@@ -13959,13 +13959,13 @@
         <v>0.1438628706464202</v>
       </c>
       <c r="L108" t="n">
-        <v>0.07827268071561355</v>
+        <v>0.07827259046984558</v>
       </c>
       <c r="M108" t="n">
         <v>0.2489960010667958</v>
       </c>
       <c r="N108" t="n">
-        <v>0.4421520865788595</v>
+        <v>0.4421524094445493</v>
       </c>
       <c r="O108" t="n">
         <v>0.6580507426734081</v>
@@ -14026,10 +14026,10 @@
         <v>0.1698878415471274</v>
       </c>
       <c r="O109" t="n">
-        <v>1.831945702775993</v>
+        <v>1.831945480826255</v>
       </c>
       <c r="P109" t="n">
-        <v>0.4147997490387982</v>
+        <v>0.4147997120778211</v>
       </c>
     </row>
     <row r="110">
@@ -14075,19 +14075,19 @@
         <v>0.3918158291051093</v>
       </c>
       <c r="L110" t="n">
-        <v>0.1822674072213568</v>
+        <v>0.1822673276746378</v>
       </c>
       <c r="M110" t="n">
         <v>0.07366655763910956</v>
       </c>
       <c r="N110" t="n">
-        <v>-0.006617832123474998</v>
+        <v>-0.006617944442553703</v>
       </c>
       <c r="O110" t="n">
-        <v>-0.01672982295609038</v>
+        <v>-0.01672960286792557</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.005607998509453815</v>
+        <v>-0.005607924316927804</v>
       </c>
     </row>
     <row r="111">
@@ -14197,13 +14197,13 @@
         <v>0.2763035598303567</v>
       </c>
       <c r="N112" t="n">
-        <v>0.1631207935519596</v>
+        <v>0.1631207107553512</v>
       </c>
       <c r="O112" t="n">
-        <v>-0.01077882666690888</v>
+        <v>-0.01077888655627535</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.003605929319590251</v>
+        <v>-0.003605949427466504</v>
       </c>
     </row>
     <row r="113">
@@ -14255,13 +14255,13 @@
         <v>0.2746186991705282</v>
       </c>
       <c r="N113" t="n">
-        <v>0.3475074504576852</v>
+        <v>0.3475072936755179</v>
       </c>
       <c r="O113" t="n">
-        <v>0.6546433147836668</v>
+        <v>0.6546430783860577</v>
       </c>
       <c r="P113" t="n">
-        <v>0.1827731660595122</v>
+        <v>0.1827731097322141</v>
       </c>
     </row>
     <row r="114">
@@ -14316,10 +14316,10 @@
         <v>0.14544047367494</v>
       </c>
       <c r="O114" t="n">
-        <v>0.6793894268308638</v>
+        <v>0.6793895814471118</v>
       </c>
       <c r="P114" t="n">
-        <v>0.1886403572584339</v>
+        <v>0.1886403937365935</v>
       </c>
     </row>
     <row r="115">
@@ -14374,10 +14374,10 @@
         <v>0.3429423822904287</v>
       </c>
       <c r="O115" t="n">
-        <v>3.962501740161588</v>
+        <v>3.962501323990302</v>
       </c>
       <c r="P115" t="n">
-        <v>0.7056904740795562</v>
+        <v>0.7056904263979999</v>
       </c>
     </row>
     <row r="116">
@@ -14426,16 +14426,16 @@
         <v>0.1015927802689764</v>
       </c>
       <c r="M116" t="n">
-        <v>0.3125975439662974</v>
+        <v>0.3125976797594658</v>
       </c>
       <c r="N116" t="n">
         <v>0.4389178071347937</v>
       </c>
       <c r="O116" t="n">
-        <v>0.01739204206665201</v>
+        <v>0.01739212364810006</v>
       </c>
       <c r="P116" t="n">
-        <v>0.005764059141998734</v>
+        <v>0.005764086025010329</v>
       </c>
     </row>
     <row r="117">
@@ -14490,10 +14490,10 @@
         <v>0.4294762414589659</v>
       </c>
       <c r="O117" t="n">
-        <v>0.7134118142195378</v>
+        <v>0.7134116412068636</v>
       </c>
       <c r="P117" t="n">
-        <v>0.1966135574723291</v>
+        <v>0.1966135171960963</v>
       </c>
     </row>
     <row r="118">
@@ -14548,10 +14548,10 @@
         <v>0.2851685895676568</v>
       </c>
       <c r="O118" t="n">
-        <v>-0.1176068890312512</v>
+        <v>-0.1176069483105699</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.04084814820769389</v>
+        <v>-0.04084816968635563</v>
       </c>
     </row>
     <row r="119">
@@ -14777,7 +14777,7 @@
         <v>0.2975946500769548</v>
       </c>
       <c r="N122" t="n">
-        <v>0.5295761834905974</v>
+        <v>0.5295760278082895</v>
       </c>
       <c r="O122" t="n">
         <v>0.9785588952344213</v>
@@ -14832,10 +14832,10 @@
         <v>0.08613277259415653</v>
       </c>
       <c r="M123" t="n">
-        <v>0.2183982474577384</v>
+        <v>0.2183981209832431</v>
       </c>
       <c r="N123" t="n">
-        <v>0.2117295231354435</v>
+        <v>0.2117296482292743</v>
       </c>
       <c r="O123" t="n">
         <v>-0.09707560142083205</v>
@@ -14887,10 +14887,10 @@
         <v>-0.004277260686983864</v>
       </c>
       <c r="L124" t="n">
-        <v>0.2514529455154624</v>
+        <v>0.2514528211409788</v>
       </c>
       <c r="M124" t="n">
-        <v>0.2846662895263998</v>
+        <v>0.2846664205902691</v>
       </c>
       <c r="N124" t="n">
         <v>0.4107492705147933</v>
@@ -14951,7 +14951,7 @@
         <v>0.2891072519895097</v>
       </c>
       <c r="N125" t="n">
-        <v>0.489357521969974</v>
+        <v>0.4893573524391608</v>
       </c>
       <c r="O125" t="n">
         <v>0.4282056675401571</v>
@@ -15070,10 +15070,10 @@
         <v>-0.00412858060613841</v>
       </c>
       <c r="O127" t="n">
-        <v>0.1275579757653804</v>
+        <v>0.127557820018563</v>
       </c>
       <c r="P127" t="n">
-        <v>0.0408295820976059</v>
+        <v>0.04082953417519142</v>
       </c>
     </row>
     <row r="128">
@@ -15125,13 +15125,13 @@
         <v>0.3285570226198724</v>
       </c>
       <c r="N128" t="n">
-        <v>0.1885824527325894</v>
+        <v>0.1885825782071193</v>
       </c>
       <c r="O128" t="n">
-        <v>0.7887814429505917</v>
+        <v>0.7887811587588884</v>
       </c>
       <c r="P128" t="n">
-        <v>0.2139079628615699</v>
+        <v>0.2139078985752385</v>
       </c>
     </row>
     <row r="129">
@@ -15186,10 +15186,10 @@
         <v>0.3949838191975967</v>
       </c>
       <c r="O129" t="n">
-        <v>0.0884491216955392</v>
+        <v>0.08844904158646494</v>
       </c>
       <c r="P129" t="n">
-        <v>0.02865413865089161</v>
+        <v>0.02865411341482216</v>
       </c>
     </row>
     <row r="130">
@@ -15244,10 +15244,10 @@
         <v>0.1366640768107714</v>
       </c>
       <c r="O130" t="n">
-        <v>2.326183255813332</v>
+        <v>2.326183626299121</v>
       </c>
       <c r="P130" t="n">
-        <v>0.4927327378778639</v>
+        <v>0.4927327933003709</v>
       </c>
     </row>
     <row r="131">
@@ -15299,13 +15299,13 @@
         <v>0.213470794935358</v>
       </c>
       <c r="N131" t="n">
-        <v>0.424704297969895</v>
+        <v>0.4247041784479628</v>
       </c>
       <c r="O131" t="n">
-        <v>2.404363978608596</v>
+        <v>2.404364319833086</v>
       </c>
       <c r="P131" t="n">
-        <v>0.5043376634128267</v>
+        <v>0.5043377136734959</v>
       </c>
     </row>
     <row r="132">
@@ -15357,13 +15357,13 @@
         <v>0.4286345728852454</v>
       </c>
       <c r="N132" t="n">
-        <v>0.3892580135966492</v>
+        <v>0.3892581267344162</v>
       </c>
       <c r="O132" t="n">
-        <v>0.4382182372097838</v>
+        <v>0.4382181159571188</v>
       </c>
       <c r="P132" t="n">
-        <v>0.1287772916005137</v>
+        <v>0.1287772598790278</v>
       </c>
     </row>
     <row r="133">
@@ -15409,19 +15409,19 @@
         <v>0.1642709169014573</v>
       </c>
       <c r="L133" t="n">
-        <v>0.2603379142153077</v>
+        <v>0.2603380157308517</v>
       </c>
       <c r="M133" t="n">
         <v>0.1143841200756968</v>
       </c>
       <c r="N133" t="n">
-        <v>0.1876780013179744</v>
+        <v>0.1876780914659477</v>
       </c>
       <c r="O133" t="n">
-        <v>0.4535001184824548</v>
+        <v>0.4534998484483816</v>
       </c>
       <c r="P133" t="n">
-        <v>0.1327611798584409</v>
+        <v>0.1327611097095798</v>
       </c>
     </row>
     <row r="134">
@@ -15470,16 +15470,16 @@
         <v>0.2054818318539198</v>
       </c>
       <c r="M134" t="n">
-        <v>0.2910116688314941</v>
+        <v>0.2910115198275587</v>
       </c>
       <c r="N134" t="n">
-        <v>0.22578580009878</v>
+        <v>0.2257856657707709</v>
       </c>
       <c r="O134" t="n">
-        <v>0.6044250449419524</v>
+        <v>0.604425390139476</v>
       </c>
       <c r="P134" t="n">
-        <v>0.1706843452866096</v>
+        <v>0.1706844292455143</v>
       </c>
     </row>
     <row r="135">
@@ -15592,10 +15592,10 @@
         <v>0.4949092469348817</v>
       </c>
       <c r="O136" t="n">
-        <v>1.926751212124375</v>
+        <v>1.926751421365977</v>
       </c>
       <c r="P136" t="n">
-        <v>0.4304146045634205</v>
+        <v>0.4304146386515288</v>
       </c>
     </row>
     <row r="137">
@@ -15650,10 +15650,10 @@
         <v>0.3317216769369402</v>
       </c>
       <c r="O137" t="n">
-        <v>-0.06234580245585541</v>
+        <v>-0.06234573570232038</v>
       </c>
       <c r="P137" t="n">
-        <v>-0.02122943371821595</v>
+        <v>-0.02122941049131843</v>
       </c>
     </row>
     <row r="138">
@@ -15812,16 +15812,16 @@
         <v>0.03134859182514882</v>
       </c>
       <c r="M140" t="n">
-        <v>0.2329599419481621</v>
+        <v>0.2329598628556209</v>
       </c>
       <c r="N140" t="n">
         <v>0.2984128751251267</v>
       </c>
       <c r="O140" t="n">
-        <v>1.129531323350005</v>
+        <v>1.129531087407796</v>
       </c>
       <c r="P140" t="n">
-        <v>0.2865539746551584</v>
+        <v>0.2865539271404158</v>
       </c>
     </row>
     <row r="141">
@@ -15989,13 +15989,13 @@
         <v>0.5785246041634116</v>
       </c>
       <c r="N143" t="n">
-        <v>0.2568200712589073</v>
+        <v>0.2568201645501904</v>
       </c>
       <c r="O143" t="n">
-        <v>-0.2093521619552619</v>
+        <v>-0.2093522357951362</v>
       </c>
       <c r="P143" t="n">
-        <v>-0.07531382916215834</v>
+        <v>-0.07531385794813583</v>
       </c>
     </row>
     <row r="144">
@@ -16047,7 +16047,7 @@
         <v>0.04431473844230838</v>
       </c>
       <c r="N144" t="n">
-        <v>0.2734266080216023</v>
+        <v>0.2734266981468585</v>
       </c>
       <c r="O144" t="n">
         <v>1.535119681564909</v>
@@ -16099,7 +16099,7 @@
         <v>0.07795467624929864</v>
       </c>
       <c r="L145" t="n">
-        <v>0.1970090395166713</v>
+        <v>0.1970091295222776</v>
       </c>
       <c r="M145" t="n">
         <v>0.2578867067157695</v>
@@ -16108,10 +16108,10 @@
         <v>0.2313059321513449</v>
       </c>
       <c r="O145" t="n">
-        <v>1.32128797664444</v>
+        <v>1.321288145884335</v>
       </c>
       <c r="P145" t="n">
-        <v>0.3240661228443613</v>
+        <v>0.3240661550225901</v>
       </c>
     </row>
     <row r="146">
@@ -16163,7 +16163,7 @@
         <v>0.1838827511158549</v>
       </c>
       <c r="N146" t="n">
-        <v>0.292484269248277</v>
+        <v>0.2924841885427183</v>
       </c>
       <c r="O146" t="n">
         <v>0.9997779837562946</v>
@@ -16221,13 +16221,13 @@
         <v>0.1447760335307755</v>
       </c>
       <c r="N147" t="n">
-        <v>0.1582229220675435</v>
+        <v>0.1582230178351427</v>
       </c>
       <c r="O147" t="n">
-        <v>0.8772403156916144</v>
+        <v>0.8772404414810104</v>
       </c>
       <c r="P147" t="n">
-        <v>0.2335969611246458</v>
+        <v>0.2335969886781086</v>
       </c>
     </row>
     <row r="148">
@@ -16273,19 +16273,19 @@
         <v>0.04487185604100019</v>
       </c>
       <c r="L148" t="n">
-        <v>0.1230179402292575</v>
+        <v>0.1230178078412973</v>
       </c>
       <c r="M148" t="n">
-        <v>0.3467959016676196</v>
+        <v>0.3467959968702088</v>
       </c>
       <c r="N148" t="n">
         <v>0.2784792153299733</v>
       </c>
       <c r="O148" t="n">
-        <v>0.2179506422733377</v>
+        <v>0.2179507201315742</v>
       </c>
       <c r="P148" t="n">
-        <v>0.06793108890651256</v>
+        <v>0.06793111166256049</v>
       </c>
     </row>
     <row r="149">
@@ -16340,10 +16340,10 @@
         <v>0.3538859059075903</v>
       </c>
       <c r="O149" t="n">
-        <v>1.328428345987268</v>
+        <v>1.328428576116147</v>
       </c>
       <c r="P149" t="n">
-        <v>0.3254223589554059</v>
+        <v>0.3254224026211903</v>
       </c>
     </row>
     <row r="150">
@@ -16395,7 +16395,7 @@
         <v>0.3634206942701363</v>
       </c>
       <c r="N150" t="n">
-        <v>0.4224251792415534</v>
+        <v>0.4224252999901867</v>
       </c>
       <c r="O150" t="n">
         <v>0.8425698923229534</v>
@@ -16514,10 +16514,10 @@
         <v>0.3735626514626775</v>
       </c>
       <c r="O152" t="n">
-        <v>0.6611583453243297</v>
+        <v>0.6611581068455408</v>
       </c>
       <c r="P152" t="n">
-        <v>0.1843234924706931</v>
+        <v>0.1843234357961752</v>
       </c>
     </row>
     <row r="153">
@@ -16572,10 +16572,10 @@
         <v>0.4867721946987498</v>
       </c>
       <c r="O153" t="n">
-        <v>1.683171903769229</v>
+        <v>1.683172063832036</v>
       </c>
       <c r="P153" t="n">
-        <v>0.3895776892397131</v>
+        <v>0.3895777168711521</v>
       </c>
     </row>
     <row r="154">
@@ -16624,16 +16624,16 @@
         <v>-0.01744462815968473</v>
       </c>
       <c r="M154" t="n">
-        <v>0.2916113793709598</v>
+        <v>0.2916114836631125</v>
       </c>
       <c r="N154" t="n">
-        <v>0.2141409841796846</v>
+        <v>0.2141408920231624</v>
       </c>
       <c r="O154" t="n">
-        <v>0.2208464444739047</v>
+        <v>0.2208466308284625</v>
       </c>
       <c r="P154" t="n">
-        <v>0.0687767908030823</v>
+        <v>0.06877684518377225</v>
       </c>
     </row>
     <row r="155">
@@ -16734,22 +16734,22 @@
         <v>-0.03731329119760241</v>
       </c>
       <c r="K156" t="n">
-        <v>0.05247957686064297</v>
+        <v>0.05247947384771567</v>
       </c>
       <c r="L156" t="n">
-        <v>0.2249437886869279</v>
+        <v>0.224943928226307</v>
       </c>
       <c r="M156" t="n">
-        <v>0.2878742185789576</v>
+        <v>0.2878739872113814</v>
       </c>
       <c r="N156" t="n">
-        <v>0.1981597418259</v>
+        <v>0.1981600088337048</v>
       </c>
       <c r="O156" t="n">
-        <v>0.2378485466443114</v>
+        <v>0.2378486891392666</v>
       </c>
       <c r="P156" t="n">
-        <v>0.07371537094290881</v>
+        <v>0.07371541214316135</v>
       </c>
     </row>
     <row r="157">
@@ -16798,16 +16798,16 @@
         <v>0.2304215916080661</v>
       </c>
       <c r="M157" t="n">
-        <v>0.1410295487966213</v>
+        <v>0.1410296744443262</v>
       </c>
       <c r="N157" t="n">
         <v>0.3342361814661652</v>
       </c>
       <c r="O157" t="n">
-        <v>0.7987254474877439</v>
+        <v>0.7987256036084578</v>
       </c>
       <c r="P157" t="n">
-        <v>0.2161532170307978</v>
+        <v>0.2161532522162126</v>
       </c>
     </row>
     <row r="158">
@@ -16859,13 +16859,13 @@
         <v>0.2819217672111272</v>
       </c>
       <c r="N158" t="n">
-        <v>0.243154394401182</v>
+        <v>0.2431545113493874</v>
       </c>
       <c r="O158" t="n">
-        <v>0.8429787220392835</v>
+        <v>0.8429788505543541</v>
       </c>
       <c r="P158" t="n">
-        <v>0.226046025228265</v>
+        <v>0.2260460537265843</v>
       </c>
     </row>
     <row r="159">
@@ -16914,16 +16914,16 @@
         <v>0.03636033953264262</v>
       </c>
       <c r="M159" t="n">
-        <v>0.2522371862482315</v>
+        <v>0.2522371073636409</v>
       </c>
       <c r="N159" t="n">
-        <v>0.3761728104382769</v>
+        <v>0.3761726198944455</v>
       </c>
       <c r="O159" t="n">
-        <v>1.490298569540114</v>
+        <v>1.490298101575486</v>
       </c>
       <c r="P159" t="n">
-        <v>0.3554509502513574</v>
+        <v>0.3554508653481323</v>
       </c>
     </row>
     <row r="160">
@@ -17036,10 +17036,10 @@
         <v>0.3026887794442004</v>
       </c>
       <c r="O161" t="n">
-        <v>0.9160141014856669</v>
+        <v>0.9160135800648161</v>
       </c>
       <c r="P161" t="n">
-        <v>0.2420323292023978</v>
+        <v>0.2420322165341922</v>
       </c>
     </row>
     <row r="162">
@@ -17085,7 +17085,7 @@
         <v>0.04968146872702084</v>
       </c>
       <c r="L162" t="n">
-        <v>0.2240435901216065</v>
+        <v>0.2240436984388623</v>
       </c>
       <c r="M162" t="n">
         <v>0.2395852693886775</v>
@@ -17146,10 +17146,10 @@
         <v>0.1482278575978557</v>
       </c>
       <c r="M163" t="n">
-        <v>0.2421554695518013</v>
+        <v>0.2421553708118682</v>
       </c>
       <c r="N163" t="n">
-        <v>0.2311635313357527</v>
+        <v>0.2311634343356033</v>
       </c>
       <c r="O163" t="n">
         <v>1.148255786777997</v>
@@ -17259,10 +17259,10 @@
         <v>0.5311902987777097</v>
       </c>
       <c r="O165" t="n">
-        <v>0.9563229359193908</v>
+        <v>0.9563227280791873</v>
       </c>
       <c r="P165" t="n">
-        <v>0.2506818543215883</v>
+        <v>0.2506818100306762</v>
       </c>
     </row>
     <row r="166">
@@ -17311,10 +17311,10 @@
         <v>0.1710917111162615</v>
       </c>
       <c r="M166" t="n">
-        <v>0.2353552443989169</v>
+        <v>0.2353553511980366</v>
       </c>
       <c r="N166" t="n">
-        <v>0.2389387873867357</v>
+        <v>0.2389385725475344</v>
       </c>
       <c r="O166" t="n">
         <v>1.31098115873893</v>
@@ -17375,10 +17375,10 @@
         <v>0.4769964124812023</v>
       </c>
       <c r="O167" t="n">
-        <v>1.14456123380937</v>
+        <v>1.144560847370294</v>
       </c>
       <c r="P167" t="n">
-        <v>0.2895736495039569</v>
+        <v>0.2895735720457382</v>
       </c>
     </row>
     <row r="168">
@@ -17433,10 +17433,10 @@
         <v>0.4113977517934175</v>
       </c>
       <c r="O168" t="n">
-        <v>2.074993179297946</v>
+        <v>2.07499278588909</v>
       </c>
       <c r="P168" t="n">
-        <v>0.4541684536254289</v>
+        <v>0.4541683916108987</v>
       </c>
     </row>
     <row r="169">
@@ -17549,10 +17549,10 @@
         <v>0.2986602020042002</v>
       </c>
       <c r="O170" t="n">
-        <v>1.043550862897364</v>
+        <v>1.043551137372892</v>
       </c>
       <c r="P170" t="n">
-        <v>0.2690005700370139</v>
+        <v>0.2690006268514527</v>
       </c>
     </row>
     <row r="171">
@@ -17601,16 +17601,16 @@
         <v>0.1696323502578716</v>
       </c>
       <c r="M171" t="n">
-        <v>0.08680577635626219</v>
+        <v>0.08680567427261554</v>
       </c>
       <c r="N171" t="n">
-        <v>0.0795743239586697</v>
+        <v>0.07957442468835429</v>
       </c>
       <c r="O171" t="n">
-        <v>0.7328316224618203</v>
+        <v>0.732831492703552</v>
       </c>
       <c r="P171" t="n">
-        <v>0.2011173903348409</v>
+        <v>0.2011173603540637</v>
       </c>
     </row>
     <row r="172">
@@ -17659,16 +17659,16 @@
         <v>0.09786358261962413</v>
       </c>
       <c r="M172" t="n">
-        <v>0.1413677725245885</v>
+        <v>0.1413678524262574</v>
       </c>
       <c r="N172" t="n">
         <v>0.2226410832641426</v>
       </c>
       <c r="O172" t="n">
-        <v>0.851668842500132</v>
+        <v>0.8516692630924538</v>
       </c>
       <c r="P172" t="n">
-        <v>0.2279700454811644</v>
+        <v>0.2279701384558046</v>
       </c>
     </row>
     <row r="173">
@@ -17717,16 +17717,16 @@
         <v>0.04250262912988578</v>
       </c>
       <c r="M173" t="n">
-        <v>0.2452085799143073</v>
+        <v>0.2452084639480916</v>
       </c>
       <c r="N173" t="n">
         <v>0.2428798187585159</v>
       </c>
       <c r="O173" t="n">
-        <v>0.1545181672710392</v>
+        <v>0.1545182669604197</v>
       </c>
       <c r="P173" t="n">
-        <v>0.04905982879761872</v>
+        <v>0.04905985899206833</v>
       </c>
     </row>
     <row r="174">
@@ -17781,10 +17781,10 @@
         <v>0.1024373616220888</v>
       </c>
       <c r="O174" t="n">
-        <v>0.05144151890255588</v>
+        <v>0.05144170135440063</v>
       </c>
       <c r="P174" t="n">
-        <v>0.01686127255464154</v>
+        <v>0.01686133137173562</v>
       </c>
     </row>
     <row r="175">
@@ -17839,10 +17839,10 @@
         <v>0.176378020085888</v>
       </c>
       <c r="O175" t="n">
-        <v>1.242520810732938</v>
+        <v>1.242521018427754</v>
       </c>
       <c r="P175" t="n">
-        <v>0.3089171578759304</v>
+        <v>0.3089171982851133</v>
       </c>
     </row>
     <row r="176">
@@ -17894,13 +17894,13 @@
         <v>0.03715070385135322</v>
       </c>
       <c r="N176" t="n">
-        <v>0.1552985334289123</v>
+        <v>0.1552986027722234</v>
       </c>
       <c r="O176" t="n">
-        <v>0.3180301178740463</v>
+        <v>0.3180302081281179</v>
       </c>
       <c r="P176" t="n">
-        <v>0.09641536091793612</v>
+        <v>0.09641538594415944</v>
       </c>
     </row>
     <row r="177">
@@ -17949,16 +17949,16 @@
         <v>-0.03068866000893766</v>
       </c>
       <c r="M177" t="n">
-        <v>0.1176290157208588</v>
+        <v>0.1176291014670925</v>
       </c>
       <c r="N177" t="n">
         <v>0.2806973539762798</v>
       </c>
       <c r="O177" t="n">
-        <v>1.141235625784828</v>
+        <v>1.141235468416049</v>
       </c>
       <c r="P177" t="n">
-        <v>0.28890671662407</v>
+        <v>0.2889066850482704</v>
       </c>
     </row>
     <row r="178">
@@ -18013,10 +18013,10 @@
         <v>0.1271626805092443</v>
       </c>
       <c r="O178" t="n">
-        <v>0.09584276157544269</v>
+        <v>0.09584265826104854</v>
       </c>
       <c r="P178" t="n">
-        <v>0.03097803904494145</v>
+        <v>0.03097800664525829</v>
       </c>
     </row>
     <row r="179">
@@ -18062,7 +18062,7 @@
         <v>0.06607646394112177</v>
       </c>
       <c r="L179" t="n">
-        <v>0.1706689415684008</v>
+        <v>0.1706690218742766</v>
       </c>
       <c r="M179" t="n">
         <v>0.1498347702920988</v>
@@ -18071,10 +18071,10 @@
         <v>0.2177247957462911</v>
       </c>
       <c r="O179" t="n">
-        <v>0.06442926773284818</v>
+        <v>0.06442920134131658</v>
       </c>
       <c r="P179" t="n">
-        <v>0.02103101815380981</v>
+        <v>0.02103099692559018</v>
       </c>
     </row>
     <row r="180">
@@ -18120,7 +18120,7 @@
         <v>0.2055224595251719</v>
       </c>
       <c r="L180" t="n">
-        <v>0.1047233018190161</v>
+        <v>0.1047232102562701</v>
       </c>
       <c r="M180" t="n">
         <v>-0.000278943877526916</v>
@@ -18245,10 +18245,10 @@
         <v>0.3082669094185753</v>
       </c>
       <c r="O182" t="n">
-        <v>1.528324231882894</v>
+        <v>1.528323986571711</v>
       </c>
       <c r="P182" t="n">
-        <v>0.3623151583844602</v>
+        <v>0.362315114324822</v>
       </c>
     </row>
     <row r="183">
@@ -18303,10 +18303,10 @@
         <v>0.268122654494126</v>
       </c>
       <c r="O183" t="n">
-        <v>0.575044754092561</v>
+        <v>0.5750445948837712</v>
       </c>
       <c r="P183" t="n">
-        <v>0.1634944058628354</v>
+        <v>0.163494366660025</v>
       </c>
     </row>
     <row r="184">
@@ -18361,10 +18361,10 @@
         <v>0.0579209537268075</v>
       </c>
       <c r="O184" t="n">
-        <v>0.07774061339786953</v>
+        <v>0.07774049433259833</v>
       </c>
       <c r="P184" t="n">
-        <v>0.02526960614373785</v>
+        <v>0.02526956838758809</v>
       </c>
     </row>
     <row r="185">
@@ -18416,13 +18416,13 @@
         <v>0.1340464949314923</v>
       </c>
       <c r="N185" t="n">
-        <v>0.2113637004201205</v>
+        <v>0.2113635997059464</v>
       </c>
       <c r="O185" t="n">
-        <v>-0.01597255414376197</v>
+        <v>-0.01597242122508835</v>
       </c>
       <c r="P185" t="n">
-        <v>-0.005352785908328217</v>
+        <v>-0.005352741123946458</v>
       </c>
     </row>
     <row r="186">
@@ -18471,16 +18471,16 @@
         <v>0.2127145303330842</v>
       </c>
       <c r="M186" t="n">
-        <v>0.01234920936926986</v>
+        <v>0.0123492726873573</v>
       </c>
       <c r="N186" t="n">
-        <v>-0.0003732136710953293</v>
+        <v>-0.0003732754077094835</v>
       </c>
       <c r="O186" t="n">
-        <v>0.5123075167946143</v>
+        <v>0.5123076580962946</v>
       </c>
       <c r="P186" t="n">
-        <v>0.1478365163551449</v>
+        <v>0.1478365521043166</v>
       </c>
     </row>
     <row r="187">
@@ -18590,7 +18590,7 @@
         <v>0.02542620522488548</v>
       </c>
       <c r="N188" t="n">
-        <v>-0.008514095652394693</v>
+        <v>-0.008514003440756701</v>
       </c>
       <c r="O188" t="n">
         <v>0.66626591536739</v>
@@ -18648,13 +18648,13 @@
         <v>0.2180921372356444</v>
       </c>
       <c r="N189" t="n">
-        <v>0.2158638293818411</v>
+        <v>0.2158639358451626</v>
       </c>
       <c r="O189" t="n">
-        <v>1.118649400234907</v>
+        <v>1.118649561863549</v>
       </c>
       <c r="P189" t="n">
-        <v>0.2843587973677497</v>
+        <v>0.2843588300283624</v>
       </c>
     </row>
     <row r="190">
@@ -18761,16 +18761,16 @@
         <v>0.1340677243589328</v>
       </c>
       <c r="M191" t="n">
-        <v>0.1753984749748039</v>
+        <v>0.175398562607654</v>
       </c>
       <c r="N191" t="n">
-        <v>0.1570177576562064</v>
+        <v>0.1570178425697057</v>
       </c>
       <c r="O191" t="n">
-        <v>0.913369265629153</v>
+        <v>0.9133691495205969</v>
       </c>
       <c r="P191" t="n">
-        <v>0.2414605720487162</v>
+        <v>0.2414605469369582</v>
       </c>
     </row>
     <row r="192">
@@ -18819,16 +18819,16 @@
         <v>0.1078560961737958</v>
       </c>
       <c r="M192" t="n">
-        <v>0.1319946888340637</v>
+        <v>0.1319945603240829</v>
       </c>
       <c r="N192" t="n">
         <v>0.1643162304339845</v>
       </c>
       <c r="O192" t="n">
-        <v>0.6209952765618514</v>
+        <v>0.6209954083212696</v>
       </c>
       <c r="P192" t="n">
-        <v>0.1747007601495278</v>
+        <v>0.1747007919772754</v>
       </c>
     </row>
     <row r="193">
@@ -18883,10 +18883,10 @@
         <v>0.003565246606173078</v>
       </c>
       <c r="O193" t="n">
-        <v>0.4498257067477778</v>
+        <v>0.4498258411956955</v>
       </c>
       <c r="P193" t="n">
-        <v>0.131805843794959</v>
+        <v>0.1318058787805285</v>
       </c>
     </row>
     <row r="194">
@@ -18996,7 +18996,7 @@
         <v>0.0752466814768511</v>
       </c>
       <c r="N195" t="n">
-        <v>-0.09857386892444187</v>
+        <v>-0.098574080996914</v>
       </c>
       <c r="O195" t="n">
         <v>0.07430734027525832</v>
@@ -19051,16 +19051,16 @@
         <v>0.0392327780441688</v>
       </c>
       <c r="M196" t="n">
-        <v>0.09330681635800819</v>
+        <v>0.09330674003327188</v>
       </c>
       <c r="N196" t="n">
-        <v>0.2678957906291812</v>
+        <v>0.2678956879816956</v>
       </c>
       <c r="O196" t="n">
-        <v>1.40800860617339</v>
+        <v>1.408008791299357</v>
       </c>
       <c r="P196" t="n">
-        <v>0.3403534758761309</v>
+        <v>0.3403535102245996</v>
       </c>
     </row>
     <row r="197">
@@ -19115,10 +19115,10 @@
         <v>-0.0771485050363937</v>
       </c>
       <c r="O197" t="n">
-        <v>0.1472525657660366</v>
+        <v>0.1472526407154466</v>
       </c>
       <c r="P197" t="n">
-        <v>0.04685455216448386</v>
+        <v>0.04685457496130341</v>
       </c>
     </row>
     <row r="198">
@@ -19173,10 +19173,10 @@
         <v>0.2108563114828639</v>
       </c>
       <c r="O198" t="n">
-        <v>0.7859867474796767</v>
+        <v>0.7859868959052196</v>
       </c>
       <c r="P198" t="n">
-        <v>0.2132754519439868</v>
+        <v>0.2132754855539902</v>
       </c>
     </row>
     <row r="199">
@@ -19225,10 +19225,10 @@
         <v>0.09008649367930799</v>
       </c>
       <c r="M199" t="n">
-        <v>0.1820720148857022</v>
+        <v>0.1820719023737434</v>
       </c>
       <c r="N199" t="n">
-        <v>0.2094208262441726</v>
+        <v>0.2094207084657596</v>
       </c>
       <c r="O199" t="n">
         <v>0.6002986416482554</v>
@@ -19280,10 +19280,10 @@
         <v>-0.06807555835170931</v>
       </c>
       <c r="L200" t="n">
-        <v>0.1356632119597103</v>
+        <v>0.1356633282839514</v>
       </c>
       <c r="M200" t="n">
-        <v>0.08063932435212839</v>
+        <v>0.08063942967741378</v>
       </c>
       <c r="N200" t="n">
         <v>0.4494956582968035</v>
@@ -19402,7 +19402,7 @@
         <v>0.2577594946321746</v>
       </c>
       <c r="N202" t="n">
-        <v>-0.02125160383620073</v>
+        <v>-0.02125154069250756</v>
       </c>
       <c r="O202" t="n">
         <v>0.693276263260767</v>
@@ -19457,16 +19457,16 @@
         <v>0.04845959788781573</v>
       </c>
       <c r="M203" t="n">
-        <v>0.1894037606587771</v>
+        <v>0.189403860107435</v>
       </c>
       <c r="N203" t="n">
-        <v>0.2810435197014811</v>
+        <v>0.2810436350648904</v>
       </c>
       <c r="O203" t="n">
-        <v>1.511481156137209</v>
+        <v>1.511481377839492</v>
       </c>
       <c r="P203" t="n">
-        <v>0.3592832793859122</v>
+        <v>0.3592833193830534</v>
       </c>
     </row>
     <row r="204">
@@ -19518,13 +19518,13 @@
         <v>0.11181783584016</v>
       </c>
       <c r="N204" t="n">
-        <v>0.0290064380292816</v>
+        <v>0.02900633086005522</v>
       </c>
       <c r="O204" t="n">
-        <v>-0.1640314466505015</v>
+        <v>-0.1640315881137936</v>
       </c>
       <c r="P204" t="n">
-        <v>-0.05797308008080582</v>
+        <v>-0.05797313321766773</v>
       </c>
     </row>
     <row r="205">
@@ -19628,7 +19628,7 @@
         <v>0.2055846506899686</v>
       </c>
       <c r="L206" t="n">
-        <v>0.06060322903130855</v>
+        <v>0.06060334800473344</v>
       </c>
       <c r="M206" t="n">
         <v>0.03852487817908834</v>
@@ -19637,10 +19637,10 @@
         <v>0.007232887581357428</v>
       </c>
       <c r="O206" t="n">
-        <v>0.3717945137238154</v>
+        <v>0.3717944142079965</v>
       </c>
       <c r="P206" t="n">
-        <v>0.1111252592660168</v>
+        <v>0.1111252323974294</v>
       </c>
     </row>
     <row r="207">
@@ -19689,7 +19689,7 @@
         <v>0.02304976423684013</v>
       </c>
       <c r="M207" t="n">
-        <v>0.1401513155717735</v>
+        <v>0.1401513965333583</v>
       </c>
       <c r="N207" t="n">
         <v>0.2775571201304647</v>
@@ -19747,16 +19747,16 @@
         <v>0.1120945940127538</v>
       </c>
       <c r="M208" t="n">
-        <v>0.2663505334459697</v>
+        <v>0.2663504290977456</v>
       </c>
       <c r="N208" t="n">
-        <v>0.202223177647064</v>
+        <v>0.2022230835995367</v>
       </c>
       <c r="O208" t="n">
-        <v>0.365207316062421</v>
+        <v>0.3652074373383123</v>
       </c>
       <c r="P208" t="n">
-        <v>0.1093439068579387</v>
+        <v>0.1093439397068365</v>
       </c>
     </row>
     <row r="209">
@@ -19805,16 +19805,16 @@
         <v>0.03932397679538191</v>
       </c>
       <c r="M209" t="n">
-        <v>0.1706536208256988</v>
+        <v>0.1706534959497721</v>
       </c>
       <c r="N209" t="n">
         <v>0.2193835243298787</v>
       </c>
       <c r="O209" t="n">
-        <v>2.81795141460679</v>
+        <v>2.817951082542089</v>
       </c>
       <c r="P209" t="n">
-        <v>0.5629441735300025</v>
+        <v>0.5629441282178664</v>
       </c>
     </row>
     <row r="210">
@@ -19863,16 +19863,16 @@
         <v>-0.02160406519615021</v>
       </c>
       <c r="M210" t="n">
-        <v>0.1669267064240272</v>
+        <v>0.1669267772594991</v>
       </c>
       <c r="N210" t="n">
-        <v>0.2607808460898504</v>
+        <v>0.2607807634017942</v>
       </c>
       <c r="O210" t="n">
-        <v>0.9710756355683472</v>
+        <v>0.9710760397720346</v>
       </c>
       <c r="P210" t="n">
-        <v>0.2538177965933179</v>
+        <v>0.2538178822991008</v>
       </c>
     </row>
     <row r="211">
@@ -19921,16 +19921,16 @@
         <v>0.2431647340209244</v>
       </c>
       <c r="M211" t="n">
-        <v>0.08839802107767358</v>
+        <v>0.08839793847980792</v>
       </c>
       <c r="N211" t="n">
         <v>0.06447015031387315</v>
       </c>
       <c r="O211" t="n">
-        <v>0.157984733741551</v>
+        <v>0.1579845467469947</v>
       </c>
       <c r="P211" t="n">
-        <v>0.05010875177184548</v>
+        <v>0.0501086952470271</v>
       </c>
     </row>
     <row r="212">
@@ -19976,19 +19976,19 @@
         <v>0.0951125337378329</v>
       </c>
       <c r="L212" t="n">
-        <v>0.06454638667181367</v>
+        <v>0.06454630545746554</v>
       </c>
       <c r="M212" t="n">
         <v>0.2113439314198904</v>
       </c>
       <c r="N212" t="n">
-        <v>0.04214464872202539</v>
+        <v>0.04214472655428758</v>
       </c>
       <c r="O212" t="n">
-        <v>0.5708287849336515</v>
+        <v>0.5708284312693575</v>
       </c>
       <c r="P212" t="n">
-        <v>0.162455358195345</v>
+        <v>0.1624552709549896</v>
       </c>
     </row>
     <row r="213">
@@ -20037,16 +20037,16 @@
         <v>0.05423117447738623</v>
       </c>
       <c r="M213" t="n">
-        <v>0.2638191532248622</v>
+        <v>0.2638192908882959</v>
       </c>
       <c r="N213" t="n">
-        <v>-0.02391680779675787</v>
+        <v>-0.0239168899117238</v>
       </c>
       <c r="O213" t="n">
-        <v>0.2871390738938639</v>
+        <v>0.2871387883127172</v>
       </c>
       <c r="P213" t="n">
-        <v>0.08778189164539674</v>
+        <v>0.08778181119565365</v>
       </c>
     </row>
     <row r="214">
@@ -20098,7 +20098,7 @@
         <v>0.2301887534796838</v>
       </c>
       <c r="N214" t="n">
-        <v>0.04695220786359133</v>
+        <v>0.04695212318713748</v>
       </c>
       <c r="O214" t="n">
         <v>0.9469629013297141</v>
@@ -20150,7 +20150,7 @@
         <v>0.03160482752319482</v>
       </c>
       <c r="L215" t="n">
-        <v>-0.02985863955835788</v>
+        <v>-0.02985852729146166</v>
       </c>
       <c r="M215" t="n">
         <v>0.2053295878636661</v>
@@ -20159,10 +20159,10 @@
         <v>0.2562539293688757</v>
       </c>
       <c r="O215" t="n">
-        <v>1.202155104903509</v>
+        <v>1.202154526438199</v>
       </c>
       <c r="P215" t="n">
-        <v>0.3010159917400042</v>
+        <v>0.3010158778224024</v>
       </c>
     </row>
     <row r="216">
@@ -20208,7 +20208,7 @@
         <v>0.04911885493606616</v>
       </c>
       <c r="L216" t="n">
-        <v>0.03258308085126771</v>
+        <v>0.03258298419404859</v>
       </c>
       <c r="M216" t="n">
         <v>0.1394786009075113</v>
@@ -20217,10 +20217,10 @@
         <v>0.2206264808963063</v>
       </c>
       <c r="O216" t="n">
-        <v>0.7012353327323269</v>
+        <v>0.7012355951017273</v>
       </c>
       <c r="P216" t="n">
-        <v>0.193772209942374</v>
+        <v>0.1937722713113641</v>
       </c>
     </row>
     <row r="217">
@@ -20272,7 +20272,7 @@
         <v>0.300975089239649</v>
       </c>
       <c r="N217" t="n">
-        <v>0.05486347030845629</v>
+        <v>0.05486340340727724</v>
       </c>
       <c r="O217" t="n">
         <v>1.249707755198103</v>
@@ -20333,10 +20333,10 @@
         <v>-0.0207166873234671</v>
       </c>
       <c r="O218" t="n">
-        <v>0.4009382062945495</v>
+        <v>0.4009383112090723</v>
       </c>
       <c r="P218" t="n">
-        <v>0.1189387817577878</v>
+        <v>0.1189388096897659</v>
       </c>
     </row>
     <row r="219">
@@ -20385,16 +20385,16 @@
         <v>0.1265045198636598</v>
       </c>
       <c r="M219" t="n">
-        <v>0.06864765127591754</v>
+        <v>0.06864754736003587</v>
       </c>
       <c r="N219" t="n">
-        <v>0.4360074517406756</v>
+        <v>0.4360075455608676</v>
       </c>
       <c r="O219" t="n">
-        <v>1.467613910721168</v>
+        <v>1.46761418775791</v>
       </c>
       <c r="P219" t="n">
-        <v>0.351322692796771</v>
+        <v>0.351322743367354</v>
       </c>
     </row>
     <row r="220">
@@ -20449,10 +20449,10 @@
         <v>-0.1628749458867979</v>
       </c>
       <c r="O220" t="n">
-        <v>-0.2329339259406973</v>
+        <v>-0.2329337567336455</v>
       </c>
       <c r="P220" t="n">
-        <v>-0.08459996428007555</v>
+        <v>-0.08459989697073722</v>
       </c>
     </row>
     <row r="221">
@@ -20504,7 +20504,7 @@
         <v>0.1413006956936205</v>
       </c>
       <c r="N221" t="n">
-        <v>-0.01188188639516941</v>
+        <v>-0.01188177467997364</v>
       </c>
       <c r="O221" t="n">
         <v>0.5734068656021303</v>
@@ -20556,19 +20556,19 @@
         <v>0.06423370601154921</v>
       </c>
       <c r="L222" t="n">
-        <v>0.05562015413722277</v>
+        <v>0.05562008084361314</v>
       </c>
       <c r="M222" t="n">
-        <v>0.2009614044040078</v>
+        <v>0.2009613095383853</v>
       </c>
       <c r="N222" t="n">
-        <v>0.1009045786928575</v>
+        <v>0.1009044989760095</v>
       </c>
       <c r="O222" t="n">
-        <v>0.7118847524146905</v>
+        <v>0.7118851379196196</v>
       </c>
       <c r="P222" t="n">
-        <v>0.196257961701769</v>
+        <v>0.1962580514981773</v>
       </c>
     </row>
     <row r="223">
@@ -20617,16 +20617,16 @@
         <v>0.1891382934762578</v>
       </c>
       <c r="M223" t="n">
-        <v>-0.002223406937595152</v>
+        <v>-0.00222350354793277</v>
       </c>
       <c r="N223" t="n">
-        <v>0.0637442557921053</v>
+        <v>0.06374414598475053</v>
       </c>
       <c r="O223" t="n">
-        <v>1.671663595168679</v>
+        <v>1.671663768333872</v>
       </c>
       <c r="P223" t="n">
-        <v>0.387588177419103</v>
+        <v>0.3875882073981729</v>
       </c>
     </row>
     <row r="224">
@@ -20672,7 +20672,7 @@
         <v>0.1536758216416354</v>
       </c>
       <c r="L224" t="n">
-        <v>0.03516336327524083</v>
+        <v>0.03516347975022249</v>
       </c>
       <c r="M224" t="n">
         <v>0.1154412994533758</v>
@@ -20733,16 +20733,16 @@
         <v>0.1186607838963176</v>
       </c>
       <c r="M225" t="n">
-        <v>0.15712076945321</v>
+        <v>0.1571206522525201</v>
       </c>
       <c r="N225" t="n">
-        <v>0.184665207296574</v>
+        <v>0.1846653301434582</v>
       </c>
       <c r="O225" t="n">
-        <v>1.239511206979274</v>
+        <v>1.239510987471818</v>
       </c>
       <c r="P225" t="n">
-        <v>0.3083313460579198</v>
+        <v>0.308331303312209</v>
       </c>
     </row>
     <row r="226">
@@ -20910,13 +20910,13 @@
         <v>0.2588015801844823</v>
       </c>
       <c r="N228" t="n">
-        <v>0.1387110093926409</v>
+        <v>0.1387111039786717</v>
       </c>
       <c r="O228" t="n">
-        <v>1.530989987512893</v>
+        <v>1.530989753870985</v>
       </c>
       <c r="P228" t="n">
-        <v>0.3627937789230375</v>
+        <v>0.3627937369887548</v>
       </c>
     </row>
     <row r="229">
@@ -20962,7 +20962,7 @@
         <v>0.02089427526356902</v>
       </c>
       <c r="L229" t="n">
-        <v>0.06829156439156114</v>
+        <v>0.06829163013471273</v>
       </c>
       <c r="M229" t="n">
         <v>0.1683562083345307</v>
@@ -21026,13 +21026,13 @@
         <v>0.109149624817066</v>
       </c>
       <c r="N230" t="n">
-        <v>0.2239190246730505</v>
+        <v>0.2239191210036677</v>
       </c>
       <c r="O230" t="n">
-        <v>-0.005287264062173946</v>
+        <v>-0.005287073175490264</v>
       </c>
       <c r="P230" t="n">
-        <v>-0.001765536639219412</v>
+        <v>-0.001765472785054234</v>
       </c>
     </row>
     <row r="231">
@@ -21084,13 +21084,13 @@
         <v>0.1384849973295821</v>
       </c>
       <c r="N231" t="n">
-        <v>0.1746908663067173</v>
+        <v>0.174690982880656</v>
       </c>
       <c r="O231" t="n">
-        <v>0.4620644371908027</v>
+        <v>0.4620647983655464</v>
       </c>
       <c r="P231" t="n">
-        <v>0.1349816442633731</v>
+        <v>0.1349817377217872</v>
       </c>
     </row>
     <row r="232">
@@ -21139,16 +21139,16 @@
         <v>0.2905852622592935</v>
       </c>
       <c r="M232" t="n">
-        <v>0.02132762911232056</v>
+        <v>0.02132773926179521</v>
       </c>
       <c r="N232" t="n">
-        <v>-0.2162434898015546</v>
+        <v>-0.2162434249359336</v>
       </c>
       <c r="O232" t="n">
-        <v>-0.3010934805861309</v>
+        <v>-0.3010933258428657</v>
       </c>
       <c r="P232" t="n">
-        <v>-0.112558575296919</v>
+        <v>-0.1125585098014773</v>
       </c>
     </row>
     <row r="233">
@@ -21258,13 +21258,13 @@
         <v>-0.06126743543824997</v>
       </c>
       <c r="N234" t="n">
-        <v>-0.01278701488189071</v>
+        <v>-0.01278694537798408</v>
       </c>
       <c r="O234" t="n">
-        <v>1.243057572350056</v>
+        <v>1.243057392943513</v>
       </c>
       <c r="P234" t="n">
-        <v>0.3090215820933919</v>
+        <v>0.3090215471935531</v>
       </c>
     </row>
     <row r="235">
@@ -21319,10 +21319,10 @@
         <v>0.2463301626694421</v>
       </c>
       <c r="O235" t="n">
-        <v>2.495886953345639</v>
+        <v>2.495886470958852</v>
       </c>
       <c r="P235" t="n">
-        <v>0.5176995084268383</v>
+        <v>0.5176994386192584</v>
       </c>
     </row>
     <row r="236">
@@ -21371,16 +21371,16 @@
         <v>0.1951201698989662</v>
       </c>
       <c r="M236" t="n">
-        <v>0.2453153237897789</v>
+        <v>0.2453154014704948</v>
       </c>
       <c r="N236" t="n">
         <v>0.4196434831693501</v>
       </c>
       <c r="O236" t="n">
-        <v>1.488063153039489</v>
+        <v>1.488062997998224</v>
       </c>
       <c r="P236" t="n">
-        <v>0.3550452553231567</v>
+        <v>0.3550452271770417</v>
       </c>
     </row>
     <row r="237">
@@ -21426,13 +21426,13 @@
         <v>0.09361935647880304</v>
       </c>
       <c r="L237" t="n">
-        <v>0.1024281133156366</v>
+        <v>0.102428224017262</v>
       </c>
       <c r="M237" t="n">
         <v>0.03612090345860586</v>
       </c>
       <c r="N237" t="n">
-        <v>0.1078724947566081</v>
+        <v>0.1078723829588975</v>
       </c>
       <c r="O237" t="n">
         <v>1.047831393721584</v>
@@ -21548,7 +21548,7 @@
         <v>0.1023748038468508</v>
       </c>
       <c r="N239" t="n">
-        <v>0.2534413132455724</v>
+        <v>0.2534414202693061</v>
       </c>
       <c r="O239" t="n">
         <v>0.3745573907044371</v>
@@ -21606,13 +21606,13 @@
         <v>0.04834116966012592</v>
       </c>
       <c r="N240" t="n">
-        <v>0.01254271553204678</v>
+        <v>0.01254260127687323</v>
       </c>
       <c r="O240" t="n">
-        <v>0.6956877579690004</v>
+        <v>0.6956882386227867</v>
       </c>
       <c r="P240" t="n">
-        <v>0.1924732024840772</v>
+        <v>0.1924733151555096</v>
       </c>
     </row>
     <row r="241">
@@ -21664,13 +21664,13 @@
         <v>0.07721921384480601</v>
       </c>
       <c r="N241" t="n">
-        <v>0.2617005395124281</v>
+        <v>0.2617006527195631</v>
       </c>
       <c r="O241" t="n">
-        <v>0.5185101513830779</v>
+        <v>0.5185098234188439</v>
       </c>
       <c r="P241" t="n">
-        <v>0.1494036356903163</v>
+        <v>0.1494035529418167</v>
       </c>
     </row>
     <row r="242">
@@ -21725,10 +21725,10 @@
         <v>0.1356850463135897</v>
       </c>
       <c r="O242" t="n">
-        <v>1.307348602858556</v>
+        <v>1.307348833746541</v>
       </c>
       <c r="P242" t="n">
-        <v>0.3214104534191142</v>
+        <v>0.3214104974953591</v>
       </c>
     </row>
     <row r="243">
@@ -21774,19 +21774,19 @@
         <v>0.1863440426642571</v>
       </c>
       <c r="L243" t="n">
-        <v>0.1088460591249019</v>
+        <v>0.1088459845125174</v>
       </c>
       <c r="M243" t="n">
-        <v>0.06678355800444025</v>
+        <v>0.06678348894532138</v>
       </c>
       <c r="N243" t="n">
         <v>-0.1494774758221601</v>
       </c>
       <c r="O243" t="n">
-        <v>0.1341903491633578</v>
+        <v>0.1341901930391436</v>
       </c>
       <c r="P243" t="n">
-        <v>0.04286633753523783</v>
+        <v>0.04286628968415918</v>
       </c>
     </row>
     <row r="244">
@@ -21832,13 +21832,13 @@
         <v>0.2277152259109085</v>
       </c>
       <c r="L244" t="n">
-        <v>0.04599597307281389</v>
+        <v>0.04599608005620426</v>
       </c>
       <c r="M244" t="n">
         <v>-0.009905501960508323</v>
       </c>
       <c r="N244" t="n">
-        <v>-0.09135516727742654</v>
+        <v>-0.09135524800921468</v>
       </c>
       <c r="O244" t="n">
         <v>0.4997953469928034</v>
@@ -21896,13 +21896,13 @@
         <v>0.104115394288214</v>
       </c>
       <c r="N245" t="n">
-        <v>-0.001301882930558329</v>
+        <v>-0.001301958836211425</v>
       </c>
       <c r="O245" t="n">
-        <v>0.6629598644165524</v>
+        <v>0.6629599696464772</v>
       </c>
       <c r="P245" t="n">
-        <v>0.1847514690423435</v>
+        <v>0.1847514940321839</v>
       </c>
     </row>
     <row r="246">
@@ -21948,19 +21948,19 @@
         <v>0.04647671220027516</v>
       </c>
       <c r="L246" t="n">
-        <v>-0.01966213933747307</v>
+        <v>-0.0196622070600494</v>
       </c>
       <c r="M246" t="n">
         <v>0.1622532922687836</v>
       </c>
       <c r="N246" t="n">
-        <v>0.157382445817295</v>
+        <v>0.1573823514251842</v>
       </c>
       <c r="O246" t="n">
-        <v>0.3435430117167404</v>
+        <v>0.3435428845173418</v>
       </c>
       <c r="P246" t="n">
-        <v>0.1034445774027393</v>
+        <v>0.103444542580013</v>
       </c>
     </row>
     <row r="247">
@@ -22012,7 +22012,7 @@
         <v>0.1186750823250835</v>
       </c>
       <c r="N247" t="n">
-        <v>0.2589487819113832</v>
+        <v>0.2589486945902977</v>
       </c>
       <c r="O247" t="n">
         <v>0.2441556554336897</v>
@@ -22125,16 +22125,16 @@
         <v>0.01159366321938027</v>
       </c>
       <c r="M249" t="n">
-        <v>0.1498015728041941</v>
+        <v>0.1498016954500354</v>
       </c>
       <c r="N249" t="n">
-        <v>0.2025945227832098</v>
+        <v>0.2025946569501373</v>
       </c>
       <c r="O249" t="n">
-        <v>0.7231120833364304</v>
+        <v>0.7231119456142123</v>
       </c>
       <c r="P249" t="n">
-        <v>0.1988674692907724</v>
+        <v>0.1988674373503678</v>
       </c>
     </row>
     <row r="250">
@@ -22180,13 +22180,13 @@
         <v>0.2920833213231009</v>
       </c>
       <c r="L250" t="n">
-        <v>0.1387501112952645</v>
+        <v>0.1387500182769272</v>
       </c>
       <c r="M250" t="n">
-        <v>-0.1222344056997267</v>
+        <v>-0.1222343504323467</v>
       </c>
       <c r="N250" t="n">
-        <v>-0.2138442587155532</v>
+        <v>-0.2138440813827772</v>
       </c>
       <c r="O250" t="n">
         <v>-0.1181853293624905</v>
@@ -22244,7 +22244,7 @@
         <v>-0.1064816599862901</v>
       </c>
       <c r="N251" t="n">
-        <v>-0.001672676069171208</v>
+        <v>-0.001672771218918512</v>
       </c>
       <c r="O251" t="n">
         <v>0.1000898693213736</v>
@@ -22357,16 +22357,16 @@
         <v>-0.02489724113362346</v>
       </c>
       <c r="M253" t="n">
-        <v>0.1433333096793574</v>
+        <v>0.1433331867503773</v>
       </c>
       <c r="N253" t="n">
-        <v>0.0594734052410395</v>
+        <v>0.05947329968363868</v>
       </c>
       <c r="O253" t="n">
-        <v>0.1419222304372034</v>
+        <v>0.1419221078114692</v>
       </c>
       <c r="P253" t="n">
-        <v>0.04523074517740189</v>
+        <v>0.04523070776323923</v>
       </c>
     </row>
     <row r="254">
@@ -22473,10 +22473,10 @@
         <v>0.04401249789535289</v>
       </c>
       <c r="M255" t="n">
-        <v>0.2424875238407</v>
+        <v>0.2424876477682201</v>
       </c>
       <c r="N255" t="n">
-        <v>0.1054310850793798</v>
+        <v>0.1054311831744148</v>
       </c>
       <c r="O255" t="n">
         <v>0.4749516236377627</v>
@@ -22528,19 +22528,19 @@
         <v>0.1869514175609523</v>
       </c>
       <c r="L256" t="n">
-        <v>-0.09036174038656863</v>
+        <v>-0.09036181815772359</v>
       </c>
       <c r="M256" t="n">
-        <v>-0.03313257665325275</v>
+        <v>-0.03313266451806085</v>
       </c>
       <c r="N256" t="n">
-        <v>0.09838289736394934</v>
+        <v>0.09838278397032729</v>
       </c>
       <c r="O256" t="n">
-        <v>0.8735719867983731</v>
+        <v>0.8735721517634294</v>
       </c>
       <c r="P256" t="n">
-        <v>0.2327929102452064</v>
+        <v>0.2327929464270289</v>
       </c>
     </row>
     <row r="257">
@@ -22589,16 +22589,16 @@
         <v>0.03414223216199463</v>
       </c>
       <c r="M257" t="n">
-        <v>0.1146865878965706</v>
+        <v>0.1146866877146524</v>
       </c>
       <c r="N257" t="n">
         <v>0.193333084081329</v>
       </c>
       <c r="O257" t="n">
-        <v>0.5832950957364491</v>
+        <v>0.5832951964290121</v>
       </c>
       <c r="P257" t="n">
-        <v>0.1655223935667092</v>
+        <v>0.1655224182745554</v>
       </c>
     </row>
     <row r="258">
@@ -22702,7 +22702,7 @@
         <v>0.185187934969657</v>
       </c>
       <c r="L259" t="n">
-        <v>0.2372340185672654</v>
+        <v>0.2372339313934235</v>
       </c>
       <c r="M259" t="n">
         <v>-0.08714970882931816</v>
@@ -22711,10 +22711,10 @@
         <v>-0.1955886393656519</v>
       </c>
       <c r="O259" t="n">
-        <v>0.3079791819381541</v>
+        <v>0.3079792793662484</v>
       </c>
       <c r="P259" t="n">
-        <v>0.0936212589434946</v>
+        <v>0.093621286097197</v>
       </c>
     </row>
     <row r="260">
@@ -22763,10 +22763,10 @@
         <v>0.05771805692954879</v>
       </c>
       <c r="M260" t="n">
-        <v>0.2327704276752069</v>
+        <v>0.232770342633654</v>
       </c>
       <c r="N260" t="n">
-        <v>0.1067963498125235</v>
+        <v>0.1067964869108904</v>
       </c>
       <c r="O260" t="n">
         <v>0.9436927664853569</v>
@@ -22824,13 +22824,13 @@
         <v>0.09210234117973415</v>
       </c>
       <c r="N261" t="n">
-        <v>0.3694200355968236</v>
+        <v>0.3694199266455036</v>
       </c>
       <c r="O261" t="n">
-        <v>0.4702000579798977</v>
+        <v>0.4702001835574703</v>
       </c>
       <c r="P261" t="n">
-        <v>0.1370829437980954</v>
+        <v>0.1370829761728531</v>
       </c>
     </row>
     <row r="262">
@@ -22879,16 +22879,16 @@
         <v>0.1640877372690788</v>
       </c>
       <c r="M262" t="n">
-        <v>0.1350347732230073</v>
+        <v>0.1350348428826755</v>
       </c>
       <c r="N262" t="n">
         <v>0.009883769440016454</v>
       </c>
       <c r="O262" t="n">
-        <v>0.3909857508321806</v>
+        <v>0.3909859600691707</v>
       </c>
       <c r="P262" t="n">
-        <v>0.1162827845329322</v>
+        <v>0.1162828405046625</v>
       </c>
     </row>
     <row r="263">
@@ -22940,13 +22940,13 @@
         <v>0.06611981273585466</v>
       </c>
       <c r="N263" t="n">
-        <v>0.1268659007539441</v>
+        <v>0.1268660153100556</v>
       </c>
       <c r="O263" t="n">
-        <v>0.7345040172987873</v>
+        <v>0.7345041530033354</v>
       </c>
       <c r="P263" t="n">
-        <v>0.2015036745752088</v>
+        <v>0.2015037059097204</v>
       </c>
     </row>
     <row r="264">
@@ -23001,10 +23001,10 @@
         <v>0.02585254313501117</v>
       </c>
       <c r="O264" t="n">
-        <v>0.2751778758348329</v>
+        <v>0.2751777415562955</v>
       </c>
       <c r="P264" t="n">
-        <v>0.08440186640267111</v>
+        <v>0.08440182833951027</v>
       </c>
     </row>
     <row r="265">
@@ -23053,16 +23053,16 @@
         <v>0.1087650620430203</v>
       </c>
       <c r="M265" t="n">
-        <v>0.1326816943328415</v>
+        <v>0.1326817649018055</v>
       </c>
       <c r="N265" t="n">
         <v>0.08565657279835315</v>
       </c>
       <c r="O265" t="n">
-        <v>0.3788058173589903</v>
+        <v>0.3788057127897069</v>
       </c>
       <c r="P265" t="n">
-        <v>0.1130150470892173</v>
+        <v>0.1130150189520212</v>
       </c>
     </row>
     <row r="266">
@@ -23114,13 +23114,13 @@
         <v>0.0638209166998247</v>
       </c>
       <c r="N266" t="n">
-        <v>0.1008244796569047</v>
+        <v>0.1008244131981455</v>
       </c>
       <c r="O266" t="n">
-        <v>0.5351217075622294</v>
+        <v>0.5351215783208199</v>
       </c>
       <c r="P266" t="n">
-        <v>0.1535796981893218</v>
+        <v>0.1535796658161512</v>
       </c>
     </row>
     <row r="267">
@@ -23169,16 +23169,16 @@
         <v>0.1244451212152071</v>
       </c>
       <c r="M267" t="n">
-        <v>0.1509544494031574</v>
+        <v>0.1509543781594744</v>
       </c>
       <c r="N267" t="n">
-        <v>-0.0468432993409057</v>
+        <v>-0.04684339706208018</v>
       </c>
       <c r="O267" t="n">
-        <v>0.3295018195507593</v>
+        <v>0.3295020096752421</v>
       </c>
       <c r="P267" t="n">
-        <v>0.09958712316228846</v>
+        <v>0.0995871755775164</v>
       </c>
     </row>
     <row r="268">
@@ -23224,10 +23224,10 @@
         <v>-0.06046671062513387</v>
       </c>
       <c r="L268" t="n">
-        <v>-0.07350587859453006</v>
+        <v>-0.07350593516608417</v>
       </c>
       <c r="M268" t="n">
-        <v>0.1974628565584147</v>
+        <v>0.1974629510595305</v>
       </c>
       <c r="N268" t="n">
         <v>0.2930504445237723</v>
@@ -23282,13 +23282,13 @@
         <v>-0.1253464324537674</v>
       </c>
       <c r="L269" t="n">
-        <v>-0.09202741863314456</v>
+        <v>-0.09202752498722955</v>
       </c>
       <c r="M269" t="n">
         <v>0.3374990283562946</v>
       </c>
       <c r="N269" t="n">
-        <v>0.2939717603393948</v>
+        <v>0.2939718683405486</v>
       </c>
       <c r="O269" t="n">
         <v>-0.3455796985458148</v>
@@ -23346,13 +23346,13 @@
         <v>0.07521430599182577</v>
       </c>
       <c r="N270" t="n">
-        <v>0.1244135385998755</v>
+        <v>0.1244134303954083</v>
       </c>
       <c r="O270" t="n">
-        <v>0.7369635341231253</v>
+        <v>0.7369634050177054</v>
       </c>
       <c r="P270" t="n">
-        <v>0.2020713148134876</v>
+        <v>0.202071285030877</v>
       </c>
     </row>
     <row r="271">
@@ -23407,10 +23407,10 @@
         <v>0.02955876640061339</v>
       </c>
       <c r="O271" t="n">
-        <v>-0.03723127912050406</v>
+        <v>-0.0372313938676232</v>
       </c>
       <c r="P271" t="n">
-        <v>-0.01256771208136709</v>
+        <v>-0.01256775131024668</v>
       </c>
     </row>
     <row r="272">
@@ -23456,13 +23456,13 @@
         <v>-0.1620975822376001</v>
       </c>
       <c r="L272" t="n">
-        <v>0.04855168807700383</v>
+        <v>0.04855156857607623</v>
       </c>
       <c r="M272" t="n">
         <v>0.1174144204257586</v>
       </c>
       <c r="N272" t="n">
-        <v>0.4337214509104907</v>
+        <v>0.4337215626202828</v>
       </c>
       <c r="O272" t="n">
         <v>1.540634070860181</v>
@@ -23520,13 +23520,13 @@
         <v>0.1015219688985436</v>
       </c>
       <c r="N273" t="n">
-        <v>0.2699252129540883</v>
+        <v>0.2699250905018629</v>
       </c>
       <c r="O273" t="n">
-        <v>-0.2592461249967659</v>
+        <v>-0.259246041669268</v>
       </c>
       <c r="P273" t="n">
-        <v>-0.09518878005228115</v>
+        <v>-0.0951887461248393</v>
       </c>
     </row>
     <row r="274">
@@ -23575,16 +23575,16 @@
         <v>0.04957565205478431</v>
       </c>
       <c r="M274" t="n">
-        <v>0.06849959645119319</v>
+        <v>0.0684996839051577</v>
       </c>
       <c r="N274" t="n">
-        <v>-0.01098054343765553</v>
+        <v>-0.01098061836500674</v>
       </c>
       <c r="O274" t="n">
-        <v>-0.1071882556847049</v>
+        <v>-0.1071881335664511</v>
       </c>
       <c r="P274" t="n">
-        <v>-0.03708792796964</v>
+        <v>-0.03708788406746388</v>
       </c>
     </row>
     <row r="275">
@@ -23636,7 +23636,7 @@
         <v>0.1827263480266828</v>
       </c>
       <c r="N275" t="n">
-        <v>0.07638463091107828</v>
+        <v>0.07638473089350684</v>
       </c>
       <c r="O275" t="n">
         <v>0.2957528701945473</v>
@@ -23813,10 +23813,10 @@
         <v>-0.003338549913721067</v>
       </c>
       <c r="O278" t="n">
-        <v>0.5712434956316201</v>
+        <v>0.5712436385304744</v>
       </c>
       <c r="P278" t="n">
-        <v>0.1625576482007458</v>
+        <v>0.1625576834442013</v>
       </c>
     </row>
     <row r="279">
@@ -23862,19 +23862,19 @@
         <v>0.08336098270482784</v>
       </c>
       <c r="L279" t="n">
-        <v>-0.0108765388187555</v>
+        <v>-0.01087643146072492</v>
       </c>
       <c r="M279" t="n">
-        <v>0.09041122541899949</v>
+        <v>0.090411355890051</v>
       </c>
       <c r="N279" t="n">
         <v>0.02078944744951272</v>
       </c>
       <c r="O279" t="n">
-        <v>0.5760690764228793</v>
+        <v>0.5760688038492079</v>
       </c>
       <c r="P279" t="n">
-        <v>0.1637465754244589</v>
+        <v>0.163746508336305</v>
       </c>
     </row>
     <row r="280">
@@ -23987,10 +23987,10 @@
         <v>0.03300162521957839</v>
       </c>
       <c r="O281" t="n">
-        <v>0.2100953315424237</v>
+        <v>0.2100954147011374</v>
       </c>
       <c r="P281" t="n">
-        <v>0.06563022101925697</v>
+        <v>0.06563024542957518</v>
       </c>
     </row>
     <row r="282">
@@ -24042,13 +24042,13 @@
         <v>0.06342824513181844</v>
       </c>
       <c r="N282" t="n">
-        <v>0.2360498210231938</v>
+        <v>0.2360496819759128</v>
       </c>
       <c r="O282" t="n">
-        <v>0.3712854352482524</v>
+        <v>0.3712853496792829</v>
       </c>
       <c r="P282" t="n">
-        <v>0.1109877945720033</v>
+        <v>0.1109877714632519</v>
       </c>
     </row>
     <row r="283">
@@ -24155,16 +24155,16 @@
         <v>-0.0256866986127845</v>
       </c>
       <c r="M284" t="n">
-        <v>0.1542484696907691</v>
+        <v>0.1542483660130718</v>
       </c>
       <c r="N284" t="n">
         <v>0.1593336684045441</v>
       </c>
       <c r="O284" t="n">
-        <v>0.4497993005473457</v>
+        <v>0.4497996276865799</v>
       </c>
       <c r="P284" t="n">
-        <v>0.1317989724233934</v>
+        <v>0.1317990575514572</v>
       </c>
     </row>
     <row r="285">
@@ -24213,10 +24213,10 @@
         <v>0.04537078635655312</v>
       </c>
       <c r="M285" t="n">
-        <v>0.08233798598003483</v>
+        <v>0.08233790837066191</v>
       </c>
       <c r="N285" t="n">
-        <v>0.1055818941317903</v>
+        <v>0.1055819751103915</v>
       </c>
       <c r="O285" t="n">
         <v>0.640203549622012</v>
@@ -24271,16 +24271,16 @@
         <v>-0.1916908412420987</v>
       </c>
       <c r="M286" t="n">
-        <v>0.1729328789877635</v>
+        <v>0.1729329572964764</v>
       </c>
       <c r="N286" t="n">
         <v>0.1979783945313716</v>
       </c>
       <c r="O286" t="n">
-        <v>0.3726936646611096</v>
+        <v>0.3726939864213294</v>
       </c>
       <c r="P286" t="n">
-        <v>0.1113679708154478</v>
+        <v>0.1113680576505476</v>
       </c>
     </row>
     <row r="287">
@@ -24335,10 +24335,10 @@
         <v>0.05703932437856563</v>
       </c>
       <c r="O287" t="n">
-        <v>1.002893970646676</v>
+        <v>1.002893745038872</v>
       </c>
       <c r="P287" t="n">
-        <v>0.2605284527772449</v>
+        <v>0.2605284054482182</v>
       </c>
     </row>
     <row r="288">
@@ -24387,16 +24387,16 @@
         <v>-0.01173385232729918</v>
       </c>
       <c r="M288" t="n">
-        <v>0.06928051063044727</v>
+        <v>0.0692805912138319</v>
       </c>
       <c r="N288" t="n">
         <v>0.1299632497287093</v>
       </c>
       <c r="O288" t="n">
-        <v>0.7488548231900747</v>
+        <v>0.7488546076293507</v>
       </c>
       <c r="P288" t="n">
-        <v>0.2048082138692489</v>
+        <v>0.2048081643684101</v>
       </c>
     </row>
     <row r="289">
@@ -24451,10 +24451,10 @@
         <v>0.04195769467207144</v>
       </c>
       <c r="O289" t="n">
-        <v>0.1964520947843873</v>
+        <v>0.1964519297827532</v>
       </c>
       <c r="P289" t="n">
-        <v>0.0616102542800514</v>
+        <v>0.06161020547814333</v>
       </c>
     </row>
     <row r="290">
@@ -24503,16 +24503,16 @@
         <v>-0.03811878408598757</v>
       </c>
       <c r="M290" t="n">
-        <v>-0.009477218541369292</v>
+        <v>-0.009477130838150827</v>
       </c>
       <c r="N290" t="n">
         <v>0.03694941525462925</v>
       </c>
       <c r="O290" t="n">
-        <v>-0.0005534615243732999</v>
+        <v>-0.0005533722337753844</v>
       </c>
       <c r="P290" t="n">
-        <v>-0.0001845212207778335</v>
+        <v>-0.0001844914462589831</v>
       </c>
     </row>
     <row r="291">
@@ -24567,10 +24567,10 @@
         <v>-0.09396650482501911</v>
       </c>
       <c r="O291" t="n">
-        <v>0.15978506349583</v>
+        <v>0.1597852976526211</v>
       </c>
       <c r="P291" t="n">
-        <v>0.05065267463873657</v>
+        <v>0.05065274534650532</v>
       </c>
     </row>
     <row r="292">
@@ -24622,7 +24622,7 @@
         <v>0.1305904727482923</v>
       </c>
       <c r="N292" t="n">
-        <v>0.08247095177045449</v>
+        <v>0.08247087159384714</v>
       </c>
       <c r="O292" t="n">
         <v>1.226538021478444</v>
@@ -24683,10 +24683,10 @@
         <v>0.0339425632269601</v>
       </c>
       <c r="O293" t="n">
-        <v>0.04609390455610907</v>
+        <v>0.04609381807443591</v>
       </c>
       <c r="P293" t="n">
-        <v>0.01513442841045798</v>
+        <v>0.01513440043638359</v>
       </c>
     </row>
     <row r="294">
@@ -24741,10 +24741,10 @@
         <v>-0.1217041088998335</v>
       </c>
       <c r="O294" t="n">
-        <v>-0.2894574495395481</v>
+        <v>-0.2894572895786319</v>
       </c>
       <c r="P294" t="n">
-        <v>-0.1076606799219325</v>
+        <v>-0.1076606129592975</v>
       </c>
     </row>
     <row r="295">
@@ -24848,19 +24848,19 @@
         <v>0.03003789162752413</v>
       </c>
       <c r="L296" t="n">
-        <v>-0.03646395880727737</v>
+        <v>-0.03646378468869083</v>
       </c>
       <c r="M296" t="n">
-        <v>0.1072202112339469</v>
+        <v>0.1072200579538323</v>
       </c>
       <c r="N296" t="n">
-        <v>0.08886108426855688</v>
+        <v>0.08886101014900349</v>
       </c>
       <c r="O296" t="n">
-        <v>0.3033440054832264</v>
+        <v>0.3033442178741999</v>
       </c>
       <c r="P296" t="n">
-        <v>0.092327882785741</v>
+        <v>0.09232794212043927</v>
       </c>
     </row>
     <row r="297">
@@ -24912,13 +24912,13 @@
         <v>0.2725883147338</v>
       </c>
       <c r="N297" t="n">
-        <v>0.2631710328526848</v>
+        <v>0.2631711603569677</v>
       </c>
       <c r="O297" t="n">
-        <v>0.9200091013296197</v>
+        <v>0.9200089540383656</v>
       </c>
       <c r="P297" t="n">
-        <v>0.2428949662636655</v>
+        <v>0.2428949344812532</v>
       </c>
     </row>
     <row r="298">
@@ -24973,10 +24973,10 @@
         <v>0.105608308764813</v>
       </c>
       <c r="O298" t="n">
-        <v>0.4849333450944964</v>
+        <v>0.4849328722279542</v>
       </c>
       <c r="P298" t="n">
-        <v>0.1408686682466258</v>
+        <v>0.1408685471460882</v>
       </c>
     </row>
     <row r="299">
@@ -25086,13 +25086,13 @@
         <v>0.06769866555297011</v>
       </c>
       <c r="N300" t="n">
-        <v>-0.07241626725478667</v>
+        <v>-0.07241633136043968</v>
       </c>
       <c r="O300" t="n">
-        <v>1.082485153392319</v>
+        <v>1.082485476505002</v>
       </c>
       <c r="P300" t="n">
-        <v>0.2770090389184465</v>
+        <v>0.2770091049641827</v>
       </c>
     </row>
     <row r="301">
@@ -25260,13 +25260,13 @@
         <v>0.07512817923354742</v>
       </c>
       <c r="N303" t="n">
-        <v>-0.009774811819821316</v>
+        <v>-0.009774704596475003</v>
       </c>
       <c r="O303" t="n">
-        <v>0.8288781945871171</v>
+        <v>0.8288780117093559</v>
       </c>
       <c r="P303" t="n">
-        <v>0.2229112135654201</v>
+        <v>0.2229111728039535</v>
       </c>
     </row>
     <row r="304">
@@ -25315,16 +25315,16 @@
         <v>0.2900887708200171</v>
       </c>
       <c r="M304" t="n">
-        <v>-0.1303774308983372</v>
+        <v>-0.1303775141428763</v>
       </c>
       <c r="N304" t="n">
-        <v>-0.1844597231942506</v>
+        <v>-0.1844598696191507</v>
       </c>
       <c r="O304" t="n">
-        <v>0.4317486794551015</v>
+        <v>0.4317487922781451</v>
       </c>
       <c r="P304" t="n">
-        <v>0.1270822156912006</v>
+        <v>0.1270822452962201</v>
       </c>
     </row>
     <row r="305">
@@ -25376,13 +25376,13 @@
         <v>0.1531875669882101</v>
       </c>
       <c r="N305" t="n">
-        <v>0.08155181100185316</v>
+        <v>0.08155192853798043</v>
       </c>
       <c r="O305" t="n">
-        <v>0.3369732256666749</v>
+        <v>0.3369733154699397</v>
       </c>
       <c r="P305" t="n">
-        <v>0.1016430612630708</v>
+        <v>0.1016430859285216</v>
       </c>
     </row>
     <row r="306">
@@ -25428,10 +25428,10 @@
         <v>0.05085223683927764</v>
       </c>
       <c r="L306" t="n">
-        <v>-0.04992303902957096</v>
+        <v>-0.04992295277399517</v>
       </c>
       <c r="M306" t="n">
-        <v>0.121893009012312</v>
+        <v>0.1218928887381328</v>
       </c>
       <c r="N306" t="n">
         <v>0.006809014610812181</v>
@@ -25486,19 +25486,19 @@
         <v>0.08464858782612272</v>
       </c>
       <c r="L307" t="n">
-        <v>-0.03523727603327742</v>
+        <v>-0.03523734011475466</v>
       </c>
       <c r="M307" t="n">
-        <v>0.05735785165557505</v>
+        <v>0.05735777468309644</v>
       </c>
       <c r="N307" t="n">
         <v>-0.01729629597053939</v>
       </c>
       <c r="O307" t="n">
-        <v>0.5689697784629637</v>
+        <v>0.5689696089821177</v>
       </c>
       <c r="P307" t="n">
-        <v>0.1619966056561628</v>
+        <v>0.1619965638163565</v>
       </c>
     </row>
     <row r="308">
@@ -25550,13 +25550,13 @@
         <v>0.1533750429036564</v>
       </c>
       <c r="N308" t="n">
-        <v>0.06581129238137184</v>
+        <v>0.06581140732354407</v>
       </c>
       <c r="O308" t="n">
-        <v>0.244538239423304</v>
+        <v>0.2445383177852551</v>
       </c>
       <c r="P308" t="n">
-        <v>0.07564612015396444</v>
+        <v>0.07564614272986825</v>
       </c>
     </row>
     <row r="309">
@@ -25605,10 +25605,10 @@
         <v>-0.04412156003974044</v>
       </c>
       <c r="M309" t="n">
-        <v>0.0146550968636836</v>
+        <v>0.01465519644092983</v>
       </c>
       <c r="N309" t="n">
-        <v>-0.08116290275822857</v>
+        <v>-0.08116282109994111</v>
       </c>
       <c r="O309" t="n">
         <v>0.4249525352754333</v>
@@ -25660,7 +25660,7 @@
         <v>0.1948366530522365</v>
       </c>
       <c r="L310" t="n">
-        <v>-0.05855629998129463</v>
+        <v>-0.05855620953411589</v>
       </c>
       <c r="M310" t="n">
         <v>-0.1601838888645114</v>
@@ -25669,10 +25669,10 @@
         <v>0.006364083846232216</v>
       </c>
       <c r="O310" t="n">
-        <v>1.806165834705379</v>
+        <v>1.806165633808625</v>
       </c>
       <c r="P310" t="n">
-        <v>0.4104935707637041</v>
+        <v>0.4104935371040652</v>
       </c>
     </row>
     <row r="311">
@@ -25727,10 +25727,10 @@
         <v>0.1155890810587066</v>
       </c>
       <c r="O311" t="n">
-        <v>0.4770499126167573</v>
+        <v>0.4770496438621767</v>
       </c>
       <c r="P311" t="n">
-        <v>0.1388461477506981</v>
+        <v>0.1388460786783003</v>
       </c>
     </row>
     <row r="312">
@@ -25953,16 +25953,16 @@
         <v>-0.003302678124690095</v>
       </c>
       <c r="M315" t="n">
-        <v>0.009921433020189996</v>
+        <v>0.009921346807762133</v>
       </c>
       <c r="N315" t="n">
-        <v>-0.09453745640419164</v>
+        <v>-0.09453738710379078</v>
       </c>
       <c r="O315" t="n">
-        <v>-0.02566899116950272</v>
+        <v>-0.02566883068324488</v>
       </c>
       <c r="P315" t="n">
-        <v>-0.008630603414981675</v>
+        <v>-0.008630548984076558</v>
       </c>
     </row>
     <row r="316">
@@ -26017,10 +26017,10 @@
         <v>0.6015157583285091</v>
       </c>
       <c r="O316" t="n">
-        <v>-0.2643900687851378</v>
+        <v>-0.2643900050599988</v>
       </c>
       <c r="P316" t="n">
-        <v>-0.09728804380169453</v>
+        <v>-0.09728801773468954</v>
       </c>
     </row>
     <row r="317">
@@ -26072,13 +26072,13 @@
         <v>-0.005475761057378237</v>
       </c>
       <c r="N317" t="n">
-        <v>-0.04374397132590235</v>
+        <v>-0.04374402931250543</v>
       </c>
       <c r="O317" t="n">
-        <v>0.451253976900273</v>
+        <v>0.451253843343435</v>
       </c>
       <c r="P317" t="n">
-        <v>0.1321773813201816</v>
+        <v>0.1321773465892895</v>
       </c>
     </row>
     <row r="318">
@@ -26246,13 +26246,13 @@
         <v>0.02513597147956315</v>
       </c>
       <c r="N320" t="n">
-        <v>-0.06943882818037805</v>
+        <v>-0.06943888966598888</v>
       </c>
       <c r="O320" t="n">
-        <v>0.7317221711735606</v>
+        <v>0.731722277639363</v>
       </c>
       <c r="P320" t="n">
-        <v>0.20086099578838</v>
+        <v>0.200861020397914</v>
       </c>
     </row>
     <row r="321">
@@ -26298,10 +26298,10 @@
         <v>-0.04873775874043218</v>
       </c>
       <c r="L321" t="n">
-        <v>-0.05704215591521378</v>
+        <v>-0.05704206820088953</v>
       </c>
       <c r="M321" t="n">
-        <v>0.03715761476548018</v>
+        <v>0.03715772088016589</v>
       </c>
       <c r="N321" t="n">
         <v>0.2412530975895923</v>
@@ -26362,7 +26362,7 @@
         <v>-0.03695358401202298</v>
       </c>
       <c r="N322" t="n">
-        <v>-0.1015974898443408</v>
+        <v>-0.1015975543046201</v>
       </c>
     </row>
     <row r="323">
@@ -26408,7 +26408,7 @@
         <v>-0.02966137654831813</v>
       </c>
       <c r="L323" t="n">
-        <v>0.1009674331704362</v>
+        <v>0.10096735124439</v>
       </c>
       <c r="M323" t="n">
         <v>0.09439255191490492</v>
@@ -26417,10 +26417,10 @@
         <v>-0.02096091812613043</v>
       </c>
       <c r="O323" t="n">
-        <v>-0.07016804702639501</v>
+        <v>-0.07016816389879355</v>
       </c>
       <c r="P323" t="n">
-        <v>-0.02395878823996089</v>
+        <v>-0.02395882913347291</v>
       </c>
     </row>
     <row r="324">
@@ -26466,19 +26466,19 @@
         <v>0.1884412273542824</v>
       </c>
       <c r="L324" t="n">
-        <v>0.08205000830024711</v>
+        <v>0.08205009860978163</v>
       </c>
       <c r="M324" t="n">
-        <v>-0.1079940422204783</v>
+        <v>-0.1079939808478897</v>
       </c>
       <c r="N324" t="n">
-        <v>-0.2374726668079031</v>
+        <v>-0.2374724874131128</v>
       </c>
       <c r="O324" t="n">
-        <v>-0.1786153453641104</v>
+        <v>-0.1786152933247321</v>
       </c>
       <c r="P324" t="n">
-        <v>-0.06348329528288887</v>
+        <v>-0.06348327550500699</v>
       </c>
     </row>
     <row r="325">
@@ -26530,13 +26530,13 @@
         <v>0.1134885369575989</v>
       </c>
       <c r="N325" t="n">
-        <v>0.009516518409723673</v>
+        <v>0.009516589274620735</v>
       </c>
       <c r="O325" t="n">
-        <v>-0.1326452822559828</v>
+        <v>-0.1326450730096497</v>
       </c>
       <c r="P325" t="n">
-        <v>-0.04632825654746919</v>
+        <v>-0.0463281798574694</v>
       </c>
     </row>
     <row r="326">
@@ -26640,19 +26640,19 @@
         <v>0.08250684718492729</v>
       </c>
       <c r="L327" t="n">
-        <v>0.006555125371887183</v>
+        <v>0.006555207411222508</v>
       </c>
       <c r="M327" t="n">
         <v>0.02402905251140597</v>
       </c>
       <c r="N327" t="n">
-        <v>-0.0907152869061969</v>
+        <v>-0.09071521995678289</v>
       </c>
       <c r="O327" t="n">
-        <v>-0.1969489584549192</v>
+        <v>-0.1969489062353488</v>
       </c>
       <c r="P327" t="n">
-        <v>-0.07050359034965403</v>
+        <v>-0.07050357020236597</v>
       </c>
     </row>
     <row r="328">
@@ -26762,7 +26762,7 @@
         <v>0.1491428405646973</v>
       </c>
       <c r="N329" t="n">
-        <v>0.2367212316118232</v>
+        <v>0.2367210896488661</v>
       </c>
       <c r="O329" t="n">
         <v>0.6459000535531332</v>
@@ -26878,13 +26878,13 @@
         <v>0.0474126383501432</v>
       </c>
       <c r="N331" t="n">
-        <v>0.1844353810899799</v>
+        <v>0.1844354757916336</v>
       </c>
       <c r="O331" t="n">
-        <v>-0.02041522802533924</v>
+        <v>-0.02041535757872648</v>
       </c>
       <c r="P331" t="n">
-        <v>-0.006851917552888054</v>
+        <v>-0.006851961335283652</v>
       </c>
     </row>
     <row r="332">
@@ -26939,10 +26939,10 @@
         <v>-0.01925983980584911</v>
       </c>
       <c r="O332" t="n">
-        <v>0.752025570964171</v>
+        <v>0.7520257456296144</v>
       </c>
       <c r="P332" t="n">
-        <v>0.2055358970252457</v>
+        <v>0.2055359370865815</v>
       </c>
     </row>
     <row r="333">
@@ -26991,16 +26991,16 @@
         <v>-0.008374324606868933</v>
       </c>
       <c r="M333" t="n">
-        <v>0.06194933649992707</v>
+        <v>0.06194941055218273</v>
       </c>
       <c r="N333" t="n">
-        <v>0.0774135443882471</v>
+        <v>0.07741362061291812</v>
       </c>
       <c r="O333" t="n">
-        <v>0.4745763877074609</v>
+        <v>0.4745761021489368</v>
       </c>
       <c r="P333" t="n">
-        <v>0.1382100739523735</v>
+        <v>0.1382100004791571</v>
       </c>
     </row>
     <row r="334">
@@ -27046,7 +27046,7 @@
         <v>0.09111572233240839</v>
       </c>
       <c r="L334" t="n">
-        <v>-0.006635219570332529</v>
+        <v>-0.006635311918879117</v>
       </c>
       <c r="M334" t="n">
         <v>0.00393038595256967</v>
@@ -27113,10 +27113,10 @@
         <v>-0.1031531045708215</v>
       </c>
       <c r="O335" t="n">
-        <v>0.3282431453141035</v>
+        <v>0.3282428890795077</v>
       </c>
       <c r="P335" t="n">
-        <v>0.09924001094434076</v>
+        <v>0.09923994025865368</v>
       </c>
     </row>
     <row r="336">
@@ -27168,13 +27168,13 @@
         <v>0.07979102654344228</v>
       </c>
       <c r="N336" t="n">
-        <v>0.04431170299462783</v>
+        <v>0.04431177162312228</v>
       </c>
       <c r="O336" t="n">
-        <v>0.491207216574173</v>
+        <v>0.4912074964402269</v>
       </c>
       <c r="P336" t="n">
-        <v>0.1424731412906939</v>
+        <v>0.1424732127628601</v>
       </c>
     </row>
     <row r="337">
@@ -27287,10 +27287,10 @@
         <v>0.05377056288447601</v>
       </c>
       <c r="O338" t="n">
-        <v>1.152639586080574</v>
+        <v>1.152639721576225</v>
       </c>
       <c r="P338" t="n">
-        <v>0.291190853158638</v>
+        <v>0.291190880249524</v>
       </c>
     </row>
     <row r="339">
@@ -27339,10 +27339,10 @@
         <v>-0.06098970204786036</v>
       </c>
       <c r="M339" t="n">
-        <v>0.05896367908525857</v>
+        <v>0.05896356463627872</v>
       </c>
       <c r="N339" t="n">
-        <v>0.02472358216472625</v>
+        <v>0.02472347499718675</v>
       </c>
       <c r="O339" t="n">
         <v>0.2460300645861617</v>
@@ -27403,10 +27403,10 @@
         <v>-0.1336735003178946</v>
       </c>
       <c r="O340" t="n">
-        <v>-0.3035671259337228</v>
+        <v>-0.3035670556640728</v>
       </c>
       <c r="P340" t="n">
-        <v>-0.1136067890625206</v>
+        <v>-0.1136067592503445</v>
       </c>
     </row>
     <row r="341">
@@ -27458,7 +27458,7 @@
         <v>0.1299909323217765</v>
       </c>
       <c r="N341" t="n">
-        <v>0.09815436832590585</v>
+        <v>0.09815448919976566</v>
       </c>
       <c r="O341" t="n">
         <v>0.9901333847180067</v>
@@ -27574,13 +27574,13 @@
         <v>0.04958428926962966</v>
       </c>
       <c r="N343" t="n">
-        <v>-0.1662868646210254</v>
+        <v>-0.1662869161416787</v>
       </c>
       <c r="O343" t="n">
-        <v>-0.08638217052919683</v>
+        <v>-0.08638210865960338</v>
       </c>
       <c r="P343" t="n">
-        <v>-0.0296653900100794</v>
+        <v>-0.0296653681066078</v>
       </c>
     </row>
     <row r="344">
@@ -27635,10 +27635,10 @@
         <v>0.09869505137818413</v>
       </c>
       <c r="O344" t="n">
-        <v>0.3535266040333085</v>
+        <v>0.3535267308231651</v>
       </c>
       <c r="P344" t="n">
-        <v>0.1061709920831997</v>
+        <v>0.1061710266229117</v>
       </c>
     </row>
     <row r="345">
@@ -27684,19 +27684,19 @@
         <v>-0.02983990213286525</v>
       </c>
       <c r="L345" t="n">
-        <v>-0.02943703668072206</v>
+        <v>-0.02943713996947195</v>
       </c>
       <c r="M345" t="n">
-        <v>0.1205779436229493</v>
+        <v>0.1205778747799542</v>
       </c>
       <c r="N345" t="n">
         <v>-0.009369721656483421</v>
       </c>
       <c r="O345" t="n">
-        <v>0.2469979550988632</v>
+        <v>0.2469980403513694</v>
       </c>
       <c r="P345" t="n">
-        <v>0.07635429244393532</v>
+        <v>0.07635431697268413</v>
       </c>
     </row>
     <row r="346">
@@ -27751,10 +27751,10 @@
         <v>-0.1833663237022397</v>
       </c>
       <c r="O346" t="n">
-        <v>0.1150748367503809</v>
+        <v>0.1150749266511424</v>
       </c>
       <c r="P346" t="n">
-        <v>0.0369743287188562</v>
+        <v>0.03697435658687498</v>
       </c>
     </row>
     <row r="347">
@@ -27806,13 +27806,13 @@
         <v>0.108074965653703</v>
       </c>
       <c r="N347" t="n">
-        <v>0.1531696761524382</v>
+        <v>0.1531696070220832</v>
       </c>
       <c r="O347" t="n">
-        <v>0.004612433966331819</v>
+        <v>0.004612538898712382</v>
       </c>
       <c r="P347" t="n">
-        <v>0.001535120188898009</v>
+        <v>0.001535155059214421</v>
       </c>
     </row>
     <row r="348">
@@ -27867,10 +27867,10 @@
         <v>0.03576962096800118</v>
       </c>
       <c r="O348" t="n">
-        <v>1.092095826919405</v>
+        <v>1.092095970260883</v>
       </c>
       <c r="P348" t="n">
-        <v>0.2789704911374382</v>
+        <v>0.2789705203473043</v>
       </c>
     </row>
     <row r="349">
@@ -27925,10 +27925,10 @@
         <v>0.109057632267024</v>
       </c>
       <c r="O349" t="n">
-        <v>0.7477576774286252</v>
+        <v>0.7477578112972272</v>
       </c>
       <c r="P349" t="n">
-        <v>0.2045562152994049</v>
+        <v>0.2045562460535257</v>
       </c>
     </row>
     <row r="350">
@@ -28032,19 +28032,19 @@
         <v>0.09245666935834573</v>
       </c>
       <c r="L351" t="n">
-        <v>-0.06984892550594202</v>
+        <v>-0.0698489927307786</v>
       </c>
       <c r="M351" t="n">
         <v>-0.1608300049522268</v>
       </c>
       <c r="N351" t="n">
-        <v>0.06224336260908259</v>
+        <v>0.06224345028309664</v>
       </c>
       <c r="O351" t="n">
-        <v>0.2073820713806125</v>
+        <v>0.2073819581113148</v>
       </c>
       <c r="P351" t="n">
-        <v>0.06483317756449969</v>
+        <v>0.06483314426575837</v>
       </c>
     </row>
     <row r="352">
@@ -28090,19 +28090,19 @@
         <v>0.1364759154239907</v>
       </c>
       <c r="L352" t="n">
-        <v>0.1621459523387629</v>
+        <v>0.1621458548817405</v>
       </c>
       <c r="M352" t="n">
         <v>-0.1835675856682274</v>
       </c>
       <c r="N352" t="n">
-        <v>-0.232126078054916</v>
+        <v>-0.2321259078658118</v>
       </c>
       <c r="O352" t="n">
-        <v>0.7171975846647949</v>
+        <v>0.7171979038360015</v>
       </c>
       <c r="P352" t="n">
-        <v>0.1974942120590351</v>
+        <v>0.1974942862507787</v>
       </c>
     </row>
     <row r="353">
@@ -28151,16 +28151,16 @@
         <v>-0.08106516201652747</v>
       </c>
       <c r="M353" t="n">
-        <v>0.02343031356748293</v>
+        <v>0.02343040866002188</v>
       </c>
       <c r="N353" t="n">
         <v>0.04940682974438304</v>
       </c>
       <c r="O353" t="n">
-        <v>0.5831118424631649</v>
+        <v>0.5831119562319396</v>
       </c>
       <c r="P353" t="n">
-        <v>0.1654774253155658</v>
+        <v>0.1654774532341945</v>
       </c>
     </row>
     <row r="354">
@@ -28212,13 +28212,13 @@
         <v>-0.1013491557652327</v>
       </c>
       <c r="N354" t="n">
-        <v>-0.01026796306964028</v>
+        <v>-0.01026789227082514</v>
       </c>
       <c r="O354" t="n">
-        <v>-0.5559762603863377</v>
+        <v>-0.5559762888855627</v>
       </c>
       <c r="P354" t="n">
-        <v>-0.2370980410541578</v>
+        <v>-0.2370980573761943</v>
       </c>
     </row>
     <row r="355">
@@ -28264,7 +28264,7 @@
         <v>-0.03324506357464585</v>
       </c>
       <c r="L355" t="n">
-        <v>-0.07121579488562513</v>
+        <v>-0.0712156989884577</v>
       </c>
       <c r="M355" t="n">
         <v>0.08231719257168613</v>
@@ -28273,10 +28273,10 @@
         <v>0.05262707685495482</v>
       </c>
       <c r="O355" t="n">
-        <v>0.4816336053472396</v>
+        <v>0.4816338493854342</v>
       </c>
       <c r="P355" t="n">
-        <v>0.140022982338367</v>
+        <v>0.1400230449289952</v>
       </c>
     </row>
     <row r="356">
@@ -28331,10 +28331,10 @@
         <v>-0.05753710045944016</v>
       </c>
       <c r="O356" t="n">
-        <v>0.03016533534657273</v>
+        <v>0.03016511288135737</v>
       </c>
       <c r="P356" t="n">
-        <v>0.009955667546188041</v>
+        <v>0.009955594845876936</v>
       </c>
     </row>
     <row r="357">
@@ -28383,16 +28383,16 @@
         <v>-0.07582496533594407</v>
       </c>
       <c r="M357" t="n">
-        <v>0.05856312100283878</v>
+        <v>0.05856299915048013</v>
       </c>
       <c r="N357" t="n">
-        <v>0.01524802059462593</v>
+        <v>0.01524779642608065</v>
       </c>
       <c r="O357" t="n">
-        <v>0.5525764488000344</v>
+        <v>0.5525765798619464</v>
       </c>
       <c r="P357" t="n">
-        <v>0.157935400279916</v>
+        <v>0.1579354328625784</v>
       </c>
     </row>
     <row r="358">
@@ -28441,16 +28441,16 @@
         <v>-0.1054788530196705</v>
       </c>
       <c r="M358" t="n">
-        <v>-0.2371782609087228</v>
+        <v>-0.2371783125641018</v>
       </c>
       <c r="N358" t="n">
-        <v>-0.07063620966841755</v>
+        <v>-0.07063628634114605</v>
       </c>
       <c r="O358" t="n">
-        <v>0.3245741984315089</v>
+        <v>0.3245740426836841</v>
       </c>
       <c r="P358" t="n">
-        <v>0.09822695035228057</v>
+        <v>0.09822690730789052</v>
       </c>
     </row>
     <row r="359">
@@ -28502,13 +28502,13 @@
         <v>-0.01766312384776914</v>
       </c>
       <c r="N359" t="n">
-        <v>-0.1922005276991379</v>
+        <v>-0.1922004594820208</v>
       </c>
       <c r="O359" t="n">
-        <v>0.2033161771000294</v>
+        <v>0.2033159500419905</v>
       </c>
       <c r="P359" t="n">
-        <v>0.06363654775234151</v>
+        <v>0.06363648085187412</v>
       </c>
     </row>
     <row r="360">
@@ -28557,16 +28557,16 @@
         <v>0.1193344519596227</v>
       </c>
       <c r="M360" t="n">
-        <v>-0.07597736434236635</v>
+        <v>-0.07597743504035459</v>
       </c>
       <c r="N360" t="n">
-        <v>0.07409358428477719</v>
+        <v>0.07409367981178017</v>
       </c>
       <c r="O360" t="n">
-        <v>3.455684256333186</v>
+        <v>3.455683434392253</v>
       </c>
       <c r="P360" t="n">
-        <v>0.6455262041470871</v>
+        <v>0.645526102963569</v>
       </c>
     </row>
     <row r="361">
@@ -28673,16 +28673,16 @@
         <v>-0.09267151305850563</v>
       </c>
       <c r="M362" t="n">
-        <v>0.04244676329925623</v>
+        <v>0.04244666897814198</v>
       </c>
       <c r="N362" t="n">
         <v>0.05912650872656555</v>
       </c>
       <c r="O362" t="n">
-        <v>0.2128941103744337</v>
+        <v>0.2128942380615302</v>
       </c>
       <c r="P362" t="n">
-        <v>0.06645113896387533</v>
+        <v>0.06645117638732501</v>
       </c>
     </row>
     <row r="363">
@@ -28728,19 +28728,19 @@
         <v>-0.01703753724106538</v>
       </c>
       <c r="L363" t="n">
-        <v>-0.07193568465935329</v>
+        <v>-0.07193561081707978</v>
       </c>
       <c r="M363" t="n">
         <v>0.06566532357163757</v>
       </c>
       <c r="N363" t="n">
-        <v>0.01209321592548052</v>
+        <v>0.0120933037447748</v>
       </c>
       <c r="O363" t="n">
-        <v>0.4526746352215372</v>
+        <v>0.4526744543019743</v>
       </c>
       <c r="P363" t="n">
-        <v>0.1325466970260383</v>
+        <v>0.1325466500093475</v>
       </c>
     </row>
     <row r="364">
@@ -28792,13 +28792,13 @@
         <v>0.04453911758717566</v>
       </c>
       <c r="N364" t="n">
-        <v>0.01013659081245044</v>
+        <v>0.01013651931965898</v>
       </c>
       <c r="O364" t="n">
-        <v>0.4509042006131796</v>
+        <v>0.450904348108961</v>
       </c>
       <c r="P364" t="n">
-        <v>0.1320864161672333</v>
+        <v>0.1320864545290503</v>
       </c>
     </row>
     <row r="365">
@@ -28850,13 +28850,13 @@
         <v>0.04845665611901584</v>
       </c>
       <c r="N365" t="n">
-        <v>0.03130765134334301</v>
+        <v>0.03130757554856367</v>
       </c>
       <c r="O365" t="n">
-        <v>0.4077249188925649</v>
+        <v>0.4077250601133056</v>
       </c>
       <c r="P365" t="n">
-        <v>0.1207427362125413</v>
+        <v>0.1207427736895872</v>
       </c>
     </row>
     <row r="366">
@@ -28908,7 +28908,7 @@
         <v>-0.009605025739587658</v>
       </c>
       <c r="N366" t="n">
-        <v>0.1074627110599824</v>
+        <v>0.1074628205399426</v>
       </c>
       <c r="O366" t="n">
         <v>0.3178875258866638</v>
@@ -28966,13 +28966,13 @@
         <v>-0.00385149938893603</v>
       </c>
       <c r="N367" t="n">
-        <v>-0.02929068837907545</v>
+        <v>-0.02929059211501039</v>
       </c>
       <c r="O367" t="n">
-        <v>0.3373989474418417</v>
+        <v>0.337399221535549</v>
       </c>
       <c r="P367" t="n">
-        <v>0.1017599780070904</v>
+        <v>0.10176005327395</v>
       </c>
     </row>
     <row r="368">
@@ -29024,7 +29024,7 @@
         <v>0.2381314670134329</v>
       </c>
       <c r="N368" t="n">
-        <v>0.2452665261732423</v>
+        <v>0.2452666526992846</v>
       </c>
       <c r="O368" t="n">
         <v>-0.09637197671484832</v>
@@ -29079,16 +29079,16 @@
         <v>-0.009646314489645036</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.06514681449034077</v>
+        <v>-0.06514669663415429</v>
       </c>
       <c r="N369" t="n">
         <v>-0.0295942790099567</v>
       </c>
       <c r="O369" t="n">
-        <v>0.5502858310026288</v>
+        <v>0.5502859930563881</v>
       </c>
       <c r="P369" t="n">
-        <v>0.1573656606658982</v>
+        <v>0.157365700992967</v>
       </c>
     </row>
     <row r="370">
@@ -29140,13 +29140,13 @@
         <v>-0.07149394270489084</v>
       </c>
       <c r="N370" t="n">
-        <v>-0.1613091504842213</v>
+        <v>-0.1613091004827369</v>
       </c>
       <c r="O370" t="n">
-        <v>0.18985514392864</v>
+        <v>0.1898553452071075</v>
       </c>
       <c r="P370" t="n">
-        <v>0.05965550212738546</v>
+        <v>0.059655561878587</v>
       </c>
     </row>
     <row r="371">
@@ -29192,7 +29192,7 @@
         <v>-0.04229301727918688</v>
       </c>
       <c r="L371" t="n">
-        <v>0.0270182100806533</v>
+        <v>0.02701832677905958</v>
       </c>
       <c r="M371" t="n">
         <v>0.06437652449813225</v>
@@ -29201,10 +29201,10 @@
         <v>-0.06250964624622035</v>
       </c>
       <c r="O371" t="n">
-        <v>0.03859477565419223</v>
+        <v>0.03859465631013337</v>
       </c>
       <c r="P371" t="n">
-        <v>0.01270287882876109</v>
+        <v>0.01270284003914535</v>
       </c>
     </row>
     <row r="372">
@@ -29305,22 +29305,22 @@
         <v>-0.05627344045427984</v>
       </c>
       <c r="K373" t="n">
-        <v>-0.05779451921444156</v>
+        <v>-0.05779442543149416</v>
       </c>
       <c r="L373" t="n">
-        <v>-0.01114636058023633</v>
+        <v>-0.01114646387934382</v>
       </c>
       <c r="M373" t="n">
-        <v>0.06821580576884978</v>
+        <v>0.06821592631424633</v>
       </c>
       <c r="N373" t="n">
-        <v>-0.02664624814874494</v>
+        <v>-0.02664614806258159</v>
       </c>
       <c r="O373" t="n">
-        <v>0.06300091959604259</v>
+        <v>0.06300103896733922</v>
       </c>
       <c r="P373" t="n">
-        <v>0.0205741095813381</v>
+        <v>0.02057414778364119</v>
       </c>
     </row>
     <row r="374">
@@ -29433,10 +29433,10 @@
         <v>-0.1852692564719159</v>
       </c>
       <c r="O375" t="n">
-        <v>0.4645569910505183</v>
+        <v>0.4645568095253558</v>
       </c>
       <c r="P375" t="n">
-        <v>0.1356262571550335</v>
+        <v>0.1356262102364656</v>
       </c>
     </row>
     <row r="376">
@@ -29488,13 +29488,13 @@
         <v>-0.1152024378522141</v>
       </c>
       <c r="N376" t="n">
-        <v>-0.2780337384422846</v>
+        <v>-0.2780337967689095</v>
       </c>
       <c r="O376" t="n">
-        <v>-0.04699336781643637</v>
+        <v>-0.04699326618572464</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.0159164451089282</v>
+        <v>-0.01591641012732181</v>
       </c>
     </row>
     <row r="377">
@@ -29546,13 +29546,13 @@
         <v>-0.1143731585595548</v>
       </c>
       <c r="N377" t="n">
-        <v>-0.003131912066932863</v>
+        <v>-0.00313198603814524</v>
       </c>
       <c r="O377" t="n">
-        <v>0.6761742692968296</v>
+        <v>0.6761746875659715</v>
       </c>
       <c r="P377" t="n">
-        <v>0.1878813299257451</v>
+        <v>0.1878814287329063</v>
       </c>
     </row>
     <row r="378">
@@ -29604,13 +29604,13 @@
         <v>0.05075147085157927</v>
       </c>
       <c r="N378" t="n">
-        <v>-0.01752991818135485</v>
+        <v>-0.01752998851134469</v>
       </c>
       <c r="O378" t="n">
-        <v>0.1416737678751643</v>
+        <v>0.1416736729052761</v>
       </c>
       <c r="P378" t="n">
-        <v>0.04515493162382023</v>
+        <v>0.04515490264348965</v>
       </c>
     </row>
     <row r="379">
@@ -29665,10 +29665,10 @@
         <v>0.01658269145167002</v>
       </c>
       <c r="O379" t="n">
-        <v>-0.1247272447348347</v>
+        <v>-0.1247274980347639</v>
       </c>
       <c r="P379" t="n">
-        <v>-0.04343503569060947</v>
+        <v>-0.04343512796579252</v>
       </c>
     </row>
     <row r="380">
@@ -29720,13 +29720,13 @@
         <v>0.02563805631153082</v>
       </c>
       <c r="N380" t="n">
-        <v>0.1052443609071392</v>
+        <v>0.1052442651918162</v>
       </c>
       <c r="O380" t="n">
-        <v>0.4169373701092551</v>
+        <v>0.4169372127956976</v>
       </c>
       <c r="P380" t="n">
-        <v>0.1231822153652764</v>
+        <v>0.1231821737986787</v>
       </c>
     </row>
     <row r="381">
@@ -29775,7 +29775,7 @@
         <v>-0.0286611352056283</v>
       </c>
       <c r="M381" t="n">
-        <v>-0.03046561386853508</v>
+        <v>-0.03046568730296673</v>
       </c>
       <c r="N381" t="n">
         <v>-0.01054937984314563</v>
@@ -29839,10 +29839,10 @@
         <v>-0.3704679209012931</v>
       </c>
       <c r="O382" t="n">
-        <v>-0.4821810099007359</v>
+        <v>-0.4821810501945909</v>
       </c>
       <c r="P382" t="n">
-        <v>-0.196980685649759</v>
+        <v>-0.1969807064786234</v>
       </c>
     </row>
     <row r="383">
@@ -29897,10 +29897,10 @@
         <v>-0.2006416504331082</v>
       </c>
       <c r="O383" t="n">
-        <v>0.5388324139506806</v>
+        <v>0.5388320870302223</v>
       </c>
       <c r="P383" t="n">
-        <v>0.1545084304478801</v>
+        <v>0.1545083486905581</v>
       </c>
     </row>
     <row r="384">
@@ -29946,19 +29946,19 @@
         <v>-0.1191898470998632</v>
       </c>
       <c r="L384" t="n">
-        <v>0.02028899469875922</v>
+        <v>0.02028892751790989</v>
       </c>
       <c r="M384" t="n">
-        <v>0.127460559917151</v>
+        <v>0.1274604778816566</v>
       </c>
       <c r="N384" t="n">
         <v>-0.08521363803597248</v>
       </c>
       <c r="O384" t="n">
-        <v>0.0496115944542137</v>
+        <v>0.04961166555204977</v>
       </c>
       <c r="P384" t="n">
-        <v>0.01627101628511896</v>
+        <v>0.01627103923159723</v>
       </c>
     </row>
     <row r="385">
@@ -30004,19 +30004,19 @@
         <v>-0.08002681564695013</v>
       </c>
       <c r="L385" t="n">
-        <v>-0.08641706888822165</v>
+        <v>-0.08641714487568675</v>
       </c>
       <c r="M385" t="n">
-        <v>0.03427500172083597</v>
+        <v>0.03427509911168136</v>
       </c>
       <c r="N385" t="n">
-        <v>0.06940529690757669</v>
+        <v>0.06940540102675774</v>
       </c>
       <c r="O385" t="n">
-        <v>0.7055442905910032</v>
+        <v>0.7055440257580792</v>
       </c>
       <c r="P385" t="n">
-        <v>0.1947792384317233</v>
+        <v>0.1947791765908793</v>
       </c>
     </row>
     <row r="386">
@@ -30071,10 +30071,10 @@
         <v>-0.2012170512979304</v>
       </c>
       <c r="O386" t="n">
-        <v>-0.3460933569837851</v>
+        <v>-0.3460934435394294</v>
       </c>
       <c r="P386" t="n">
-        <v>-0.1320289306611173</v>
+        <v>-0.1320289689580206</v>
       </c>
     </row>
     <row r="387">
@@ -30123,16 +30123,16 @@
         <v>-0.09430097603963183</v>
       </c>
       <c r="M387" t="n">
-        <v>-0.001606585883747402</v>
+        <v>-0.001606696436134758</v>
       </c>
       <c r="N387" t="n">
         <v>0.003523959014693823</v>
       </c>
       <c r="O387" t="n">
-        <v>0.3517298586067987</v>
+        <v>0.3517297572822811</v>
       </c>
       <c r="P387" t="n">
-        <v>0.1056813113345545</v>
+        <v>0.1056812837075776</v>
       </c>
     </row>
     <row r="388">
@@ -30184,13 +30184,13 @@
         <v>-0.05226063362529765</v>
       </c>
       <c r="N388" t="n">
-        <v>-0.06463603265330942</v>
+        <v>-0.06463594378362847</v>
       </c>
       <c r="O388" t="n">
-        <v>0.08506708472739577</v>
+        <v>0.0850669651344842</v>
       </c>
       <c r="P388" t="n">
-        <v>0.02758761939979992</v>
+        <v>0.02758758164723396</v>
       </c>
     </row>
     <row r="389">
@@ -30242,13 +30242,13 @@
         <v>-0.03243412629827991</v>
       </c>
       <c r="N389" t="n">
-        <v>-0.1442010921597175</v>
+        <v>-0.1442009990855709</v>
       </c>
       <c r="O389" t="n">
-        <v>0.5221160117886554</v>
+        <v>0.5221158645740052</v>
       </c>
       <c r="P389" t="n">
-        <v>0.1503127093616703</v>
+        <v>0.1503126722766983</v>
       </c>
     </row>
     <row r="390">
@@ -30300,13 +30300,13 @@
         <v>0.1003714999822065</v>
       </c>
       <c r="N390" t="n">
-        <v>0.1744777509659252</v>
+        <v>0.1744776622757993</v>
       </c>
       <c r="O390" t="n">
-        <v>-0.0133573854237532</v>
+        <v>-0.01335732283367663</v>
       </c>
       <c r="P390" t="n">
-        <v>-0.004472434659486879</v>
+        <v>-0.004472413608249015</v>
       </c>
     </row>
     <row r="391">
@@ -30419,10 +30419,10 @@
         <v>-0.1393162383795922</v>
       </c>
       <c r="O392" t="n">
-        <v>-0.1133313794750955</v>
+        <v>-0.113331579678223</v>
       </c>
       <c r="P392" t="n">
-        <v>-0.03930149919618431</v>
+        <v>-0.03930157150236291</v>
       </c>
     </row>
     <row r="393">
@@ -30471,16 +30471,16 @@
         <v>-0.01380687019487592</v>
       </c>
       <c r="M393" t="n">
-        <v>0.01101996696518937</v>
+        <v>0.01102002794316204</v>
       </c>
       <c r="N393" t="n">
-        <v>-0.07389626695533891</v>
+        <v>-0.07389636928527565</v>
       </c>
       <c r="O393" t="n">
-        <v>0.05520488299535997</v>
+        <v>0.05520468372245801</v>
       </c>
       <c r="P393" t="n">
-        <v>0.01807302565245505</v>
+        <v>0.01807296156557103</v>
       </c>
     </row>
     <row r="394">
@@ -30526,19 +30526,19 @@
         <v>-0.04866173141222541</v>
       </c>
       <c r="L394" t="n">
-        <v>-0.04917757234337328</v>
+        <v>-0.04917764834001059</v>
       </c>
       <c r="M394" t="n">
-        <v>0.04556319907088358</v>
+        <v>0.04556310717498779</v>
       </c>
       <c r="N394" t="n">
-        <v>-0.09375693713011812</v>
+        <v>-0.09375700616759863</v>
       </c>
       <c r="O394" t="n">
-        <v>-0.2230180374504144</v>
+        <v>-0.223018138946055</v>
       </c>
       <c r="P394" t="n">
-        <v>-0.08067237117813886</v>
+        <v>-0.08067241120813318</v>
       </c>
     </row>
     <row r="395">
@@ -30648,13 +30648,13 @@
         <v>-0.07757116016310173</v>
       </c>
       <c r="N396" t="n">
-        <v>-0.1818547144146593</v>
+        <v>-0.1818547810094862</v>
       </c>
       <c r="O396" t="n">
-        <v>1.077502232519099</v>
+        <v>1.077502661919805</v>
       </c>
       <c r="P396" t="n">
-        <v>0.2759896931929657</v>
+        <v>0.2759897811047585</v>
       </c>
     </row>
     <row r="397">
@@ -30709,10 +30709,10 @@
         <v>0.0002136422955165695</v>
       </c>
       <c r="O397" t="n">
-        <v>0.2147678421252392</v>
+        <v>0.214768166512542</v>
       </c>
       <c r="P397" t="n">
-        <v>0.06700002316674047</v>
+        <v>0.06700011814270113</v>
       </c>
     </row>
     <row r="398">
@@ -30758,19 +30758,19 @@
         <v>0.1148723689712632</v>
       </c>
       <c r="L398" t="n">
-        <v>-0.2428354576763734</v>
+        <v>-0.2428353706375525</v>
       </c>
       <c r="M398" t="n">
         <v>-0.167216486816138</v>
       </c>
       <c r="N398" t="n">
-        <v>-0.03193555188140129</v>
+        <v>-0.03193548074187125</v>
       </c>
       <c r="O398" t="n">
-        <v>0.5041422915423766</v>
+        <v>0.5041424632858778</v>
       </c>
       <c r="P398" t="n">
-        <v>0.1457669941075375</v>
+        <v>0.1457670377155633</v>
       </c>
     </row>
     <row r="399">
@@ -30819,16 +30819,16 @@
         <v>-0.04103542599089061</v>
       </c>
       <c r="M399" t="n">
-        <v>-0.08288063629943976</v>
+        <v>-0.08288072089136667</v>
       </c>
       <c r="N399" t="n">
         <v>-0.1887884647673524</v>
       </c>
       <c r="O399" t="n">
-        <v>3.590567429970525</v>
+        <v>3.59056795981698</v>
       </c>
       <c r="P399" t="n">
-        <v>0.6619659571701146</v>
+        <v>0.6619660211118639</v>
       </c>
     </row>
     <row r="400">
@@ -30941,10 +30941,10 @@
         <v>-0.05743445253624901</v>
       </c>
       <c r="O401" t="n">
-        <v>0.07922187148734761</v>
+        <v>0.07922177035371503</v>
       </c>
       <c r="P401" t="n">
-        <v>0.02573910490888376</v>
+        <v>0.02573907286829114</v>
       </c>
     </row>
     <row r="402">
@@ -31054,7 +31054,7 @@
         <v>-0.1571960596221004</v>
       </c>
       <c r="N403" t="n">
-        <v>-0.1127683546069727</v>
+        <v>-0.1127682996197265</v>
       </c>
       <c r="O403" t="n">
         <v>0.008736231919187709</v>
@@ -31115,10 +31115,10 @@
         <v>-0.05799193275026204</v>
       </c>
       <c r="O404" t="n">
-        <v>0.7182626319889016</v>
+        <v>0.7182624340041164</v>
       </c>
       <c r="P404" t="n">
-        <v>0.1977417324828024</v>
+        <v>0.1977416864800077</v>
       </c>
     </row>
     <row r="405">
@@ -31170,13 +31170,13 @@
         <v>-0.1188257467848123</v>
       </c>
       <c r="N405" t="n">
-        <v>-0.260950415578472</v>
+        <v>-0.2609504840745677</v>
       </c>
       <c r="O405" t="n">
-        <v>-0.07569681261692751</v>
+        <v>-0.07569670547791107</v>
       </c>
       <c r="P405" t="n">
-        <v>-0.02589714350357564</v>
+        <v>-0.02589710586642391</v>
       </c>
     </row>
     <row r="406">
@@ -31231,10 +31231,10 @@
         <v>-0.2336856155047184</v>
       </c>
       <c r="O406" t="n">
-        <v>1.793884689513603</v>
+        <v>1.793884914668496</v>
       </c>
       <c r="P406" t="n">
-        <v>0.4084328932529377</v>
+        <v>0.4084329310874206</v>
       </c>
     </row>
     <row r="407">
@@ -31344,13 +31344,13 @@
         <v>-0.02018778042358926</v>
       </c>
       <c r="N408" t="n">
-        <v>-0.04817863969467751</v>
+        <v>-0.04817855991218256</v>
       </c>
       <c r="O408" t="n">
-        <v>-0.09366703980173952</v>
+        <v>-0.09366696746277869</v>
       </c>
       <c r="P408" t="n">
-        <v>-0.03225131166878925</v>
+        <v>-0.03225128592183757</v>
       </c>
     </row>
     <row r="409">
@@ -31396,10 +31396,10 @@
         <v>-0.03671988896147282</v>
       </c>
       <c r="L409" t="n">
-        <v>-0.09433452825615851</v>
+        <v>-0.09433461254841968</v>
       </c>
       <c r="M409" t="n">
-        <v>-0.03375891181234236</v>
+        <v>-0.03375881586716079</v>
       </c>
       <c r="N409" t="n">
         <v>-0.04359620881849136</v>
@@ -31463,10 +31463,10 @@
         <v>0.02864688209350774</v>
       </c>
       <c r="O410" t="n">
-        <v>-0.1109335763388206</v>
+        <v>-0.1109334746085134</v>
       </c>
       <c r="P410" t="n">
-        <v>-0.03843627836064989</v>
+        <v>-0.03843624168541149</v>
       </c>
     </row>
     <row r="411">
@@ -31576,13 +31576,13 @@
         <v>-0.07823587979636326</v>
       </c>
       <c r="N412" t="n">
-        <v>0.0833922934831679</v>
+        <v>0.08339216896666768</v>
       </c>
       <c r="O412" t="n">
-        <v>0.4513621882219188</v>
+        <v>0.4513619647582043</v>
       </c>
       <c r="P412" t="n">
-        <v>0.132205520517453</v>
+        <v>0.1322054624095443</v>
       </c>
     </row>
     <row r="413">
@@ -31695,10 +31695,10 @@
         <v>-0.1423345131841176</v>
       </c>
       <c r="O414" t="n">
-        <v>-0.03258387101750271</v>
+        <v>-0.03258359968632241</v>
       </c>
       <c r="P414" t="n">
-        <v>-0.01098144095991416</v>
+        <v>-0.01098134849658494</v>
       </c>
     </row>
     <row r="415">
@@ -31918,7 +31918,7 @@
         <v>-0.1623440209149758</v>
       </c>
       <c r="L418" t="n">
-        <v>-0.1788915105774531</v>
+        <v>-0.1788915980733415</v>
       </c>
       <c r="M418" t="n">
         <v>0.01202449407955553</v>
@@ -31927,10 +31927,10 @@
         <v>0.1361775260842917</v>
       </c>
       <c r="O418" t="n">
-        <v>2.937481169536796</v>
+        <v>2.937480918039354</v>
       </c>
       <c r="P418" t="n">
-        <v>0.5790873821618918</v>
+        <v>0.5790873485417145</v>
       </c>
     </row>
     <row r="419">
@@ -31976,7 +31976,7 @@
         <v>-0.198748650829613</v>
       </c>
       <c r="L419" t="n">
-        <v>-0.157962072078681</v>
+        <v>-0.1579621441566648</v>
       </c>
       <c r="M419" t="n">
         <v>-0.01061792866860856</v>
@@ -32092,19 +32092,19 @@
         <v>-0.1128775461270379</v>
       </c>
       <c r="L421" t="n">
-        <v>-0.1379213701781223</v>
+        <v>-0.1379213167126787</v>
       </c>
       <c r="M421" t="n">
         <v>-0.05826963357897263</v>
       </c>
       <c r="N421" t="n">
-        <v>0.0455895778830826</v>
+        <v>0.04558949923251743</v>
       </c>
       <c r="O421" t="n">
-        <v>1.004824350530337</v>
+        <v>1.004824495108294</v>
       </c>
       <c r="P421" t="n">
-        <v>0.2609332865640837</v>
+        <v>0.2609333168748278</v>
       </c>
     </row>
     <row r="422">
@@ -32150,7 +32150,7 @@
         <v>0.02034724468716909</v>
       </c>
       <c r="L422" t="n">
-        <v>-0.1045188627510594</v>
+        <v>-0.1045189407607178</v>
       </c>
       <c r="M422" t="n">
         <v>-0.08401989590108405</v>
@@ -32159,10 +32159,10 @@
         <v>-0.2318340879367354</v>
       </c>
       <c r="O422" t="n">
-        <v>0.03071823137941854</v>
+        <v>0.03071833473061036</v>
       </c>
       <c r="P422" t="n">
-        <v>0.01013631835810869</v>
+        <v>0.01013635212058173</v>
       </c>
     </row>
     <row r="423">
@@ -32333,10 +32333,10 @@
         <v>0.01041722120705213</v>
       </c>
       <c r="O425" t="n">
-        <v>0.1632624404643965</v>
+        <v>0.1632625326959716</v>
       </c>
       <c r="P425" t="n">
-        <v>0.05170168224069083</v>
+        <v>0.05170171003610968</v>
       </c>
     </row>
     <row r="426">
@@ -32388,13 +32388,13 @@
         <v>-0.1093540379085588</v>
       </c>
       <c r="N426" t="n">
-        <v>-0.186973638101449</v>
+        <v>-0.1869737238396298</v>
       </c>
       <c r="O426" t="n">
-        <v>-0.1121568781900733</v>
+        <v>-0.1121566737021706</v>
       </c>
       <c r="P426" t="n">
-        <v>-0.03887749870905022</v>
+        <v>-0.03887742492052282</v>
       </c>
     </row>
     <row r="427">
@@ -32446,13 +32446,13 @@
         <v>-0.1634019811570314</v>
       </c>
       <c r="N427" t="n">
-        <v>-0.2362580011660514</v>
+        <v>-0.2362579154196113</v>
       </c>
       <c r="O427" t="n">
-        <v>-0.3044302884984075</v>
+        <v>-0.3044303596204112</v>
       </c>
       <c r="P427" t="n">
-        <v>-0.1139731405917915</v>
+        <v>-0.1139731707905417</v>
       </c>
     </row>
     <row r="428">
@@ -32565,10 +32565,10 @@
         <v>-0.3167791799257963</v>
       </c>
       <c r="O429" t="n">
-        <v>-0.0477492892812208</v>
+        <v>-0.04774937133783064</v>
       </c>
       <c r="P429" t="n">
-        <v>-0.01617670445637098</v>
+        <v>-0.01617673271545783</v>
       </c>
     </row>
     <row r="430">
@@ -32788,19 +32788,19 @@
         <v>-0.03726971874334062</v>
       </c>
       <c r="L433" t="n">
-        <v>-0.05389764423032817</v>
+        <v>-0.05389774285324422</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.08337987424762783</v>
+        <v>-0.0833797816754549</v>
       </c>
       <c r="N433" t="n">
-        <v>-0.2384682373356829</v>
+        <v>-0.2384683012322675</v>
       </c>
       <c r="O433" t="n">
-        <v>0.2179876489961623</v>
+        <v>0.2179878124471177</v>
       </c>
       <c r="P433" t="n">
-        <v>0.06794190495224472</v>
+        <v>0.06794195272397086</v>
       </c>
     </row>
     <row r="434">
@@ -33023,16 +33023,16 @@
         <v>-0.119892097291797</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.04962096407022443</v>
+        <v>-0.04962103224418057</v>
       </c>
       <c r="N437" t="n">
         <v>-0.1922551898353863</v>
       </c>
       <c r="O437" t="n">
-        <v>-0.03719025051024616</v>
+        <v>-0.03719032047926107</v>
       </c>
       <c r="P437" t="n">
-        <v>-0.01255368572933246</v>
+        <v>-0.01255370964913161</v>
       </c>
     </row>
     <row r="438">
@@ -33139,16 +33139,16 @@
         <v>-0.1694910195251369</v>
       </c>
       <c r="M439" t="n">
-        <v>-0.1861765492517014</v>
+        <v>-0.1861764889909578</v>
       </c>
       <c r="N439" t="n">
-        <v>-0.2665321506961486</v>
+        <v>-0.2665322485924208</v>
       </c>
       <c r="O439" t="n">
-        <v>-0.0931233267914291</v>
+        <v>-0.09312310230407661</v>
       </c>
       <c r="P439" t="n">
-        <v>-0.03205783149759656</v>
+        <v>-0.0320577516297883</v>
       </c>
     </row>
     <row r="440">
@@ -33255,16 +33255,16 @@
         <v>-0.0902473501412514</v>
       </c>
       <c r="M441" t="n">
-        <v>-0.2484744682471993</v>
+        <v>-0.2484744183743901</v>
       </c>
       <c r="N441" t="n">
-        <v>-0.2772256355617143</v>
+        <v>-0.2772256816915362</v>
       </c>
       <c r="O441" t="n">
-        <v>-0.1685927206516806</v>
+        <v>-0.1685926596131598</v>
       </c>
       <c r="P441" t="n">
-        <v>-0.05968952486606671</v>
+        <v>-0.05968950185481803</v>
       </c>
     </row>
     <row r="442">
@@ -33435,10 +33435,10 @@
         <v>-0.03780451315458433</v>
       </c>
       <c r="O444" t="n">
-        <v>0.0551561323281613</v>
+        <v>0.05515634591181917</v>
       </c>
       <c r="P444" t="n">
-        <v>0.01805734702156903</v>
+        <v>0.0180574157129505</v>
       </c>
     </row>
     <row r="445">
@@ -33490,7 +33490,7 @@
         <v>-0.07555415301769364</v>
       </c>
       <c r="N445" t="n">
-        <v>-0.1245912812813735</v>
+        <v>-0.1245912123667794</v>
       </c>
       <c r="O445" t="n">
         <v>-0.3532955318666364</v>
@@ -33551,10 +33551,10 @@
         <v>-0.09428679154934949</v>
       </c>
       <c r="O446" t="n">
-        <v>0.2896627634365374</v>
+        <v>0.289662665558202</v>
       </c>
       <c r="P446" t="n">
-        <v>0.08849236435401142</v>
+        <v>0.08849233681714241</v>
       </c>
     </row>
     <row r="447">
@@ -33606,13 +33606,13 @@
         <v>-0.05996608071961929</v>
       </c>
       <c r="N447" t="n">
-        <v>-0.2383476408857937</v>
+        <v>-0.2383475925678752</v>
       </c>
       <c r="O447" t="n">
-        <v>-0.3358158605658607</v>
+        <v>-0.3358157870803609</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.1275052276581824</v>
+        <v>-0.1275051954805034</v>
       </c>
     </row>
     <row r="448">
@@ -33719,7 +33719,7 @@
         <v>-0.1096034285959018</v>
       </c>
       <c r="M449" t="n">
-        <v>-0.2045683899301153</v>
+        <v>-0.204568478657343</v>
       </c>
       <c r="N449" t="n">
         <v>-0.2120597431443901</v>
@@ -33774,19 +33774,19 @@
         <v>0.01227429866780305</v>
       </c>
       <c r="L450" t="n">
-        <v>-0.2052037670082806</v>
+        <v>-0.2052036982172852</v>
       </c>
       <c r="M450" t="n">
-        <v>-0.1728074100223856</v>
+        <v>-0.172807484535581</v>
       </c>
       <c r="N450" t="n">
-        <v>-0.1808441666181989</v>
+        <v>-0.180844239690532</v>
       </c>
       <c r="O450" t="n">
-        <v>-0.1056139455167785</v>
+        <v>-0.1056138584063728</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.0365222872172245</v>
+        <v>-0.03652225593731973</v>
       </c>
     </row>
     <row r="451">
@@ -33835,10 +33835,10 @@
         <v>-0.2187847862794552</v>
       </c>
       <c r="M451" t="n">
-        <v>-0.08194681701511186</v>
+        <v>-0.08194676080690233</v>
       </c>
       <c r="N451" t="n">
-        <v>-0.1397562482344353</v>
+        <v>-0.1397563469389558</v>
       </c>
       <c r="O451" t="n">
         <v>0.3029727963628843</v>
@@ -33948,19 +33948,19 @@
         <v>0.02517086882988862</v>
       </c>
       <c r="L453" t="n">
-        <v>-0.1667442337021434</v>
+        <v>-0.1667442954339245</v>
       </c>
       <c r="M453" t="n">
         <v>-0.1764918043373542</v>
       </c>
       <c r="N453" t="n">
-        <v>-0.313825288541981</v>
+        <v>-0.3138253304041354</v>
       </c>
       <c r="O453" t="n">
-        <v>-0.1050279004207304</v>
+        <v>-0.1050276867758276</v>
       </c>
       <c r="P453" t="n">
-        <v>-0.03631189406392843</v>
+        <v>-0.03631181738107792</v>
       </c>
     </row>
     <row r="454">
@@ -34015,10 +34015,10 @@
         <v>-0.398575092152098</v>
       </c>
       <c r="O454" t="n">
-        <v>-0.1399847427566674</v>
+        <v>-0.1399846628062453</v>
       </c>
       <c r="P454" t="n">
-        <v>-0.04902583502262103</v>
+        <v>-0.04902580555384783</v>
       </c>
     </row>
     <row r="455">
@@ -34070,13 +34070,13 @@
         <v>-0.1736192277440284</v>
       </c>
       <c r="N455" t="n">
-        <v>-0.1789699922000842</v>
+        <v>-0.1789699118391164</v>
       </c>
       <c r="O455" t="n">
-        <v>0.1887139297861726</v>
+        <v>0.1887140140132622</v>
       </c>
       <c r="P455" t="n">
-        <v>0.05931661474912442</v>
+        <v>0.05931663976864376</v>
       </c>
     </row>
     <row r="456">
@@ -34244,13 +34244,13 @@
         <v>-0.1670511989958759</v>
       </c>
       <c r="N458" t="n">
-        <v>-0.2494132596140552</v>
+        <v>-0.2494134308591036</v>
       </c>
       <c r="O458" t="n">
-        <v>-0.07816453461687833</v>
+        <v>-0.07816440546722758</v>
       </c>
       <c r="P458" t="n">
-        <v>-0.026764808829152</v>
+        <v>-0.026764763378894</v>
       </c>
     </row>
     <row r="459">
@@ -34296,19 +34296,19 @@
         <v>-0.1343041569430897</v>
       </c>
       <c r="L459" t="n">
-        <v>-0.1619656788942767</v>
+        <v>-0.1619657674731275</v>
       </c>
       <c r="M459" t="n">
-        <v>-0.1298981563626099</v>
+        <v>-0.1298980608750705</v>
       </c>
       <c r="N459" t="n">
         <v>-0.1477382919627511</v>
       </c>
       <c r="O459" t="n">
-        <v>-0.5014770430191058</v>
+        <v>-0.5014769803278669</v>
       </c>
       <c r="P459" t="n">
-        <v>-0.2070817980873384</v>
+        <v>-0.2070817648498037</v>
       </c>
     </row>
     <row r="460">
@@ -34360,13 +34360,13 @@
         <v>-0.158060465418071</v>
       </c>
       <c r="N460" t="n">
-        <v>-0.1611585051969376</v>
+        <v>-0.1611584212524069</v>
       </c>
       <c r="O460" t="n">
-        <v>-0.01506232660534768</v>
+        <v>-0.01506255806747681</v>
       </c>
       <c r="P460" t="n">
-        <v>-0.005046196805020498</v>
+        <v>-0.005046274743672474</v>
       </c>
     </row>
     <row r="461">
@@ -34415,16 +34415,16 @@
         <v>-0.1788581908569048</v>
       </c>
       <c r="M461" t="n">
-        <v>-0.1926358368363721</v>
+        <v>-0.1926358935133373</v>
       </c>
       <c r="N461" t="n">
         <v>-0.3514105306326483</v>
       </c>
       <c r="O461" t="n">
-        <v>-0.2668382256522119</v>
+        <v>-0.266838178914512</v>
       </c>
       <c r="P461" t="n">
-        <v>-0.09829058449423866</v>
+        <v>-0.0982905653334728</v>
       </c>
     </row>
     <row r="462">
@@ -34476,7 +34476,7 @@
         <v>-0.2979558272487902</v>
       </c>
       <c r="N462" t="n">
-        <v>-0.2679919178873394</v>
+        <v>-0.2679919811510727</v>
       </c>
       <c r="O462" t="n">
         <v>0.3958507508289946</v>
@@ -34528,7 +34528,7 @@
         <v>-0.1494030811380704</v>
       </c>
       <c r="L463" t="n">
-        <v>-0.2962373872039168</v>
+        <v>-0.2962373281016941</v>
       </c>
       <c r="M463" t="n">
         <v>-0.08075569201472532</v>
@@ -34537,10 +34537,10 @@
         <v>-0.05077522979945293</v>
       </c>
       <c r="O463" t="n">
-        <v>0.6131118234650623</v>
+        <v>0.6131121339785199</v>
       </c>
       <c r="P463" t="n">
-        <v>0.1727933411256013</v>
+        <v>0.1727934163772746</v>
       </c>
     </row>
     <row r="464">
@@ -34592,7 +34592,7 @@
         <v>-0.234045238226648</v>
       </c>
       <c r="N464" t="n">
-        <v>-0.07015648746229641</v>
+        <v>-0.07015654430612905</v>
       </c>
       <c r="O464" t="n">
         <v>0.7238190362026649</v>
@@ -34650,13 +34650,13 @@
         <v>-0.1330403922759891</v>
       </c>
       <c r="N465" t="n">
-        <v>-0.1518470835198353</v>
+        <v>-0.1518471557629103</v>
       </c>
       <c r="O465" t="n">
-        <v>-0.09871410122311908</v>
+        <v>-0.09871426437910424</v>
       </c>
       <c r="P465" t="n">
-        <v>-0.03405101139361211</v>
+        <v>-0.03405106968083949</v>
       </c>
     </row>
     <row r="466">
@@ -34708,13 +34708,13 @@
         <v>-0.2759156746943849</v>
       </c>
       <c r="N466" t="n">
-        <v>-0.1823520907228305</v>
+        <v>-0.1823520344308367</v>
       </c>
       <c r="O466" t="n">
-        <v>0.7494021449573294</v>
+        <v>0.7494022738010584</v>
       </c>
       <c r="P466" t="n">
-        <v>0.204933886390023</v>
+        <v>0.2049339159712091</v>
       </c>
     </row>
     <row r="467">
@@ -34766,13 +34766,13 @@
         <v>-0.1535441259241345</v>
       </c>
       <c r="N467" t="n">
-        <v>-0.07346726342405285</v>
+        <v>-0.07346736503050055</v>
       </c>
       <c r="O467" t="n">
-        <v>0.4657705855656424</v>
+        <v>0.4657703312742221</v>
       </c>
       <c r="P467" t="n">
-        <v>0.1359398467034607</v>
+        <v>0.1359397810133778</v>
       </c>
     </row>
     <row r="468">
@@ -34876,19 +34876,19 @@
         <v>-0.05986464265339153</v>
       </c>
       <c r="L469" t="n">
-        <v>-0.2195932606580587</v>
+        <v>-0.219593338333843</v>
       </c>
       <c r="M469" t="n">
-        <v>-0.2638576049555816</v>
+        <v>-0.2638575358413685</v>
       </c>
       <c r="N469" t="n">
         <v>-0.1803030234918634</v>
       </c>
       <c r="O469" t="n">
-        <v>2.200296081572228</v>
+        <v>2.20029640813302</v>
       </c>
       <c r="P469" t="n">
-        <v>0.4736580469644265</v>
+        <v>0.4736580970888429</v>
       </c>
     </row>
     <row r="470">
@@ -35108,7 +35108,7 @@
         <v>-0.1181364064919092</v>
       </c>
       <c r="L473" t="n">
-        <v>-0.08780034673889525</v>
+        <v>-0.08780027789827283</v>
       </c>
       <c r="M473" t="n">
         <v>-0.2693245187333724</v>
@@ -35117,10 +35117,10 @@
         <v>-0.2411875769173111</v>
       </c>
       <c r="O473" t="n">
-        <v>0.004113744055356916</v>
+        <v>0.004113910880244598</v>
       </c>
       <c r="P473" t="n">
-        <v>0.001369371982885337</v>
+        <v>0.001369427439193549</v>
       </c>
     </row>
     <row r="474">
@@ -35172,7 +35172,7 @@
         <v>-0.212074956609164</v>
       </c>
       <c r="N474" t="n">
-        <v>-0.2896531085750979</v>
+        <v>-0.2896531642815933</v>
       </c>
       <c r="O474" t="n">
         <v>-0.01693769261190758</v>
@@ -35285,10 +35285,10 @@
         <v>-0.1640444261594485</v>
       </c>
       <c r="O476" t="n">
-        <v>-0.04427937555115757</v>
+        <v>-0.04427929632532535</v>
       </c>
       <c r="P476" t="n">
-        <v>-0.01498316589401816</v>
+        <v>-0.01498313867589107</v>
       </c>
     </row>
     <row r="477">
@@ -35343,10 +35343,10 @@
         <v>-0.3107499764283711</v>
       </c>
       <c r="O477" t="n">
-        <v>0.3328061378419123</v>
+        <v>0.3328063046231784</v>
       </c>
       <c r="P477" t="n">
-        <v>0.1004973337449266</v>
+        <v>0.1004973796486595</v>
       </c>
     </row>
     <row r="478">
@@ -35685,16 +35685,16 @@
         <v>-0.1966206574035999</v>
       </c>
       <c r="M483" t="n">
-        <v>-0.323662968433346</v>
+        <v>-0.3236630118566031</v>
       </c>
       <c r="N483" t="n">
         <v>-0.4242393684736605</v>
       </c>
       <c r="O483" t="n">
-        <v>-0.2654670191650975</v>
+        <v>-0.2654669167300088</v>
       </c>
       <c r="P483" t="n">
-        <v>-0.09772878952791186</v>
+        <v>-0.09772874758551231</v>
       </c>
     </row>
     <row r="484">
@@ -35743,16 +35743,16 @@
         <v>-0.2190147843340067</v>
       </c>
       <c r="M484" t="n">
-        <v>-0.3858746089552807</v>
+        <v>-0.3858745359612017</v>
       </c>
       <c r="N484" t="n">
-        <v>-0.4098645894974026</v>
+        <v>-0.4098647243026259</v>
       </c>
       <c r="O484" t="n">
-        <v>-0.236136539430453</v>
+        <v>-0.2361364829660185</v>
       </c>
       <c r="P484" t="n">
-        <v>-0.08587571793711812</v>
+        <v>-0.08587569541323692</v>
       </c>
     </row>
     <row r="485">
@@ -35966,10 +35966,10 @@
         <v>-0.3294446338741981</v>
       </c>
       <c r="O488" t="n">
-        <v>0.02040522970718683</v>
+        <v>0.02040531220296637</v>
       </c>
       <c r="P488" t="n">
-        <v>0.00675599695181206</v>
+        <v>0.006756024082575474</v>
       </c>
     </row>
     <row r="489">
@@ -36018,10 +36018,10 @@
         <v>-0.3873427952703871</v>
       </c>
       <c r="M489" t="n">
-        <v>-0.3676994785203613</v>
+        <v>-0.3676994370540432</v>
       </c>
       <c r="N489" t="n">
-        <v>-0.5059454682074148</v>
+        <v>-0.5059454175750534</v>
       </c>
       <c r="O489" t="n">
         <v>-0.5874779826380307</v>
@@ -36137,13 +36137,13 @@
         <v>-0.5094408722337951</v>
       </c>
       <c r="N491" t="n">
-        <v>-0.5198414452349354</v>
+        <v>-0.5198414893568144</v>
       </c>
       <c r="O491" t="n">
-        <v>-0.4068644077031419</v>
+        <v>-0.4068643403756063</v>
       </c>
       <c r="P491" t="n">
-        <v>-0.159796160439833</v>
+        <v>-0.1597961286489842</v>
       </c>
     </row>
     <row r="492">
@@ -36198,10 +36198,10 @@
         <v>-0.4692349600861495</v>
       </c>
       <c r="O492" t="n">
-        <v>-0.5817664365974751</v>
+        <v>-0.5817664015704771</v>
       </c>
       <c r="P492" t="n">
-        <v>-0.2521641269416883</v>
+        <v>-0.2521641060646417</v>
       </c>
     </row>
     <row r="493">
@@ -36546,10 +36546,10 @@
         <v>-0.463881328286771</v>
       </c>
       <c r="O498" t="n">
-        <v>-0.1083277851205928</v>
+        <v>-0.1083275781613476</v>
       </c>
       <c r="P498" t="n">
-        <v>-0.03749776943069316</v>
+        <v>-0.03749769496434541</v>
       </c>
     </row>
     <row r="499">
@@ -36604,10 +36604,10 @@
         <v>-0.3793504552208443</v>
       </c>
       <c r="O499" t="n">
-        <v>0.007967201770391563</v>
+        <v>0.007966979983644817</v>
       </c>
       <c r="P499" t="n">
-        <v>0.002648712053751945</v>
+        <v>0.002648638514913371</v>
       </c>
     </row>
     <row r="500">

--- a/GICS_SubIndustry_Leaderboard.xlsx
+++ b/GICS_SubIndustry_Leaderboard.xlsx
@@ -613,19 +613,19 @@
         <v>0.1611362857634756</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>1.135995095195724</v>
+        <v>1.13599511963303</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>1.776062036070464</v>
+        <v>1.776062042149841</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>2.843098559795129</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>4.792445353111361</v>
+        <v>4.792445849145279</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.6562527423407825</v>
+        <v>0.6562527678088179</v>
       </c>
     </row>
     <row r="3">
@@ -672,16 +672,16 @@
         <v>0.5824624542498996</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>1.234606680848289</v>
+        <v>1.234606753360112</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>1.105879444231004</v>
+        <v>1.105879332132841</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>1.627481586668783</v>
+        <v>1.627481561856805</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>0.3791878779610726</v>
+        <v>0.3791878747768549</v>
       </c>
     </row>
     <row r="4">
@@ -731,13 +731,13 @@
         <v>0.7491323397931646</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>1.12332116747286</v>
+        <v>1.123321186636637</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0.6388333784040061</v>
+        <v>0.6388333746289914</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.1668709712389681</v>
+        <v>0.1668709712553395</v>
       </c>
     </row>
     <row r="5">
@@ -784,16 +784,16 @@
         <v>0.8230906753862651</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0.5693667357083815</v>
+        <v>0.5693667243038335</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.4790232891654376</v>
+        <v>0.4790232991463486</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>1.888526444943315</v>
+        <v>1.888526444595404</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0.3700407147772624</v>
+        <v>0.3700407154951907</v>
       </c>
     </row>
     <row r="6">
@@ -837,19 +837,19 @@
         <v>-0.05625481490445193</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.7089849324701604</v>
+        <v>0.7089849258969384</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.7730098298266573</v>
+        <v>0.7730098158686467</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>1.123632915290036</v>
+        <v>1.123632965348806</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>2.679417431847479</v>
+        <v>2.679417733544667</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.4242657483159481</v>
+        <v>0.4242657612309176</v>
       </c>
     </row>
     <row r="7">
@@ -893,19 +893,19 @@
         <v>0.06632184479918106</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.2676265084834067</v>
+        <v>0.2676265306688032</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.635143535147045</v>
+        <v>0.6351435912894826</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>1.279974832655826</v>
+        <v>1.279974812563025</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>5.498169316359065</v>
+        <v>5.498169288734808</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0.7076796056913733</v>
+        <v>0.7076796001643998</v>
       </c>
     </row>
     <row r="8">
@@ -952,16 +952,16 @@
         <v>0.4962477003521807</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.2367990016862977</v>
+        <v>0.2367990151753991</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.5271357574125285</v>
+        <v>0.5271357677078157</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>0.3977042048202042</v>
+        <v>0.3977042376796621</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.1136740082320829</v>
+        <v>0.1136740172537954</v>
       </c>
     </row>
     <row r="9">
@@ -1008,16 +1008,16 @@
         <v>0.2491079650085596</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.7074875405981268</v>
+        <v>0.7074875534042407</v>
       </c>
       <c r="N9" s="5" t="n">
         <v>1.344335180586081</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>3.25908064530097</v>
+        <v>3.259081269295949</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.6180563032584729</v>
+        <v>0.6180563838628848</v>
       </c>
     </row>
     <row r="10">
@@ -1064,16 +1064,16 @@
         <v>0.2537112662870771</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0.5355036982021357</v>
+        <v>0.5355035967849338</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>0.5230292245903789</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.9411993345148408</v>
+        <v>0.9411996586903901</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.2474506622661323</v>
+        <v>0.2474507317065333</v>
       </c>
     </row>
     <row r="11">
@@ -1120,16 +1120,16 @@
         <v>0.4801074901454355</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.4280212298803533</v>
+        <v>0.4280212877580316</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.7924797307831595</v>
+        <v>0.7924798365563094</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>1.050076582785608</v>
+        <v>1.050076575283847</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0.2657877459482294</v>
+        <v>0.265787748974427</v>
       </c>
     </row>
     <row r="12">
@@ -1173,7 +1173,7 @@
         <v>0.129754070939609</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.3272001357166334</v>
+        <v>0.327200228296376</v>
       </c>
       <c r="M12" s="5" t="n">
         <v>0.408440436570068</v>
@@ -1182,10 +1182,10 @@
         <v>0.6172892690344007</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>1.031184725343354</v>
+        <v>1.03118494218465</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.2664356887566306</v>
+        <v>0.2664357338231942</v>
       </c>
     </row>
     <row r="13">
@@ -1238,10 +1238,10 @@
         <v>0.3099003465012313</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>0.5173559309803064</v>
+        <v>0.517355834252994</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>0.1491123410945128</v>
+        <v>0.1491123166769173</v>
       </c>
     </row>
     <row r="14">
@@ -1344,16 +1344,16 @@
         <v>0.2872890337467728</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>0.552428459128981</v>
+        <v>0.5524284810323588</v>
       </c>
       <c r="N15" s="5" t="n">
         <v>0.718196785641525</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>4.703960932252484</v>
+        <v>4.703960734206651</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>0.576745972627247</v>
+        <v>0.5767459439973092</v>
       </c>
     </row>
     <row r="16">
@@ -1400,16 +1400,16 @@
         <v>0.7236922496064682</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.3462912839507295</v>
+        <v>0.346291289775193</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.4298214892911658</v>
+        <v>0.4298214451956857</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>-0.1477508591182217</v>
+        <v>-0.1477508212113302</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>-0.05259420113846458</v>
+        <v>-0.05259418850850159</v>
       </c>
     </row>
     <row r="17">
@@ -1456,16 +1456,16 @@
         <v>0.2079871053134983</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.5032704459868829</v>
+        <v>0.5032704957300124</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.9980903314394459</v>
+        <v>0.9980902705120139</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>5.30671299549694</v>
+        <v>5.306712983587976</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.8196058049688695</v>
+        <v>0.8196058009637825</v>
       </c>
     </row>
     <row r="18">
@@ -1571,13 +1571,13 @@
         <v>0.4323574595920114</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.2314413721640167</v>
+        <v>0.23144129170238</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>1.87425914423009</v>
+        <v>1.874258267546017</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>0.421811340577299</v>
+        <v>0.4218111960206878</v>
       </c>
     </row>
     <row r="20">
@@ -1630,10 +1630,10 @@
         <v>0.2486430715178712</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.6431598413871431</v>
+        <v>0.6431598651449268</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0.1554135540260133</v>
+        <v>0.1554135635749139</v>
       </c>
     </row>
     <row r="21">
@@ -1683,13 +1683,13 @@
         <v>0.3903728939088826</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.4064290554197965</v>
+        <v>0.4064289551146021</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0.4745759090294986</v>
+        <v>0.474575925213734</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0.1378959800784044</v>
+        <v>0.1378959853573027</v>
       </c>
     </row>
     <row r="22">
@@ -1736,16 +1736,16 @@
         <v>0.07902371385883494</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0.3703703143167832</v>
+        <v>0.3703703705409384</v>
       </c>
       <c r="N22" s="5" t="n">
         <v>0.4251086870403529</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0.1407654396173422</v>
+        <v>0.140765458061176</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.04474192825204903</v>
+        <v>0.04474193491560574</v>
       </c>
     </row>
     <row r="23">
@@ -1789,19 +1789,19 @@
         <v>0.1035879214547338</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.1201876377957416</v>
+        <v>0.120187626135129</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>0.178499860183519</v>
+        <v>0.1784998458780548</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>0.435805289664831</v>
+        <v>0.4358053420850644</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>0.4520246468327899</v>
+        <v>0.4520246115652254</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0.1072234599962167</v>
+        <v>0.1072234539796979</v>
       </c>
     </row>
     <row r="24">
@@ -1854,10 +1854,10 @@
         <v>0.3992848312151301</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>2.488616954249843</v>
+        <v>2.488617091454167</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.4791406092015087</v>
+        <v>0.4791406317640437</v>
       </c>
     </row>
     <row r="25">
@@ -1907,13 +1907,13 @@
         <v>0.3492842643660561</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0.4475307077557258</v>
+        <v>0.4475306483594685</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>3.487115043562966</v>
+        <v>3.487115422554595</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0.5652648119736532</v>
+        <v>0.5652648549054998</v>
       </c>
     </row>
     <row r="26">
@@ -1966,10 +1966,10 @@
         <v>0.2195557880879589</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>1.3107448967063</v>
+        <v>1.310744943598787</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.3192541942392511</v>
+        <v>0.319254203926353</v>
       </c>
     </row>
     <row r="27">
@@ -2019,13 +2019,13 @@
         <v>0.06876840694591846</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>-0.03770257371681929</v>
+        <v>-0.03770246397862298</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>-0.03211404205222101</v>
+        <v>-0.03211382001918706</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>-0.0108213601185132</v>
+        <v>-0.01082128447932729</v>
       </c>
     </row>
     <row r="28">
@@ -2069,19 +2069,19 @@
         <v>0.03337461176149877</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.2730194635512734</v>
+        <v>0.2730194910669267</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.1701408979656686</v>
+        <v>0.17014092243723</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0.2246500135427918</v>
+        <v>0.2246500165708508</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>0.5883880484912412</v>
+        <v>0.5883880927134186</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.166260573825659</v>
+        <v>0.166260585048141</v>
       </c>
     </row>
     <row r="29">
@@ -2125,19 +2125,19 @@
         <v>0.03050347073768656</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.1629314261573414</v>
+        <v>0.1629313480035408</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>0.2404908466300451</v>
+        <v>0.2404908178109177</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>0.2689222118196166</v>
+        <v>0.268922177827581</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>1.16619897508292</v>
+        <v>1.166198606468092</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>0.2792219440197703</v>
+        <v>0.2792218748759335</v>
       </c>
     </row>
     <row r="30">
@@ -2184,16 +2184,16 @@
         <v>0.03763065741680438</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.308161021976088</v>
+        <v>0.3081610021354772</v>
       </c>
       <c r="N30" s="5" t="n">
         <v>0.3488645738608498</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>1.430234596080491</v>
+        <v>1.430234821879625</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.331847024611019</v>
+        <v>0.3318470622395644</v>
       </c>
     </row>
     <row r="31">
@@ -2240,16 +2240,16 @@
         <v>0.1669552052099153</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>0.1963375254673886</v>
+        <v>0.196337590387483</v>
       </c>
       <c r="N31" s="5" t="n">
-        <v>0.2448172274149325</v>
+        <v>0.2448172382009014</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>0.5472489017068604</v>
+        <v>0.5472488986969707</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>0.1560118549827728</v>
+        <v>0.1560118535296945</v>
       </c>
     </row>
     <row r="32">
@@ -2302,10 +2302,10 @@
         <v>0.1530009396324745</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>2.412658137002376</v>
+        <v>2.41265774700231</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>0.505558360901206</v>
+        <v>0.5055583035492475</v>
       </c>
     </row>
     <row r="33">
@@ -2352,16 +2352,16 @@
         <v>-0.03778196483602747</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0.2887268515227807</v>
+        <v>0.288726767907123</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>0.3776202483378501</v>
+        <v>0.3776202747358413</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>0.1883276663253163</v>
+        <v>0.1883276733986721</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>0.04716159084153097</v>
+        <v>0.04716159388394936</v>
       </c>
     </row>
     <row r="34">
@@ -2408,16 +2408,16 @@
         <v>0.02763525745446501</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.2676132726687844</v>
+        <v>0.2676132267020821</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>0.1083892527592326</v>
+        <v>0.1083892659905436</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>0.2988533786614906</v>
+        <v>0.2988532174299992</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.07802839510083359</v>
+        <v>0.07802835090011546</v>
       </c>
     </row>
     <row r="35">
@@ -2461,19 +2461,19 @@
         <v>0.06847335084320731</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-0.06955323009480925</v>
+        <v>-0.06955320489408323</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.2881244356883932</v>
+        <v>0.2881244575966404</v>
       </c>
       <c r="N35" s="5" t="n">
         <v>0.2866295483970352</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>0.2663842779345755</v>
+        <v>0.2663842156878057</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>0.0791663989355928</v>
+        <v>0.07916638080420292</v>
       </c>
     </row>
     <row r="36">
@@ -2520,10 +2520,10 @@
         <v>0.203705769793442</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>0.1918145121708712</v>
+        <v>0.1918145721651607</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>0.1713346533274459</v>
+        <v>0.1713346018533013</v>
       </c>
       <c r="O36" s="5" t="n">
         <v>1.294389026098374</v>
@@ -2579,13 +2579,13 @@
         <v>0.09853441378123666</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>0.09449412124323227</v>
+        <v>0.09449415846471927</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>0.3041636902177664</v>
+        <v>0.3041637289847425</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>0.09067622963153776</v>
+        <v>0.09067623951461419</v>
       </c>
     </row>
     <row r="38">
@@ -2632,16 +2632,16 @@
         <v>0.1507304287265664</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.230933453162545</v>
+        <v>0.2309334965926568</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0.1711375045893588</v>
+        <v>0.1711374462996843</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>1.16014933364441</v>
+        <v>1.160149572646857</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.2922029019514403</v>
+        <v>0.292202953194064</v>
       </c>
     </row>
     <row r="39">
@@ -2685,19 +2685,19 @@
         <v>0.00725429063774965</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.1639572976610746</v>
+        <v>0.1639572787605831</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>0.2553625596039029</v>
+        <v>0.2553625834104431</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>0.1694848526217878</v>
+        <v>0.1694848767784324</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>0.545287986553437</v>
+        <v>0.5452879157879066</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>0.1485006903529539</v>
+        <v>0.1485006696478948</v>
       </c>
     </row>
     <row r="40">
@@ -2747,7 +2747,7 @@
         <v>0.1244247819090012</v>
       </c>
       <c r="N40" s="5" t="n">
-        <v>0.1214635478841306</v>
+        <v>0.1214634448081811</v>
       </c>
       <c r="O40" s="5" t="n">
         <v>0.002421455505570158</v>
@@ -2797,19 +2797,19 @@
         <v>-0.09384583395610002</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.08077200860021838</v>
+        <v>0.08077198324626239</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>0.1937736633485231</v>
+        <v>0.1937736327906197</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>0.4194809240766039</v>
+        <v>0.4194809759685037</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>1.446053978928094</v>
+        <v>1.446054145708345</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>0.3365951607589767</v>
+        <v>0.3365951900406638</v>
       </c>
     </row>
     <row r="42">
@@ -2853,19 +2853,19 @@
         <v>-0.1283311911055905</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.145548471188405</v>
+        <v>0.1455483841963872</v>
       </c>
       <c r="M42" s="5" t="n">
         <v>0.457045341361257</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0.1428804776542043</v>
+        <v>0.1428805642414968</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>1.046613438252552</v>
+        <v>1.046613715919508</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>0.269634184480029</v>
+        <v>0.2696342418977182</v>
       </c>
     </row>
     <row r="43">
@@ -2912,16 +2912,16 @@
         <v>0.05216118476578222</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>0.1253047850350286</v>
+        <v>0.1253048060386016</v>
       </c>
       <c r="N43" s="5" t="n">
-        <v>0.2603639148915777</v>
+        <v>0.2603639023430751</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>0.5229092986276365</v>
+        <v>0.5229092296383803</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>0.143142543568572</v>
+        <v>0.1431425283302209</v>
       </c>
     </row>
     <row r="44">
@@ -2965,19 +2965,19 @@
         <v>-0.003658602139326728</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.2581830065738749</v>
+        <v>0.2581829874081634</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.09128394028878845</v>
+        <v>0.09128391336841352</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>0.1346314625171394</v>
+        <v>0.1346314421823871</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>3.343271946856845</v>
+        <v>3.343271856005815</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.5311732267059254</v>
+        <v>0.5311732108894393</v>
       </c>
     </row>
     <row r="45">
@@ -3021,19 +3021,19 @@
         <v>0.000788309155685063</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.1178547823014088</v>
+        <v>0.1178548128308292</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0.1289307660098923</v>
+        <v>0.1289307915520649</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0.2277457994740709</v>
+        <v>0.2277458659649126</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.287956441843437</v>
+        <v>0.2879564473421303</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>0.07801084329856126</v>
+        <v>0.07801084178521761</v>
       </c>
     </row>
     <row r="46">
@@ -3083,7 +3083,7 @@
         <v>0.04456567666361486</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>0.2269470856457282</v>
+        <v>0.2269470874568588</v>
       </c>
       <c r="O46" s="5" t="n">
         <v>0.8811783979006572</v>
@@ -3133,19 +3133,19 @@
         <v>-0.03793744171677688</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.07173933472198549</v>
+        <v>0.07173936219883489</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>0.1018616751147575</v>
+        <v>0.1018616952312488</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>0.3710984835377759</v>
+        <v>0.3710985812807477</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>0.4460601117848496</v>
+        <v>0.4460601183322078</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>0.1170248523911023</v>
+        <v>0.1170248508132653</v>
       </c>
     </row>
     <row r="48">
@@ -3192,16 +3192,16 @@
         <v>0.2294357092346662</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>0.074809375812805</v>
+        <v>0.07480925521084458</v>
       </c>
       <c r="N48" s="5" t="n">
         <v>-0.09383776052038328</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>-0.2570556023425523</v>
+        <v>-0.2570556599666469</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>-0.09429776931155887</v>
+        <v>-0.09429779272752037</v>
       </c>
     </row>
     <row r="49">
@@ -3251,7 +3251,7 @@
         <v>0.4337045802564258</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>0.3509413357821056</v>
+        <v>0.3509414085107104</v>
       </c>
       <c r="O49" s="5" t="n">
         <v>0.86810302734375</v>
@@ -3301,19 +3301,19 @@
         <v>0.02697379570456068</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>0.2256717595414048</v>
+        <v>0.2256717661335862</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.0590494509593182</v>
+        <v>0.05904943109660141</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>0.09929145502530783</v>
+        <v>0.09929146583908277</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>0.9410226466324323</v>
+        <v>0.941022705219999</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.2269409126908235</v>
+        <v>0.2269409180267827</v>
       </c>
     </row>
     <row r="51">
@@ -3357,19 +3357,19 @@
         <v>0.01506921076567162</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0.1920737853456493</v>
+        <v>0.1920738248225055</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>0.1665946528846152</v>
+        <v>0.1665946211136093</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>0.04677861950918405</v>
+        <v>0.04677859612125179</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>1.006228727780588</v>
+        <v>1.006228998779529</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>0.256416933930061</v>
+        <v>0.2564169874812465</v>
       </c>
     </row>
     <row r="52">
@@ -3413,19 +3413,19 @@
         <v>-0.06440128711594284</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0.06287460727155858</v>
+        <v>0.06287465293964478</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>0.2946162782306139</v>
+        <v>0.2946162173492747</v>
       </c>
       <c r="N52" s="5" t="n">
         <v>0.1956823872058243</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>0.5612225825139924</v>
+        <v>0.5612226371251281</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>0.1599460034764316</v>
+        <v>0.1599460167188484</v>
       </c>
     </row>
     <row r="53">
@@ -3469,19 +3469,19 @@
         <v>0.1404583914889476</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0.209351116373003</v>
+        <v>0.209351164126953</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>-0.002047235875621833</v>
+        <v>-0.002047171301880535</v>
       </c>
       <c r="N53" s="5" t="n">
         <v>-0.1090501706381427</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>0.104120340278563</v>
+        <v>0.1041203425004413</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>0.03296942823560312</v>
+        <v>0.03296942774369216</v>
       </c>
     </row>
     <row r="54">
@@ -3528,7 +3528,7 @@
         <v>0.1516783499490315</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>0.06042398760529932</v>
+        <v>0.06042395407815604</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>-0.07126485992882758</v>
@@ -3581,19 +3581,19 @@
         <v>0.05216260424951125</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>0.1212210824508976</v>
+        <v>0.1212210152152568</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>0.08555029564436416</v>
+        <v>0.08555040033486949</v>
       </c>
       <c r="N55" s="5" t="n">
         <v>0.0521284213946666</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>0.3164649644516236</v>
+        <v>0.3164650621936774</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>0.0909396677841872</v>
+        <v>0.09093968651863334</v>
       </c>
     </row>
     <row r="56">
@@ -3637,19 +3637,19 @@
         <v>-0.02450962808429602</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0.01654772460133813</v>
+        <v>0.01654779161921027</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.137297412598987</v>
+        <v>0.1372974964837717</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>0.2292225584710019</v>
+        <v>0.2292224604777728</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>0.2374060016876662</v>
+        <v>0.2374062002923845</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.07358740053254609</v>
+        <v>0.07358745796977417</v>
       </c>
     </row>
     <row r="57">
@@ -3696,10 +3696,10 @@
         <v>-0.1876475009569749</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>0.2936224923920017</v>
+        <v>0.2936223809829337</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>0.3151372830978185</v>
+        <v>0.3151371679521506</v>
       </c>
       <c r="O57" s="5" t="n">
         <v>-0.3222818137273923</v>
@@ -3755,13 +3755,13 @@
         <v>0.08695517569313305</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>0.1936807391751014</v>
+        <v>0.1936808648214865</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>0.501846094780656</v>
+        <v>0.5018461942282939</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>0.145183661360837</v>
+        <v>0.1451836866376852</v>
       </c>
     </row>
     <row r="59">
@@ -3802,22 +3802,22 @@
         <v>-0.02344996077767455</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0.05010041228893761</v>
+        <v>0.05010044699205304</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0.1113951354663144</v>
+        <v>0.1113951743577798</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0.02249557856035896</v>
+        <v>0.02249551386470735</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>0.07489150881458025</v>
+        <v>0.07489154297326069</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>-0.08490717619989334</v>
+        <v>-0.08490714124652265</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>-0.03222340220525699</v>
+        <v>-0.03222339044106207</v>
       </c>
     </row>
     <row r="60">
@@ -3861,19 +3861,19 @@
         <v>0.04684627540942951</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0.1383982618248219</v>
+        <v>0.1383982901438668</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>-0.01626454793273557</v>
+        <v>-0.01626459949079712</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0.07632261076652389</v>
+        <v>0.07632263093956107</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>1.568860003474444</v>
+        <v>1.568859797032614</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>0.369512668235535</v>
+        <v>0.3695126320122847</v>
       </c>
     </row>
     <row r="61">
@@ -3923,13 +3923,13 @@
         <v>0.1128064765580315</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>0.1927306929111746</v>
+        <v>0.1927306429365847</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>0.1143584934610892</v>
+        <v>0.1143584358679423</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>0.02532208659688227</v>
+        <v>0.02532207024538746</v>
       </c>
     </row>
     <row r="62">
@@ -3976,16 +3976,16 @@
         <v>-0.07485885562540623</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.147737088676175</v>
+        <v>0.147737131960278</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>0.03332293971477213</v>
+        <v>0.03332297163450043</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>0.8347630129733244</v>
+        <v>0.8347632176987883</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>0.2235858339342112</v>
+        <v>0.2235858787232121</v>
       </c>
     </row>
     <row r="63">
@@ -4032,16 +4032,16 @@
         <v>0.1554399702257946</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>0.0496829242788831</v>
+        <v>0.0496828929777603</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>0.2409736879865052</v>
+        <v>0.2409736393480502</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>1.124681436246375</v>
+        <v>1.124681473936281</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>0.27957578785452</v>
+        <v>0.2795757971955752</v>
       </c>
     </row>
     <row r="64">
@@ -4088,16 +4088,16 @@
         <v>0.1370666309873171</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>0.03076302502344075</v>
+        <v>0.03076303921265861</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>0.1350783878383978</v>
+        <v>0.1350784311678422</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>1.333618265562591</v>
+        <v>1.333618387949937</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.3202908434165653</v>
+        <v>0.3202908660805077</v>
       </c>
     </row>
     <row r="65">
@@ -4141,19 +4141,19 @@
         <v>0.1282057872582762</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>0.04543644326323796</v>
+        <v>0.0454364624796977</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>-0.05042204907365024</v>
+        <v>-0.05042208372596298</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>-0.03245140858514151</v>
+        <v>-0.0324514215990617</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>0.5627342864427808</v>
+        <v>0.5627343863799014</v>
       </c>
       <c r="P65" s="5" t="n">
-        <v>0.1431340476665566</v>
+        <v>0.1431340729030341</v>
       </c>
     </row>
     <row r="66">
@@ -4197,19 +4197,19 @@
         <v>-0.03000101226702949</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>0.02878730510338579</v>
+        <v>0.0287872850005938</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.06846277650315573</v>
+        <v>0.06846275399622266</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>0.1756303886490783</v>
+        <v>0.1756304881364769</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>0.6672716924056156</v>
+        <v>0.667271814693844</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>0.1764512032025165</v>
+        <v>0.1764512294225279</v>
       </c>
     </row>
     <row r="67">
@@ -4256,16 +4256,16 @@
         <v>0.04369223358288332</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0.07300382240370151</v>
+        <v>0.07300388797555768</v>
       </c>
       <c r="N67" s="5" t="n">
         <v>0.2073200768189316</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>0.2934254724820111</v>
+        <v>0.2934252819238015</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>0.08954992850988064</v>
+        <v>0.08954987500268885</v>
       </c>
     </row>
     <row r="68">
@@ -4312,16 +4312,16 @@
         <v>0.07845462617466303</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-0.06357211218830498</v>
+        <v>-0.06357213712026206</v>
       </c>
       <c r="N68" s="5" t="n">
         <v>0.1631831464657084</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>0.8197384302846368</v>
+        <v>0.8197383237085761</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>0.2069745387863692</v>
+        <v>0.2069745202338897</v>
       </c>
     </row>
     <row r="69">
@@ -4371,13 +4371,13 @@
         <v>-0.136684521326227</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>0.004453456998952721</v>
+        <v>0.004453420181227297</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>0.6086566445725137</v>
+        <v>0.6086566338354269</v>
       </c>
       <c r="P69" s="5" t="n">
-        <v>0.1703942817778884</v>
+        <v>0.1703942807748652</v>
       </c>
     </row>
     <row r="70">
@@ -4421,19 +4421,19 @@
         <v>-0.01534466510260624</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>0.08122257768216024</v>
+        <v>0.08122261268467919</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>-0.004415336249286361</v>
+        <v>-0.004415359440044305</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>0.1195212035316708</v>
+        <v>0.119521237833884</v>
       </c>
       <c r="O70" s="5" t="n">
-        <v>0.6273521079745944</v>
+        <v>0.6273521552313721</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.1730486776981538</v>
+        <v>0.1730486844661977</v>
       </c>
     </row>
     <row r="71">
@@ -4477,13 +4477,13 @@
         <v>-0.08665326748162405</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.0257204264681779</v>
+        <v>-0.02572038494784634</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>0.07755344150414689</v>
+        <v>0.07755338611718354</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>0.2863961179647578</v>
+        <v>0.2863962233448856</v>
       </c>
       <c r="O71" s="5" t="n">
         <v>0.8463128022461933</v>
@@ -4592,16 +4592,16 @@
         <v>0.07318760985266744</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-0.06614507261685318</v>
+        <v>-0.0661450790343788</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>-0.1034527226036949</v>
+        <v>-0.103452728833985</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>0.09791101615594268</v>
+        <v>0.09791101278511516</v>
       </c>
       <c r="P73" s="5" t="n">
-        <v>0.01152414316733564</v>
+        <v>0.0115241428486697</v>
       </c>
     </row>
     <row r="74">
@@ -4648,16 +4648,16 @@
         <v>0.04735593358654742</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>0.02973555976142081</v>
+        <v>0.02973554389601521</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>0.0782802384486377</v>
+        <v>0.07828024616659221</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>0.7386094172711383</v>
+        <v>0.7386093334141758</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>0.1984090942436988</v>
+        <v>0.1984090787521726</v>
       </c>
     </row>
     <row r="75">
@@ -4701,7 +4701,7 @@
         <v>0.05801783176120945</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-0.006091298469065864</v>
+        <v>-0.006091411752262244</v>
       </c>
       <c r="M75" s="5" t="n">
         <v>0.03876001865908996</v>
@@ -4710,10 +4710,10 @@
         <v>-0.003571739539309782</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>0.08240540409537367</v>
+        <v>0.08240547127266562</v>
       </c>
       <c r="P75" s="5" t="n">
-        <v>0.02674670379400612</v>
+        <v>0.02674672503498821</v>
       </c>
     </row>
     <row r="76">
@@ -4760,16 +4760,16 @@
         <v>0.01582186430987814</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0.1557973359507743</v>
+        <v>0.155797295503656</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>0.02859973834290608</v>
+        <v>0.02859977030895461</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>0.1953170812779514</v>
+        <v>0.1953171369191659</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>0.06020889476707381</v>
+        <v>0.06020891026844633</v>
       </c>
     </row>
     <row r="77">
@@ -4816,16 +4816,16 @@
         <v>-0.01197281676022591</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>-0.276644250420388</v>
+        <v>-0.2766442665352344</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>-0.1854491427977891</v>
+        <v>-0.1854491932426207</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>-0.06274010946165126</v>
+        <v>-0.06274015103675948</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>-0.04737340016662675</v>
+        <v>-0.04737341668431988</v>
       </c>
     </row>
     <row r="78">
@@ -4872,7 +4872,7 @@
         <v>0.05891639580333371</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>-0.006864453756000051</v>
+        <v>-0.006864403868899749</v>
       </c>
       <c r="N78" s="5" t="n">
         <v>0.1608769338716396</v>
@@ -4925,19 +4925,19 @@
         <v>-0.02469005283108215</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>0.02524131106168035</v>
+        <v>0.02524131608025269</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>0.03318033040318665</v>
+        <v>0.03318031932289239</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>0.09620319586991156</v>
+        <v>0.09620320143664794</v>
       </c>
       <c r="O79" s="5" t="n">
-        <v>0.3841482122694485</v>
+        <v>0.3841481821491456</v>
       </c>
       <c r="P79" s="5" t="n">
-        <v>0.1040657294172992</v>
+        <v>0.1040657217653086</v>
       </c>
     </row>
     <row r="80">
@@ -4981,19 +4981,19 @@
         <v>-0.07076302279981343</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.09479194417954051</v>
+        <v>0.09479194725634214</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>0.03364378129389953</v>
+        <v>0.03364376481402611</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>0.1123376080844529</v>
+        <v>0.1123376227638715</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>1.109799479448194</v>
+        <v>1.109799335404815</v>
       </c>
       <c r="P80" s="5" t="n">
-        <v>0.2788805103425835</v>
+        <v>0.2788804808746438</v>
       </c>
     </row>
     <row r="81">
@@ -5040,16 +5040,16 @@
         <v>0.06116896056172955</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>0.0949040501275073</v>
+        <v>0.09490401760014028</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>0.08483276172047494</v>
+        <v>0.08483289394014565</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>0.3230355152837811</v>
+        <v>0.3230354787754071</v>
       </c>
       <c r="P81" s="5" t="n">
-        <v>0.08794362509788567</v>
+        <v>0.08794361252723815</v>
       </c>
     </row>
     <row r="82">
@@ -5093,19 +5093,19 @@
         <v>0.09077898640315757</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>0.02303291680865054</v>
+        <v>0.02303289876719521</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>-0.07787217175200167</v>
+        <v>-0.07787218094845133</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>-0.06598843264033383</v>
+        <v>-0.06598845101404031</v>
       </c>
       <c r="O82" s="5" t="n">
-        <v>0.07724941433347909</v>
+        <v>0.07724939671769546</v>
       </c>
       <c r="P82" s="5" t="n">
-        <v>0.01928678681187936</v>
+        <v>0.01928678515673809</v>
       </c>
     </row>
     <row r="83">
@@ -5155,13 +5155,13 @@
         <v>-0.159530872382811</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>-0.2018357620578377</v>
+        <v>-0.2018357576546494</v>
       </c>
       <c r="O83" s="5" t="n">
-        <v>1.013277435068792</v>
+        <v>1.013277440137022</v>
       </c>
       <c r="P83" s="5" t="n">
-        <v>0.1155192994720127</v>
+        <v>0.1155193019083678</v>
       </c>
     </row>
     <row r="84">
@@ -5205,19 +5205,19 @@
         <v>-0.08275510535345303</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>0.03143583738501891</v>
+        <v>0.03143584945593318</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>0.1001336671830792</v>
+        <v>0.1001336891096266</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>0.08150872436400428</v>
+        <v>0.08150870424493928</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>0.5027130139334656</v>
+        <v>0.5027131003733414</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>0.1405615993431001</v>
+        <v>0.1405616274193464</v>
       </c>
     </row>
     <row r="85">
@@ -5261,7 +5261,7 @@
         <v>-0.09098334504285766</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>0.05795536278250912</v>
+        <v>0.05795530099118396</v>
       </c>
       <c r="M85" s="5" t="n">
         <v>0.1042649304259755</v>
@@ -5270,10 +5270,10 @@
         <v>0.03467910040754252</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>0.2279379896985977</v>
+        <v>0.2279379497233298</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>0.07084181011332169</v>
+        <v>0.07084179847888639</v>
       </c>
     </row>
     <row r="86">
@@ -5323,13 +5323,13 @@
         <v>0.024070866860189</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>-0.05281302083598882</v>
+        <v>-0.0528130843786111</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>-0.08009040722997229</v>
+        <v>-0.08009034729448394</v>
       </c>
       <c r="P86" s="5" t="n">
-        <v>-0.02744303318044239</v>
+        <v>-0.02744301205855681</v>
       </c>
     </row>
     <row r="87">
@@ -5541,19 +5541,19 @@
         <v>-0.002751339825529373</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>0.005272241344384199</v>
+        <v>0.005272234186370128</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>-0.03010359278331898</v>
+        <v>-0.0301036044870996</v>
       </c>
       <c r="N90" s="5" t="n">
         <v>-0.07141096715568361</v>
       </c>
       <c r="O90" s="5" t="n">
-        <v>-0.1538707694634646</v>
+        <v>-0.1538707843321684</v>
       </c>
       <c r="P90" s="5" t="n">
-        <v>-0.05948694529922764</v>
+        <v>-0.05948695245186855</v>
       </c>
     </row>
     <row r="91">
@@ -5597,19 +5597,19 @@
         <v>-0.05699149702341276</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>-0.0007513453787523058</v>
+        <v>-0.0007513229516605031</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>0.007417090984369268</v>
+        <v>0.007417079957665654</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>-0.03468684343175007</v>
+        <v>-0.03468684855393641</v>
       </c>
       <c r="O91" s="5" t="n">
-        <v>0.5649978731993684</v>
+        <v>0.564997869577752</v>
       </c>
       <c r="P91" s="5" t="n">
-        <v>0.141470869065388</v>
+        <v>0.1414708714677613</v>
       </c>
     </row>
     <row r="92">
@@ -5653,19 +5653,19 @@
         <v>-0.04716857331324531</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>-0.03446342068343936</v>
+        <v>-0.03446342155599166</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>0.03437699409257328</v>
+        <v>0.03437696841476651</v>
       </c>
       <c r="N92" s="5" t="n">
-        <v>-0.05657678471945812</v>
+        <v>-0.05657674789819941</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>-0.01870483371763768</v>
+        <v>-0.01870487213593922</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>-0.01125991709227778</v>
+        <v>-0.01125993226865274</v>
       </c>
     </row>
     <row r="93">
@@ -5706,22 +5706,22 @@
         <v>-0.08658483517589437</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.07895710967195826</v>
+        <v>-0.07895712767469365</v>
       </c>
       <c r="L93" s="5" t="n">
         <v>0.04671411718192318</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>-0.02153134181636458</v>
+        <v>-0.02153138389063274</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>-0.04061071757949084</v>
+        <v>-0.04061072406273325</v>
       </c>
       <c r="O93" s="5" t="n">
-        <v>0.1578310134381262</v>
+        <v>0.1578310377388052</v>
       </c>
       <c r="P93" s="5" t="n">
-        <v>0.04850902738695728</v>
+        <v>0.04850903410518637</v>
       </c>
     </row>
     <row r="94">
@@ -5768,16 +5768,16 @@
         <v>0.05533932362284327</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>0.1613003062028024</v>
+        <v>0.1613002984820349</v>
       </c>
       <c r="N94" s="5" t="n">
         <v>0.5378438007819961</v>
       </c>
       <c r="O94" s="5" t="n">
-        <v>0.08870838897152689</v>
+        <v>0.08870849461638219</v>
       </c>
       <c r="P94" s="5" t="n">
-        <v>0.02536874829715702</v>
+        <v>0.02536877825357081</v>
       </c>
     </row>
     <row r="95">
@@ -5821,13 +5821,13 @@
         <v>0.2063135217678718</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.03084104869228321</v>
+        <v>-0.03084096100730171</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>-0.267763063273432</v>
+        <v>-0.2677631133273858</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>-0.2999517501469291</v>
+        <v>-0.2999517958969263</v>
       </c>
       <c r="O95" s="5" t="n">
         <v>-0.06351099873250599</v>
@@ -5877,19 +5877,19 @@
         <v>-0.01893185088223607</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.06656665772603509</v>
+        <v>-0.06656668542523124</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>-0.06818981475993303</v>
+        <v>-0.06818983103736485</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>-0.0644968533077465</v>
+        <v>-0.06449687921088952</v>
       </c>
       <c r="O96" s="5" t="n">
-        <v>0.09127024919451092</v>
+        <v>0.09127022211378089</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>0.02288715219175902</v>
+        <v>0.02288714679426529</v>
       </c>
     </row>
     <row r="97">
@@ -5933,13 +5933,13 @@
         <v>0.1396870774288536</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>-0.1143179340366862</v>
+        <v>-0.1143179644623363</v>
       </c>
       <c r="M97" s="5" t="n">
         <v>-0.2276176202329149</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>-0.1993530314889532</v>
+        <v>-0.1993530503237055</v>
       </c>
       <c r="O97" s="5" t="n">
         <v>0.09905855805746133</v>
@@ -5992,16 +5992,16 @@
         <v>0.004571123026479928</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>-0.1017775142477096</v>
+        <v>-0.1017775269509521</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>-0.1971488791827722</v>
+        <v>-0.1971488920773453</v>
       </c>
       <c r="O98" s="5" t="n">
-        <v>0.690724103912109</v>
+        <v>0.6907241725112326</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>0.175106218232401</v>
+        <v>0.175106233529755</v>
       </c>
     </row>
     <row r="99">
@@ -6045,19 +6045,19 @@
         <v>0.03478883633286475</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>-0.03182527209660089</v>
+        <v>-0.03182527648633563</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>-0.1471583036345371</v>
+        <v>-0.1471582888914789</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>-0.2106763335613876</v>
+        <v>-0.2106762976047467</v>
       </c>
       <c r="O99" s="5" t="n">
-        <v>-0.0109574302696118</v>
+        <v>-0.01095737737787215</v>
       </c>
       <c r="P99" s="5" t="n">
-        <v>-0.008355527483318304</v>
+        <v>-0.008355508382129321</v>
       </c>
     </row>
     <row r="100">
@@ -6107,7 +6107,7 @@
         <v>-0.1886758498353153</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>-0.08399667905504438</v>
+        <v>-0.08399674556374503</v>
       </c>
       <c r="O100" s="5" t="n">
         <v>1.175555067492459</v>
@@ -6166,10 +6166,10 @@
         <v>-0.2405484905630676</v>
       </c>
       <c r="O101" s="5" t="n">
-        <v>0.2152368920736392</v>
+        <v>0.2152370060562523</v>
       </c>
       <c r="P101" s="5" t="n">
-        <v>0.05248388836107609</v>
+        <v>0.05248391796200106</v>
       </c>
     </row>
     <row r="102">
@@ -6216,10 +6216,10 @@
         <v>-0.028935679202783</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>-0.065897728994597</v>
+        <v>-0.06589769175541627</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>-0.04158018649825823</v>
+        <v>-0.04158020400628393</v>
       </c>
       <c r="O102" s="5" t="n">
         <v>-0.5217909683620867</v>
@@ -6269,19 +6269,19 @@
         <v>-0.1133325797927034</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>-0.08469884788177477</v>
+        <v>-0.08469883527870886</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>-0.03069618163991258</v>
+        <v>-0.03069617350804013</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>-0.03967335156117839</v>
+        <v>-0.0396733484858702</v>
       </c>
       <c r="O103" s="5" t="n">
-        <v>0.6622389711228615</v>
+        <v>0.6622388902961571</v>
       </c>
       <c r="P103" s="5" t="n">
-        <v>0.1630523536468373</v>
+        <v>0.1630523308265919</v>
       </c>
     </row>
     <row r="104">
@@ -6334,10 +6334,10 @@
         <v>-0.03894411872202175</v>
       </c>
       <c r="O104" s="5" t="n">
-        <v>0.515890666793986</v>
+        <v>0.5158907790045171</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.1487423344272145</v>
+        <v>0.1487423627716036</v>
       </c>
     </row>
     <row r="105">
@@ -6384,16 +6384,16 @@
         <v>-0.1010994111725191</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>-0.01898840871354738</v>
+        <v>-0.01898840472310452</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>-0.007987661759561809</v>
+        <v>-0.007987663307783943</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>0.28950130864614</v>
+        <v>0.2895012867588148</v>
       </c>
       <c r="P105" s="5" t="n">
-        <v>0.08498236827368146</v>
+        <v>0.0849823617432181</v>
       </c>
     </row>
     <row r="106">
@@ -6440,16 +6440,16 @@
         <v>-0.101003279298898</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>-0.07242933031576848</v>
+        <v>-0.07242932273438758</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>-0.02769012472534375</v>
+        <v>-0.02769011592995267</v>
       </c>
       <c r="O106" s="5" t="n">
-        <v>1.048676442907951</v>
+        <v>1.048676422452881</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>0.2323352427119361</v>
+        <v>0.2323352385750032</v>
       </c>
     </row>
     <row r="107">
@@ -6499,13 +6499,13 @@
         <v>-0.001423753938692096</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>-0.005161808962482362</v>
+        <v>-0.005161835885980959</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>0.7647743188506799</v>
+        <v>0.7647741371847362</v>
       </c>
       <c r="P107" s="5" t="n">
-        <v>0.2008717707930299</v>
+        <v>0.2008717302725993</v>
       </c>
     </row>
     <row r="108">
@@ -6552,16 +6552,16 @@
         <v>-0.03536492919710049</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>-0.09052176650623694</v>
+        <v>-0.09052174043013952</v>
       </c>
       <c r="N108" s="5" t="n">
         <v>-0.1923452272797346</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>0.1979984940153661</v>
+        <v>0.1979984310789321</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.05332915076210754</v>
+        <v>0.05332913658185701</v>
       </c>
     </row>
     <row r="109">
@@ -6605,19 +6605,19 @@
         <v>-0.1159217895611486</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>-0.04657461209019099</v>
+        <v>-0.04657460320478325</v>
       </c>
       <c r="M109" s="5" t="n">
         <v>-0.1224245057416796</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>-0.0481369238415169</v>
+        <v>-0.04813692359276547</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>0.7610890035932516</v>
+        <v>0.7610889261944981</v>
       </c>
       <c r="P109" s="5" t="n">
-        <v>0.1910230662442725</v>
+        <v>0.191023051325669</v>
       </c>
     </row>
     <row r="110">
@@ -6664,16 +6664,16 @@
         <v>-0.09678195732396577</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>-0.1391105085646993</v>
+        <v>-0.1391104918106733</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>-0.1436378218612757</v>
+        <v>-0.1436378063658535</v>
       </c>
       <c r="O110" s="5" t="n">
-        <v>0.2673357517675218</v>
+        <v>0.2673355696250695</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>0.07656472503218419</v>
+        <v>0.0765646656733685</v>
       </c>
     </row>
     <row r="111">
@@ -6720,16 +6720,16 @@
         <v>-0.04088992334686633</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>-0.08377548583870542</v>
+        <v>-0.08377554131169314</v>
       </c>
       <c r="N111" s="5" t="n">
-        <v>-0.1415685873072288</v>
+        <v>-0.1415685624815494</v>
       </c>
       <c r="O111" s="5" t="n">
-        <v>-0.01961728349349756</v>
+        <v>-0.01961716220387799</v>
       </c>
       <c r="P111" s="5" t="n">
-        <v>-0.00801482034412789</v>
+        <v>-0.008014783036830675</v>
       </c>
     </row>
     <row r="112">
@@ -6835,13 +6835,13 @@
         <v>-0.07708661036921016</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>-0.1000162090180036</v>
+        <v>-0.1000161360422424</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>-0.2560640969081206</v>
+        <v>-0.2560640470449042</v>
       </c>
       <c r="P113" s="5" t="n">
-        <v>-0.0938950431229536</v>
+        <v>-0.09389502287868856</v>
       </c>
     </row>
     <row r="114">
@@ -6941,19 +6941,19 @@
         <v>-0.1025246971799034</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>-0.1753556733024863</v>
+        <v>-0.1753557029584409</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>-0.1399805553493447</v>
+        <v>-0.1399805887451161</v>
       </c>
       <c r="N115" s="5" t="n">
         <v>-0.01728456476190049</v>
       </c>
       <c r="O115" s="5" t="n">
-        <v>2.217997454233947</v>
+        <v>2.217997526230125</v>
       </c>
       <c r="P115" s="5" t="n">
-        <v>0.404096877816137</v>
+        <v>0.4040968984941677</v>
       </c>
     </row>
     <row r="116">
@@ -6997,19 +6997,19 @@
         <v>-0.123089182418588</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>-0.1271907995280301</v>
+        <v>-0.1271907959450422</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>-0.126143936281795</v>
+        <v>-0.126143975557142</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>-0.1039004399992178</v>
+        <v>-0.1039004680927857</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>0.9152399501896585</v>
+        <v>0.9152400617933147</v>
       </c>
       <c r="P116" s="5" t="n">
-        <v>0.2131678679014897</v>
+        <v>0.2131679033536837</v>
       </c>
     </row>
     <row r="117">
@@ -7115,13 +7115,13 @@
         <v>-0.2474471359623402</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>-0.3369718209670517</v>
+        <v>-0.3369718392381647</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>-0.2080617051557176</v>
+        <v>-0.2080617285553989</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>-0.07552788694454071</v>
+        <v>-0.07552789660151354</v>
       </c>
     </row>
     <row r="119">
@@ -7165,19 +7165,19 @@
         <v>-0.08852908886741256</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>-0.1320056781475007</v>
+        <v>-0.1320057479360536</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>-0.1593252587117395</v>
+        <v>-0.1593251933174075</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>-0.2528884403874103</v>
+        <v>-0.2528884687423647</v>
       </c>
       <c r="O119" s="5" t="n">
-        <v>0.00675785617078839</v>
+        <v>0.006757969175738898</v>
       </c>
       <c r="P119" s="5" t="n">
-        <v>0.002058682972157999</v>
+        <v>0.002058719476523641</v>
       </c>
     </row>
     <row r="120">
@@ -7221,19 +7221,19 @@
         <v>-0.1945157271120297</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>-0.1438421784901527</v>
+        <v>-0.1438421960004958</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>-0.2390934198857857</v>
+        <v>-0.2390934097988326</v>
       </c>
       <c r="N120" s="5" t="n">
-        <v>-0.1707365180071566</v>
+        <v>-0.1707365050273943</v>
       </c>
       <c r="O120" s="5" t="n">
-        <v>-0.04595904813738779</v>
+        <v>-0.04595902186160779</v>
       </c>
       <c r="P120" s="5" t="n">
-        <v>-0.01595545396709001</v>
+        <v>-0.01595544469007189</v>
       </c>
     </row>
     <row r="121">
@@ -7283,7 +7283,7 @@
         <v>-0.2890118131040159</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>-0.2425951834487193</v>
+        <v>-0.2425952371303223</v>
       </c>
       <c r="O121" s="5" t="n">
         <v>3.743444648505034</v>
@@ -7333,19 +7333,19 @@
         <v>-0.1974366020498225</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>-0.1318661842565061</v>
+        <v>-0.1318662202714328</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>-0.2362544950668478</v>
+        <v>-0.2362544704027482</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>-0.2052650223748348</v>
+        <v>-0.205265049020377</v>
       </c>
       <c r="O122" s="5" t="n">
-        <v>0.3747372313107791</v>
+        <v>0.3747371677619107</v>
       </c>
       <c r="P122" s="5" t="n">
-        <v>0.1095352303281942</v>
+        <v>0.1095352119428211</v>
       </c>
     </row>
     <row r="123">
@@ -7454,10 +7454,10 @@
         <v>-0.2057689298375081</v>
       </c>
       <c r="O124" s="5" t="n">
-        <v>0.9833753996274716</v>
+        <v>0.9833751893277958</v>
       </c>
       <c r="P124" s="5" t="n">
-        <v>0.1147479193002703</v>
+        <v>0.1147478861174735</v>
       </c>
     </row>
     <row r="125">
@@ -7883,13 +7883,13 @@
         <v>2.883622776681344</v>
       </c>
       <c r="N4" t="n">
-        <v>5.451537557963221</v>
+        <v>5.451538150479654</v>
       </c>
       <c r="O4" t="n">
-        <v>14.73546345058386</v>
+        <v>14.73546697537246</v>
       </c>
       <c r="P4" t="n">
-        <v>1.505877554941292</v>
+        <v>1.50587774204918</v>
       </c>
     </row>
     <row r="5">
@@ -7944,10 +7944,10 @@
         <v>3.178595699949488</v>
       </c>
       <c r="O5" t="n">
-        <v>2.646883528184924</v>
+        <v>2.646883942006804</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5392433917849229</v>
+        <v>0.5392434500056444</v>
       </c>
     </row>
     <row r="6">
@@ -8002,10 +8002,10 @@
         <v>3.083145910109416</v>
       </c>
       <c r="O6" t="n">
-        <v>14.02936917314449</v>
+        <v>14.02937197120281</v>
       </c>
       <c r="P6" t="n">
-        <v>1.467820594087385</v>
+        <v>1.46782074723432</v>
       </c>
     </row>
     <row r="7">
@@ -8170,16 +8170,16 @@
         <v>2.356477604610771</v>
       </c>
       <c r="M9" t="n">
-        <v>3.34774702977868</v>
+        <v>3.347747292073787</v>
       </c>
       <c r="N9" t="n">
         <v>3.144979246725678</v>
       </c>
       <c r="O9" t="n">
-        <v>7.235962059453355</v>
+        <v>7.235963941890125</v>
       </c>
       <c r="P9" t="n">
-        <v>1.019473285166705</v>
+        <v>1.019473439025698</v>
       </c>
     </row>
     <row r="10">
@@ -8341,19 +8341,19 @@
         <v>0.2773437212949303</v>
       </c>
       <c r="L12" t="n">
-        <v>1.825922036449772</v>
+        <v>1.825922280822835</v>
       </c>
       <c r="M12" t="n">
-        <v>1.566093680886127</v>
+        <v>1.566093479384795</v>
       </c>
       <c r="N12" t="n">
         <v>1.568984650022719</v>
       </c>
       <c r="O12" t="n">
-        <v>2.939449962436506</v>
+        <v>2.939450674789834</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5793505265320249</v>
+        <v>0.5793506217276778</v>
       </c>
     </row>
     <row r="13">
@@ -8408,10 +8408,10 @@
         <v>2.503830406360786</v>
       </c>
       <c r="O13" t="n">
-        <v>4.035000919492099</v>
+        <v>4.035000548824106</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7139567210544762</v>
+        <v>0.7139566789949729</v>
       </c>
     </row>
     <row r="14">
@@ -8518,16 +8518,16 @@
         <v>0.5968872464133808</v>
       </c>
       <c r="M15" t="n">
-        <v>1.314762735656624</v>
+        <v>1.314762953192094</v>
       </c>
       <c r="N15" t="n">
         <v>1.252529941458666</v>
       </c>
       <c r="O15" t="n">
-        <v>1.809548132591331</v>
+        <v>1.80954749164757</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4110600369265534</v>
+        <v>0.4110599296245778</v>
       </c>
     </row>
     <row r="16">
@@ -8579,13 +8579,13 @@
         <v>1.361111309523092</v>
       </c>
       <c r="N16" t="n">
-        <v>1.068775235498811</v>
+        <v>1.068774899204323</v>
       </c>
       <c r="O16" t="n">
-        <v>1.685074317002609</v>
+        <v>1.685074883510437</v>
       </c>
       <c r="P16" t="n">
-        <v>0.389906022837883</v>
+        <v>0.3899061205872054</v>
       </c>
     </row>
     <row r="17">
@@ -8872,10 +8872,10 @@
         <v>0.6183241775501449</v>
       </c>
       <c r="O21" t="n">
-        <v>1.738211720886205</v>
+        <v>1.738211138156232</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3990149058023336</v>
+        <v>0.3990148065589758</v>
       </c>
     </row>
     <row r="22">
@@ -8988,10 +8988,10 @@
         <v>1.894964143109716</v>
       </c>
       <c r="O23" t="n">
-        <v>3.123390904642378</v>
+        <v>3.123391571331341</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6035586033878508</v>
+        <v>0.6035586898114433</v>
       </c>
     </row>
     <row r="24">
@@ -9153,10 +9153,10 @@
         <v>0.4234145534039839</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6327486928204835</v>
+        <v>0.6327485496992458</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4592827072811592</v>
+        <v>0.4592825929553537</v>
       </c>
       <c r="N26" t="n">
         <v>0.6626172599715885</v>
@@ -9385,7 +9385,7 @@
         <v>0.2860190402376683</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1350791257357751</v>
+        <v>0.1350792382042874</v>
       </c>
       <c r="M30" t="n">
         <v>0.8359367975923198</v>
@@ -9394,10 +9394,10 @@
         <v>0.8851242987778287</v>
       </c>
       <c r="O30" t="n">
-        <v>0.2180138399680858</v>
+        <v>0.2180134514563019</v>
       </c>
       <c r="P30" t="n">
-        <v>0.06794955971951233</v>
+        <v>0.06794944617098531</v>
       </c>
     </row>
     <row r="31">
@@ -9501,19 +9501,19 @@
         <v>0.2454354953000217</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2968987781550896</v>
+        <v>0.2968986914976615</v>
       </c>
       <c r="M32" t="n">
         <v>0.4388465411595022</v>
       </c>
       <c r="N32" t="n">
-        <v>0.9063057902693963</v>
+        <v>0.9063059775008628</v>
       </c>
       <c r="O32" t="n">
-        <v>0.5259082129960138</v>
+        <v>0.5259083329598977</v>
       </c>
       <c r="P32" t="n">
-        <v>0.1512672138234572</v>
+        <v>0.1512672439935729</v>
       </c>
     </row>
     <row r="33">
@@ -9568,10 +9568,10 @@
         <v>1.374689204429794</v>
       </c>
       <c r="O33" t="n">
-        <v>2.566365567014165</v>
+        <v>2.566366385244366</v>
       </c>
       <c r="P33" t="n">
-        <v>0.5278308885565217</v>
+        <v>0.5278310053997763</v>
       </c>
     </row>
     <row r="34">
@@ -9620,10 +9620,10 @@
         <v>1.219184973688179</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4734966757572436</v>
+        <v>0.4734965873593415</v>
       </c>
       <c r="N34" t="n">
-        <v>0.4717709621274684</v>
+        <v>0.4717707857455478</v>
       </c>
       <c r="O34" t="n">
         <v>-0.2133841244366659</v>
@@ -9739,13 +9739,13 @@
         <v>0.5228668328018944</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8504337739857248</v>
+        <v>0.8504339855320246</v>
       </c>
       <c r="O36" t="n">
-        <v>0.6837111487625107</v>
+        <v>0.6837113239058037</v>
       </c>
       <c r="P36" t="n">
-        <v>0.1896590951464312</v>
+        <v>0.1896591363967379</v>
       </c>
     </row>
     <row r="37">
@@ -9852,16 +9852,16 @@
         <v>0.3193738990695676</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7594878954891606</v>
+        <v>0.7594880492190736</v>
       </c>
       <c r="N38" t="n">
         <v>1.34449260429946</v>
       </c>
       <c r="O38" t="n">
-        <v>4.088509748960493</v>
+        <v>4.088510391851067</v>
       </c>
       <c r="P38" t="n">
-        <v>0.7200069574444201</v>
+        <v>0.7200070298805732</v>
       </c>
     </row>
     <row r="39">
@@ -10084,16 +10084,16 @@
         <v>0.3939541895546999</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1503538990314475</v>
+        <v>0.1503540204333602</v>
       </c>
       <c r="N42" t="n">
-        <v>0.4212621715321068</v>
+        <v>0.4212622641896906</v>
       </c>
       <c r="O42" t="n">
-        <v>0.3360854774053115</v>
+        <v>0.3360856411740807</v>
       </c>
       <c r="P42" t="n">
-        <v>0.1013991774831868</v>
+        <v>0.1013992224839952</v>
       </c>
     </row>
     <row r="43">
@@ -10203,7 +10203,7 @@
         <v>0.457868326185416</v>
       </c>
       <c r="N44" t="n">
-        <v>0.8465566732642957</v>
+        <v>0.8465568632065694</v>
       </c>
       <c r="O44" t="n">
         <v>1.014435294834501</v>
@@ -10322,10 +10322,10 @@
         <v>0.3232223158563245</v>
       </c>
       <c r="O46" t="n">
-        <v>0.5181661911192617</v>
+        <v>0.5181662974853822</v>
       </c>
       <c r="P46" t="n">
-        <v>0.1493168446928903</v>
+        <v>0.1493168715341262</v>
       </c>
     </row>
     <row r="47">
@@ -10374,7 +10374,7 @@
         <v>0.5592336219492959</v>
       </c>
       <c r="M47" t="n">
-        <v>0.3576834704115255</v>
+        <v>0.3576836200728264</v>
       </c>
       <c r="N47" t="n">
         <v>0.5033595025008066</v>
@@ -10435,13 +10435,13 @@
         <v>0.4477880424509357</v>
       </c>
       <c r="N48" t="n">
-        <v>0.1618844060850331</v>
+        <v>0.161884293460713</v>
       </c>
       <c r="O48" t="n">
-        <v>0.04532028098729435</v>
+        <v>0.04532000750685272</v>
       </c>
       <c r="P48" t="n">
-        <v>0.01488412405151562</v>
+        <v>0.014884035545633</v>
       </c>
     </row>
     <row r="49">
@@ -10548,16 +10548,16 @@
         <v>0.2537112662870771</v>
       </c>
       <c r="M50" t="n">
-        <v>0.5355036982021357</v>
+        <v>0.5355035967849338</v>
       </c>
       <c r="N50" t="n">
         <v>0.5230292245903789</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9411993345148408</v>
+        <v>0.9411996586903901</v>
       </c>
       <c r="P50" t="n">
-        <v>0.2474506622661323</v>
+        <v>0.2474507317065333</v>
       </c>
     </row>
     <row r="51">
@@ -10603,7 +10603,7 @@
         <v>0.129754070939609</v>
       </c>
       <c r="L51" t="n">
-        <v>0.3272001357166334</v>
+        <v>0.327200228296376</v>
       </c>
       <c r="M51" t="n">
         <v>0.408440436570068</v>
@@ -10612,10 +10612,10 @@
         <v>0.6172892690344007</v>
       </c>
       <c r="O51" t="n">
-        <v>1.031184725343354</v>
+        <v>1.03118494218465</v>
       </c>
       <c r="P51" t="n">
-        <v>0.2664356887566306</v>
+        <v>0.2664357338231942</v>
       </c>
     </row>
     <row r="52">
@@ -10664,16 +10664,16 @@
         <v>0.4773513336677664</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4020442887621778</v>
+        <v>0.4020441220790507</v>
       </c>
       <c r="N52" t="n">
-        <v>0.6342072928484257</v>
+        <v>0.6342071796207771</v>
       </c>
       <c r="O52" t="n">
-        <v>1.918234544269707</v>
+        <v>1.918234905329121</v>
       </c>
       <c r="P52" t="n">
-        <v>0.4290257834228528</v>
+        <v>0.4290258423583933</v>
       </c>
     </row>
     <row r="53">
@@ -10728,10 +10728,10 @@
         <v>0.3781331105588466</v>
       </c>
       <c r="O53" t="n">
-        <v>0.06219264007924208</v>
+        <v>0.06219252138249254</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02031537091628288</v>
+        <v>0.02031533291058363</v>
       </c>
     </row>
     <row r="54">
@@ -10783,13 +10783,13 @@
         <v>0.6866330193709804</v>
       </c>
       <c r="N54" t="n">
-        <v>1.025800051879349</v>
+        <v>1.02579989782309</v>
       </c>
       <c r="O54" t="n">
-        <v>8.634923031823327</v>
+        <v>8.634923903033163</v>
       </c>
       <c r="P54" t="n">
-        <v>1.12789119034082</v>
+        <v>1.127891254476939</v>
       </c>
     </row>
     <row r="55">
@@ -10844,10 +10844,10 @@
         <v>0.3099003465012313</v>
       </c>
       <c r="O55" t="n">
-        <v>0.5173559309803064</v>
+        <v>0.517355834252994</v>
       </c>
       <c r="P55" t="n">
-        <v>0.1491123410945128</v>
+        <v>0.1491123166769173</v>
       </c>
     </row>
     <row r="56">
@@ -11134,10 +11134,10 @@
         <v>0.699163104173339</v>
       </c>
       <c r="O60" t="n">
-        <v>2.576190612996716</v>
+        <v>2.576191302537049</v>
       </c>
       <c r="P60" t="n">
-        <v>0.5292326185820042</v>
+        <v>0.5292327168679196</v>
       </c>
     </row>
     <row r="61">
@@ -11244,16 +11244,16 @@
         <v>0.4135146786829549</v>
       </c>
       <c r="M62" t="n">
-        <v>0.3331756269588122</v>
+        <v>0.3331757427141688</v>
       </c>
       <c r="N62" t="n">
         <v>0.7345256875805941</v>
       </c>
       <c r="O62" t="n">
-        <v>1.416442016808706</v>
+        <v>1.416441826661891</v>
       </c>
       <c r="P62" t="n">
-        <v>0.3419163967500276</v>
+        <v>0.3419163615521161</v>
       </c>
     </row>
     <row r="63">
@@ -11302,16 +11302,16 @@
         <v>0.1835388744083475</v>
       </c>
       <c r="M63" t="n">
-        <v>0.7382740557729399</v>
+        <v>0.7382742050023283</v>
       </c>
       <c r="N63" t="n">
-        <v>0.923792257059969</v>
+        <v>0.9237920742776731</v>
       </c>
       <c r="O63" t="n">
-        <v>4.268699826538588</v>
+        <v>4.268700169278573</v>
       </c>
       <c r="P63" t="n">
-        <v>0.7400744041089096</v>
+        <v>0.7400744418407399</v>
       </c>
     </row>
     <row r="64">
@@ -11534,16 +11534,16 @@
         <v>0.4600439915050436</v>
       </c>
       <c r="M67" t="n">
-        <v>0.5654267763286382</v>
+        <v>0.5654266391685228</v>
       </c>
       <c r="N67" t="n">
         <v>0.5363659315629112</v>
       </c>
       <c r="O67" t="n">
-        <v>0.853025173827185</v>
+        <v>0.8530249816397648</v>
       </c>
       <c r="P67" t="n">
-        <v>0.2282697980980903</v>
+        <v>0.2282697556345528</v>
       </c>
     </row>
     <row r="68">
@@ -11595,13 +11595,13 @@
         <v>0.5665042755465841</v>
       </c>
       <c r="N68" t="n">
-        <v>0.4130908340890658</v>
+        <v>0.413090960370337</v>
       </c>
       <c r="O68" t="n">
-        <v>0.5345219563164896</v>
+        <v>0.5345218073992701</v>
       </c>
       <c r="P68" t="n">
-        <v>0.1534294493029909</v>
+        <v>0.1534294119915856</v>
       </c>
     </row>
     <row r="69">
@@ -11650,16 +11650,16 @@
         <v>0.1556078437332624</v>
       </c>
       <c r="M69" t="n">
-        <v>0.3290867135449893</v>
+        <v>0.3290866134067401</v>
       </c>
       <c r="N69" t="n">
-        <v>0.5587041858563109</v>
+        <v>0.5587040481287813</v>
       </c>
       <c r="O69" t="n">
-        <v>0.8263178933294764</v>
+        <v>0.8263171370088356</v>
       </c>
       <c r="P69" t="n">
-        <v>0.2223402837399202</v>
+        <v>0.2223401150067335</v>
       </c>
     </row>
     <row r="70">
@@ -11769,13 +11769,13 @@
         <v>0.4323574595920114</v>
       </c>
       <c r="N71" t="n">
-        <v>0.2314413721640167</v>
+        <v>0.23144129170238</v>
       </c>
       <c r="O71" t="n">
-        <v>1.87425914423009</v>
+        <v>1.874258267546017</v>
       </c>
       <c r="P71" t="n">
-        <v>0.421811340577299</v>
+        <v>0.4218111960206878</v>
       </c>
     </row>
     <row r="72">
@@ -11888,10 +11888,10 @@
         <v>0.4551620484357899</v>
       </c>
       <c r="O73" t="n">
-        <v>0.6596309931988433</v>
+        <v>0.6596308897034966</v>
       </c>
       <c r="P73" t="n">
-        <v>0.1839604057360182</v>
+        <v>0.183960381125247</v>
       </c>
     </row>
     <row r="74">
@@ -11946,10 +11946,10 @@
         <v>0.5093589106409917</v>
       </c>
       <c r="O74" t="n">
-        <v>1.793562340348918</v>
+        <v>1.793562136599284</v>
       </c>
       <c r="P74" t="n">
-        <v>0.4083787243950159</v>
+        <v>0.408378690154785</v>
       </c>
     </row>
     <row r="75">
@@ -12004,10 +12004,10 @@
         <v>0.3929198444311646</v>
       </c>
       <c r="O75" t="n">
-        <v>0.1797652229334676</v>
+        <v>0.1797650936706465</v>
       </c>
       <c r="P75" t="n">
-        <v>0.0566517175464909</v>
+        <v>0.05665167895525691</v>
       </c>
     </row>
     <row r="76">
@@ -12114,10 +12114,10 @@
         <v>0.2041818438130578</v>
       </c>
       <c r="M77" t="n">
-        <v>0.3401632009521869</v>
+        <v>0.340163115688815</v>
       </c>
       <c r="N77" t="n">
-        <v>0.4473475567168463</v>
+        <v>0.4473474572695937</v>
       </c>
       <c r="O77" t="n">
         <v>0.4892669550380218</v>
@@ -12172,16 +12172,16 @@
         <v>0.4025580356306757</v>
       </c>
       <c r="M78" t="n">
-        <v>0.4047578968924384</v>
+        <v>0.4047580119599048</v>
       </c>
       <c r="N78" t="n">
         <v>0.4337432184527477</v>
       </c>
       <c r="O78" t="n">
-        <v>0.5361776296471732</v>
+        <v>0.5361777672516179</v>
       </c>
       <c r="P78" t="n">
-        <v>0.1538441313166645</v>
+        <v>0.1538441657688601</v>
       </c>
     </row>
     <row r="79">
@@ -12236,10 +12236,10 @@
         <v>0.3295009431493743</v>
       </c>
       <c r="O79" t="n">
-        <v>0.9542206658648151</v>
+        <v>0.9542203200516433</v>
       </c>
       <c r="P79" t="n">
-        <v>0.2502336983565001</v>
+        <v>0.2502336246105967</v>
       </c>
     </row>
     <row r="80">
@@ -12291,13 +12291,13 @@
         <v>0.2096025096436467</v>
       </c>
       <c r="N80" t="n">
-        <v>0.2758481073144872</v>
+        <v>0.2758479712303512</v>
       </c>
       <c r="O80" t="n">
-        <v>-0.06896263733458241</v>
+        <v>-0.06896270980216679</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.02353719898001316</v>
+        <v>-0.02353722431444305</v>
       </c>
     </row>
     <row r="81">
@@ -12349,7 +12349,7 @@
         <v>-0.09194469101126868</v>
       </c>
       <c r="N81" t="n">
-        <v>-0.02030128955554078</v>
+        <v>-0.02030122791090538</v>
       </c>
       <c r="O81" t="n">
         <v>0.172869663655506</v>
@@ -12404,16 +12404,16 @@
         <v>0.06421324510785387</v>
       </c>
       <c r="M82" t="n">
-        <v>0.3801462239058253</v>
+        <v>0.3801460838200628</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5406811085454637</v>
+        <v>0.5406812831153798</v>
       </c>
       <c r="O82" t="n">
-        <v>-0.05098070171434621</v>
+        <v>-0.05098076795031548</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.01729081641173025</v>
+        <v>-0.01729083927417252</v>
       </c>
     </row>
     <row r="83">
@@ -12465,13 +12465,13 @@
         <v>0.3771928612652422</v>
       </c>
       <c r="N83" t="n">
-        <v>0.4559270876894681</v>
+        <v>0.4559268870790794</v>
       </c>
       <c r="O83" t="n">
-        <v>0.5480141215095906</v>
+        <v>0.5480140081145566</v>
       </c>
       <c r="P83" t="n">
-        <v>0.156800069516376</v>
+        <v>0.1568000412704265</v>
       </c>
     </row>
     <row r="84">
@@ -12520,16 +12520,16 @@
         <v>0.3120491122106128</v>
       </c>
       <c r="M84" t="n">
-        <v>0.1605431071790933</v>
+        <v>0.1605430236094123</v>
       </c>
       <c r="N84" t="n">
-        <v>0.4140376592091797</v>
+        <v>0.4140377832738749</v>
       </c>
       <c r="O84" t="n">
-        <v>1.418755870880329</v>
+        <v>1.418755326375849</v>
       </c>
       <c r="P84" t="n">
-        <v>0.3423445756130166</v>
+        <v>0.342344474884553</v>
       </c>
     </row>
     <row r="85">
@@ -12578,7 +12578,7 @@
         <v>0.02132722439484169</v>
       </c>
       <c r="M85" t="n">
-        <v>0.4117708592169718</v>
+        <v>0.4117709779313505</v>
       </c>
       <c r="N85" t="n">
         <v>0.4135897669275128</v>
@@ -12633,10 +12633,10 @@
         <v>0.1864658605736211</v>
       </c>
       <c r="L86" t="n">
-        <v>0.2012668541453884</v>
+        <v>0.2012667596429309</v>
       </c>
       <c r="M86" t="n">
-        <v>0.3481898410016055</v>
+        <v>0.3481899600343064</v>
       </c>
       <c r="N86" t="n">
         <v>0.2680602754077712</v>
@@ -12697,13 +12697,13 @@
         <v>0.02515684596129608</v>
       </c>
       <c r="N87" t="n">
-        <v>0.4191683925070351</v>
+        <v>0.4191685458172452</v>
       </c>
       <c r="O87" t="n">
-        <v>-0.01873513296616436</v>
+        <v>-0.01873505967093569</v>
       </c>
       <c r="P87" t="n">
-        <v>-0.006284455975382741</v>
+        <v>-0.006284431233640864</v>
       </c>
     </row>
     <row r="88">
@@ -12749,19 +12749,19 @@
         <v>-0.1182158368515169</v>
       </c>
       <c r="L88" t="n">
-        <v>0.3626872596980402</v>
+        <v>0.3626873928104186</v>
       </c>
       <c r="M88" t="n">
-        <v>0.3840265987226668</v>
+        <v>0.3840267360367011</v>
       </c>
       <c r="N88" t="n">
-        <v>0.6084363972620825</v>
+        <v>0.6084362118091331</v>
       </c>
       <c r="O88" t="n">
-        <v>1.150418206451659</v>
+        <v>1.150418040706124</v>
       </c>
       <c r="P88" t="n">
-        <v>0.2907465595190084</v>
+        <v>0.2907465263571667</v>
       </c>
     </row>
     <row r="89">
@@ -12813,13 +12813,13 @@
         <v>0.4045289968555248</v>
       </c>
       <c r="N89" t="n">
-        <v>0.5805497433888944</v>
+        <v>0.5805499412891446</v>
       </c>
       <c r="O89" t="n">
-        <v>1.300435376745628</v>
+        <v>1.30043516713177</v>
       </c>
       <c r="P89" t="n">
-        <v>0.3200894063916899</v>
+        <v>0.3200893662965201</v>
       </c>
     </row>
     <row r="90">
@@ -12874,10 +12874,10 @@
         <v>0.3569310231501248</v>
       </c>
       <c r="O90" t="n">
-        <v>0.4011376965494067</v>
+        <v>0.4011378423129115</v>
       </c>
       <c r="P90" t="n">
-        <v>0.1189918906404328</v>
+        <v>0.118991929444179</v>
       </c>
     </row>
     <row r="91">
@@ -12990,10 +12990,10 @@
         <v>0.4929447198858941</v>
       </c>
       <c r="O92" t="n">
-        <v>2.085488788958551</v>
+        <v>2.085489217643431</v>
       </c>
       <c r="P92" t="n">
-        <v>0.4558210375325606</v>
+        <v>0.4558211049544485</v>
       </c>
     </row>
     <row r="93">
@@ -13042,16 +13042,16 @@
         <v>0.3522363990457573</v>
       </c>
       <c r="M93" t="n">
-        <v>0.3922718798471871</v>
+        <v>0.3922717183249376</v>
       </c>
       <c r="N93" t="n">
-        <v>0.4039912304304998</v>
+        <v>0.4039910661776018</v>
       </c>
       <c r="O93" t="n">
-        <v>3.234014094091205</v>
+        <v>3.234013720644295</v>
       </c>
       <c r="P93" t="n">
-        <v>0.6177724419234309</v>
+        <v>0.6177723943600453</v>
       </c>
     </row>
     <row r="94">
@@ -13158,16 +13158,16 @@
         <v>0.3368207229333753</v>
       </c>
       <c r="M95" t="n">
-        <v>0.3040961276130554</v>
+        <v>0.3040960137168442</v>
       </c>
       <c r="N95" t="n">
-        <v>0.430179514241384</v>
+        <v>0.4301796512258282</v>
       </c>
       <c r="O95" t="n">
-        <v>0.7004384757674464</v>
+        <v>0.7004386694149936</v>
       </c>
       <c r="P95" t="n">
-        <v>0.1935857935886607</v>
+        <v>0.1935858388975531</v>
       </c>
     </row>
     <row r="96">
@@ -13216,16 +13216,16 @@
         <v>0.4245681635208873</v>
       </c>
       <c r="M96" t="n">
-        <v>0.2267685992176536</v>
+        <v>0.2267688354716717</v>
       </c>
       <c r="N96" t="n">
         <v>0.2447056136230032</v>
       </c>
       <c r="O96" t="n">
-        <v>0.6491465475640645</v>
+        <v>0.6491463340914025</v>
       </c>
       <c r="P96" t="n">
-        <v>0.1814619788629426</v>
+        <v>0.1814619278850909</v>
       </c>
     </row>
     <row r="97">
@@ -13274,16 +13274,16 @@
         <v>0.228796597695399</v>
       </c>
       <c r="M97" t="n">
-        <v>0.2461748424270929</v>
+        <v>0.2461747109242236</v>
       </c>
       <c r="N97" t="n">
         <v>0.3244697835416075</v>
       </c>
       <c r="O97" t="n">
-        <v>1.259344846510371</v>
+        <v>1.259344414253128</v>
       </c>
       <c r="P97" t="n">
-        <v>0.3121822970311461</v>
+        <v>0.3121822133490206</v>
       </c>
     </row>
     <row r="98">
@@ -13500,7 +13500,7 @@
         <v>0.1023128414689709</v>
       </c>
       <c r="M101" t="n">
-        <v>0.303311188368981</v>
+        <v>0.3033110775950543</v>
       </c>
       <c r="N101" t="n">
         <v>0.619489772597176</v>
@@ -13564,10 +13564,10 @@
         <v>0.4622591083394603</v>
       </c>
       <c r="O102" t="n">
-        <v>0.1557117100819743</v>
+        <v>0.1557114438648521</v>
       </c>
       <c r="P102" t="n">
-        <v>0.04942121089519547</v>
+        <v>0.04942113031745454</v>
       </c>
     </row>
     <row r="103">
@@ -13613,13 +13613,13 @@
         <v>0.1034198169104752</v>
       </c>
       <c r="L103" t="n">
-        <v>0.1874286211453875</v>
+        <v>0.1874287432630695</v>
       </c>
       <c r="M103" t="n">
         <v>0.2852585776894085</v>
       </c>
       <c r="N103" t="n">
-        <v>0.3555954008435449</v>
+        <v>0.355595559999798</v>
       </c>
       <c r="O103" t="n">
         <v>0.6672338364025647</v>
@@ -13674,16 +13674,16 @@
         <v>0.2459218542747452</v>
       </c>
       <c r="M104" t="n">
-        <v>0.4861641056085357</v>
+        <v>0.4861640159091922</v>
       </c>
       <c r="N104" t="n">
         <v>0.7631947705053534</v>
       </c>
       <c r="O104" t="n">
-        <v>3.258056360586844</v>
+        <v>3.258056728757022</v>
       </c>
       <c r="P104" t="n">
-        <v>0.6208287636450993</v>
+        <v>0.6208288103597461</v>
       </c>
     </row>
     <row r="105">
@@ -13729,19 +13729,19 @@
         <v>0.1691075433412836</v>
       </c>
       <c r="L105" t="n">
-        <v>0.4154892401543213</v>
+        <v>0.4154890774645816</v>
       </c>
       <c r="M105" t="n">
         <v>0.2426216493906066</v>
       </c>
       <c r="N105" t="n">
-        <v>0.02953954500555422</v>
+        <v>0.02953945893926102</v>
       </c>
       <c r="O105" t="n">
-        <v>-0.3411774718941119</v>
+        <v>-0.3411774014063056</v>
       </c>
       <c r="P105" t="n">
-        <v>-0.1298593048672925</v>
+        <v>-0.1298592738350069</v>
       </c>
     </row>
     <row r="106">
@@ -13848,16 +13848,16 @@
         <v>0.2951264594859881</v>
       </c>
       <c r="M107" t="n">
-        <v>0.2924094208848458</v>
+        <v>0.2924093356494368</v>
       </c>
       <c r="N107" t="n">
-        <v>0.4010989395973596</v>
+        <v>0.4010988394228037</v>
       </c>
       <c r="O107" t="n">
-        <v>2.76978514142965</v>
+        <v>2.769785866621858</v>
       </c>
       <c r="P107" t="n">
-        <v>0.5563437743991351</v>
+        <v>0.556343874196892</v>
       </c>
     </row>
     <row r="108">
@@ -13909,13 +13909,13 @@
         <v>0.4597595457011148</v>
       </c>
       <c r="N108" t="n">
-        <v>0.6313008595449321</v>
+        <v>0.631300987457402</v>
       </c>
       <c r="O108" t="n">
-        <v>2.3813751026794</v>
+        <v>2.381375652260126</v>
       </c>
       <c r="P108" t="n">
-        <v>0.5009438656101068</v>
+        <v>0.5009439469271006</v>
       </c>
     </row>
     <row r="109">
@@ -13967,13 +13967,13 @@
         <v>0.03474549707494612</v>
       </c>
       <c r="N109" t="n">
-        <v>-0.008878822593938018</v>
+        <v>-0.008878762708471544</v>
       </c>
       <c r="O109" t="n">
-        <v>0.6160834825197465</v>
+        <v>0.6160831640813769</v>
       </c>
       <c r="P109" t="n">
-        <v>0.1735130688778941</v>
+        <v>0.1735129918002725</v>
       </c>
     </row>
     <row r="110">
@@ -14144,10 +14144,10 @@
         <v>0.2668848858699566</v>
       </c>
       <c r="O112" t="n">
-        <v>4.435796034935206</v>
+        <v>4.435797034591407</v>
       </c>
       <c r="P112" t="n">
-        <v>0.7582787099952339</v>
+        <v>0.7582788177791473</v>
       </c>
     </row>
     <row r="113">
@@ -14193,19 +14193,19 @@
         <v>0.04115270142450123</v>
       </c>
       <c r="L113" t="n">
-        <v>0.2680506289074729</v>
+        <v>0.2680507141746198</v>
       </c>
       <c r="M113" t="n">
         <v>0.0792342205557337</v>
       </c>
       <c r="N113" t="n">
-        <v>0.5505758720099143</v>
+        <v>0.550575999505337</v>
       </c>
       <c r="O113" t="n">
-        <v>1.134175483229904</v>
+        <v>1.134175724758644</v>
       </c>
       <c r="P113" t="n">
-        <v>0.2874885502696041</v>
+        <v>0.2874885988387867</v>
       </c>
     </row>
     <row r="114">
@@ -14254,7 +14254,7 @@
         <v>0.233945933778261</v>
       </c>
       <c r="M114" t="n">
-        <v>0.1219292273560282</v>
+        <v>0.1219291241085021</v>
       </c>
       <c r="N114" t="n">
         <v>-0.01161769372321875</v>
@@ -14312,16 +14312,16 @@
         <v>0.2698583201298184</v>
       </c>
       <c r="M115" t="n">
-        <v>0.288197886554131</v>
+        <v>0.2881977831260916</v>
       </c>
       <c r="N115" t="n">
         <v>0.1799833583947807</v>
       </c>
       <c r="O115" t="n">
-        <v>0.08638996361213547</v>
+        <v>0.08638981649116206</v>
       </c>
       <c r="P115" t="n">
-        <v>0.02800505039613066</v>
+        <v>0.02800500399133554</v>
       </c>
     </row>
     <row r="116">
@@ -14376,10 +14376,10 @@
         <v>0.2038745949030996</v>
       </c>
       <c r="O116" t="n">
-        <v>1.14181584864308</v>
+        <v>1.14181568910761</v>
       </c>
       <c r="P116" t="n">
-        <v>0.2890231269170007</v>
+        <v>0.2890230949122394</v>
       </c>
     </row>
     <row r="117">
@@ -14434,10 +14434,10 @@
         <v>0.4028933869863134</v>
       </c>
       <c r="O117" t="n">
-        <v>0.57740644355245</v>
+        <v>0.5774065441221992</v>
       </c>
       <c r="P117" t="n">
-        <v>0.1640756465365611</v>
+        <v>0.1640756712756497</v>
       </c>
     </row>
     <row r="118">
@@ -14483,7 +14483,7 @@
         <v>0.06003481247780407</v>
       </c>
       <c r="L118" t="n">
-        <v>0.1873102608175619</v>
+        <v>0.1873101672411925</v>
       </c>
       <c r="M118" t="n">
         <v>0.2434280499716643</v>
@@ -14492,10 +14492,10 @@
         <v>0.3518066131092066</v>
       </c>
       <c r="O118" t="n">
-        <v>1.942559503055994</v>
+        <v>1.942558640912764</v>
       </c>
       <c r="P118" t="n">
-        <v>0.4329853525931819</v>
+        <v>0.4329852126426004</v>
       </c>
     </row>
     <row r="119">
@@ -14541,19 +14541,19 @@
         <v>-0.1734470979243943</v>
       </c>
       <c r="L119" t="n">
-        <v>0.1615722239698596</v>
+        <v>0.1615721225540356</v>
       </c>
       <c r="M119" t="n">
         <v>0.4027373342147798</v>
       </c>
       <c r="N119" t="n">
-        <v>0.7385932122899406</v>
+        <v>0.7385933258901982</v>
       </c>
       <c r="O119" t="n">
-        <v>2.101789724167589</v>
+        <v>2.101790447333808</v>
       </c>
       <c r="P119" t="n">
-        <v>0.4583802836006075</v>
+        <v>0.4583803969385369</v>
       </c>
     </row>
     <row r="120">
@@ -14776,16 +14776,16 @@
         <v>0.2806075474317227</v>
       </c>
       <c r="M123" t="n">
-        <v>0.2597694309774481</v>
+        <v>0.2597695701578053</v>
       </c>
       <c r="N123" t="n">
-        <v>0.361278726631282</v>
+        <v>0.3612788078881188</v>
       </c>
       <c r="O123" t="n">
-        <v>1.728341877290632</v>
+        <v>1.728342366905601</v>
       </c>
       <c r="P123" t="n">
-        <v>0.397331972640933</v>
+        <v>0.3973320562270619</v>
       </c>
     </row>
     <row r="124">
@@ -14840,10 +14840,10 @@
         <v>0.2602788682703172</v>
       </c>
       <c r="O124" t="n">
-        <v>-0.03639833484571176</v>
+        <v>-0.03639827309442067</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.01228303346739268</v>
+        <v>-0.01228301236849572</v>
       </c>
     </row>
     <row r="125">
@@ -15008,16 +15008,16 @@
         <v>0.1611759291884636</v>
       </c>
       <c r="M127" t="n">
-        <v>0.197455151828585</v>
+        <v>0.1974552450799218</v>
       </c>
       <c r="N127" t="n">
         <v>0.7923196783298816</v>
       </c>
       <c r="O127" t="n">
-        <v>0.2745470743304379</v>
+        <v>0.2745472856201485</v>
       </c>
       <c r="P127" t="n">
-        <v>0.08422302726028819</v>
+        <v>0.08422308717311577</v>
       </c>
     </row>
     <row r="128">
@@ -15069,13 +15069,13 @@
         <v>0.05796844231305687</v>
       </c>
       <c r="N128" t="n">
-        <v>-0.01175024730819807</v>
+        <v>-0.01175033601239683</v>
       </c>
       <c r="O128" t="n">
-        <v>-0.2716189788671852</v>
+        <v>-0.2716190270539758</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.1002547959412622</v>
+        <v>-0.1002548157824503</v>
       </c>
     </row>
     <row r="129">
@@ -15121,7 +15121,7 @@
         <v>0.1599101838035186</v>
       </c>
       <c r="L129" t="n">
-        <v>0.08876640525941037</v>
+        <v>0.0887663250254036</v>
       </c>
       <c r="M129" t="n">
         <v>0.1910975542508206</v>
@@ -15130,10 +15130,10 @@
         <v>0.2497442050257621</v>
       </c>
       <c r="O129" t="n">
-        <v>0.04545500540154679</v>
+        <v>0.04545515335661232</v>
       </c>
       <c r="P129" t="n">
-        <v>0.01492772274497955</v>
+        <v>0.01492777062323669</v>
       </c>
     </row>
     <row r="130">
@@ -15188,10 +15188,10 @@
         <v>0.2556310087071092</v>
       </c>
       <c r="O130" t="n">
-        <v>-0.06273786320393893</v>
+        <v>-0.06273766141384074</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.02136587030568626</v>
+        <v>-0.02136580007323119</v>
       </c>
     </row>
     <row r="131">
@@ -15246,10 +15246,10 @@
         <v>0.3199983311336032</v>
       </c>
       <c r="O131" t="n">
-        <v>3.0383914559864</v>
+        <v>3.038391077519522</v>
       </c>
       <c r="P131" t="n">
-        <v>0.5924634434339906</v>
+        <v>0.5924633936868993</v>
       </c>
     </row>
     <row r="132">
@@ -15301,7 +15301,7 @@
         <v>0.4416566393816044</v>
       </c>
       <c r="N132" t="n">
-        <v>0.5061040959209417</v>
+        <v>0.5061042413781514</v>
       </c>
     </row>
     <row r="133">
@@ -15356,10 +15356,10 @@
         <v>0.1764416684032228</v>
       </c>
       <c r="O133" t="n">
-        <v>0.02352683680385326</v>
+        <v>0.02352698110083384</v>
       </c>
       <c r="P133" t="n">
-        <v>0.007781569052391912</v>
+        <v>0.007781616411459691</v>
       </c>
     </row>
     <row r="134">
@@ -15463,10 +15463,10 @@
         <v>0.05924875548077302</v>
       </c>
       <c r="L135" t="n">
-        <v>0.03094295260144464</v>
+        <v>0.03094306693946658</v>
       </c>
       <c r="M135" t="n">
-        <v>0.3979695690265095</v>
+        <v>0.3979694639061675</v>
       </c>
       <c r="N135" t="n">
         <v>0.2688745690365633</v>
@@ -15585,7 +15585,7 @@
         <v>0.2096993657857555</v>
       </c>
       <c r="N137" t="n">
-        <v>0.09685890221798399</v>
+        <v>0.09685902300120719</v>
       </c>
       <c r="O137" t="n">
         <v>0.5344192772569114</v>
@@ -15643,13 +15643,13 @@
         <v>0.207852537958588</v>
       </c>
       <c r="N138" t="n">
-        <v>0.03591388403071027</v>
+        <v>0.03591399569517129</v>
       </c>
       <c r="O138" t="n">
-        <v>0.4951086766703079</v>
+        <v>0.4951087929712361</v>
       </c>
       <c r="P138" t="n">
-        <v>0.1434686281966147</v>
+        <v>0.1434686578458439</v>
       </c>
     </row>
     <row r="139">
@@ -15695,19 +15695,19 @@
         <v>0.0106549018478348</v>
       </c>
       <c r="L139" t="n">
-        <v>0.2299356304907236</v>
+        <v>0.2299354896056913</v>
       </c>
       <c r="M139" t="n">
-        <v>0.3625924618842384</v>
+        <v>0.3625923754268563</v>
       </c>
       <c r="N139" t="n">
-        <v>0.1584939754616426</v>
+        <v>0.1584937254745411</v>
       </c>
       <c r="O139" t="n">
-        <v>0.3207883213743929</v>
+        <v>0.3207880776731418</v>
       </c>
       <c r="P139" t="n">
-        <v>0.09717964027357828</v>
+        <v>0.09717957279264944</v>
       </c>
     </row>
     <row r="140">
@@ -15762,10 +15762,10 @@
         <v>0.3282486622814267</v>
       </c>
       <c r="O140" t="n">
-        <v>0.6564045154231217</v>
+        <v>0.6564043455502537</v>
       </c>
       <c r="P140" t="n">
-        <v>0.1831926647698092</v>
+        <v>0.1831926243222946</v>
       </c>
     </row>
     <row r="141">
@@ -15814,10 +15814,10 @@
         <v>0.2212023219392891</v>
       </c>
       <c r="M141" t="n">
-        <v>0.3098373256777838</v>
+        <v>0.3098374456663628</v>
       </c>
       <c r="N141" t="n">
-        <v>0.2132687507679107</v>
+        <v>0.2132686478196215</v>
       </c>
       <c r="O141" t="n">
         <v>1.65824820632565</v>
@@ -15878,10 +15878,10 @@
         <v>0.746335426559219</v>
       </c>
       <c r="O142" t="n">
-        <v>5.851679563433592</v>
+        <v>5.851678843589145</v>
       </c>
       <c r="P142" t="n">
-        <v>0.8993238187980568</v>
+        <v>0.8993237522830881</v>
       </c>
     </row>
     <row r="143">
@@ -15933,13 +15933,13 @@
         <v>0.06876840694591846</v>
       </c>
       <c r="N143" t="n">
-        <v>-0.03770257371681929</v>
+        <v>-0.03770246397862298</v>
       </c>
       <c r="O143" t="n">
-        <v>-0.03211404205222101</v>
+        <v>-0.03211382001918706</v>
       </c>
       <c r="P143" t="n">
-        <v>-0.0108213601185132</v>
+        <v>-0.01082128447932729</v>
       </c>
     </row>
     <row r="144">
@@ -15988,16 +15988,16 @@
         <v>0.1008726431875597</v>
       </c>
       <c r="M144" t="n">
-        <v>0.2149390316537567</v>
+        <v>0.2149389544668314</v>
       </c>
       <c r="N144" t="n">
-        <v>0.3589949093664841</v>
+        <v>0.3589948127902141</v>
       </c>
       <c r="O144" t="n">
-        <v>1.765303526970865</v>
+        <v>1.765303327035146</v>
       </c>
       <c r="P144" t="n">
-        <v>0.4036137129777941</v>
+        <v>0.4036136791499798</v>
       </c>
     </row>
     <row r="145">
@@ -16046,16 +16046,16 @@
         <v>0.1672894275792689</v>
       </c>
       <c r="M145" t="n">
-        <v>0.1945370956683683</v>
+        <v>0.1945371746908182</v>
       </c>
       <c r="N145" t="n">
-        <v>0.2340427334954245</v>
+        <v>0.2340426491597063</v>
       </c>
       <c r="O145" t="n">
-        <v>0.4067876670114596</v>
+        <v>0.4067875574120412</v>
       </c>
       <c r="P145" t="n">
-        <v>0.1204939538380143</v>
+        <v>0.1204939247396906</v>
       </c>
     </row>
     <row r="146">
@@ -16110,10 +16110,10 @@
         <v>0.2006110882352896</v>
       </c>
       <c r="O146" t="n">
-        <v>0.4119572585993982</v>
+        <v>0.4119573879483274</v>
       </c>
       <c r="P146" t="n">
-        <v>0.1218647873998326</v>
+        <v>0.1218648216577167</v>
       </c>
     </row>
     <row r="147">
@@ -16165,13 +16165,13 @@
         <v>0.208877084719957</v>
       </c>
       <c r="N147" t="n">
-        <v>0.2074954391471784</v>
+        <v>0.2074953225678293</v>
       </c>
       <c r="O147" t="n">
-        <v>1.285943798589527</v>
+        <v>1.285943589683133</v>
       </c>
       <c r="P147" t="n">
-        <v>0.3173116003114651</v>
+        <v>0.317311560182916</v>
       </c>
     </row>
     <row r="148">
@@ -16226,10 +16226,10 @@
         <v>0.08559263565214681</v>
       </c>
       <c r="O148" t="n">
-        <v>1.021567870515343</v>
+        <v>1.021568329124859</v>
       </c>
       <c r="P148" t="n">
-        <v>0.2644338357085021</v>
+        <v>0.2644339313242787</v>
       </c>
     </row>
     <row r="149">
@@ -16275,19 +16275,19 @@
         <v>-0.02762495629290196</v>
       </c>
       <c r="L149" t="n">
-        <v>0.4150754646979842</v>
+        <v>0.4150755831285529</v>
       </c>
       <c r="M149" t="n">
-        <v>0.2694740798463908</v>
+        <v>0.2694739845333733</v>
       </c>
       <c r="N149" t="n">
-        <v>0.08919156012856333</v>
+        <v>0.08919148996476656</v>
       </c>
       <c r="O149" t="n">
-        <v>1.447861036405585</v>
+        <v>1.447861390792892</v>
       </c>
       <c r="P149" t="n">
-        <v>0.3477073177998269</v>
+        <v>0.3477073828376069</v>
       </c>
     </row>
     <row r="150">
@@ -16339,7 +16339,7 @@
         <v>0.2907275401831786</v>
       </c>
       <c r="N150" t="n">
-        <v>0.3753777913687988</v>
+        <v>0.37537795426105</v>
       </c>
       <c r="O150" t="n">
         <v>0.6935591552401408</v>
@@ -16458,10 +16458,10 @@
         <v>0.3148048537365535</v>
       </c>
       <c r="O152" t="n">
-        <v>0.5923294787465485</v>
+        <v>0.5923296924027526</v>
       </c>
       <c r="P152" t="n">
-        <v>0.167735038812987</v>
+        <v>0.1677350910412534</v>
       </c>
     </row>
     <row r="153">
@@ -16510,16 +16510,16 @@
         <v>0.1995774392234393</v>
       </c>
       <c r="M153" t="n">
-        <v>0.1538830817549821</v>
+        <v>0.1538832131752486</v>
       </c>
       <c r="N153" t="n">
         <v>0.1944165983564763</v>
       </c>
       <c r="O153" t="n">
-        <v>0.6783702304277859</v>
+        <v>0.6783700914055764</v>
       </c>
       <c r="P153" t="n">
-        <v>0.1883998525623221</v>
+        <v>0.1883998197499395</v>
       </c>
     </row>
     <row r="154">
@@ -16568,7 +16568,7 @@
         <v>0.2555068158625295</v>
       </c>
       <c r="M154" t="n">
-        <v>-0.07226420144123757</v>
+        <v>-0.07226426788433493</v>
       </c>
       <c r="N154" t="n">
         <v>0.1426800390812863</v>
@@ -16632,10 +16632,10 @@
         <v>0.4423474534686043</v>
       </c>
       <c r="O155" t="n">
-        <v>1.64974874520415</v>
+        <v>1.649748425475968</v>
       </c>
       <c r="P155" t="n">
-        <v>0.3837837672562667</v>
+        <v>0.3837837115988281</v>
       </c>
     </row>
     <row r="156">
@@ -16684,16 +16684,16 @@
         <v>-0.06590404692040119</v>
       </c>
       <c r="M156" t="n">
-        <v>0.2818284225067413</v>
+        <v>0.2818285349550516</v>
       </c>
       <c r="N156" t="n">
         <v>0.4572975296495412</v>
       </c>
       <c r="O156" t="n">
-        <v>0.1017656563012168</v>
+        <v>0.1017658224517055</v>
       </c>
       <c r="P156" t="n">
-        <v>0.03283213895760717</v>
+        <v>0.03283219087595457</v>
       </c>
     </row>
     <row r="157">
@@ -16745,13 +16745,13 @@
         <v>0.2483037384729827</v>
       </c>
       <c r="N157" t="n">
-        <v>0.3129699712231659</v>
+        <v>0.3129700540282272</v>
       </c>
       <c r="O157" t="n">
-        <v>0.911935110506779</v>
+        <v>0.911934759331867</v>
       </c>
       <c r="P157" t="n">
-        <v>0.2411503179335819</v>
+        <v>0.2411502419440992</v>
       </c>
     </row>
     <row r="158">
@@ -16806,10 +16806,10 @@
         <v>0.2388355618116293</v>
       </c>
       <c r="O158" t="n">
-        <v>0.04612124584484145</v>
+        <v>0.04612150873463827</v>
       </c>
       <c r="P158" t="n">
-        <v>0.01514327237165647</v>
+        <v>0.01514335740666461</v>
       </c>
     </row>
     <row r="159">
@@ -16855,19 +16855,19 @@
         <v>-0.07753013108769946</v>
       </c>
       <c r="L159" t="n">
-        <v>0.02460786663099657</v>
+        <v>0.02460797653839419</v>
       </c>
       <c r="M159" t="n">
-        <v>0.2398391406574298</v>
+        <v>0.2398392211233948</v>
       </c>
       <c r="N159" t="n">
-        <v>0.5741932995851784</v>
+        <v>0.574193429302408</v>
       </c>
       <c r="O159" t="n">
-        <v>0.4714191636736986</v>
+        <v>0.47141927700617</v>
       </c>
       <c r="P159" t="n">
-        <v>0.1373971507666498</v>
+        <v>0.137397179968396</v>
       </c>
     </row>
     <row r="160">
@@ -17032,16 +17032,16 @@
         <v>0.2750026746194478</v>
       </c>
       <c r="M162" t="n">
-        <v>0.04894762167250888</v>
+        <v>0.04894768534480676</v>
       </c>
       <c r="N162" t="n">
         <v>-0.0618142238700774</v>
       </c>
       <c r="O162" t="n">
-        <v>0.1837162105834809</v>
+        <v>0.1837162916680311</v>
       </c>
       <c r="P162" t="n">
-        <v>0.05782996499858273</v>
+        <v>0.05782998915236348</v>
       </c>
     </row>
     <row r="163">
@@ -17087,19 +17087,19 @@
         <v>0.05757284577156141</v>
       </c>
       <c r="L163" t="n">
-        <v>0.2260943506342663</v>
+        <v>0.2260942272816813</v>
       </c>
       <c r="M163" t="n">
-        <v>0.2518171883600926</v>
+        <v>0.2518174455254247</v>
       </c>
       <c r="N163" t="n">
         <v>0.09266136313305973</v>
       </c>
       <c r="O163" t="n">
-        <v>0.5138342569752308</v>
+        <v>0.5138344450182553</v>
       </c>
       <c r="P163" t="n">
-        <v>0.1482226500652055</v>
+        <v>0.148222697607894</v>
       </c>
     </row>
     <row r="164">
@@ -17154,10 +17154,10 @@
         <v>0.1530009396324745</v>
       </c>
       <c r="O164" t="n">
-        <v>2.412658137002376</v>
+        <v>2.41265774700231</v>
       </c>
       <c r="P164" t="n">
-        <v>0.505558360901206</v>
+        <v>0.5055583035492475</v>
       </c>
     </row>
     <row r="165">
@@ -17212,10 +17212,10 @@
         <v>0.2745893115330065</v>
       </c>
       <c r="O165" t="n">
-        <v>0.9273561556131025</v>
+        <v>0.9273565802440549</v>
       </c>
       <c r="P165" t="n">
-        <v>0.2444782910301169</v>
+        <v>0.2444783824237013</v>
       </c>
     </row>
     <row r="166">
@@ -17328,10 +17328,10 @@
         <v>0.03822551634811489</v>
       </c>
       <c r="O167" t="n">
-        <v>1.049661707551535</v>
+        <v>1.049661848228994</v>
       </c>
       <c r="P167" t="n">
-        <v>0.2702642117852143</v>
+        <v>0.2702642408465199</v>
       </c>
     </row>
     <row r="168">
@@ -17496,10 +17496,10 @@
         <v>0.01395888034870985</v>
       </c>
       <c r="M170" t="n">
-        <v>0.2269082431864082</v>
+        <v>0.2269084427269985</v>
       </c>
       <c r="N170" t="n">
-        <v>-0.01048832539111022</v>
+        <v>-0.01048826049496643</v>
       </c>
       <c r="O170" t="n">
         <v>0.7118812587798358</v>
@@ -17554,16 +17554,16 @@
         <v>0.1678191026609244</v>
       </c>
       <c r="M171" t="n">
-        <v>0.1873442739150646</v>
+        <v>0.1873443631823717</v>
       </c>
       <c r="N171" t="n">
         <v>0.1561673044687533</v>
       </c>
       <c r="O171" t="n">
-        <v>0.7450322838704402</v>
+        <v>0.7450328623225477</v>
       </c>
       <c r="P171" t="n">
-        <v>0.2039297749790323</v>
+        <v>0.2039299080072567</v>
       </c>
     </row>
     <row r="172">
@@ -17664,7 +17664,7 @@
         <v>0.1244247819090012</v>
       </c>
       <c r="N173" t="n">
-        <v>0.1214635478841306</v>
+        <v>0.1214634448081811</v>
       </c>
       <c r="O173" t="n">
         <v>0.002421455505570158</v>
@@ -17838,7 +17838,7 @@
         <v>0.06953106401649012</v>
       </c>
       <c r="N176" t="n">
-        <v>0.1924384482616248</v>
+        <v>0.1924383496966522</v>
       </c>
       <c r="O176" t="n">
         <v>1.034044531355252</v>
@@ -17896,7 +17896,7 @@
         <v>0.1154520280342326</v>
       </c>
       <c r="N177" t="n">
-        <v>0.2964660468880005</v>
+        <v>0.2964661948989955</v>
       </c>
       <c r="O177" t="n">
         <v>1.235249100818372</v>
@@ -17957,10 +17957,10 @@
         <v>0.2882601769348367</v>
       </c>
       <c r="O178" t="n">
-        <v>1.584999815615978</v>
+        <v>1.585000025586331</v>
       </c>
       <c r="P178" t="n">
-        <v>0.372419369561487</v>
+        <v>0.372419406720403</v>
       </c>
     </row>
     <row r="179">
@@ -18122,19 +18122,19 @@
         <v>0.02292750614860717</v>
       </c>
       <c r="L181" t="n">
-        <v>0.1077038972157727</v>
+        <v>0.107703809599818</v>
       </c>
       <c r="M181" t="n">
-        <v>0.1695011502615353</v>
+        <v>0.1695010525969445</v>
       </c>
       <c r="N181" t="n">
         <v>0.1820077809136185</v>
       </c>
       <c r="O181" t="n">
-        <v>0.6417672588580468</v>
+        <v>0.641767066389842</v>
       </c>
       <c r="P181" t="n">
-        <v>0.1796971498140552</v>
+        <v>0.1796971037145039</v>
       </c>
     </row>
     <row r="182">
@@ -18186,13 +18186,13 @@
         <v>-0.01632012943876315</v>
       </c>
       <c r="N182" t="n">
-        <v>0.09339247031380449</v>
+        <v>0.09339237474596862</v>
       </c>
       <c r="O182" t="n">
-        <v>1.04169263085051</v>
+        <v>1.041692964077696</v>
       </c>
       <c r="P182" t="n">
-        <v>0.2686158128508469</v>
+        <v>0.2686158818682964</v>
       </c>
     </row>
     <row r="183">
@@ -18238,19 +18238,19 @@
         <v>-0.03713916661413796</v>
       </c>
       <c r="L183" t="n">
-        <v>0.2334931673923351</v>
+        <v>0.2334933049706014</v>
       </c>
       <c r="M183" t="n">
         <v>0.1925861926918726</v>
       </c>
       <c r="N183" t="n">
-        <v>0.1608182282218265</v>
+        <v>0.160818106377677</v>
       </c>
       <c r="O183" t="n">
-        <v>0.5710274758630605</v>
+        <v>0.5710275874501329</v>
       </c>
       <c r="P183" t="n">
-        <v>0.1625043683315093</v>
+        <v>0.1625043958549948</v>
       </c>
     </row>
     <row r="184">
@@ -18305,10 +18305,10 @@
         <v>0.07591169636447659</v>
       </c>
       <c r="O184" t="n">
-        <v>0.5733346295830346</v>
+        <v>0.573334316145411</v>
       </c>
       <c r="P184" t="n">
-        <v>0.16307316050861</v>
+        <v>0.1630730832733109</v>
       </c>
     </row>
     <row r="185">
@@ -18354,19 +18354,19 @@
         <v>-0.1283311911055905</v>
       </c>
       <c r="L185" t="n">
-        <v>0.145548471188405</v>
+        <v>0.1455483841963872</v>
       </c>
       <c r="M185" t="n">
         <v>0.457045341361257</v>
       </c>
       <c r="N185" t="n">
-        <v>0.1428804776542043</v>
+        <v>0.1428805642414968</v>
       </c>
       <c r="O185" t="n">
-        <v>1.046613438252552</v>
+        <v>1.046613715919508</v>
       </c>
       <c r="P185" t="n">
-        <v>0.269634184480029</v>
+        <v>0.2696342418977182</v>
       </c>
     </row>
     <row r="186">
@@ -18473,16 +18473,16 @@
         <v>0.3938930491355672</v>
       </c>
       <c r="M187" t="n">
-        <v>0.1657352102225396</v>
+        <v>0.1657353219182958</v>
       </c>
       <c r="N187" t="n">
         <v>0.09631141133604948</v>
       </c>
       <c r="O187" t="n">
-        <v>-0.2187836263978854</v>
+        <v>-0.2187836765604173</v>
       </c>
       <c r="P187" t="n">
-        <v>-0.07900533947178467</v>
+        <v>-0.07900535918438778</v>
       </c>
     </row>
     <row r="188">
@@ -18534,13 +18534,13 @@
         <v>0.07837394135196396</v>
       </c>
       <c r="N188" t="n">
-        <v>0.1097553796996988</v>
+        <v>0.1097554900465578</v>
       </c>
       <c r="O188" t="n">
-        <v>1.279184203091325</v>
+        <v>1.279184435811651</v>
       </c>
       <c r="P188" t="n">
-        <v>0.3160118767638935</v>
+        <v>0.3160119215551689</v>
       </c>
     </row>
     <row r="189">
@@ -18586,7 +18586,7 @@
         <v>-0.02335209165622532</v>
       </c>
       <c r="L189" t="n">
-        <v>0.1198074176279937</v>
+        <v>0.1198075309041733</v>
       </c>
       <c r="M189" t="n">
         <v>0.07678436188004967</v>
@@ -18595,10 +18595,10 @@
         <v>0.3458975007247715</v>
       </c>
       <c r="O189" t="n">
-        <v>1.618385538959852</v>
+        <v>1.618384919634363</v>
       </c>
       <c r="P189" t="n">
-        <v>0.3783024598914682</v>
+        <v>0.3783023512217174</v>
       </c>
     </row>
     <row r="190">
@@ -18647,16 +18647,16 @@
         <v>0.2294357092346662</v>
       </c>
       <c r="M190" t="n">
-        <v>0.074809375812805</v>
+        <v>0.07480925521084458</v>
       </c>
       <c r="N190" t="n">
         <v>-0.09383776052038328</v>
       </c>
       <c r="O190" t="n">
-        <v>-0.2570556023425523</v>
+        <v>-0.2570556599666469</v>
       </c>
       <c r="P190" t="n">
-        <v>-0.09429776931155887</v>
+        <v>-0.09429779272752037</v>
       </c>
     </row>
     <row r="191">
@@ -18711,10 +18711,10 @@
         <v>0.1224256069704703</v>
       </c>
       <c r="O191" t="n">
-        <v>0.114802877921439</v>
+        <v>0.114802767153918</v>
       </c>
       <c r="P191" t="n">
-        <v>0.03689001830757577</v>
+        <v>0.03688998396555809</v>
       </c>
     </row>
     <row r="192">
@@ -18763,16 +18763,16 @@
         <v>-0.03283454936074814</v>
       </c>
       <c r="M192" t="n">
-        <v>-0.2931313461439555</v>
+        <v>-0.2931314106033416</v>
       </c>
       <c r="N192" t="n">
         <v>-0.1063324677881976</v>
       </c>
       <c r="O192" t="n">
-        <v>-0.1031241984017149</v>
+        <v>-0.1031243021720744</v>
       </c>
       <c r="P192" t="n">
-        <v>-0.03562908851453062</v>
+        <v>-0.03562912570775911</v>
       </c>
     </row>
     <row r="193">
@@ -18821,16 +18821,16 @@
         <v>0.122692410346956</v>
       </c>
       <c r="M193" t="n">
-        <v>0.2529898216051329</v>
+        <v>0.2529899084653566</v>
       </c>
       <c r="N193" t="n">
         <v>0.1347795700315393</v>
       </c>
       <c r="O193" t="n">
-        <v>1.034354868699292</v>
+        <v>1.034355555610581</v>
       </c>
       <c r="P193" t="n">
-        <v>0.2670942035914154</v>
+        <v>0.267094346205212</v>
       </c>
     </row>
     <row r="194">
@@ -18885,10 +18885,10 @@
         <v>0.2322398198137805</v>
       </c>
       <c r="O194" t="n">
-        <v>1.00171638951557</v>
+        <v>1.001716128144358</v>
       </c>
       <c r="P194" t="n">
-        <v>0.260281366054123</v>
+        <v>0.2602813112009841</v>
       </c>
     </row>
     <row r="195">
@@ -18937,10 +18937,10 @@
         <v>0.1933715993574465</v>
       </c>
       <c r="M195" t="n">
-        <v>0.1216285540509048</v>
+        <v>0.1216284812989576</v>
       </c>
       <c r="N195" t="n">
-        <v>0.3079702452246413</v>
+        <v>0.3079704430911661</v>
       </c>
       <c r="O195" t="n">
         <v>2.534108961387751</v>
@@ -18995,10 +18995,10 @@
         <v>0.1216615709725282</v>
       </c>
       <c r="M196" t="n">
-        <v>0.06321435490120098</v>
+        <v>0.06321425191648089</v>
       </c>
       <c r="N196" t="n">
-        <v>0.3309601088764262</v>
+        <v>0.330960189568575</v>
       </c>
       <c r="O196" t="n">
         <v>1.576402496780561</v>
@@ -19053,16 +19053,16 @@
         <v>0.0388007602175795</v>
       </c>
       <c r="M197" t="n">
-        <v>0.2056446369006655</v>
+        <v>0.2056444990005586</v>
       </c>
       <c r="N197" t="n">
         <v>0.1683303935197449</v>
       </c>
       <c r="O197" t="n">
-        <v>0.6147401888901698</v>
+        <v>0.614739941529153</v>
       </c>
       <c r="P197" t="n">
-        <v>0.173187836175819</v>
+        <v>0.1731877762691845</v>
       </c>
     </row>
     <row r="198">
@@ -19114,13 +19114,13 @@
         <v>0.04725371684911206</v>
       </c>
       <c r="N198" t="n">
-        <v>-0.03541540402104593</v>
+        <v>-0.03541550462432019</v>
       </c>
       <c r="O198" t="n">
-        <v>0.326822533160736</v>
+        <v>0.326822628336688</v>
       </c>
       <c r="P198" t="n">
-        <v>0.09884797660290867</v>
+        <v>0.09884800287718343</v>
       </c>
     </row>
     <row r="199">
@@ -19175,10 +19175,10 @@
         <v>0.3184305662713962</v>
       </c>
       <c r="O199" t="n">
-        <v>1.885944295831312</v>
+        <v>1.885944707444284</v>
       </c>
       <c r="P199" t="n">
-        <v>0.4237355021765301</v>
+        <v>0.4237355698641352</v>
       </c>
     </row>
     <row r="200">
@@ -19227,10 +19227,10 @@
         <v>-0.06543663032148173</v>
       </c>
       <c r="M200" t="n">
-        <v>0.2980460724722998</v>
+        <v>0.2980459617110891</v>
       </c>
       <c r="N200" t="n">
-        <v>0.2045246154396769</v>
+        <v>0.2045245200637347</v>
       </c>
       <c r="O200" t="n">
         <v>0.7460271330508419</v>
@@ -19285,16 +19285,16 @@
         <v>0.2600770574390281</v>
       </c>
       <c r="M201" t="n">
-        <v>-0.02993959092761389</v>
+        <v>-0.02993965935490206</v>
       </c>
       <c r="N201" t="n">
         <v>-0.07587538362187429</v>
       </c>
       <c r="O201" t="n">
-        <v>0.474869493734895</v>
+        <v>0.4748698100857944</v>
       </c>
       <c r="P201" t="n">
-        <v>0.1382854841139507</v>
+        <v>0.1382855654991428</v>
       </c>
     </row>
     <row r="202">
@@ -19340,19 +19340,19 @@
         <v>0.01956677338930901</v>
       </c>
       <c r="L202" t="n">
-        <v>0.07758735901146308</v>
+        <v>0.07758743378536126</v>
       </c>
       <c r="M202" t="n">
-        <v>0.1044664310903802</v>
+        <v>0.1044663525396863</v>
       </c>
       <c r="N202" t="n">
         <v>0.1832005210851206</v>
       </c>
       <c r="O202" t="n">
-        <v>0.07490734023436629</v>
+        <v>0.0749075634416787</v>
       </c>
       <c r="P202" t="n">
-        <v>0.0243703736549723</v>
+        <v>0.02437044455936044</v>
       </c>
     </row>
     <row r="203">
@@ -19514,19 +19514,19 @@
         <v>-0.1174530474668555</v>
       </c>
       <c r="L205" t="n">
-        <v>0.220509464667644</v>
+        <v>0.2205093500945725</v>
       </c>
       <c r="M205" t="n">
         <v>0.1234523427681868</v>
       </c>
       <c r="N205" t="n">
-        <v>0.2620513419349415</v>
+        <v>0.2620514644401013</v>
       </c>
       <c r="O205" t="n">
-        <v>1.611157514508621</v>
+        <v>1.611158038913257</v>
       </c>
       <c r="P205" t="n">
-        <v>0.3770330281681331</v>
+        <v>0.3770331203523403</v>
       </c>
     </row>
     <row r="206">
@@ -19578,13 +19578,13 @@
         <v>-0.02374194781473071</v>
       </c>
       <c r="N206" t="n">
-        <v>-0.01151073400243841</v>
+        <v>-0.01151084051429674</v>
       </c>
       <c r="O206" t="n">
-        <v>0.4171290610331213</v>
+        <v>0.4171292799468351</v>
       </c>
       <c r="P206" t="n">
-        <v>0.1232328631291673</v>
+        <v>0.1232329209670104</v>
       </c>
     </row>
     <row r="207">
@@ -19633,7 +19633,7 @@
         <v>0.1296537850261308</v>
       </c>
       <c r="M207" t="n">
-        <v>0.1083386741992398</v>
+        <v>0.1083387467271788</v>
       </c>
       <c r="N207" t="n">
         <v>0.2531286554250669</v>
@@ -19691,10 +19691,10 @@
         <v>0.1146690682985669</v>
       </c>
       <c r="M208" t="n">
-        <v>0.09301165974629644</v>
+        <v>0.09301177548412953</v>
       </c>
       <c r="N208" t="n">
-        <v>0.09751556176305964</v>
+        <v>0.09751567845668463</v>
       </c>
       <c r="O208" t="n">
         <v>0.6575525945566716</v>
@@ -19752,13 +19752,13 @@
         <v>0.1263487145150688</v>
       </c>
       <c r="N209" t="n">
-        <v>0.354217323111514</v>
+        <v>0.3542174822604978</v>
       </c>
       <c r="O209" t="n">
-        <v>0.8608317452555891</v>
+        <v>0.8608312945089933</v>
       </c>
       <c r="P209" t="n">
-        <v>0.2299922323645425</v>
+        <v>0.2299921330514516</v>
       </c>
     </row>
     <row r="210">
@@ -19810,7 +19810,7 @@
         <v>0.01869824403809406</v>
       </c>
       <c r="N210" t="n">
-        <v>0.03103508007573197</v>
+        <v>0.03103514459810586</v>
       </c>
       <c r="O210" t="n">
         <v>0.5694213694357344</v>
@@ -19871,10 +19871,10 @@
         <v>0.3876550210284095</v>
       </c>
       <c r="O211" t="n">
-        <v>-0.130063432360547</v>
+        <v>-0.1300633449045101</v>
       </c>
       <c r="P211" t="n">
-        <v>-0.04538293081021205</v>
+        <v>-0.04538289882051461</v>
       </c>
     </row>
     <row r="212">
@@ -19923,16 +19923,16 @@
         <v>0.1754879948100831</v>
       </c>
       <c r="M212" t="n">
-        <v>0.05029580151675028</v>
+        <v>0.05029590125482652</v>
       </c>
       <c r="N212" t="n">
-        <v>0.09991421606651718</v>
+        <v>0.09991432545091028</v>
       </c>
       <c r="O212" t="n">
-        <v>1.474150864109736</v>
+        <v>1.474151417574707</v>
       </c>
       <c r="P212" t="n">
-        <v>0.3525149031577808</v>
+        <v>0.3525150040098315</v>
       </c>
     </row>
     <row r="213">
@@ -19987,10 +19987,10 @@
         <v>0.2260503985944828</v>
       </c>
       <c r="O213" t="n">
-        <v>0.6253757627530716</v>
+        <v>0.6253760032672775</v>
       </c>
       <c r="P213" t="n">
-        <v>0.1757579567733258</v>
+        <v>0.1757580147673978</v>
       </c>
     </row>
     <row r="214">
@@ -20039,7 +20039,7 @@
         <v>0.1609852515062458</v>
       </c>
       <c r="M214" t="n">
-        <v>-0.1083466658530802</v>
+        <v>-0.1083467236108108</v>
       </c>
       <c r="N214" t="n">
         <v>-0.2111783356488608</v>
@@ -20161,10 +20161,10 @@
         <v>0.1464298613616704</v>
       </c>
       <c r="O216" t="n">
-        <v>0.7094488699463157</v>
+        <v>0.7094489897589547</v>
       </c>
       <c r="P216" t="n">
-        <v>0.1956902975150221</v>
+        <v>0.1956903254497186</v>
       </c>
     </row>
     <row r="217">
@@ -20277,10 +20277,10 @@
         <v>-0.2046635943006113</v>
       </c>
       <c r="O218" t="n">
-        <v>-0.3867872667254293</v>
+        <v>-0.3867873292555027</v>
       </c>
       <c r="P218" t="n">
-        <v>-0.150421092878779</v>
+        <v>-0.1504211217563231</v>
       </c>
     </row>
     <row r="219">
@@ -20329,7 +20329,7 @@
         <v>0.1577468651635856</v>
       </c>
       <c r="M219" t="n">
-        <v>0.1013052487506894</v>
+        <v>0.1013051592412286</v>
       </c>
       <c r="N219" t="n">
         <v>0.1839532500816738</v>
@@ -20390,13 +20390,13 @@
         <v>0.1248544627486428</v>
       </c>
       <c r="N220" t="n">
-        <v>0.1601501902002829</v>
+        <v>0.1601500896049579</v>
       </c>
       <c r="O220" t="n">
-        <v>1.117684951583852</v>
+        <v>1.117684783996177</v>
       </c>
       <c r="P220" t="n">
-        <v>0.2841638797759916</v>
+        <v>0.2841638459009426</v>
       </c>
     </row>
     <row r="221">
@@ -20445,7 +20445,7 @@
         <v>0.1403468706642472</v>
       </c>
       <c r="M221" t="n">
-        <v>0.04764631667017838</v>
+        <v>0.04764624961589181</v>
       </c>
       <c r="N221" t="n">
         <v>-0.06903470029249159</v>
@@ -20500,19 +20500,19 @@
         <v>-0.02450962808429602</v>
       </c>
       <c r="L222" t="n">
-        <v>0.01654772460133813</v>
+        <v>0.01654779161921027</v>
       </c>
       <c r="M222" t="n">
-        <v>0.137297412598987</v>
+        <v>0.1372974964837717</v>
       </c>
       <c r="N222" t="n">
-        <v>0.2292225584710019</v>
+        <v>0.2292224604777728</v>
       </c>
       <c r="O222" t="n">
-        <v>0.2374060016876662</v>
+        <v>0.2374062002923845</v>
       </c>
       <c r="P222" t="n">
-        <v>0.07358740053254609</v>
+        <v>0.07358745796977417</v>
       </c>
     </row>
     <row r="223">
@@ -20561,10 +20561,10 @@
         <v>-0.1876475009569749</v>
       </c>
       <c r="M223" t="n">
-        <v>0.2936224923920017</v>
+        <v>0.2936223809829337</v>
       </c>
       <c r="N223" t="n">
-        <v>0.3151372830978185</v>
+        <v>0.3151371679521506</v>
       </c>
       <c r="O223" t="n">
         <v>-0.3222818137273923</v>
@@ -20625,10 +20625,10 @@
         <v>-0.12160413915276</v>
       </c>
       <c r="O224" t="n">
-        <v>0.5409373487912685</v>
+        <v>0.5409374663583197</v>
       </c>
       <c r="P224" t="n">
-        <v>0.1550345994623281</v>
+        <v>0.1550346288370912</v>
       </c>
     </row>
     <row r="225">
@@ -20680,7 +20680,7 @@
         <v>0.1063165329576226</v>
       </c>
       <c r="N225" t="n">
-        <v>0.07315819573082116</v>
+        <v>0.0731582600021512</v>
       </c>
       <c r="O225" t="n">
         <v>0.257448790421108</v>
@@ -20738,13 +20738,13 @@
         <v>0.08695517569313305</v>
       </c>
       <c r="N226" t="n">
-        <v>0.1936807391751014</v>
+        <v>0.1936808648214865</v>
       </c>
       <c r="O226" t="n">
-        <v>0.501846094780656</v>
+        <v>0.5018461942282939</v>
       </c>
       <c r="P226" t="n">
-        <v>0.145183661360837</v>
+        <v>0.1451836866376852</v>
       </c>
     </row>
     <row r="227">
@@ -20857,10 +20857,10 @@
         <v>0.214916290876604</v>
       </c>
       <c r="O228" t="n">
-        <v>1.850467592172451</v>
+        <v>1.850467269626609</v>
       </c>
       <c r="P228" t="n">
-        <v>0.4178774730411536</v>
+        <v>0.4178774195609807</v>
       </c>
     </row>
     <row r="229">
@@ -20915,10 +20915,10 @@
         <v>-0.04297302344824327</v>
       </c>
       <c r="O229" t="n">
-        <v>-0.1769534518688678</v>
+        <v>-0.1769535604900081</v>
       </c>
       <c r="P229" t="n">
-        <v>-0.06285210804875674</v>
+        <v>-0.06285214927529381</v>
       </c>
     </row>
     <row r="230">
@@ -20973,10 +20973,10 @@
         <v>-0.03335051094494557</v>
       </c>
       <c r="O230" t="n">
-        <v>0.5618655863706314</v>
+        <v>0.5618656833197901</v>
       </c>
       <c r="P230" t="n">
-        <v>0.1602401371580484</v>
+        <v>0.1602401611644468</v>
       </c>
     </row>
     <row r="231">
@@ -21141,16 +21141,16 @@
         <v>-0.003341926837353904</v>
       </c>
       <c r="M233" t="n">
-        <v>0.07624318584521617</v>
+        <v>0.07624311832441699</v>
       </c>
       <c r="N233" t="n">
-        <v>0.3695881671927557</v>
+        <v>0.3695882765372187</v>
       </c>
       <c r="O233" t="n">
-        <v>0.5169728357694483</v>
+        <v>0.5169729699138084</v>
       </c>
       <c r="P233" t="n">
-        <v>0.149015625380239</v>
+        <v>0.1490156592489977</v>
       </c>
     </row>
     <row r="234">
@@ -21254,19 +21254,19 @@
         <v>0.1001104831000912</v>
       </c>
       <c r="L235" t="n">
-        <v>0.06027900683461795</v>
+        <v>0.06027890748444942</v>
       </c>
       <c r="M235" t="n">
-        <v>-0.03077798864080605</v>
+        <v>-0.03077790562230298</v>
       </c>
       <c r="N235" t="n">
         <v>0.08135171377217953</v>
       </c>
       <c r="O235" t="n">
-        <v>0.0120402553442831</v>
+        <v>0.0120401648285946</v>
       </c>
       <c r="P235" t="n">
-        <v>0.003997417806926418</v>
+        <v>0.003997387874809855</v>
       </c>
     </row>
     <row r="236">
@@ -21312,19 +21312,19 @@
         <v>0.1794728941371533</v>
       </c>
       <c r="L236" t="n">
-        <v>0.001797486920679603</v>
+        <v>0.001797584865637747</v>
       </c>
       <c r="M236" t="n">
-        <v>-0.02463004388261159</v>
+        <v>-0.02463013672811465</v>
       </c>
       <c r="N236" t="n">
-        <v>-0.05745540885651501</v>
+        <v>-0.05745532215513338</v>
       </c>
       <c r="O236" t="n">
-        <v>0.4731995975446659</v>
+        <v>0.4731997034494027</v>
       </c>
       <c r="P236" t="n">
-        <v>0.1378557203409636</v>
+        <v>0.1378557476068565</v>
       </c>
     </row>
     <row r="237">
@@ -21379,10 +21379,10 @@
         <v>-0.003850354590233862</v>
       </c>
       <c r="O237" t="n">
-        <v>-0.04851254014665296</v>
+        <v>-0.04851242772626863</v>
       </c>
       <c r="P237" t="n">
-        <v>-0.01643962705471613</v>
+        <v>-0.01643958831809389</v>
       </c>
     </row>
     <row r="238">
@@ -21431,7 +21431,7 @@
         <v>-0.01962881807617511</v>
       </c>
       <c r="M238" t="n">
-        <v>0.2163059508886978</v>
+        <v>0.2163058715262545</v>
       </c>
       <c r="N238" t="n">
         <v>0.1936095575539696</v>
@@ -21486,7 +21486,7 @@
         <v>0.05852789673987457</v>
       </c>
       <c r="L239" t="n">
-        <v>0.09851767424241742</v>
+        <v>0.09851774532567936</v>
       </c>
       <c r="M239" t="n">
         <v>-0.09611010640127415</v>
@@ -21550,13 +21550,13 @@
         <v>0.08447569955799561</v>
       </c>
       <c r="N240" t="n">
-        <v>0.0617259859252719</v>
+        <v>0.06172611172083342</v>
       </c>
       <c r="O240" t="n">
-        <v>0.4200487529103776</v>
+        <v>0.4200488654270607</v>
       </c>
       <c r="P240" t="n">
-        <v>0.1240037278064272</v>
+        <v>0.1240037574930062</v>
       </c>
     </row>
     <row r="241">
@@ -21660,7 +21660,7 @@
         <v>0.07105449518173201</v>
       </c>
       <c r="L242" t="n">
-        <v>0.05087317708047956</v>
+        <v>0.05087309240306825</v>
       </c>
       <c r="M242" t="n">
         <v>-0.006855024360169604</v>
@@ -21669,10 +21669,10 @@
         <v>0.07306712322150921</v>
       </c>
       <c r="O242" t="n">
-        <v>0.8802517514638755</v>
+        <v>0.8802516159234108</v>
       </c>
       <c r="P242" t="n">
-        <v>0.2342562468674416</v>
+        <v>0.2342562172097695</v>
       </c>
     </row>
     <row r="243">
@@ -21776,13 +21776,13 @@
         <v>-0.001733269825582417</v>
       </c>
       <c r="L244" t="n">
-        <v>0.02088975636283052</v>
+        <v>0.02088967355220905</v>
       </c>
       <c r="M244" t="n">
-        <v>0.1369589510608908</v>
+        <v>0.1369588483496638</v>
       </c>
       <c r="N244" t="n">
-        <v>0.1155355119257973</v>
+        <v>0.1155356108027847</v>
       </c>
       <c r="O244" t="n">
         <v>0.05122748267531874</v>
@@ -21895,10 +21895,10 @@
         <v>-0.1079010046297073</v>
       </c>
       <c r="M246" t="n">
-        <v>0.01629470983702319</v>
+        <v>0.01629459344031314</v>
       </c>
       <c r="N246" t="n">
-        <v>0.07386829523937277</v>
+        <v>0.07386823026030997</v>
       </c>
       <c r="O246" t="n">
         <v>0.5254751888218594</v>
@@ -21959,10 +21959,10 @@
         <v>0.0524022581086947</v>
       </c>
       <c r="O247" t="n">
-        <v>0.6595590553342774</v>
+        <v>0.6595587515992649</v>
       </c>
       <c r="P247" t="n">
-        <v>0.1839432989586069</v>
+        <v>0.1839432267295704</v>
       </c>
     </row>
     <row r="248">
@@ -22014,7 +22014,7 @@
         <v>0.06315416662895679</v>
       </c>
       <c r="N248" t="n">
-        <v>0.1270353831001976</v>
+        <v>0.1270354551865183</v>
       </c>
       <c r="O248" t="n">
         <v>0.760251404776535</v>
@@ -22075,10 +22075,10 @@
         <v>0.1073295924306996</v>
       </c>
       <c r="O249" t="n">
-        <v>1.102613200514846</v>
+        <v>1.102612901574736</v>
       </c>
       <c r="P249" t="n">
-        <v>0.2811101210227491</v>
+        <v>0.2811100603085834</v>
       </c>
     </row>
     <row r="250">
@@ -22124,13 +22124,13 @@
         <v>-0.04429590151005736</v>
       </c>
       <c r="L250" t="n">
-        <v>0.1090484540681964</v>
+        <v>0.1090483685953252</v>
       </c>
       <c r="M250" t="n">
-        <v>0.08560610312658046</v>
+        <v>0.08560602122886163</v>
       </c>
       <c r="N250" t="n">
-        <v>0.1258133465224862</v>
+        <v>0.1258134345989976</v>
       </c>
       <c r="O250" t="n">
         <v>0.9386943474263159</v>
@@ -22182,19 +22182,19 @@
         <v>-0.0631066974418254</v>
       </c>
       <c r="L251" t="n">
-        <v>0.04217303664233185</v>
+        <v>0.04217312797850425</v>
       </c>
       <c r="M251" t="n">
-        <v>0.2033045700046801</v>
+        <v>0.2033044482420017</v>
       </c>
       <c r="N251" t="n">
         <v>0.07194305305319482</v>
       </c>
       <c r="O251" t="n">
-        <v>0.6117179135465614</v>
+        <v>0.6117180227688328</v>
       </c>
       <c r="P251" t="n">
-        <v>0.1724554353570846</v>
+        <v>0.1724554618419183</v>
       </c>
     </row>
     <row r="252">
@@ -22249,10 +22249,10 @@
         <v>0.1579762522015904</v>
       </c>
       <c r="O252" t="n">
-        <v>0.3531477147877109</v>
+        <v>0.3531474707366027</v>
       </c>
       <c r="P252" t="n">
-        <v>0.1060677665771006</v>
+        <v>0.1060677000810146</v>
       </c>
     </row>
     <row r="253">
@@ -22304,13 +22304,13 @@
         <v>0.08184658942701595</v>
       </c>
       <c r="N253" t="n">
-        <v>0.1347682560165511</v>
+        <v>0.1347683437223448</v>
       </c>
       <c r="O253" t="n">
-        <v>1.071424348935389</v>
+        <v>1.071424641183766</v>
       </c>
       <c r="P253" t="n">
-        <v>0.2747441442643876</v>
+        <v>0.2747442042137793</v>
       </c>
     </row>
     <row r="254">
@@ -22362,13 +22362,13 @@
         <v>-0.1990565265448342</v>
       </c>
       <c r="N254" t="n">
-        <v>-0.06440018533220138</v>
+        <v>-0.06440025896765222</v>
       </c>
       <c r="O254" t="n">
-        <v>0.4470802001176037</v>
+        <v>0.4470802881944922</v>
       </c>
       <c r="P254" t="n">
-        <v>0.1310909661463828</v>
+        <v>0.1310909890944247</v>
       </c>
     </row>
     <row r="255">
@@ -22478,7 +22478,7 @@
         <v>-0.06186488124742462</v>
       </c>
       <c r="N256" t="n">
-        <v>-0.0853867497926194</v>
+        <v>-0.08538668322897836</v>
       </c>
     </row>
     <row r="257">
@@ -22527,7 +22527,7 @@
         <v>-0.02653753909376066</v>
       </c>
       <c r="M257" t="n">
-        <v>-0.08894376658381409</v>
+        <v>-0.08894366156594913</v>
       </c>
       <c r="N257" t="n">
         <v>0.1869309580021532</v>
@@ -22585,16 +22585,16 @@
         <v>0.04211775320818067</v>
       </c>
       <c r="M258" t="n">
-        <v>-0.06115371109112255</v>
+        <v>-0.06115363578546196</v>
       </c>
       <c r="N258" t="n">
         <v>-0.0290273192638455</v>
       </c>
       <c r="O258" t="n">
-        <v>0.2173720133395016</v>
+        <v>0.2173723931846792</v>
       </c>
       <c r="P258" t="n">
-        <v>0.06776194310565575</v>
+        <v>0.06776205416022751</v>
       </c>
     </row>
     <row r="259">
@@ -22649,10 +22649,10 @@
         <v>0.1977792151320006</v>
       </c>
       <c r="O259" t="n">
-        <v>0.05685315961140169</v>
+        <v>0.05685304678782854</v>
       </c>
       <c r="P259" t="n">
-        <v>0.01860284155467773</v>
+        <v>0.01860280530794678</v>
       </c>
     </row>
     <row r="260">
@@ -22701,16 +22701,16 @@
         <v>0.04369223358288332</v>
       </c>
       <c r="M260" t="n">
-        <v>0.07300382240370151</v>
+        <v>0.07300388797555768</v>
       </c>
       <c r="N260" t="n">
         <v>0.2073200768189316</v>
       </c>
       <c r="O260" t="n">
-        <v>0.2934254724820111</v>
+        <v>0.2934252819238015</v>
       </c>
       <c r="P260" t="n">
-        <v>0.08954992850988064</v>
+        <v>0.08954987500268885</v>
       </c>
     </row>
     <row r="261">
@@ -22820,7 +22820,7 @@
         <v>0.2034907755430173</v>
       </c>
       <c r="N262" t="n">
-        <v>0.1684373236196683</v>
+        <v>0.1684372127817022</v>
       </c>
       <c r="O262" t="n">
         <v>2.605339506588402</v>
@@ -22878,7 +22878,7 @@
         <v>-0.07765022336319227</v>
       </c>
       <c r="N263" t="n">
-        <v>0.04054136915181794</v>
+        <v>0.04054147496131311</v>
       </c>
       <c r="O263" t="n">
         <v>0.7220150225445872</v>
@@ -22997,10 +22997,10 @@
         <v>0.1059596863815906</v>
       </c>
       <c r="O265" t="n">
-        <v>0.3739838899247416</v>
+        <v>0.3739836703164323</v>
       </c>
       <c r="P265" t="n">
-        <v>0.1117160615920696</v>
+        <v>0.1117160023623363</v>
       </c>
     </row>
     <row r="266">
@@ -23043,22 +23043,22 @@
         <v>-0.06186589889055316</v>
       </c>
       <c r="K266" t="n">
-        <v>-0.01791727630516349</v>
+        <v>-0.01791717219581723</v>
       </c>
       <c r="L266" t="n">
-        <v>0.03965917667094043</v>
+        <v>0.0396592933453368</v>
       </c>
       <c r="M266" t="n">
-        <v>0.08743478180744479</v>
+        <v>0.08743465416358731</v>
       </c>
       <c r="N266" t="n">
         <v>0.08708145076727969</v>
       </c>
       <c r="O266" t="n">
-        <v>-0.01438258110449264</v>
+        <v>-0.0143824762443806</v>
       </c>
       <c r="P266" t="n">
-        <v>-0.004817363426377064</v>
+        <v>-0.00481732813379232</v>
       </c>
     </row>
     <row r="267">
@@ -23220,13 +23220,13 @@
         <v>0.1651264926344931</v>
       </c>
       <c r="L269" t="n">
-        <v>0.0260570824856432</v>
+        <v>0.02605718994308748</v>
       </c>
       <c r="M269" t="n">
         <v>-0.09145770471334924</v>
       </c>
       <c r="N269" t="n">
-        <v>-0.1118603351474197</v>
+        <v>-0.1118601741251206</v>
       </c>
       <c r="O269" t="n">
         <v>0.4584672397291001</v>
@@ -23281,7 +23281,7 @@
         <v>0.1262771662011257</v>
       </c>
       <c r="M270" t="n">
-        <v>0.00740920855489513</v>
+        <v>0.007409133759023856</v>
       </c>
       <c r="N270" t="n">
         <v>0.1545872397289216</v>
@@ -23342,13 +23342,13 @@
         <v>0.1429752066881242</v>
       </c>
       <c r="N271" t="n">
-        <v>0.1266468001080709</v>
+        <v>0.1266466972374365</v>
       </c>
       <c r="O271" t="n">
-        <v>0.083644830306566</v>
+        <v>0.08364492547432612</v>
       </c>
       <c r="P271" t="n">
-        <v>0.02713845207135246</v>
+        <v>0.02713848213977221</v>
       </c>
     </row>
     <row r="272">
@@ -23400,13 +23400,13 @@
         <v>-0.007580849490898767</v>
       </c>
       <c r="N272" t="n">
-        <v>-0.04257858330276265</v>
+        <v>-0.04257847782861635</v>
       </c>
       <c r="O272" t="n">
-        <v>0.7182443119360375</v>
+        <v>0.7182439722251714</v>
       </c>
       <c r="P272" t="n">
-        <v>0.1977374757082688</v>
+        <v>0.1977373967741189</v>
       </c>
     </row>
     <row r="273">
@@ -23455,16 +23455,16 @@
         <v>-0.09919683817722535</v>
       </c>
       <c r="M273" t="n">
-        <v>0.07157951933050066</v>
+        <v>0.07157960589870682</v>
       </c>
       <c r="N273" t="n">
-        <v>-0.0797839819321261</v>
+        <v>-0.07978391809266949</v>
       </c>
       <c r="O273" t="n">
-        <v>0.9600771560003332</v>
+        <v>0.9600774456386219</v>
       </c>
       <c r="P273" t="n">
-        <v>0.2514813703534002</v>
+        <v>0.2514814319967056</v>
       </c>
     </row>
     <row r="274">
@@ -23519,10 +23519,10 @@
         <v>0.07330709933010682</v>
       </c>
       <c r="O274" t="n">
-        <v>0.7702330890274236</v>
+        <v>0.7702329794763616</v>
       </c>
       <c r="P274" t="n">
-        <v>0.209697597409394</v>
+        <v>0.2096975724553056</v>
       </c>
     </row>
     <row r="275">
@@ -23568,7 +23568,7 @@
         <v>0.05801783176120945</v>
       </c>
       <c r="L275" t="n">
-        <v>-0.006091298469065864</v>
+        <v>-0.006091411752262244</v>
       </c>
       <c r="M275" t="n">
         <v>0.03876001865908996</v>
@@ -23577,10 +23577,10 @@
         <v>-0.003571739539309782</v>
       </c>
       <c r="O275" t="n">
-        <v>0.08240540409537367</v>
+        <v>0.08240547127266562</v>
       </c>
       <c r="P275" t="n">
-        <v>0.02674670379400612</v>
+        <v>0.02674672503498821</v>
       </c>
     </row>
     <row r="276">
@@ -23626,19 +23626,19 @@
         <v>0.06955734973304328</v>
       </c>
       <c r="L276" t="n">
-        <v>0.07915849762975435</v>
+        <v>0.0791585726329338</v>
       </c>
       <c r="M276" t="n">
         <v>-0.07446167091938993</v>
       </c>
       <c r="N276" t="n">
-        <v>0.002475081802757684</v>
+        <v>0.002475017080103559</v>
       </c>
       <c r="O276" t="n">
-        <v>0.497472341285716</v>
+        <v>0.4974724857055481</v>
       </c>
       <c r="P276" t="n">
-        <v>0.1440708928403263</v>
+        <v>0.1440709296193075</v>
       </c>
     </row>
     <row r="277">
@@ -23687,7 +23687,7 @@
         <v>0.07544192757333734</v>
       </c>
       <c r="M277" t="n">
-        <v>0.1159198982734411</v>
+        <v>0.115919811421713</v>
       </c>
       <c r="N277" t="n">
         <v>0.14057487400985</v>
@@ -23803,10 +23803,10 @@
         <v>0.1663680271624723</v>
       </c>
       <c r="M279" t="n">
-        <v>0.01320027791915823</v>
+        <v>0.01320035239751971</v>
       </c>
       <c r="N279" t="n">
-        <v>0.006408919200304064</v>
+        <v>0.006408992683572867</v>
       </c>
       <c r="O279" t="n">
         <v>-0.5298799986820912</v>
@@ -23864,13 +23864,13 @@
         <v>0.03069090555910359</v>
       </c>
       <c r="N280" t="n">
-        <v>-0.2562534693311129</v>
+        <v>-0.2562535559184511</v>
       </c>
       <c r="O280" t="n">
-        <v>-0.2527020092221874</v>
+        <v>-0.2527020966384255</v>
       </c>
       <c r="P280" t="n">
-        <v>-0.09253210017630908</v>
+        <v>-0.09253213556042361</v>
       </c>
     </row>
     <row r="281">
@@ -23922,7 +23922,7 @@
         <v>-0.01079182542168411</v>
       </c>
       <c r="N281" t="n">
-        <v>0.03068849371589533</v>
+        <v>0.03068838635268945</v>
       </c>
       <c r="O281" t="n">
         <v>0.1381071462379906</v>
@@ -23980,13 +23980,13 @@
         <v>-0.190102778524369</v>
       </c>
       <c r="N282" t="n">
-        <v>0.003755556253113301</v>
+        <v>0.003755659897798358</v>
       </c>
       <c r="O282" t="n">
-        <v>0.04516755335905565</v>
+        <v>0.04516766573230835</v>
       </c>
       <c r="P282" t="n">
-        <v>0.01483469473704635</v>
+        <v>0.01483473110769684</v>
       </c>
     </row>
     <row r="283">
@@ -24038,13 +24038,13 @@
         <v>0.01172056248673536</v>
       </c>
       <c r="N283" t="n">
-        <v>0.174970177609967</v>
+        <v>0.1749702715773087</v>
       </c>
       <c r="O283" t="n">
-        <v>0.4731097751972153</v>
+        <v>0.4731099229016331</v>
       </c>
       <c r="P283" t="n">
-        <v>0.1378325944976682</v>
+        <v>0.1378326325267181</v>
       </c>
     </row>
     <row r="284">
@@ -24264,7 +24264,7 @@
         <v>-0.1402489543772688</v>
       </c>
       <c r="L287" t="n">
-        <v>0.1369263879885703</v>
+        <v>0.1369264722447843</v>
       </c>
       <c r="M287" t="n">
         <v>0.05362770738898193</v>
@@ -24273,10 +24273,10 @@
         <v>0.1841162106050931</v>
       </c>
       <c r="O287" t="n">
-        <v>2.053138237231285</v>
+        <v>2.053137933422651</v>
       </c>
       <c r="P287" t="n">
-        <v>0.4507151822279882</v>
+        <v>0.4507151341092135</v>
       </c>
     </row>
     <row r="288">
@@ -24331,10 +24331,10 @@
         <v>0.107305469495431</v>
       </c>
       <c r="O288" t="n">
-        <v>0.6531884300391799</v>
+        <v>0.6531886959328692</v>
       </c>
       <c r="P288" t="n">
-        <v>0.1824264038665664</v>
+        <v>0.1824264672591591</v>
       </c>
     </row>
     <row r="289">
@@ -24380,7 +24380,7 @@
         <v>-0.09841004476394122</v>
       </c>
       <c r="L289" t="n">
-        <v>0.07755716814252667</v>
+        <v>0.07755704455987633</v>
       </c>
       <c r="M289" t="n">
         <v>0.1384142468246436</v>
@@ -24389,10 +24389,10 @@
         <v>0.05772784098680761</v>
       </c>
       <c r="O289" t="n">
-        <v>0.2257086306317542</v>
+        <v>0.2257085506812184</v>
       </c>
       <c r="P289" t="n">
-        <v>0.07019376076824591</v>
+        <v>0.0701937374993753</v>
       </c>
     </row>
     <row r="290">
@@ -24438,19 +24438,19 @@
         <v>0.07743604497162515</v>
       </c>
       <c r="L290" t="n">
-        <v>0.1436995581265581</v>
+        <v>0.1436996536344581</v>
       </c>
       <c r="M290" t="n">
-        <v>-0.05304209342375255</v>
+        <v>-0.05304202794856783</v>
       </c>
       <c r="N290" t="n">
         <v>-0.156286117406208</v>
       </c>
       <c r="O290" t="n">
-        <v>0.0245244699736451</v>
+        <v>0.02452439333285161</v>
       </c>
       <c r="P290" t="n">
-        <v>0.008108891472623503</v>
+        <v>0.008108866335020837</v>
       </c>
     </row>
     <row r="291">
@@ -24554,13 +24554,13 @@
         <v>-0.06648179299651558</v>
       </c>
       <c r="L292" t="n">
-        <v>0.01794406678573801</v>
+        <v>0.01794413704575071</v>
       </c>
       <c r="M292" t="n">
         <v>0.01447915482248363</v>
       </c>
       <c r="N292" t="n">
-        <v>0.1665839149093091</v>
+        <v>0.1665838226325578</v>
       </c>
       <c r="O292" t="n">
         <v>0.01831545611639163</v>
@@ -24737,10 +24737,10 @@
         <v>0.2097380524665642</v>
       </c>
       <c r="O295" t="n">
-        <v>-0.2602509393143168</v>
+        <v>-0.2602510264573551</v>
       </c>
       <c r="P295" t="n">
-        <v>-0.09559808319461294</v>
+        <v>-0.09559811870770707</v>
       </c>
     </row>
     <row r="296">
@@ -24786,19 +24786,19 @@
         <v>0.04055599291237355</v>
       </c>
       <c r="L296" t="n">
-        <v>0.04064835312679649</v>
+        <v>0.04064844404059609</v>
       </c>
       <c r="M296" t="n">
-        <v>0.02439677767731263</v>
+        <v>0.02439668958091734</v>
       </c>
       <c r="N296" t="n">
-        <v>-0.08429493275171773</v>
+        <v>-0.08429500314528426</v>
       </c>
       <c r="O296" t="n">
-        <v>-0.2002265745051514</v>
+        <v>-0.2002265208074449</v>
       </c>
       <c r="P296" t="n">
-        <v>-0.07176988036013709</v>
+        <v>-0.07176985958599202</v>
       </c>
     </row>
     <row r="297">
@@ -24853,10 +24853,10 @@
         <v>-0.03006769432805956</v>
       </c>
       <c r="O297" t="n">
-        <v>0.3531438908944597</v>
+        <v>0.3531437884193476</v>
       </c>
       <c r="P297" t="n">
-        <v>0.1060667246881266</v>
+        <v>0.1060666967668993</v>
       </c>
     </row>
     <row r="298">
@@ -24911,10 +24911,10 @@
         <v>-0.1848919375617611</v>
       </c>
       <c r="O298" t="n">
-        <v>0.6759953192036665</v>
+        <v>0.6759945479699725</v>
       </c>
       <c r="P298" t="n">
-        <v>0.1878390552761093</v>
+        <v>0.187838873075592</v>
       </c>
     </row>
     <row r="299">
@@ -24966,7 +24966,7 @@
         <v>0.05231615531486966</v>
       </c>
       <c r="N299" t="n">
-        <v>-0.005086963404825284</v>
+        <v>-0.005086860928783965</v>
       </c>
       <c r="O299" t="n">
         <v>0.05226193234634113</v>
@@ -25027,10 +25027,10 @@
         <v>0.05514088002484674</v>
       </c>
       <c r="O300" t="n">
-        <v>3.422994964472405</v>
+        <v>3.422995384915184</v>
       </c>
       <c r="P300" t="n">
-        <v>0.6414921681595995</v>
+        <v>0.641492220172132</v>
       </c>
     </row>
     <row r="301">
@@ -25082,13 +25082,13 @@
         <v>0.01462240425719785</v>
       </c>
       <c r="N301" t="n">
-        <v>-0.04323775317446032</v>
+        <v>-0.04323783874575859</v>
       </c>
       <c r="O301" t="n">
-        <v>0.3164610034964708</v>
+        <v>0.3164610845004081</v>
       </c>
       <c r="P301" t="n">
-        <v>0.09598009411397213</v>
+        <v>0.09598011659310379</v>
       </c>
     </row>
     <row r="302">
@@ -25137,7 +25137,7 @@
         <v>-0.002669244128748915</v>
       </c>
       <c r="M302" t="n">
-        <v>0.01168566752177025</v>
+        <v>0.01168575849834097</v>
       </c>
       <c r="N302" t="n">
         <v>0.0810238665823646</v>
@@ -25195,7 +25195,7 @@
         <v>-0.006558286600209073</v>
       </c>
       <c r="M303" t="n">
-        <v>0.08338781790511707</v>
+        <v>0.08338794102959768</v>
       </c>
       <c r="N303" t="n">
         <v>0.05942286042606448</v>
@@ -25259,10 +25259,10 @@
         <v>0.07250266737941868</v>
       </c>
       <c r="O304" t="n">
-        <v>0.9404762926613384</v>
+        <v>0.9404761398523598</v>
       </c>
       <c r="P304" t="n">
-        <v>0.2472957630017305</v>
+        <v>0.247295730260972</v>
       </c>
     </row>
     <row r="305">
@@ -25314,7 +25314,7 @@
         <v>0.05583073876378153</v>
       </c>
       <c r="N305" t="n">
-        <v>0.1673214669195422</v>
+        <v>0.1673213315623077</v>
       </c>
       <c r="O305" t="n">
         <v>1.096955649957236</v>
@@ -25430,13 +25430,13 @@
         <v>0.06253314170397184</v>
       </c>
       <c r="N307" t="n">
-        <v>0.07573093133407038</v>
+        <v>0.07573084529263197</v>
       </c>
       <c r="O307" t="n">
-        <v>0.2511576603265477</v>
+        <v>0.2511575439342018</v>
       </c>
       <c r="P307" t="n">
-        <v>0.0775497895505326</v>
+        <v>0.07754975613653103</v>
       </c>
     </row>
     <row r="308">
@@ -25488,13 +25488,13 @@
         <v>0.008932546755808346</v>
       </c>
       <c r="N308" t="n">
-        <v>-0.05262647342376459</v>
+        <v>-0.05262640915808181</v>
       </c>
       <c r="O308" t="n">
-        <v>0.5071407149877152</v>
+        <v>0.5071405523414239</v>
       </c>
       <c r="P308" t="n">
-        <v>0.146527829555104</v>
+        <v>0.1465277883117739</v>
       </c>
     </row>
     <row r="309">
@@ -25546,13 +25546,13 @@
         <v>0.06354303669309225</v>
       </c>
       <c r="N309" t="n">
-        <v>0.03544269320724691</v>
+        <v>0.03544261690322958</v>
       </c>
       <c r="O309" t="n">
-        <v>-0.116293131511645</v>
+        <v>-0.1162931870907737</v>
       </c>
       <c r="P309" t="n">
-        <v>-0.04037237080470868</v>
+        <v>-0.04037239092271794</v>
       </c>
     </row>
     <row r="310">
@@ -25601,7 +25601,7 @@
         <v>-0.05049728194277703</v>
       </c>
       <c r="M310" t="n">
-        <v>0.1251454605770199</v>
+        <v>0.1251453518841479</v>
       </c>
       <c r="N310" t="n">
         <v>0.2833679232341106</v>
@@ -25662,13 +25662,13 @@
         <v>-0.03525233849710063</v>
       </c>
       <c r="N311" t="n">
-        <v>-0.08770337447560428</v>
+        <v>-0.08770345473637986</v>
       </c>
       <c r="O311" t="n">
-        <v>0.6315856136460973</v>
+        <v>0.6315853569312901</v>
       </c>
       <c r="P311" t="n">
-        <v>0.1772534064440707</v>
+        <v>0.1772533447007796</v>
       </c>
     </row>
     <row r="312">
@@ -25723,10 +25723,10 @@
         <v>0.06257127876267465</v>
       </c>
       <c r="O312" t="n">
-        <v>0.448097161641835</v>
+        <v>0.4480969815571036</v>
       </c>
       <c r="P312" t="n">
-        <v>0.1313558689115095</v>
+        <v>0.1313558220132001</v>
       </c>
     </row>
     <row r="313">
@@ -25778,13 +25778,13 @@
         <v>0.08482505097924387</v>
       </c>
       <c r="N313" t="n">
-        <v>0.04358233246620591</v>
+        <v>0.04358240038267103</v>
       </c>
       <c r="O313" t="n">
-        <v>0.4754640755988013</v>
+        <v>0.475464211361021</v>
       </c>
       <c r="P313" t="n">
-        <v>0.1384384271322261</v>
+        <v>0.1384384620493584</v>
       </c>
     </row>
     <row r="314">
@@ -25836,13 +25836,13 @@
         <v>0.024070866860189</v>
       </c>
       <c r="N314" t="n">
-        <v>-0.05281302083598882</v>
+        <v>-0.0528130843786111</v>
       </c>
       <c r="O314" t="n">
-        <v>-0.08009040722997229</v>
+        <v>-0.08009034729448394</v>
       </c>
       <c r="P314" t="n">
-        <v>-0.02744303318044239</v>
+        <v>-0.02744301205855681</v>
       </c>
     </row>
     <row r="315">
@@ -25952,13 +25952,13 @@
         <v>0.09419677424891026</v>
       </c>
       <c r="N316" t="n">
-        <v>0.1194429688314971</v>
+        <v>0.1194430651813487</v>
       </c>
       <c r="O316" t="n">
-        <v>1.265828145638486</v>
+        <v>1.265828343003898</v>
       </c>
       <c r="P316" t="n">
-        <v>0.3134362218819902</v>
+        <v>0.3134362600176968</v>
       </c>
     </row>
     <row r="317">
@@ -26010,13 +26010,13 @@
         <v>0.01743667117654391</v>
       </c>
       <c r="N317" t="n">
-        <v>0.05167697983658037</v>
+        <v>0.05167708538127336</v>
       </c>
       <c r="O317" t="n">
-        <v>2.661100359307629</v>
+        <v>2.661100039539732</v>
       </c>
       <c r="P317" t="n">
-        <v>0.5412409684859274</v>
+        <v>0.5412409236142268</v>
       </c>
     </row>
     <row r="318">
@@ -26126,7 +26126,7 @@
         <v>0.01673832078389581</v>
       </c>
       <c r="N319" t="n">
-        <v>-0.02474809734961003</v>
+        <v>-0.02474815654720142</v>
       </c>
       <c r="O319" t="n">
         <v>0.1543098983394677</v>
@@ -26239,16 +26239,16 @@
         <v>0.02632664222766046</v>
       </c>
       <c r="M321" t="n">
-        <v>0.005111514004812134</v>
+        <v>0.00511142010144372</v>
       </c>
       <c r="N321" t="n">
-        <v>0.2529224188701584</v>
+        <v>0.2529222729547933</v>
       </c>
       <c r="O321" t="n">
-        <v>0.5597743585029811</v>
+        <v>0.5597744715726982</v>
       </c>
       <c r="P321" t="n">
-        <v>0.1597220793028009</v>
+        <v>0.1597221073259665</v>
       </c>
     </row>
     <row r="322">
@@ -26297,16 +26297,16 @@
         <v>-0.01212198487681193</v>
       </c>
       <c r="M322" t="n">
-        <v>-0.02129808951355094</v>
+        <v>-0.02129815908582477</v>
       </c>
       <c r="N322" t="n">
         <v>0.07430282070949623</v>
       </c>
       <c r="O322" t="n">
-        <v>0.6425334197640231</v>
+        <v>0.6425332238056911</v>
       </c>
       <c r="P322" t="n">
-        <v>0.1798806304040765</v>
+        <v>0.1798805834831745</v>
       </c>
     </row>
     <row r="323">
@@ -26410,19 +26410,19 @@
         <v>-0.2088360896932284</v>
       </c>
       <c r="L324" t="n">
-        <v>0.233431076510989</v>
+        <v>0.2334309779126602</v>
       </c>
       <c r="M324" t="n">
-        <v>0.05555024618999815</v>
+        <v>0.05555017397995421</v>
       </c>
       <c r="N324" t="n">
-        <v>0.061956299404333</v>
+        <v>0.06195637249352104</v>
       </c>
       <c r="O324" t="n">
-        <v>0.2616605798711209</v>
+        <v>0.2616604767079107</v>
       </c>
       <c r="P324" t="n">
-        <v>0.08055657750808543</v>
+        <v>0.08055654805650647</v>
       </c>
     </row>
     <row r="325">
@@ -26471,16 +26471,16 @@
         <v>-0.01107181985630012</v>
       </c>
       <c r="M325" t="n">
-        <v>0.1158435320768898</v>
+        <v>0.1158434511826532</v>
       </c>
       <c r="N325" t="n">
-        <v>-0.008017626494342567</v>
+        <v>-0.008017562562245506</v>
       </c>
       <c r="O325" t="n">
-        <v>0.3087532514155047</v>
+        <v>0.3087533626979335</v>
       </c>
       <c r="P325" t="n">
-        <v>0.09383695348140209</v>
+        <v>0.09383698448414712</v>
       </c>
     </row>
     <row r="326">
@@ -26526,7 +26526,7 @@
         <v>-0.1123439494260712</v>
       </c>
       <c r="L326" t="n">
-        <v>0.05019112397762715</v>
+        <v>0.05019122791130814</v>
       </c>
       <c r="M326" t="n">
         <v>-0.009948850663024977</v>
@@ -26535,10 +26535,10 @@
         <v>0.1244705262761916</v>
       </c>
       <c r="O326" t="n">
-        <v>1.205685888977078</v>
+        <v>1.205685201278649</v>
       </c>
       <c r="P326" t="n">
-        <v>0.3017109403221201</v>
+        <v>0.3017108050377222</v>
       </c>
     </row>
     <row r="327">
@@ -26590,13 +26590,13 @@
         <v>-0.07920194340701636</v>
       </c>
       <c r="N327" t="n">
-        <v>-0.06496105449226863</v>
+        <v>-0.06496111896513435</v>
       </c>
       <c r="O327" t="n">
-        <v>0.313327220934736</v>
+        <v>0.3133273481278316</v>
       </c>
       <c r="P327" t="n">
-        <v>0.09510975761136331</v>
+        <v>0.09510979296442024</v>
       </c>
     </row>
     <row r="328">
@@ -26761,16 +26761,16 @@
         <v>-0.0395552517840605</v>
       </c>
       <c r="M330" t="n">
-        <v>0.07498595811955688</v>
+        <v>0.07498605389890756</v>
       </c>
       <c r="N330" t="n">
-        <v>0.09787534908099227</v>
+        <v>0.09787524917942658</v>
       </c>
       <c r="O330" t="n">
-        <v>0.34040242142097</v>
+        <v>0.340402570335379</v>
       </c>
       <c r="P330" t="n">
-        <v>0.1025841233543805</v>
+        <v>0.1025841641855654</v>
       </c>
     </row>
     <row r="331">
@@ -26816,19 +26816,19 @@
         <v>0.1513102792449037</v>
       </c>
       <c r="L331" t="n">
-        <v>0.0003053722207884135</v>
+        <v>0.0003052984546809689</v>
       </c>
       <c r="M331" t="n">
-        <v>-0.153578864981929</v>
+        <v>-0.1535788121660245</v>
       </c>
       <c r="N331" t="n">
-        <v>-0.2208254150097639</v>
+        <v>-0.2208253254956951</v>
       </c>
       <c r="O331" t="n">
-        <v>0.1223703135662129</v>
+        <v>0.1223704064337812</v>
       </c>
       <c r="P331" t="n">
-        <v>0.03923091363422948</v>
+        <v>0.03923094229703472</v>
       </c>
     </row>
     <row r="332">
@@ -26877,16 +26877,16 @@
         <v>0.04314084863344791</v>
       </c>
       <c r="M332" t="n">
-        <v>-0.02513794799851754</v>
+        <v>-0.02513784085145065</v>
       </c>
       <c r="N332" t="n">
         <v>-0.06179974592469339</v>
       </c>
       <c r="O332" t="n">
-        <v>0.678943037145038</v>
+        <v>0.6789428782406846</v>
       </c>
       <c r="P332" t="n">
-        <v>0.1885350325084945</v>
+        <v>0.1885349950120074</v>
       </c>
     </row>
     <row r="333">
@@ -26999,10 +26999,10 @@
         <v>-0.1194303358988301</v>
       </c>
       <c r="O334" t="n">
-        <v>-0.08392586231056276</v>
+        <v>-0.08392578715472443</v>
       </c>
       <c r="P334" t="n">
-        <v>-0.02879657010735337</v>
+        <v>-0.02879654354778316</v>
       </c>
     </row>
     <row r="335">
@@ -27115,10 +27115,10 @@
         <v>0.1288424308308804</v>
       </c>
       <c r="O336" t="n">
-        <v>0.6664137880381</v>
+        <v>0.6664132512224343</v>
       </c>
       <c r="P336" t="n">
-        <v>0.1855711343103148</v>
+        <v>0.1855710070043539</v>
       </c>
     </row>
     <row r="337">
@@ -27173,10 +27173,10 @@
         <v>0.1842975028398273</v>
       </c>
       <c r="O337" t="n">
-        <v>4.036511986439706</v>
+        <v>4.036512409402148</v>
       </c>
       <c r="P337" t="n">
-        <v>0.7141281638769579</v>
+        <v>0.7141282118606826</v>
       </c>
     </row>
     <row r="338">
@@ -27222,19 +27222,19 @@
         <v>-0.005871390968125167</v>
       </c>
       <c r="L338" t="n">
-        <v>0.01992600961012303</v>
+        <v>0.0199261146176799</v>
       </c>
       <c r="M338" t="n">
         <v>-0.1103129874670479</v>
       </c>
       <c r="N338" t="n">
-        <v>0.00967147835250981</v>
+        <v>0.009671581259149242</v>
       </c>
       <c r="O338" t="n">
-        <v>0.3121667485466577</v>
+        <v>0.3121666616443703</v>
       </c>
       <c r="P338" t="n">
-        <v>0.0947871116602681</v>
+        <v>0.09478708749171716</v>
       </c>
     </row>
     <row r="339">
@@ -27289,10 +27289,10 @@
         <v>-0.05422594248497314</v>
       </c>
       <c r="O339" t="n">
-        <v>-0.01765098384410657</v>
+        <v>-0.01765109362065054</v>
       </c>
       <c r="P339" t="n">
-        <v>-0.005918622260880024</v>
+        <v>-0.00591865929008939</v>
       </c>
     </row>
     <row r="340">
@@ -27399,16 +27399,16 @@
         <v>0.05826690163560788</v>
       </c>
       <c r="M341" t="n">
-        <v>-0.1187861034660723</v>
+        <v>-0.1187860311276764</v>
       </c>
       <c r="N341" t="n">
-        <v>-0.008107522992982896</v>
+        <v>-0.008107614643583783</v>
       </c>
       <c r="O341" t="n">
-        <v>1.136399178858901</v>
+        <v>1.136399604037165</v>
       </c>
       <c r="P341" t="n">
-        <v>0.2879355595715591</v>
+        <v>0.2879356450116111</v>
       </c>
     </row>
     <row r="342">
@@ -27457,10 +27457,10 @@
         <v>0.01468738527831115</v>
       </c>
       <c r="M342" t="n">
-        <v>-0.03336080319293055</v>
+        <v>-0.03336090582153217</v>
       </c>
       <c r="N342" t="n">
-        <v>-0.009250567870324633</v>
+        <v>-0.009250675682366594</v>
       </c>
       <c r="O342" t="n">
         <v>0.1249051339689056</v>
@@ -27521,10 +27521,10 @@
         <v>0.08720849079060677</v>
       </c>
       <c r="O343" t="n">
-        <v>1.107792505483031</v>
+        <v>1.107792352150045</v>
       </c>
       <c r="P343" t="n">
-        <v>0.2821611653945519</v>
+        <v>0.2821611343039514</v>
       </c>
     </row>
     <row r="344">
@@ -27576,13 +27576,13 @@
         <v>0.06305993134069254</v>
       </c>
       <c r="N344" t="n">
-        <v>-0.03563101034770844</v>
+        <v>-0.03563107309022151</v>
       </c>
       <c r="O344" t="n">
-        <v>0.6852918186185195</v>
+        <v>0.6852916270052241</v>
       </c>
       <c r="P344" t="n">
-        <v>0.1900312631238923</v>
+        <v>0.1900312180227377</v>
       </c>
     </row>
     <row r="345">
@@ -27628,13 +27628,13 @@
         <v>-0.08578645761864201</v>
       </c>
       <c r="L345" t="n">
-        <v>-0.08340013247317224</v>
+        <v>-0.0834001927815482</v>
       </c>
       <c r="M345" t="n">
         <v>0.05077120231228704</v>
       </c>
       <c r="N345" t="n">
-        <v>0.04754761905478055</v>
+        <v>0.04754769782565416</v>
       </c>
       <c r="O345" t="n">
         <v>0.2056580383560733</v>
@@ -27744,7 +27744,7 @@
         <v>0.06707556718373042</v>
       </c>
       <c r="L347" t="n">
-        <v>0.06588533639899197</v>
+        <v>0.06588526090828761</v>
       </c>
       <c r="M347" t="n">
         <v>-0.1042663401882686</v>
@@ -27808,13 +27808,13 @@
         <v>-0.1761416026412569</v>
       </c>
       <c r="N348" t="n">
-        <v>-0.1273621481361327</v>
+        <v>-0.127362090967522</v>
       </c>
       <c r="O348" t="n">
-        <v>0.1842877158860039</v>
+        <v>0.1842880317683353</v>
       </c>
       <c r="P348" t="n">
-        <v>0.05800017983006467</v>
+        <v>0.05800027389603901</v>
       </c>
     </row>
     <row r="349">
@@ -27860,13 +27860,13 @@
         <v>0.2063135217678718</v>
       </c>
       <c r="L349" t="n">
-        <v>-0.03084104869228321</v>
+        <v>-0.03084096100730171</v>
       </c>
       <c r="M349" t="n">
-        <v>-0.267763063273432</v>
+        <v>-0.2677631133273858</v>
       </c>
       <c r="N349" t="n">
-        <v>-0.2999517501469291</v>
+        <v>-0.2999517958969263</v>
       </c>
       <c r="O349" t="n">
         <v>-0.06351099873250599</v>
@@ -27924,13 +27924,13 @@
         <v>0.0118485898030245</v>
       </c>
       <c r="N350" t="n">
-        <v>-0.02175711742340103</v>
+        <v>-0.0217572299024883</v>
       </c>
       <c r="O350" t="n">
-        <v>0.1915046298176559</v>
+        <v>0.1915043795175251</v>
       </c>
       <c r="P350" t="n">
-        <v>0.06014493978006241</v>
+        <v>0.06014486554495124</v>
       </c>
     </row>
     <row r="351">
@@ -27985,10 +27985,10 @@
         <v>-0.2666875697852323</v>
       </c>
       <c r="O351" t="n">
-        <v>-0.244739248188379</v>
+        <v>-0.2447391531572441</v>
       </c>
       <c r="P351" t="n">
-        <v>-0.089320335550787</v>
+        <v>-0.08932029735518454</v>
       </c>
     </row>
     <row r="352">
@@ -28043,10 +28043,10 @@
         <v>0.03661372796923623</v>
       </c>
       <c r="O352" t="n">
-        <v>0.3714572203249091</v>
+        <v>0.3714570559481956</v>
       </c>
       <c r="P352" t="n">
-        <v>0.1110341849027117</v>
+        <v>0.1110341405148512</v>
       </c>
     </row>
     <row r="353">
@@ -28101,10 +28101,10 @@
         <v>-0.07941006491408809</v>
       </c>
       <c r="O353" t="n">
-        <v>0.643113332216773</v>
+        <v>0.6431129851862176</v>
       </c>
       <c r="P353" t="n">
-        <v>0.1800194701893119</v>
+        <v>0.1800193871147335</v>
       </c>
     </row>
     <row r="354">
@@ -28156,13 +28156,13 @@
         <v>-0.06352331412912271</v>
       </c>
       <c r="N354" t="n">
-        <v>-0.06178486779838788</v>
+        <v>-0.06178477968821972</v>
       </c>
       <c r="O354" t="n">
-        <v>0.1850935720560942</v>
+        <v>0.1850932908943039</v>
       </c>
       <c r="P354" t="n">
-        <v>0.05824009975540934</v>
+        <v>0.05824001606674223</v>
       </c>
     </row>
     <row r="355">
@@ -28214,7 +28214,7 @@
         <v>0.0250906914189577</v>
       </c>
       <c r="N355" t="n">
-        <v>0.01650995001084699</v>
+        <v>0.01651002905031729</v>
       </c>
       <c r="O355" t="n">
         <v>0.3629223294715647</v>
@@ -28269,16 +28269,16 @@
         <v>-0.01341156998916826</v>
       </c>
       <c r="M356" t="n">
-        <v>0.007548259248033151</v>
+        <v>0.007548168546477108</v>
       </c>
       <c r="N356" t="n">
-        <v>-0.08700236997463284</v>
+        <v>-0.08700229549759442</v>
       </c>
       <c r="O356" t="n">
-        <v>0.1414559372906092</v>
+        <v>0.1414562865296234</v>
       </c>
       <c r="P356" t="n">
-        <v>0.0450884557772171</v>
+        <v>0.04508856236203651</v>
       </c>
     </row>
     <row r="357">
@@ -28324,19 +28324,19 @@
         <v>-0.08447417436846627</v>
       </c>
       <c r="L357" t="n">
-        <v>-0.0620029298437732</v>
+        <v>-0.06200286948920186</v>
       </c>
       <c r="M357" t="n">
-        <v>0.03413208174776483</v>
+        <v>0.03413215510774958</v>
       </c>
       <c r="N357" t="n">
         <v>-0.01517558157885068</v>
       </c>
       <c r="O357" t="n">
-        <v>0.2744090948668805</v>
+        <v>0.2744098747386656</v>
       </c>
       <c r="P357" t="n">
-        <v>0.08418390070480242</v>
+        <v>0.08418412185939217</v>
       </c>
     </row>
     <row r="358">
@@ -28562,7 +28562,7 @@
         <v>-0.1638045589102987</v>
       </c>
       <c r="N361" t="n">
-        <v>-0.03870339305647397</v>
+        <v>-0.03870359258257594</v>
       </c>
       <c r="O361" t="n">
         <v>1.393853931967944</v>
@@ -28620,13 +28620,13 @@
         <v>-0.1512823877227347</v>
       </c>
       <c r="N362" t="n">
-        <v>-0.1274904219994204</v>
+        <v>-0.1274905154064827</v>
       </c>
       <c r="O362" t="n">
-        <v>0.4342783078802044</v>
+        <v>0.434278181675315</v>
       </c>
       <c r="P362" t="n">
-        <v>0.1277456053349564</v>
+        <v>0.1277455722574583</v>
       </c>
     </row>
     <row r="363">
@@ -28675,16 +28675,16 @@
         <v>-0.05672132228623539</v>
       </c>
       <c r="M363" t="n">
-        <v>-0.07754657826036149</v>
+        <v>-0.07754668082780392</v>
       </c>
       <c r="N363" t="n">
         <v>-0.02238801837007909</v>
       </c>
       <c r="O363" t="n">
-        <v>0.8308253519883479</v>
+        <v>0.8308251499729498</v>
       </c>
       <c r="P363" t="n">
-        <v>0.2233450598544247</v>
+        <v>0.2233450148593177</v>
       </c>
     </row>
     <row r="364">
@@ -28788,7 +28788,7 @@
         <v>-0.04884694993730776</v>
       </c>
       <c r="L365" t="n">
-        <v>0.007847220850388581</v>
+        <v>0.007847300170800819</v>
       </c>
       <c r="M365" t="n">
         <v>0.01356925625297989</v>
@@ -28797,10 +28797,10 @@
         <v>-0.170557697214108</v>
       </c>
       <c r="O365" t="n">
-        <v>-0.1082509461538397</v>
+        <v>-0.1082510082522965</v>
       </c>
       <c r="P365" t="n">
-        <v>-0.0374701226671732</v>
+        <v>-0.03747014500964019</v>
       </c>
     </row>
     <row r="366">
@@ -28849,10 +28849,10 @@
         <v>-0.07834755820645434</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.04448854774873146</v>
+        <v>-0.04448848073262768</v>
       </c>
       <c r="N366" t="n">
-        <v>-0.03151956243722009</v>
+        <v>-0.03151963128485502</v>
       </c>
       <c r="O366" t="n">
         <v>0.3908909645743852</v>
@@ -28904,19 +28904,19 @@
         <v>-0.01240292391193309</v>
       </c>
       <c r="L367" t="n">
-        <v>0.03051675037984203</v>
+        <v>0.03051663690439166</v>
       </c>
       <c r="M367" t="n">
-        <v>-0.06206838146494487</v>
+        <v>-0.06206828746356052</v>
       </c>
       <c r="N367" t="n">
         <v>-0.1919638813711299</v>
       </c>
       <c r="O367" t="n">
-        <v>0.1966151481467251</v>
+        <v>0.1966150716450716</v>
       </c>
       <c r="P367" t="n">
-        <v>0.06165847776219602</v>
+        <v>0.06165845513764801</v>
       </c>
     </row>
     <row r="368">
@@ -29026,13 +29026,13 @@
         <v>-0.05112230605241752</v>
       </c>
       <c r="N369" t="n">
-        <v>-0.09338460160676454</v>
+        <v>-0.09338453986312845</v>
       </c>
       <c r="O369" t="n">
-        <v>0.5511820363749751</v>
+        <v>0.5511822171221734</v>
       </c>
       <c r="P369" t="n">
-        <v>0.1575886383675946</v>
+        <v>0.157588683329198</v>
       </c>
     </row>
     <row r="370">
@@ -29142,13 +29142,13 @@
         <v>-0.0136539522762873</v>
       </c>
       <c r="N371" t="n">
-        <v>0.09559546349496517</v>
+        <v>0.09559558239639476</v>
       </c>
       <c r="O371" t="n">
-        <v>0.2436976084005811</v>
+        <v>0.2436974551803464</v>
       </c>
       <c r="P371" t="n">
-        <v>0.07540388167193623</v>
+        <v>0.07540383750963597</v>
       </c>
     </row>
     <row r="372">
@@ -29255,7 +29255,7 @@
         <v>-0.2125634652148499</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.05522242455637516</v>
+        <v>-0.05522235786979601</v>
       </c>
       <c r="N373" t="n">
         <v>0.01397251812357103</v>
@@ -29313,7 +29313,7 @@
         <v>-0.03646719156633349</v>
       </c>
       <c r="M374" t="n">
-        <v>0.02503009641884368</v>
+        <v>0.02502997418722974</v>
       </c>
       <c r="N374" t="n">
         <v>0.2550013957655162</v>
@@ -29377,10 +29377,10 @@
         <v>-0.03999332302705005</v>
       </c>
       <c r="O375" t="n">
-        <v>0.3694926490560291</v>
+        <v>0.3694922730640104</v>
       </c>
       <c r="P375" t="n">
-        <v>0.1105034236908584</v>
+        <v>0.110503322061869</v>
       </c>
     </row>
     <row r="376">
@@ -29435,10 +29435,10 @@
         <v>-0.1502440819655985</v>
       </c>
       <c r="O376" t="n">
-        <v>-0.03548416262952492</v>
+        <v>-0.03548402742509249</v>
       </c>
       <c r="P376" t="n">
-        <v>-0.01197078202938862</v>
+        <v>-0.01197073586255604</v>
       </c>
     </row>
     <row r="377">
@@ -29481,22 +29481,22 @@
         <v>-0.1016919983177476</v>
       </c>
       <c r="K377" t="n">
-        <v>-0.1070681052347303</v>
+        <v>-0.1070681952484073</v>
       </c>
       <c r="L377" t="n">
         <v>0.0102192674676711</v>
       </c>
       <c r="M377" t="n">
-        <v>-0.02859668931924697</v>
+        <v>-0.02859679584901598</v>
       </c>
       <c r="N377" t="n">
         <v>-0.0551992729025097</v>
       </c>
       <c r="O377" t="n">
-        <v>0.06579106161397363</v>
+        <v>0.0657909333761999</v>
       </c>
       <c r="P377" t="n">
-        <v>0.02146625648562317</v>
+        <v>0.0214662155174421</v>
       </c>
     </row>
     <row r="378">
@@ -29609,10 +29609,10 @@
         <v>0.09805330230220255</v>
       </c>
       <c r="O379" t="n">
-        <v>2.150974163473452</v>
+        <v>2.15097393901056</v>
       </c>
       <c r="P379" t="n">
-        <v>0.466048306902858</v>
+        <v>0.4660482720910364</v>
       </c>
     </row>
     <row r="380">
@@ -29667,10 +29667,10 @@
         <v>-0.002529231994030878</v>
       </c>
       <c r="O380" t="n">
-        <v>0.3088529242179285</v>
+        <v>0.3088527392493106</v>
       </c>
       <c r="P380" t="n">
-        <v>0.09386472113655975</v>
+        <v>0.09386466960781226</v>
       </c>
     </row>
     <row r="381">
@@ -29719,16 +29719,16 @@
         <v>-0.01896929266382774</v>
       </c>
       <c r="M381" t="n">
-        <v>-0.1128336186492742</v>
+        <v>-0.1128336821654866</v>
       </c>
       <c r="N381" t="n">
         <v>-0.05046890175802243</v>
       </c>
       <c r="O381" t="n">
-        <v>1.312629176828259</v>
+        <v>1.312629392630781</v>
       </c>
       <c r="P381" t="n">
-        <v>0.3224177407851678</v>
+        <v>0.3224177819188809</v>
       </c>
     </row>
     <row r="382">
@@ -29835,16 +29835,16 @@
         <v>-0.07662937104978107</v>
       </c>
       <c r="M383" t="n">
-        <v>-0.2056435173442478</v>
+        <v>-0.2056435901868068</v>
       </c>
       <c r="N383" t="n">
-        <v>-0.1123889224292159</v>
+        <v>-0.112389013378593</v>
       </c>
       <c r="O383" t="n">
-        <v>0.03271097616963337</v>
+        <v>0.0327109146120006</v>
       </c>
       <c r="P383" t="n">
-        <v>0.01078688349179768</v>
+        <v>0.01078686340820201</v>
       </c>
     </row>
     <row r="384">
@@ -29954,13 +29954,13 @@
         <v>-0.05884752082606259</v>
       </c>
       <c r="N385" t="n">
-        <v>-0.09798719546058321</v>
+        <v>-0.0979872493075804</v>
       </c>
       <c r="O385" t="n">
-        <v>0.34980339832885</v>
+        <v>0.3498032777483429</v>
       </c>
       <c r="P385" t="n">
-        <v>0.1051557961171863</v>
+        <v>0.1051557632086284</v>
       </c>
     </row>
     <row r="386">
@@ -30067,16 +30067,16 @@
         <v>-0.06527774309820134</v>
       </c>
       <c r="M387" t="n">
-        <v>-0.001218748811042447</v>
+        <v>-0.001218689062181921</v>
       </c>
       <c r="N387" t="n">
-        <v>0.01281012017206895</v>
+        <v>0.01281018161118097</v>
       </c>
       <c r="O387" t="n">
-        <v>0.3745997977119302</v>
+        <v>0.3745996845393142</v>
       </c>
       <c r="P387" t="n">
-        <v>0.1118821509470123</v>
+        <v>0.1118821204327696</v>
       </c>
     </row>
     <row r="388">
@@ -30125,7 +30125,7 @@
         <v>-0.3619770489783946</v>
       </c>
       <c r="M388" t="n">
-        <v>0.1340230053063876</v>
+        <v>0.1340231221999961</v>
       </c>
       <c r="N388" t="n">
         <v>0.08819387576352167</v>
@@ -30186,7 +30186,7 @@
         <v>-0.04760334235661068</v>
       </c>
       <c r="N389" t="n">
-        <v>0.1293691104953463</v>
+        <v>0.1293692134536046</v>
       </c>
       <c r="O389" t="n">
         <v>0.3827859404051002</v>
@@ -30241,16 +30241,16 @@
         <v>0.01579819254293202</v>
       </c>
       <c r="M390" t="n">
-        <v>-0.0211440859023444</v>
+        <v>-0.02114398159795472</v>
       </c>
       <c r="N390" t="n">
         <v>-0.1468547412757493</v>
       </c>
       <c r="O390" t="n">
-        <v>0.3231050846793615</v>
+        <v>0.3231051799641806</v>
       </c>
       <c r="P390" t="n">
-        <v>0.0978207777677782</v>
+        <v>0.09782080412135441</v>
       </c>
     </row>
     <row r="391">
@@ -30305,10 +30305,10 @@
         <v>-0.04067872895288027</v>
       </c>
       <c r="O391" t="n">
-        <v>0.1923502637120738</v>
+        <v>0.1923501865827084</v>
       </c>
       <c r="P391" t="n">
-        <v>0.0603956822639018</v>
+        <v>0.06039565939935443</v>
       </c>
     </row>
     <row r="392">
@@ -30531,10 +30531,10 @@
         <v>0.1575845080841247</v>
       </c>
       <c r="M395" t="n">
-        <v>-0.2551342581430286</v>
+        <v>-0.2551343278331522</v>
       </c>
       <c r="N395" t="n">
-        <v>-0.3016574828432131</v>
+        <v>-0.3016574215866988</v>
       </c>
       <c r="O395" t="n">
         <v>0.2755638051192779</v>
@@ -30592,7 +30592,7 @@
         <v>-0.08046488736395085</v>
       </c>
       <c r="N396" t="n">
-        <v>0.131942366424767</v>
+        <v>0.1319426276794247</v>
       </c>
       <c r="O396" t="n">
         <v>0.8633896162589969</v>
@@ -30705,16 +30705,16 @@
         <v>-0.1188033829617007</v>
       </c>
       <c r="M398" t="n">
-        <v>-0.06637821686765977</v>
+        <v>-0.06637811469896948</v>
       </c>
       <c r="N398" t="n">
-        <v>-0.04542039383414698</v>
+        <v>-0.04542028702703327</v>
       </c>
       <c r="O398" t="n">
-        <v>-0.1723143287670064</v>
+        <v>-0.17231456966203</v>
       </c>
       <c r="P398" t="n">
-        <v>-0.06109465314775553</v>
+        <v>-0.06109474423613825</v>
       </c>
     </row>
     <row r="399">
@@ -30769,10 +30769,10 @@
         <v>-0.07946081747624378</v>
       </c>
       <c r="O399" t="n">
-        <v>0.6874331523384831</v>
+        <v>0.6874329757766386</v>
       </c>
       <c r="P399" t="n">
-        <v>0.1905350681688274</v>
+        <v>0.1905350266455874</v>
       </c>
     </row>
     <row r="400">
@@ -30876,7 +30876,7 @@
         <v>0.01131000976219632</v>
       </c>
       <c r="L401" t="n">
-        <v>-0.102199050155915</v>
+        <v>-0.1021989436500671</v>
       </c>
       <c r="M401" t="n">
         <v>-0.1333220991886794</v>
@@ -30943,10 +30943,10 @@
         <v>-0.1203907669417501</v>
       </c>
       <c r="O402" t="n">
-        <v>-0.09768247664528562</v>
+        <v>-0.09768254949670685</v>
       </c>
       <c r="P402" t="n">
-        <v>-0.0336826056305769</v>
+        <v>-0.03368263163679452</v>
       </c>
     </row>
     <row r="403">
@@ -30998,13 +30998,13 @@
         <v>-0.00463397891529882</v>
       </c>
       <c r="N403" t="n">
-        <v>-0.02048616159708705</v>
+        <v>-0.02048626009011356</v>
       </c>
       <c r="O403" t="n">
-        <v>0.4175000729393434</v>
+        <v>0.4174999698056605</v>
       </c>
       <c r="P403" t="n">
-        <v>0.123330877350269</v>
+        <v>0.123330850106707</v>
       </c>
     </row>
     <row r="404">
@@ -31059,10 +31059,10 @@
         <v>-0.03894411872202175</v>
       </c>
       <c r="O404" t="n">
-        <v>0.515890666793986</v>
+        <v>0.5158907790045171</v>
       </c>
       <c r="P404" t="n">
-        <v>0.1487423344272145</v>
+        <v>0.1487423627716036</v>
       </c>
     </row>
     <row r="405">
@@ -31117,10 +31117,10 @@
         <v>-0.01270176005169488</v>
       </c>
       <c r="O405" t="n">
-        <v>0.1151487422299684</v>
+        <v>0.1151488345935343</v>
       </c>
       <c r="P405" t="n">
-        <v>0.0369972379112764</v>
+        <v>0.03699726654146618</v>
       </c>
     </row>
     <row r="406">
@@ -31172,13 +31172,13 @@
         <v>-0.01004067757042115</v>
       </c>
       <c r="N406" t="n">
-        <v>-0.07995994085481994</v>
+        <v>-0.07995986348471873</v>
       </c>
       <c r="O406" t="n">
-        <v>0.3342813464794951</v>
+        <v>0.3342814278420381</v>
       </c>
       <c r="P406" t="n">
-        <v>0.1009032103688881</v>
+        <v>0.1009032327460484</v>
       </c>
     </row>
     <row r="407">
@@ -31227,7 +31227,7 @@
         <v>0.07426073435826797</v>
       </c>
       <c r="M407" t="n">
-        <v>-0.2537127202194598</v>
+        <v>-0.2537128076415444</v>
       </c>
       <c r="N407" t="n">
         <v>-0.3350446338873102</v>
@@ -31349,10 +31349,10 @@
         <v>-0.09404821369663174</v>
       </c>
       <c r="O409" t="n">
-        <v>0.2727534936040725</v>
+        <v>0.272753589703514</v>
       </c>
       <c r="P409" t="n">
-        <v>0.08371420482873404</v>
+        <v>0.08371423210406737</v>
       </c>
     </row>
     <row r="410">
@@ -31398,7 +31398,7 @@
         <v>0.003470078786707465</v>
       </c>
       <c r="L410" t="n">
-        <v>0.112053676353006</v>
+        <v>0.1120537554591832</v>
       </c>
       <c r="M410" t="n">
         <v>-0.2071642866822303</v>
@@ -31465,10 +31465,10 @@
         <v>-0.08305827719411496</v>
       </c>
       <c r="O411" t="n">
-        <v>0.417435297293355</v>
+        <v>0.4174354161180989</v>
       </c>
       <c r="P411" t="n">
-        <v>0.1233137661009103</v>
+        <v>0.1233137974903422</v>
       </c>
     </row>
     <row r="412">
@@ -31639,10 +31639,10 @@
         <v>-0.2118860187926431</v>
       </c>
       <c r="O414" t="n">
-        <v>-0.3064231207078741</v>
+        <v>-0.306423195470786</v>
       </c>
       <c r="P414" t="n">
-        <v>-0.1148201162393221</v>
+        <v>-0.1148201480447979</v>
       </c>
     </row>
     <row r="415">
@@ -31688,19 +31688,19 @@
         <v>-0.05296773616295058</v>
       </c>
       <c r="L415" t="n">
-        <v>-0.2049091563575425</v>
+        <v>-0.204909213621655</v>
       </c>
       <c r="M415" t="n">
-        <v>-0.05704162643195365</v>
+        <v>-0.05704154588777777</v>
       </c>
       <c r="N415" t="n">
         <v>-0.09022913915023689</v>
       </c>
       <c r="O415" t="n">
-        <v>-0.1142605118359876</v>
+        <v>-0.1142604407701121</v>
       </c>
       <c r="P415" t="n">
-        <v>-0.03963718568804775</v>
+        <v>-0.03963716000366257</v>
       </c>
     </row>
     <row r="416">
@@ -31752,13 +31752,13 @@
         <v>0.04486595725334164</v>
       </c>
       <c r="N416" t="n">
-        <v>-0.06348427171956861</v>
+        <v>-0.06348421099860291</v>
       </c>
       <c r="O416" t="n">
-        <v>0.08555530403533629</v>
+        <v>0.08555554879156402</v>
       </c>
       <c r="P416" t="n">
-        <v>0.02774171521514002</v>
+        <v>0.02774179245553654</v>
       </c>
     </row>
     <row r="417">
@@ -31807,16 +31807,16 @@
         <v>-0.01459136492889301</v>
       </c>
       <c r="M417" t="n">
-        <v>-0.1047148316492771</v>
+        <v>-0.1047149354908489</v>
       </c>
       <c r="N417" t="n">
-        <v>-0.1257724976399641</v>
+        <v>-0.1257725966541463</v>
       </c>
       <c r="O417" t="n">
-        <v>0.02918042087459605</v>
+        <v>0.02918055809908204</v>
       </c>
       <c r="P417" t="n">
-        <v>0.009633700739484663</v>
+        <v>0.009633745612232181</v>
       </c>
     </row>
     <row r="418">
@@ -31920,19 +31920,19 @@
         <v>0.02687199299764553</v>
       </c>
       <c r="L419" t="n">
-        <v>-0.07119070697491003</v>
+        <v>-0.07119076528005841</v>
       </c>
       <c r="M419" t="n">
-        <v>-0.1910391952853466</v>
+        <v>-0.1910391068269973</v>
       </c>
       <c r="N419" t="n">
-        <v>-0.2733911939866355</v>
+        <v>-0.2733912653516067</v>
       </c>
       <c r="O419" t="n">
-        <v>-0.1830202897891333</v>
+        <v>-0.1830203800098593</v>
       </c>
       <c r="P419" t="n">
-        <v>-0.06516042284043877</v>
+        <v>-0.06516045725251673</v>
       </c>
     </row>
     <row r="420">
@@ -31984,13 +31984,13 @@
         <v>-0.07708661036921016</v>
       </c>
       <c r="N420" t="n">
-        <v>-0.1000162090180036</v>
+        <v>-0.1000161360422424</v>
       </c>
       <c r="O420" t="n">
-        <v>-0.2560640969081206</v>
+        <v>-0.2560640470449042</v>
       </c>
       <c r="P420" t="n">
-        <v>-0.0938950431229536</v>
+        <v>-0.09389502287868856</v>
       </c>
     </row>
     <row r="421">
@@ -32161,10 +32161,10 @@
         <v>-0.3258833356899181</v>
       </c>
       <c r="O423" t="n">
-        <v>0.4149386732307214</v>
+        <v>0.4149389182294019</v>
       </c>
       <c r="P423" t="n">
-        <v>0.1226538558209322</v>
+        <v>0.1226539206173087</v>
       </c>
     </row>
     <row r="424">
@@ -32219,10 +32219,10 @@
         <v>-0.1163431150402283</v>
       </c>
       <c r="O424" t="n">
-        <v>0.1540007695693972</v>
+        <v>0.1540005361089616</v>
       </c>
       <c r="P424" t="n">
-        <v>0.04890309321088826</v>
+        <v>0.04890302247800937</v>
       </c>
     </row>
     <row r="425">
@@ -32335,10 +32335,10 @@
         <v>-0.0786163111882352</v>
       </c>
       <c r="O426" t="n">
-        <v>0.2823574481947888</v>
+        <v>0.282357550286801</v>
       </c>
       <c r="P426" t="n">
-        <v>0.08643321063772813</v>
+        <v>0.08643323946904169</v>
       </c>
     </row>
     <row r="427">
@@ -32509,10 +32509,10 @@
         <v>0.08766357753561849</v>
       </c>
       <c r="O429" t="n">
-        <v>1.17974523937251</v>
+        <v>1.17974499662113</v>
       </c>
       <c r="P429" t="n">
-        <v>0.2965877454688735</v>
+        <v>0.2965876973365702</v>
       </c>
     </row>
     <row r="430">
@@ -32622,13 +32622,13 @@
         <v>-0.2225278465102624</v>
       </c>
       <c r="N431" t="n">
-        <v>-0.3242564675170452</v>
+        <v>-0.3242564110534228</v>
       </c>
       <c r="O431" t="n">
-        <v>-0.1274260785274639</v>
+        <v>-0.1274259843798301</v>
       </c>
       <c r="P431" t="n">
-        <v>-0.04441921187482334</v>
+        <v>-0.04441917750689772</v>
       </c>
     </row>
     <row r="432">
@@ -32735,16 +32735,16 @@
         <v>-0.09209658933399856</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.100919439928164</v>
+        <v>-0.100919504982898</v>
       </c>
       <c r="N433" t="n">
-        <v>-0.2057122679278489</v>
+        <v>-0.2057121663807587</v>
       </c>
       <c r="O433" t="n">
-        <v>-0.04748812467257857</v>
+        <v>-0.04748819768932666</v>
       </c>
       <c r="P433" t="n">
-        <v>-0.01608677143867165</v>
+        <v>-0.0160867965799667</v>
       </c>
     </row>
     <row r="434">
@@ -32857,10 +32857,10 @@
         <v>-0.07384305126086688</v>
       </c>
       <c r="O435" t="n">
-        <v>-0.009757015898158361</v>
+        <v>-0.009756918498840861</v>
       </c>
       <c r="P435" t="n">
-        <v>-0.003262974052089529</v>
+        <v>-0.003262941372735639</v>
       </c>
     </row>
     <row r="436">
@@ -32906,19 +32906,19 @@
         <v>-0.02210593254889825</v>
       </c>
       <c r="L436" t="n">
-        <v>-0.08649837194288312</v>
+        <v>-0.08649827543511346</v>
       </c>
       <c r="M436" t="n">
-        <v>-0.2664573137899988</v>
+        <v>-0.2664572515607726</v>
       </c>
       <c r="N436" t="n">
-        <v>-0.2117774765123577</v>
+        <v>-0.2117774046599538</v>
       </c>
       <c r="O436" t="n">
-        <v>1.43755331025545</v>
+        <v>1.437553138467853</v>
       </c>
       <c r="P436" t="n">
-        <v>0.3458129642473713</v>
+        <v>0.345812932631792</v>
       </c>
     </row>
     <row r="437">
@@ -32970,13 +32970,13 @@
         <v>-0.2200022341481681</v>
       </c>
       <c r="N437" t="n">
-        <v>0.4324891680138927</v>
+        <v>0.4324890300416684</v>
       </c>
       <c r="O437" t="n">
-        <v>-0.2928323432274188</v>
+        <v>-0.2928324104760962</v>
       </c>
       <c r="P437" t="n">
-        <v>-0.1090757164492084</v>
+        <v>-0.1090757446902632</v>
       </c>
     </row>
     <row r="438">
@@ -33089,10 +33089,10 @@
         <v>-0.08906271770024465</v>
       </c>
       <c r="O439" t="n">
-        <v>0.2320980320020805</v>
+        <v>0.2320979403004182</v>
       </c>
       <c r="P439" t="n">
-        <v>0.07205011553843255</v>
+        <v>0.07205008894185294</v>
       </c>
     </row>
     <row r="440">
@@ -33202,7 +33202,7 @@
         <v>-0.218179189370874</v>
       </c>
       <c r="N441" t="n">
-        <v>-0.1227921234523515</v>
+        <v>-0.1227923252316778</v>
       </c>
       <c r="O441" t="n">
         <v>0.7378563229102535</v>
@@ -33257,16 +33257,16 @@
         <v>-0.1251192785264849</v>
       </c>
       <c r="M442" t="n">
-        <v>-0.2090563833256373</v>
+        <v>-0.2090564531863851</v>
       </c>
       <c r="N442" t="n">
-        <v>-0.2168744165806277</v>
+        <v>-0.2168744850671327</v>
       </c>
       <c r="O442" t="n">
-        <v>-0.1074308737387188</v>
+        <v>-0.107430606839487</v>
       </c>
       <c r="P442" t="n">
-        <v>-0.03717515838506336</v>
+        <v>-0.03717506241595669</v>
       </c>
     </row>
     <row r="443">
@@ -33312,19 +33312,19 @@
         <v>-0.07872829550368754</v>
       </c>
       <c r="L443" t="n">
-        <v>-0.08991051416027629</v>
+        <v>-0.08991059934689816</v>
       </c>
       <c r="M443" t="n">
-        <v>-0.1211933320781863</v>
+        <v>-0.1211932526471975</v>
       </c>
       <c r="N443" t="n">
-        <v>-0.257446294059461</v>
+        <v>-0.2574463507693698</v>
       </c>
       <c r="O443" t="n">
-        <v>0.04820702639696317</v>
+        <v>0.04820725240686419</v>
       </c>
       <c r="P443" t="n">
-        <v>0.01581749646136066</v>
+        <v>0.01581756947009194</v>
       </c>
     </row>
     <row r="444">
@@ -33550,13 +33550,13 @@
         <v>-0.1076306603309125</v>
       </c>
       <c r="N447" t="n">
-        <v>-0.270209476624508</v>
+        <v>-0.2702094282164607</v>
       </c>
       <c r="O447" t="n">
-        <v>-0.290238641492257</v>
+        <v>-0.2902387330670063</v>
       </c>
       <c r="P447" t="n">
-        <v>-0.1079878214460525</v>
+        <v>-0.1079878598090853</v>
       </c>
     </row>
     <row r="448">
@@ -33669,10 +33669,10 @@
         <v>-0.2838331727445718</v>
       </c>
       <c r="O449" t="n">
-        <v>-0.2741087994318248</v>
+        <v>-0.2741088462311873</v>
       </c>
       <c r="P449" t="n">
-        <v>-0.101281164222102</v>
+        <v>-0.1012811835360476</v>
       </c>
     </row>
     <row r="450">
@@ -33721,16 +33721,16 @@
         <v>-0.08805146609385095</v>
       </c>
       <c r="M450" t="n">
-        <v>-0.1404289897460369</v>
+        <v>-0.1404290604924183</v>
       </c>
       <c r="N450" t="n">
         <v>-0.1421753464069831</v>
       </c>
       <c r="O450" t="n">
-        <v>-0.4205695317649304</v>
+        <v>-0.4205695960593604</v>
       </c>
       <c r="P450" t="n">
-        <v>-0.1663179656228643</v>
+        <v>-0.1663179964583807</v>
       </c>
     </row>
     <row r="451">
@@ -33782,13 +33782,13 @@
         <v>-0.2922639170023709</v>
       </c>
       <c r="N451" t="n">
-        <v>-0.2855611299607895</v>
+        <v>-0.2855611825090132</v>
       </c>
       <c r="O451" t="n">
-        <v>-0.183329747470327</v>
+        <v>-0.1833296788075395</v>
       </c>
       <c r="P451" t="n">
-        <v>-0.06527847139510401</v>
+        <v>-0.06527844519906223</v>
       </c>
     </row>
     <row r="452">
@@ -33840,7 +33840,7 @@
         <v>-0.2875684799340863</v>
       </c>
       <c r="N452" t="n">
-        <v>-0.3901104691895317</v>
+        <v>-0.3901105057317577</v>
       </c>
       <c r="O452" t="n">
         <v>-0.1420146108796105</v>
@@ -33892,7 +33892,7 @@
         <v>-0.1813363891599254</v>
       </c>
       <c r="L453" t="n">
-        <v>-0.06979754141251182</v>
+        <v>-0.06979764945729183</v>
       </c>
       <c r="M453" t="n">
         <v>-0.1606143232743644</v>
@@ -33901,10 +33901,10 @@
         <v>-0.1726011888674269</v>
       </c>
       <c r="O453" t="n">
-        <v>0.2456729057126519</v>
+        <v>0.2456728088342688</v>
       </c>
       <c r="P453" t="n">
-        <v>0.07597291570066012</v>
+        <v>0.07597288780716349</v>
       </c>
     </row>
     <row r="454">
@@ -33959,10 +33959,10 @@
         <v>-0.1531815576277101</v>
       </c>
       <c r="O454" t="n">
-        <v>0.2270736709637524</v>
+        <v>0.2270735856298223</v>
       </c>
       <c r="P454" t="n">
-        <v>0.07059089584551104</v>
+        <v>0.07059087102827499</v>
       </c>
     </row>
     <row r="455">
@@ -34060,13 +34060,13 @@
         <v>-0.1968044973602876</v>
       </c>
       <c r="L456" t="n">
-        <v>-0.1537536944053267</v>
+        <v>-0.1537536113646636</v>
       </c>
       <c r="M456" t="n">
         <v>-0.1482043053606872</v>
       </c>
       <c r="N456" t="n">
-        <v>-0.04669753666766041</v>
+        <v>-0.04669732590740483</v>
       </c>
       <c r="O456" t="n">
         <v>0.53455400613225</v>
@@ -34124,13 +34124,13 @@
         <v>-0.07416158848990451</v>
       </c>
       <c r="N457" t="n">
-        <v>0.02021910019443873</v>
+        <v>0.02021895179168021</v>
       </c>
       <c r="O457" t="n">
-        <v>-0.08752677282863786</v>
+        <v>-0.08752695089692131</v>
       </c>
       <c r="P457" t="n">
-        <v>-0.03007077883102849</v>
+        <v>-0.03007084192462128</v>
       </c>
     </row>
     <row r="458">
@@ -34240,13 +34240,13 @@
         <v>-0.2048037683508682</v>
       </c>
       <c r="N459" t="n">
-        <v>-0.198497574203826</v>
+        <v>-0.1984975045849311</v>
       </c>
       <c r="O459" t="n">
-        <v>-0.1439222917261006</v>
+        <v>-0.1439220534584088</v>
       </c>
       <c r="P459" t="n">
-        <v>-0.05047938932084017</v>
+        <v>-0.05047930122912414</v>
       </c>
     </row>
     <row r="460">
@@ -34295,16 +34295,16 @@
         <v>-0.1137024024290897</v>
       </c>
       <c r="M460" t="n">
-        <v>-0.1651389609533311</v>
+        <v>-0.1651390366707383</v>
       </c>
       <c r="N460" t="n">
         <v>-0.2173126250053036</v>
       </c>
       <c r="O460" t="n">
-        <v>-0.1026253111258163</v>
+        <v>-0.1026252236445505</v>
       </c>
       <c r="P460" t="n">
-        <v>-0.03545031117902386</v>
+        <v>-0.03545027983573401</v>
       </c>
     </row>
     <row r="461">
@@ -34414,7 +34414,7 @@
         <v>-0.1449957359083522</v>
       </c>
       <c r="N462" t="n">
-        <v>-0.08956929219682053</v>
+        <v>-0.08956940069614072</v>
       </c>
       <c r="O462" t="n">
         <v>-0.5137019380420822</v>
@@ -34466,10 +34466,10 @@
         <v>-0.09832988223113759</v>
       </c>
       <c r="L463" t="n">
-        <v>-0.1741008421347251</v>
+        <v>-0.1741008965252091</v>
       </c>
       <c r="M463" t="n">
-        <v>-0.1974571853452927</v>
+        <v>-0.1974571339876176</v>
       </c>
       <c r="N463" t="n">
         <v>-0.2483305867153596</v>
@@ -34582,19 +34582,19 @@
         <v>-0.09727421012593029</v>
       </c>
       <c r="L465" t="n">
-        <v>-0.1975467017035077</v>
+        <v>-0.1975467610154169</v>
       </c>
       <c r="M465" t="n">
-        <v>-0.1484511759423029</v>
+        <v>-0.1484512427338458</v>
       </c>
       <c r="N465" t="n">
         <v>-0.2936674726687735</v>
       </c>
       <c r="O465" t="n">
-        <v>0.2503122701736435</v>
+        <v>0.2503124141660003</v>
       </c>
       <c r="P465" t="n">
-        <v>0.07730703963993624</v>
+        <v>0.0773070809959977</v>
       </c>
     </row>
     <row r="466">
@@ -34649,10 +34649,10 @@
         <v>-0.2860471668606027</v>
       </c>
       <c r="O466" t="n">
-        <v>0.3028084168538292</v>
+        <v>0.3028085829788842</v>
       </c>
       <c r="P466" t="n">
-        <v>0.09217823732328423</v>
+        <v>0.09217828374560288</v>
       </c>
     </row>
     <row r="467">
@@ -34707,10 +34707,10 @@
         <v>-0.2605922313237611</v>
       </c>
       <c r="O467" t="n">
-        <v>-0.01319427891395941</v>
+        <v>-0.01319438761027769</v>
       </c>
       <c r="P467" t="n">
-        <v>-0.004417579241310698</v>
+        <v>-0.00441761579566835</v>
       </c>
     </row>
     <row r="468">
@@ -34756,13 +34756,13 @@
         <v>0.09545406808793766</v>
       </c>
       <c r="L468" t="n">
-        <v>-0.2823066223568079</v>
+        <v>-0.2823066832081081</v>
       </c>
       <c r="M468" t="n">
         <v>-0.3554487407438317</v>
       </c>
       <c r="N468" t="n">
-        <v>-0.4353244824721128</v>
+        <v>-0.4353245201416174</v>
       </c>
       <c r="O468" t="n">
         <v>-0.1657380805716397</v>
@@ -34872,7 +34872,7 @@
         <v>-0.1164913758216635</v>
       </c>
       <c r="L470" t="n">
-        <v>-0.2166441267794925</v>
+        <v>-0.2166442053587146</v>
       </c>
       <c r="M470" t="n">
         <v>-0.2182742326108817</v>
@@ -34881,10 +34881,10 @@
         <v>-0.193740570606278</v>
       </c>
       <c r="O470" t="n">
-        <v>-0.05880800329026159</v>
+        <v>-0.0588080600076194</v>
       </c>
       <c r="P470" t="n">
-        <v>-0.02000000114197609</v>
+        <v>-0.02000002082730135</v>
       </c>
     </row>
     <row r="471">
@@ -34930,7 +34930,7 @@
         <v>-0.1489873262010293</v>
       </c>
       <c r="L471" t="n">
-        <v>-0.08527016188751957</v>
+        <v>-0.08527006934930059</v>
       </c>
       <c r="M471" t="n">
         <v>-0.1428324952678999</v>
@@ -34997,10 +34997,10 @@
         <v>-0.03622277085919279</v>
       </c>
       <c r="O472" t="n">
-        <v>3.093515947305979</v>
+        <v>3.093515368875189</v>
       </c>
       <c r="P472" t="n">
-        <v>0.5996764902316016</v>
+        <v>0.5996764148846225</v>
       </c>
     </row>
     <row r="473">
@@ -35223,16 +35223,16 @@
         <v>-0.1482755499326509</v>
       </c>
       <c r="M476" t="n">
-        <v>-0.2289179668236972</v>
+        <v>-0.2289178928313984</v>
       </c>
       <c r="N476" t="n">
-        <v>-0.198542911016237</v>
+        <v>-0.1985429909528637</v>
       </c>
       <c r="O476" t="n">
-        <v>0.2275811159981096</v>
+        <v>0.2275810222298877</v>
       </c>
       <c r="P476" t="n">
-        <v>0.07073845318088012</v>
+        <v>0.0707384259182573</v>
       </c>
     </row>
     <row r="477">
@@ -35339,7 +35339,7 @@
         <v>-0.282242614138612</v>
       </c>
       <c r="M478" t="n">
-        <v>-0.2105464573433437</v>
+        <v>-0.2105465052373801</v>
       </c>
       <c r="N478" t="n">
         <v>-0.1485707701587679</v>
@@ -35400,13 +35400,13 @@
         <v>-0.3003689849873629</v>
       </c>
       <c r="N479" t="n">
-        <v>-0.278726229141662</v>
+        <v>-0.2787261836246328</v>
       </c>
       <c r="O479" t="n">
-        <v>0.5765350659550739</v>
+        <v>0.5765349572247083</v>
       </c>
       <c r="P479" t="n">
-        <v>0.1638612574294724</v>
+        <v>0.1638612306731033</v>
       </c>
     </row>
     <row r="480">
@@ -35458,13 +35458,13 @@
         <v>-0.1963152403358567</v>
       </c>
       <c r="N480" t="n">
-        <v>-0.287245387454223</v>
+        <v>-0.2872454547729901</v>
       </c>
       <c r="O480" t="n">
-        <v>1.610962174374482</v>
+        <v>1.61096194853636</v>
       </c>
       <c r="P480" t="n">
-        <v>0.3769986887965568</v>
+        <v>0.3769986490948702</v>
       </c>
     </row>
     <row r="481">
@@ -35635,10 +35635,10 @@
         <v>-0.5851970462135587</v>
       </c>
       <c r="O483" t="n">
-        <v>-0.4225801865293685</v>
+        <v>-0.4225801155741487</v>
       </c>
       <c r="P483" t="n">
-        <v>-0.1672833902835714</v>
+        <v>-0.1672833561746001</v>
       </c>
     </row>
     <row r="484">
@@ -35684,7 +35684,7 @@
         <v>-0.2871668215511846</v>
       </c>
       <c r="L484" t="n">
-        <v>-0.2151786767610923</v>
+        <v>-0.2151786262772976</v>
       </c>
       <c r="M484" t="n">
         <v>-0.2410957874810917</v>
@@ -35693,10 +35693,10 @@
         <v>-0.2909668398642237</v>
       </c>
       <c r="O484" t="n">
-        <v>0.01994576099913048</v>
+        <v>0.01994567573536798</v>
       </c>
       <c r="P484" t="n">
-        <v>0.006604866691547695</v>
+        <v>0.006604838642042754</v>
       </c>
     </row>
     <row r="485">
@@ -35800,10 +35800,10 @@
         <v>-0.1741990470522379</v>
       </c>
       <c r="L486" t="n">
-        <v>-0.2653752495783572</v>
+        <v>-0.2653753021093865</v>
       </c>
       <c r="M486" t="n">
-        <v>-0.397632811424441</v>
+        <v>-0.3976327407865878</v>
       </c>
       <c r="N486" t="n">
         <v>-0.245546258785411</v>
@@ -35861,16 +35861,16 @@
         <v>-0.1905084629583685</v>
       </c>
       <c r="M487" t="n">
-        <v>-0.3434504567360691</v>
+        <v>-0.343450497113063</v>
       </c>
       <c r="N487" t="n">
-        <v>-0.3552453480346719</v>
+        <v>-0.3552453090953849</v>
       </c>
       <c r="O487" t="n">
-        <v>-0.08264186560005171</v>
+        <v>-0.08264178677271172</v>
       </c>
       <c r="P487" t="n">
-        <v>-0.02834302608721817</v>
+        <v>-0.02834299825616382</v>
       </c>
     </row>
     <row r="488">
@@ -35983,10 +35983,10 @@
         <v>-0.4749945084449949</v>
       </c>
       <c r="O489" t="n">
-        <v>-0.5745627990798954</v>
+        <v>-0.5745628373849161</v>
       </c>
       <c r="P489" t="n">
-        <v>-0.2478949797956199</v>
+        <v>-0.2478950023680067</v>
       </c>
     </row>
     <row r="490">
@@ -36096,7 +36096,7 @@
         <v>-0.464430559425164</v>
       </c>
       <c r="N491" t="n">
-        <v>-0.4319933043130234</v>
+        <v>-0.4319932688142623</v>
       </c>
       <c r="O491" t="n">
         <v>-0.3299836936364635</v>
@@ -36191,13 +36191,13 @@
         <v>-0.265745138226485</v>
       </c>
       <c r="L493" t="n">
-        <v>-0.3319689580675232</v>
+        <v>-0.3319690256754456</v>
       </c>
       <c r="M493" t="n">
         <v>-0.3567543036539703</v>
       </c>
       <c r="N493" t="n">
-        <v>-0.3910014010835563</v>
+        <v>-0.391001457270692</v>
       </c>
       <c r="O493" t="n">
         <v>1.755572560144951</v>
@@ -36475,10 +36475,10 @@
         <v>-0.4050185017914988</v>
       </c>
       <c r="O498" t="n">
-        <v>-0.09602442425953484</v>
+        <v>-0.09602480804060043</v>
       </c>
       <c r="P498" t="n">
-        <v>-0.0330910827117884</v>
+        <v>-0.03309121954490535</v>
       </c>
     </row>
     <row r="499">

--- a/GICS_SubIndustry_Leaderboard.xlsx
+++ b/GICS_SubIndustry_Leaderboard.xlsx
@@ -613,19 +613,19 @@
         <v>0.3619669890071069</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>0.7390149115258117</v>
+        <v>0.7390149011527933</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>1.233890820911311</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>1.261008925705077</v>
+        <v>1.261008934836588</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>2.113909358884403</v>
+        <v>2.113909553582148</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.4588456382431415</v>
+        <v>0.4588456676228239</v>
       </c>
     </row>
     <row r="3">
@@ -669,19 +669,19 @@
         <v>0.2271705537306038</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>0.6496587778081178</v>
+        <v>0.6496587710222738</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>1.111088767118628</v>
+        <v>1.111088811608512</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>1.648460555567095</v>
+        <v>1.648460586825769</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>4.438521490530325</v>
+        <v>4.438521581356245</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>0.6494414186751586</v>
+        <v>0.6494414239734776</v>
       </c>
     </row>
     <row r="4">
@@ -725,19 +725,19 @@
         <v>0.4521048278247998</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0.684573426005736</v>
+        <v>0.6845734376546554</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.6646806786378345</v>
+        <v>0.6646807066654963</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>1.26640110939451</v>
+        <v>1.266401119260477</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0.9051616829154987</v>
+        <v>0.9051617915096503</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.2234437415030567</v>
+        <v>0.2234437641462118</v>
       </c>
     </row>
     <row r="5">
@@ -787,13 +787,13 @@
         <v>0.6677166492493981</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.5304989477833393</v>
+        <v>0.5304989734755764</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>2.170454179649907</v>
+        <v>2.170454215628024</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0.4208213418484094</v>
+        <v>0.420821350560582</v>
       </c>
     </row>
     <row r="6">
@@ -840,16 +840,16 @@
         <v>0.6627303654135533</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.3280540401907101</v>
+        <v>0.3280540575560228</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0.5067817590766269</v>
+        <v>0.5067817798803741</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>0.7873054676438982</v>
+        <v>0.7873054400492318</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.2060500698590544</v>
+        <v>0.2060500637979616</v>
       </c>
     </row>
     <row r="7">
@@ -896,16 +896,16 @@
         <v>0.1086840639198127</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.4829726420135634</v>
+        <v>0.4829726572452988</v>
       </c>
       <c r="N7" s="5" t="n">
         <v>0.9676557598298348</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>6.502076496115528</v>
+        <v>6.502076465418921</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0.7526536351998762</v>
+        <v>0.7526536293403403</v>
       </c>
     </row>
     <row r="8">
@@ -949,19 +949,19 @@
         <v>0.2411305219512101</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.2617730333881498</v>
+        <v>0.2617729310411816</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.3504776183931915</v>
+        <v>0.3504777356363082</v>
       </c>
       <c r="N8" s="5" t="n">
         <v>0.5718334915713499</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>1.931496110105246</v>
+        <v>1.931495833881416</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.431187191224885</v>
+        <v>0.4311871462730918</v>
       </c>
     </row>
     <row r="9">
@@ -1011,13 +1011,13 @@
         <v>0.5374143125676958</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.217790374037625</v>
+        <v>0.2177902573452437</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.7420502686806452</v>
+        <v>0.742050388076396</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.2032436016502024</v>
+        <v>0.2032436291393001</v>
       </c>
     </row>
     <row r="10">
@@ -1064,16 +1064,16 @@
         <v>0.2318604243610606</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0.3680037626686319</v>
+        <v>0.3680037503152139</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0.5869422778140306</v>
+        <v>0.5869422538511663</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.8515764656645987</v>
+        <v>0.8515761960229832</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.2278439538842592</v>
+        <v>0.2278438931442037</v>
       </c>
     </row>
     <row r="11">
@@ -1117,19 +1117,19 @@
         <v>0.104195644782842</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.1975250792002797</v>
+        <v>0.1975250883609777</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.489652828237793</v>
+        <v>0.489652819731085</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.7017801238395514</v>
+        <v>0.7017801141876906</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>2.654773445944853</v>
+        <v>2.654773214715896</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0.4331699495387039</v>
+        <v>0.4331699165396227</v>
       </c>
     </row>
     <row r="12">
@@ -1232,16 +1232,16 @@
         <v>0.3562606406327981</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>0.595246086756849</v>
+        <v>0.5952461146107784</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0.4535055222071007</v>
+        <v>0.4535054567077194</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>-0.08937338108299672</v>
+        <v>-0.0893733166895781</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-0.03155471077230598</v>
+        <v>-0.03155468650560619</v>
       </c>
     </row>
     <row r="14">
@@ -1291,13 +1291,13 @@
         <v>0.5135606004280395</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.6889257301316466</v>
+        <v>0.6889256550290077</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>1.206853212423774</v>
+        <v>1.206853124537086</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2993747042586901</v>
+        <v>0.2993746919800606</v>
       </c>
     </row>
     <row r="15">
@@ -1347,13 +1347,13 @@
         <v>0.3620501243337593</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.4043724443537751</v>
+        <v>0.404372427883287</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>0.8526875827559347</v>
+        <v>0.852687613779869</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>0.2094579829371045</v>
+        <v>0.2094579936641998</v>
       </c>
     </row>
     <row r="16">
@@ -1400,16 +1400,16 @@
         <v>0.06795746605467744</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.3145736703689755</v>
+        <v>0.3145736749817712</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.4970653249838719</v>
+        <v>0.4970653189720953</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>0.3556381677889069</v>
+        <v>0.3556382746361245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.1046736238834061</v>
+        <v>0.1046736540133941</v>
       </c>
     </row>
     <row r="17">
@@ -1453,19 +1453,19 @@
         <v>0.09745122079783158</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.107254056299128</v>
+        <v>0.1072540797539269</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.265936187133008</v>
+        <v>0.2659361231625016</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.5395945465336822</v>
+        <v>0.5395945885100193</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1.590324951380912</v>
+        <v>1.590325014395487</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.3596928527861004</v>
+        <v>0.3596928582207564</v>
       </c>
     </row>
     <row r="18">
@@ -1512,16 +1512,16 @@
         <v>0.149386717553925</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.05379730427693308</v>
+        <v>0.05379736788322109</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>0.6327474019888542</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>1.052589675346219</v>
+        <v>1.052589434028013</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.2708687868514903</v>
+        <v>0.2708687370471234</v>
       </c>
     </row>
     <row r="19">
@@ -1565,13 +1565,13 @@
         <v>0.1967442633160408</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-0.08242167513329124</v>
+        <v>-0.08242176923771161</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>0.2703472479128557</v>
+        <v>0.2703471577269541</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.4111312495312711</v>
+        <v>0.4111311382483378</v>
       </c>
       <c r="O19" s="5" t="n">
         <v>-0.1567399306860341</v>
@@ -1630,10 +1630,10 @@
         <v>0.2697662740076607</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>2.587458918524339</v>
+        <v>2.587458525908715</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0.5308370999128968</v>
+        <v>0.5308370440673713</v>
       </c>
     </row>
     <row r="21">
@@ -1683,7 +1683,7 @@
         <v>0.3248508762494247</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.06283402106248848</v>
+        <v>0.06283412702938862</v>
       </c>
       <c r="O21" s="5" t="n">
         <v>-0.1446680432104441</v>
@@ -1733,19 +1733,19 @@
         <v>0.04923561318963105</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.1640750658581116</v>
+        <v>0.1640750557054922</v>
       </c>
       <c r="M22" s="5" t="n">
         <v>0.181227564146876</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0.4183164427352096</v>
+        <v>0.4183164830974858</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>0.62534602221341</v>
+        <v>0.6253461389489294</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1508905960331726</v>
+        <v>0.1508906199348264</v>
       </c>
     </row>
     <row r="23">
@@ -1795,7 +1795,7 @@
         <v>-0.1310702408828472</v>
       </c>
       <c r="N23" s="5" t="n">
-        <v>0.4493128060022002</v>
+        <v>0.4493130873505962</v>
       </c>
       <c r="O23" s="5" t="n">
         <v>2.09718329871097</v>
@@ -1848,16 +1848,16 @@
         <v>0.1185081841028163</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.3115076068048362</v>
+        <v>0.3115075150427564</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>0.3666777408444449</v>
+        <v>0.3666776741343342</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>0.7944684375682739</v>
+        <v>0.7944684515351007</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.2141043032775899</v>
+        <v>0.2141043027295391</v>
       </c>
     </row>
     <row r="25">
@@ -1901,19 +1901,19 @@
         <v>0.3359797864908457</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.2946952389123506</v>
+        <v>0.2946952572217939</v>
       </c>
       <c r="M25" s="5" t="n">
         <v>-0.1036973560838247</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>-0.07815064603170116</v>
+        <v>-0.07815062521626501</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>0.1545170652070776</v>
+        <v>0.1545169331730646</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>0.03037662584578629</v>
+        <v>0.03037659591411931</v>
       </c>
     </row>
     <row r="26">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>DE (75)</t>
+          <t>DE (74)</t>
         </is>
       </c>
       <c r="G26" s="5" t="n">
@@ -1963,13 +1963,13 @@
         <v>0.2299699524533283</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0.3840113218311731</v>
+        <v>0.3840112305891419</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>0.8465481289224408</v>
+        <v>0.8465479665034104</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.2268370336199923</v>
+        <v>0.2268369976498696</v>
       </c>
     </row>
     <row r="27">
@@ -2013,19 +2013,19 @@
         <v>-0.0448435306889762</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.2124400532907269</v>
+        <v>0.212440073301731</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>0.3590346821836954</v>
+        <v>0.3590346591865451</v>
       </c>
       <c r="N27" s="5" t="n">
-        <v>0.265467939864296</v>
+        <v>0.2654678984868648</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>0.7714537082305637</v>
+        <v>0.7714535491418266</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>0.1997008430646702</v>
+        <v>0.1997008037672</v>
       </c>
     </row>
     <row r="28">
@@ -2075,13 +2075,13 @@
         <v>0.0762550608913477</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0.2037950919045131</v>
+        <v>0.2037950582187754</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>0.1028017792043029</v>
+        <v>0.1028019001381131</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.03159149355080352</v>
+        <v>0.03159152813945998</v>
       </c>
     </row>
     <row r="29">
@@ -2134,10 +2134,10 @@
         <v>0.1165821732393897</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>1.876607219811835</v>
+        <v>1.876607451481292</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>0.4221984098034088</v>
+        <v>0.4221984479826364</v>
       </c>
     </row>
     <row r="30">
@@ -2181,19 +2181,19 @@
         <v>0.0617886868112229</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.03014179372700182</v>
+        <v>0.0301417734911069</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.1862440250453487</v>
+        <v>0.186244075059379</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>0.3672648975187876</v>
+        <v>0.3672648870946387</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>5.285029526746621</v>
+        <v>5.285029152933678</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.6189574383616585</v>
+        <v>0.6189573867074764</v>
       </c>
     </row>
     <row r="31">
@@ -2299,13 +2299,13 @@
         <v>0.1543935933147516</v>
       </c>
       <c r="N32" s="5" t="n">
-        <v>0.5012180189871677</v>
+        <v>0.5012181087415338</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>4.884223914721818</v>
+        <v>4.884223921565997</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>0.7891181431953448</v>
+        <v>0.7891181489356974</v>
       </c>
     </row>
     <row r="33">
@@ -2358,10 +2358,10 @@
         <v>0.2913783150483</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>0.05831169298445316</v>
+        <v>0.05831160463559648</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>0.01907120788864369</v>
+        <v>0.01907117953096815</v>
       </c>
     </row>
     <row r="34">
@@ -2408,16 +2408,16 @@
         <v>-0.05917920395705052</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.1469288396565439</v>
+        <v>0.1469288622066314</v>
       </c>
       <c r="N34" s="5" t="n">
-        <v>0.6545664405715989</v>
+        <v>0.6545664078662921</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>2.756676811639755</v>
+        <v>2.756676669911923</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.552171653393661</v>
+        <v>0.5521716293785648</v>
       </c>
     </row>
     <row r="35">
@@ -2464,16 +2464,16 @@
         <v>0.1272011961270431</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.09984027272811705</v>
+        <v>0.09984031569483356</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>0.2585277956077484</v>
+        <v>0.2585278179100891</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>1.004990232061306</v>
+        <v>1.004990218524758</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>0.2499167672111971</v>
+        <v>0.2499167615818033</v>
       </c>
     </row>
     <row r="36">
@@ -2498,38 +2498,38 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>URI (83), FAST (74), FERG (27)</t>
+          <t>URI (83), FAST (75), FERG (27)</t>
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.004684145019948367</v>
+        <v>0.006370594380780507</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.03039854351777649</v>
+        <v>0.03205479571666584</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>0.05316909424015111</v>
+        <v>0.05484095003663492</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0.05311312196887105</v>
+        <v>0.05483498942091525</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.04869240131413503</v>
+        <v>0.05049982452675713</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.09435745751137552</v>
+        <v>0.09631391246536296</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>0.144767129551067</v>
+        <v>0.1467929199487639</v>
       </c>
       <c r="N36" s="5" t="n">
-        <v>0.185458771105361</v>
+        <v>0.1875813750427211</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>1.176567137944809</v>
+        <v>1.179790980287283</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>0.2851049771568914</v>
+        <v>0.2858024192340413</v>
       </c>
     </row>
     <row r="37">
@@ -2576,16 +2576,16 @@
         <v>0.102705906501872</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>0.1015716256382402</v>
+        <v>0.1015716067859521</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>0.2653211086573448</v>
+        <v>0.2653210633108402</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>0.6034833192904594</v>
+        <v>0.6034833954304851</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>0.1609472453351128</v>
+        <v>0.160947266222189</v>
       </c>
     </row>
     <row r="38">
@@ -2632,16 +2632,16 @@
         <v>0.1164729722318379</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.1667760353892932</v>
+        <v>0.1667759865771365</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>0.2070439263966805</v>
+        <v>0.2070438544794566</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>0.4606363838243577</v>
+        <v>0.4606363052826924</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.1253282281363761</v>
+        <v>0.1253282078916612</v>
       </c>
     </row>
     <row r="39">
@@ -2688,16 +2688,16 @@
         <v>0.1490807426390161</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>0.1903184445180816</v>
+        <v>0.1903184190277908</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>0.2519356167161938</v>
+        <v>0.2519356269095519</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>0.6721533869215592</v>
+        <v>0.6721531931789532</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>0.1855655934531219</v>
+        <v>0.1855655462806917</v>
       </c>
     </row>
     <row r="40">
@@ -2800,10 +2800,10 @@
         <v>0.0815869233360727</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>0.1495893908611708</v>
+        <v>0.1495894414851137</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>0.1554298676472462</v>
+        <v>0.1554298210810415</v>
       </c>
       <c r="O41" s="5" t="n">
         <v>1.629029962368865</v>
@@ -2859,13 +2859,13 @@
         <v>0.1279038913591302</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>-0.01492474748762451</v>
+        <v>-0.01492480645486172</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>0.2660536764179265</v>
+        <v>0.2660535903497119</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>0.07984916007187648</v>
+        <v>0.0798491332278185</v>
       </c>
     </row>
     <row r="43">
@@ -2912,16 +2912,16 @@
         <v>0.01395974128107491</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>0.1800408438326973</v>
+        <v>0.1800408826223359</v>
       </c>
       <c r="N43" s="5" t="n">
         <v>0.2014469835804683</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>0.3138680562110048</v>
+        <v>0.3138682500177986</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>0.0943854520246884</v>
+        <v>0.09438550530343504</v>
       </c>
     </row>
     <row r="44">
@@ -2971,13 +2971,13 @@
         <v>0.06010726948966638</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>0.3553396924061464</v>
+        <v>0.3553397237058136</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>0.2264615080439827</v>
+        <v>0.22646147479917</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.06300323957804384</v>
+        <v>0.0630032282451249</v>
       </c>
     </row>
     <row r="45">
@@ -3021,19 +3021,19 @@
         <v>-0.03376403345323056</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.1028238422688431</v>
+        <v>0.1028238553818289</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0.1578506183843928</v>
+        <v>0.1578506101156672</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0.2219679963964307</v>
+        <v>0.2219679262126303</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.8910430408127081</v>
+        <v>0.8910431052876406</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>0.2319087424023707</v>
+        <v>0.2319087604498245</v>
       </c>
     </row>
     <row r="46">
@@ -3080,16 +3080,16 @@
         <v>0.03686422524559152</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>0.135529843041855</v>
+        <v>0.1355297652869174</v>
       </c>
       <c r="N46" s="5" t="n">
-        <v>0.3066595300282493</v>
+        <v>0.3066594270712804</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>0.4009429264088076</v>
+        <v>0.4009431631107689</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>0.1189400384187269</v>
+        <v>0.1189401014370655</v>
       </c>
     </row>
     <row r="47">
@@ -3133,19 +3133,19 @@
         <v>-0.02396102639330263</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.09728239846880626</v>
+        <v>0.09728242071409914</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>0.1323079432661664</v>
+        <v>0.1323079698715059</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>0.185913541342541</v>
+        <v>0.1859136051451808</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>0.7489876058924461</v>
+        <v>0.7489873462796623</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>0.2020711130560751</v>
+        <v>0.2020710585570833</v>
       </c>
     </row>
     <row r="48">
@@ -3189,19 +3189,19 @@
         <v>-0.02457065232688568</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>0.01365275205283858</v>
+        <v>0.01365272818594057</v>
       </c>
       <c r="M48" s="5" t="n">
         <v>0.05511995359660424</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>0.3471005430572107</v>
+        <v>0.3471006177851806</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>0.5647821887071108</v>
+        <v>0.5647820620095667</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>0.1520942638789271</v>
+        <v>0.1520942338773925</v>
       </c>
     </row>
     <row r="49">
@@ -3245,19 +3245,19 @@
         <v>-0.05722354328180074</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.05749970890889333</v>
+        <v>0.05749976923450295</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>0.1695587560789531</v>
+        <v>0.1695587880590532</v>
       </c>
       <c r="N49" s="5" t="n">
-        <v>0.2507722203132534</v>
+        <v>0.250772248180289</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>0.5257900184681413</v>
+        <v>0.5257897782316631</v>
       </c>
       <c r="P49" s="5" t="n">
-        <v>0.1370451268384218</v>
+        <v>0.1370450665959387</v>
       </c>
     </row>
     <row r="50">
@@ -3304,16 +3304,16 @@
         <v>0.1676232760424311</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.09922625696831137</v>
+        <v>0.09922618896201056</v>
       </c>
       <c r="N50" s="5" t="n">
-        <v>0.3053751820400356</v>
+        <v>0.3053751524175239</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>1.611895757851818</v>
+        <v>1.611895694914727</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.3733244576129999</v>
+        <v>0.3733244447149837</v>
       </c>
     </row>
     <row r="51">
@@ -3363,13 +3363,13 @@
         <v>0.07136343771983771</v>
       </c>
       <c r="N51" s="5" t="n">
-        <v>0.1341394916635166</v>
+        <v>0.1341394639592327</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>0.3570405568907922</v>
+        <v>0.3570406441391596</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>0.1011676639237042</v>
+        <v>0.1011676849845452</v>
       </c>
     </row>
     <row r="52">
@@ -3419,13 +3419,13 @@
         <v>0.2024531868708632</v>
       </c>
       <c r="N52" s="5" t="n">
-        <v>0.2503181352786965</v>
+        <v>0.2503181675081372</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>2.063300834641358</v>
+        <v>2.063300880734441</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>0.4279478713711831</v>
+        <v>0.427947881042174</v>
       </c>
     </row>
     <row r="53">
@@ -3472,16 +3472,16 @@
         <v>0.1777485313924035</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>0.002337693622577258</v>
+        <v>0.002337688233131915</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>-0.1384094274868968</v>
+        <v>-0.1384094283973997</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>1.12982938658295</v>
+        <v>1.1298293957599</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>0.1548294994050826</v>
+        <v>0.1548295027271793</v>
       </c>
     </row>
     <row r="54">
@@ -3525,10 +3525,10 @@
         <v>-0.07264306151448319</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>0.04213917255605648</v>
+        <v>0.04213910092180018</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>0.282768555561685</v>
+        <v>0.282768664095731</v>
       </c>
       <c r="N54" s="5" t="n">
         <v>0.1490815478826484</v>
@@ -3622,34 +3622,34 @@
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.02238156686863024</v>
+        <v>-0.02230523798628192</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>-0.03740830566903897</v>
+        <v>-0.03733316942657094</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>-0.01093132790883011</v>
+        <v>-0.01085426985031468</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>0.0001187422354829715</v>
+        <v>0.000196302220825284</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>0.02653568551653163</v>
+        <v>0.02661453043309137</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0.09479401289594647</v>
+        <v>0.09487722646035412</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.08176978945899338</v>
+        <v>0.08185202744631936</v>
       </c>
       <c r="N56" s="5" t="n">
-        <v>0.07043822473317196</v>
+        <v>0.07051898523467071</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>0.5208462917496934</v>
+        <v>0.5209680277954863</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.1499100052874703</v>
+        <v>0.1499401776816317</v>
       </c>
     </row>
     <row r="57">
@@ -3696,16 +3696,16 @@
         <v>0.06826298414515253</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>0.1230802876989465</v>
+        <v>0.1230803565381167</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>0.06522959009260632</v>
+        <v>0.06522971395243626</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>0.2921074522487574</v>
+        <v>0.2921076344877513</v>
       </c>
       <c r="P57" s="5" t="n">
-        <v>0.08917971341231734</v>
+        <v>0.08917976461832855</v>
       </c>
     </row>
     <row r="58">
@@ -3805,19 +3805,19 @@
         <v>0.01990639729638198</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.002680588645513978</v>
+        <v>-0.002680595788479993</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0.03523612524242723</v>
+        <v>0.0352361431320388</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>0.1852161091664353</v>
+        <v>0.185216152085661</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>0.2418100592088278</v>
+        <v>0.2418100493696745</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>0.06339045150332785</v>
+        <v>0.06339045026413852</v>
       </c>
     </row>
     <row r="60">
@@ -3864,16 +3864,16 @@
         <v>-0.01457066061167896</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>0.05473092146849982</v>
+        <v>0.05473089264681411</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0.0005735256931798846</v>
+        <v>0.0005735295870447447</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>0.09961869787953392</v>
+        <v>0.09961875933083079</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>0.03122762350436751</v>
+        <v>0.03122764684054539</v>
       </c>
     </row>
     <row r="61">
@@ -3917,19 +3917,19 @@
         <v>0.07589714987067764</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>0.1456595921834869</v>
+        <v>0.1456595973029423</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>-0.01884076893139962</v>
+        <v>-0.01884077353777391</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>-0.02437788946089165</v>
+        <v>-0.02437791304140742</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>0.2605425677161438</v>
+        <v>0.2605425827868074</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>0.07263505264662912</v>
+        <v>0.0726350563657323</v>
       </c>
     </row>
     <row r="62">
@@ -3973,19 +3973,19 @@
         <v>0.05712904702735935</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>0.07277735237051698</v>
+        <v>0.07277735941360662</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.006320732577256183</v>
+        <v>0.006320720287639698</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>0.02959418738111814</v>
+        <v>0.02959415149562082</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>0.6580003888812409</v>
+        <v>0.6580004632006156</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>0.1719561221346663</v>
+        <v>0.1719561372434334</v>
       </c>
     </row>
     <row r="63">
@@ -4032,16 +4032,16 @@
         <v>-0.05915564027475229</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>0.1887464626829334</v>
+        <v>0.1887464090643577</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>0.161743029855633</v>
+        <v>0.161742981955572</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>0.5599513629903268</v>
+        <v>0.5599515419720673</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>0.1596415467563557</v>
+        <v>0.1596415909270562</v>
       </c>
     </row>
     <row r="64">
@@ -4088,16 +4088,16 @@
         <v>0.1351163504366337</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>0.004805962338410907</v>
+        <v>0.00480586857209242</v>
       </c>
       <c r="N64" s="5" t="n">
         <v>0.1138593786755586</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>0.3835115076817992</v>
+        <v>0.3835113299160884</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.1142798026789915</v>
+        <v>0.1142797549548373</v>
       </c>
     </row>
     <row r="65">
@@ -4141,19 +4141,19 @@
         <v>-0.05641287993280949</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>0.07106032691715043</v>
+        <v>0.07106036570105845</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>0.05015856968284246</v>
+        <v>0.05015856652087777</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>0.1608112969299483</v>
+        <v>0.160811329685263</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>0.8401153755592907</v>
+        <v>0.8401154992902162</v>
       </c>
       <c r="P65" s="5" t="n">
-        <v>0.2148375247727427</v>
+        <v>0.2148375588175705</v>
       </c>
     </row>
     <row r="66">
@@ -4206,10 +4206,10 @@
         <v>0.05755675297473806</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>0.5238509126347772</v>
+        <v>0.5238509655597141</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>0.1505687858049769</v>
+        <v>0.1505687994719318</v>
       </c>
     </row>
     <row r="67">
@@ -4256,16 +4256,16 @@
         <v>-0.06697053677908335</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0.1154596913366023</v>
+        <v>0.1154597026410775</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>0.156190737525731</v>
+        <v>0.1561907211457458</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>3.04316220733772</v>
+        <v>3.043162160472603</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>0.5353666046186302</v>
+        <v>0.5353666046916545</v>
       </c>
     </row>
     <row r="68">
@@ -4318,10 +4318,10 @@
         <v>0.04553124293473521</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>1.193101718498783</v>
+        <v>1.193101722599049</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>0.2991933634375185</v>
+        <v>0.2991933645721723</v>
       </c>
     </row>
     <row r="69">
@@ -4362,22 +4362,22 @@
         <v>-0.05327872835666229</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.1357325540479656</v>
+        <v>-0.135732577401315</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>0.06535809307335176</v>
+        <v>0.06535806876104477</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>0.1570236588429839</v>
+        <v>0.1570236146830905</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>0.1893240491820214</v>
+        <v>0.1893240077708142</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>1.15593087860659</v>
+        <v>1.155930944507531</v>
       </c>
       <c r="P69" s="5" t="n">
-        <v>0.2784178084240816</v>
+        <v>0.2784178050743715</v>
       </c>
     </row>
     <row r="70">
@@ -4389,51 +4389,51 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Regional Banks</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>FITB (57), CFG (48), KEY (46)</t>
+          <t>CHD (68), CL (58), KMB (46)</t>
         </is>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.001666562546381811</v>
+        <v>-0.001405580502019971</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.006764118587868647</v>
+        <v>0.008776174663928771</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>0.05104694031064679</v>
+        <v>0.03545653690938891</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>0.02640571635199046</v>
+        <v>0.08520901327318142</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.08497754379537363</v>
+        <v>-0.02391406307913255</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>0.01604052071157223</v>
+        <v>0.05518677284459905</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.0364234673198404</v>
+        <v>0.05356785167111047</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>0.2310422719679686</v>
+        <v>0.05319592612585894</v>
       </c>
       <c r="O70" s="5" t="n">
-        <v>1.450071650033276</v>
+        <v>0.1133622761383377</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.3440418653375618</v>
+        <v>0.03262106151374972</v>
       </c>
     </row>
     <row r="71">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Asset Management &amp; Custody Banks</t>
+          <t>Regional Banks</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -4454,42 +4454,42 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>STT (80), BEN (73), BNY (72)</t>
+          <t>FITB (57), CFG (48), KEY (46)</t>
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.007864248965688733</v>
+        <v>-0.001666562546381811</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0.02104976122335618</v>
+        <v>0.006764118587868647</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>0.05397133973653922</v>
+        <v>0.05104694031064679</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>-0.002215181569457751</v>
+        <v>0.02640571635199046</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>-0.05711022963184521</v>
+        <v>-0.08497754379537363</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>0.05773648255237315</v>
+        <v>0.01604052071157223</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>0.0466803404871222</v>
+        <v>0.03642346500626659</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>0.1176806212688454</v>
+        <v>0.23104226312538</v>
       </c>
       <c r="O71" s="5" t="n">
-        <v>1.090229178957645</v>
+        <v>1.450071745757989</v>
       </c>
       <c r="P71" s="5" t="n">
-        <v>0.2609526821642235</v>
+        <v>0.3440418877369559</v>
       </c>
     </row>
     <row r="72">
@@ -4501,51 +4501,51 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Hotels, Resorts &amp; Cruise Lines</t>
+          <t>Asset Management &amp; Custody Banks</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>MAR (80), ABNB (79), HLT (75)</t>
+          <t>STT (80), BEN (73), BNY (72)</t>
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.003016952077582472</v>
+        <v>0.007864248965688733</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>-0.01397410429027264</v>
+        <v>0.02104976122335618</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>0.03654098489749838</v>
+        <v>0.05397133973653922</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>0.1025364163307282</v>
+        <v>-0.002215181569457751</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.05460374948531901</v>
+        <v>-0.05711022963184521</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>0.06767561158679157</v>
+        <v>0.05773649369785036</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>0.03694203073806267</v>
+        <v>0.04668035046305238</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>0.1099293882110286</v>
+        <v>0.1176806160765999</v>
       </c>
       <c r="O72" s="5" t="n">
-        <v>1.234464534669241</v>
+        <v>1.090229184025546</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.2875807949144813</v>
+        <v>0.2609526796113822</v>
       </c>
     </row>
     <row r="73">
@@ -4557,51 +4557,51 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Hotels, Resorts &amp; Cruise Lines</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>CHD (68), CL (58), KMB (46)</t>
+          <t>MAR (80), ABNB (79), HLT (75)</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.005013057722787623</v>
+        <v>0.003016952077582472</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.005058466557279317</v>
+        <v>-0.01397410429027264</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.03174758202948638</v>
+        <v>0.03654098489749838</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>0.08133834649723987</v>
+        <v>0.1025364163307282</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.02709221266212281</v>
+        <v>-0.05460374948531901</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0.05188623155054825</v>
+        <v>0.06767561158679157</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>0.05060047697789544</v>
+        <v>0.03694203073806267</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>0.05036287630220265</v>
+        <v>0.1099294158020486</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>0.1103941322533522</v>
+        <v>1.234464565533605</v>
       </c>
       <c r="P73" s="5" t="n">
-        <v>0.03149520242459666</v>
+        <v>0.2875808030425856</v>
       </c>
     </row>
     <row r="74">
@@ -4648,16 +4648,16 @@
         <v>0.02651070271996389</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>0.05141487728402495</v>
+        <v>0.05141490055187346</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>0.1552153771773746</v>
+        <v>0.1552153030040695</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>1.462901624873146</v>
+        <v>1.462901633236201</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>0.3454166590411475</v>
+        <v>0.345416658811811</v>
       </c>
     </row>
     <row r="75">
@@ -4710,10 +4710,10 @@
         <v>-0.2122954357522833</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>0.1161468044240499</v>
+        <v>0.116146911838596</v>
       </c>
       <c r="P75" s="5" t="n">
-        <v>0.03730651776491989</v>
+        <v>0.03730655104065161</v>
       </c>
     </row>
     <row r="76">
@@ -4757,19 +4757,19 @@
         <v>-0.04435568769334269</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.003369572129479145</v>
+        <v>-0.003369575680047484</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0.01536371258200964</v>
+        <v>0.01536370276595761</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>0.1104000608351295</v>
+        <v>0.1104000521989928</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>0.4816687528689056</v>
+        <v>0.4816687444696797</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>0.1323048625523937</v>
+        <v>0.1323048594196378</v>
       </c>
     </row>
     <row r="77">
@@ -4813,19 +4813,19 @@
         <v>-0.1133583104364025</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.04956927049276555</v>
+        <v>-0.04956930495909889</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>0.0889587400004645</v>
+        <v>0.08895868913810384</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>0.2015194574704434</v>
+        <v>0.2015194053243586</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>0.8659912078244538</v>
+        <v>0.8659912052582118</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>0.2292914429587686</v>
+        <v>0.2292914398641843</v>
       </c>
     </row>
     <row r="78">
@@ -4872,16 +4872,16 @@
         <v>-0.08076645063472288</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>0.08071879080351141</v>
+        <v>0.08071873653575057</v>
       </c>
       <c r="N78" s="5" t="n">
         <v>0.1226238456470264</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>1.047549407474524</v>
+        <v>1.047549842746282</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.261817292993466</v>
+        <v>0.2618173808697909</v>
       </c>
     </row>
     <row r="79">
@@ -4925,19 +4925,19 @@
         <v>0.07339723527840369</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>0.06930743778611292</v>
+        <v>0.06930738780910095</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>-0.1004460701661813</v>
+        <v>-0.1004460380697771</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>-0.1058356351502139</v>
+        <v>-0.105835668080814</v>
       </c>
       <c r="O79" s="5" t="n">
-        <v>0.7591279920508796</v>
+        <v>0.7591279792767833</v>
       </c>
       <c r="P79" s="5" t="n">
-        <v>0.2019427169979623</v>
+        <v>0.2019427225827246</v>
       </c>
     </row>
     <row r="80">
@@ -4984,16 +4984,16 @@
         <v>0.09659906907597388</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>0.03883194304946348</v>
+        <v>0.03883191933222042</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>-0.07343282956323546</v>
+        <v>-0.07343286331438698</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>0.2877466271455444</v>
+        <v>0.2877465686153222</v>
       </c>
       <c r="P80" s="5" t="n">
-        <v>0.0664463745024463</v>
+        <v>0.0664463565961424</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +5037,19 @@
         <v>-0.07078336212460093</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>0.1012881128095587</v>
+        <v>0.1012881331947047</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>0.01561449408865907</v>
+        <v>0.01561453046287384</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>0.03178064567174612</v>
+        <v>0.0317806052099288</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>0.3543273505286763</v>
+        <v>0.3543274813507447</v>
       </c>
       <c r="P81" s="5" t="n">
-        <v>0.1028181041289241</v>
+        <v>0.1028181416468599</v>
       </c>
     </row>
     <row r="82">
@@ -5096,16 +5096,16 @@
         <v>0.03685461640198292</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>-0.06351748506479538</v>
+        <v>-0.06351745557773784</v>
       </c>
       <c r="N82" s="5" t="n">
-        <v>0.006971739901954728</v>
+        <v>0.006971715764120774</v>
       </c>
       <c r="O82" s="5" t="n">
-        <v>1.173847927962275</v>
+        <v>1.173847966596243</v>
       </c>
       <c r="P82" s="5" t="n">
-        <v>0.2808461947788882</v>
+        <v>0.2808461891570033</v>
       </c>
     </row>
     <row r="83">
@@ -5146,22 +5146,22 @@
         <v>0.01769788880820211</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.1095856467313111</v>
+        <v>-0.1095856263269341</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.02185604321795973</v>
+        <v>-0.02185603804562926</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>0.1063168696574991</v>
+        <v>0.1063169192438333</v>
       </c>
       <c r="N83" s="5" t="n">
-        <v>0.1189111020891518</v>
+        <v>0.1189111393688591</v>
       </c>
       <c r="O83" s="5" t="n">
-        <v>0.6293366982518291</v>
+        <v>0.6293367459750506</v>
       </c>
       <c r="P83" s="5" t="n">
-        <v>0.1709601012154558</v>
+        <v>0.17096011210239</v>
       </c>
     </row>
     <row r="84">
@@ -5205,19 +5205,19 @@
         <v>-0.05674520687445707</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.005619725628819405</v>
+        <v>-0.005619730039220672</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>0.04722883209982436</v>
+        <v>0.04722884630124074</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>0.03737642146777436</v>
+        <v>0.03737639185690449</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>0.7949833639184772</v>
+        <v>0.7949832151833869</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>0.1878846988086026</v>
+        <v>0.187884672705718</v>
       </c>
     </row>
     <row r="85">
@@ -5264,16 +5264,16 @@
         <v>0.09995810896186291</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>0.001928083922256444</v>
+        <v>0.001928067021079468</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>-0.06112068799579299</v>
+        <v>-0.06112071607061076</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>0.1206835279413728</v>
+        <v>0.120683478812148</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>0.03632715027937359</v>
+        <v>0.03632713289190163</v>
       </c>
     </row>
     <row r="86">
@@ -5320,16 +5320,16 @@
         <v>-0.05889944520434587</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0.02979914959922758</v>
+        <v>0.02979908204509696</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>0.1839997926949418</v>
+        <v>0.1839998776800644</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>0.1311405331936579</v>
+        <v>0.1311404508126001</v>
       </c>
       <c r="P86" s="5" t="n">
-        <v>0.04123063405456928</v>
+        <v>0.04123060735893991</v>
       </c>
     </row>
     <row r="87">
@@ -5379,7 +5379,7 @@
         <v>-0.2226027828352786</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>-0.1115047470536594</v>
+        <v>-0.1115047675883914</v>
       </c>
       <c r="O87" s="5" t="n">
         <v>0.2608988841613679</v>
@@ -5432,16 +5432,16 @@
         <v>-0.08885557298451824</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>0.03028814761870105</v>
+        <v>0.03028817240172163</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>0.2908125612263079</v>
+        <v>0.2908126223301627</v>
       </c>
       <c r="O88" s="5" t="n">
-        <v>1.465132140722512</v>
+        <v>1.465132155974289</v>
       </c>
       <c r="P88" s="5" t="n">
-        <v>0.3379915072295037</v>
+        <v>0.3379915052087094</v>
       </c>
     </row>
     <row r="89">
@@ -5488,16 +5488,16 @@
         <v>0.1732072323014957</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>-0.1086945975593511</v>
+        <v>-0.1086944976996442</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>-0.04454855713040351</v>
+        <v>-0.04454844237993871</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>0.05052164493203892</v>
+        <v>0.05052157557075132</v>
       </c>
       <c r="P89" s="5" t="n">
-        <v>0.01656464577710115</v>
+        <v>0.01656462340401488</v>
       </c>
     </row>
     <row r="90">
@@ -5541,19 +5541,19 @@
         <v>-0.06354048885198045</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.05007415870891171</v>
+        <v>-0.05007416592429292</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>0.0271907733332098</v>
+        <v>0.02719078759540882</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>0.0341843196674895</v>
+        <v>0.03418430516047125</v>
       </c>
       <c r="O90" s="5" t="n">
-        <v>0.515459320464188</v>
+        <v>0.5154593055709653</v>
       </c>
       <c r="P90" s="5" t="n">
-        <v>0.1442818399646577</v>
+        <v>0.1442818375156476</v>
       </c>
     </row>
     <row r="91">
@@ -5597,19 +5597,19 @@
         <v>-0.03441532659035077</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>0.02794851955607924</v>
+        <v>0.02794848603719347</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>-0.03769324191563809</v>
+        <v>-0.03769329011274328</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>-0.04751962442235099</v>
+        <v>-0.04751963452719143</v>
       </c>
       <c r="O91" s="5" t="n">
-        <v>1.458269307807561</v>
+        <v>1.458269367654817</v>
       </c>
       <c r="P91" s="5" t="n">
-        <v>0.3476848199444769</v>
+        <v>0.3476848317530655</v>
       </c>
     </row>
     <row r="92">
@@ -5662,10 +5662,10 @@
         <v>0.006527993234497376</v>
       </c>
       <c r="O92" s="5" t="n">
-        <v>-0.4253428875608296</v>
+        <v>-0.4253429089876928</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>-0.1688508935037032</v>
+        <v>-0.1688509035019289</v>
       </c>
     </row>
     <row r="93">
@@ -5712,16 +5712,16 @@
         <v>0.03557911469217195</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>-0.02192858903368759</v>
+        <v>-0.02192858504732971</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>0.02879017961749127</v>
+        <v>0.02879019521370318</v>
       </c>
       <c r="O93" s="5" t="n">
-        <v>3.085366772736084</v>
+        <v>3.085366959790868</v>
       </c>
       <c r="P93" s="5" t="n">
-        <v>0.5280025732467581</v>
+        <v>0.5280026012425659</v>
       </c>
     </row>
     <row r="94">
@@ -5821,19 +5821,19 @@
         <v>-0.0547623880440966</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.0493097409185516</v>
+        <v>-0.04930975355215106</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>0.01680054100129841</v>
+        <v>0.01680054923753839</v>
       </c>
       <c r="N95" s="5" t="n">
-        <v>-0.006928321586096745</v>
+        <v>-0.006928331964337568</v>
       </c>
       <c r="O95" s="5" t="n">
-        <v>0.8591453470674276</v>
+        <v>0.8591453191100711</v>
       </c>
       <c r="P95" s="5" t="n">
-        <v>0.2104893044140964</v>
+        <v>0.2104893002572185</v>
       </c>
     </row>
     <row r="96">
@@ -5877,19 +5877,19 @@
         <v>-0.0165443543556866</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.01560971394525007</v>
+        <v>-0.01560969703584492</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>-0.08700779682477836</v>
+        <v>-0.08700775738543312</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>-0.04491513639706954</v>
+        <v>-0.04491516609945642</v>
       </c>
       <c r="O96" s="5" t="n">
-        <v>0.4035123352144623</v>
+        <v>0.4035120958609501</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>0.1147390348282452</v>
+        <v>0.1147389801331413</v>
       </c>
     </row>
     <row r="97">
@@ -5936,16 +5936,16 @@
         <v>-0.02885742682156434</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>0.05537410848165436</v>
+        <v>0.05537402906361999</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>-0.007866423531627253</v>
+        <v>-0.00786635334625263</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>0.04854573916595761</v>
+        <v>0.04854566077228273</v>
       </c>
       <c r="P97" s="5" t="n">
-        <v>0.01592690020018095</v>
+        <v>0.0159268748818624</v>
       </c>
     </row>
     <row r="98">
@@ -5989,19 +5989,19 @@
         <v>0.03991998123343195</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>0.01943366742536967</v>
+        <v>0.01943370346719194</v>
       </c>
       <c r="M98" s="5" t="n">
         <v>-0.1343552277382023</v>
       </c>
       <c r="N98" s="5" t="n">
-        <v>-0.1529938106122914</v>
+        <v>-0.1529938312113665</v>
       </c>
       <c r="O98" s="5" t="n">
-        <v>0.3445295423775899</v>
+        <v>0.3445296351070774</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>0.08478011303267607</v>
+        <v>0.08478013567191263</v>
       </c>
     </row>
     <row r="99">
@@ -6048,16 +6048,16 @@
         <v>-0.02909945769101735</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>-0.0750197217390647</v>
+        <v>-0.07501973676164703</v>
       </c>
       <c r="N99" s="5" t="n">
-        <v>-0.02042082304100782</v>
+        <v>-0.02042085167733659</v>
       </c>
       <c r="O99" s="5" t="n">
-        <v>0.1639806675714092</v>
+        <v>0.163980583767961</v>
       </c>
       <c r="P99" s="5" t="n">
-        <v>0.04467093561276906</v>
+        <v>0.04467091476500551</v>
       </c>
     </row>
     <row r="100">
@@ -6101,19 +6101,19 @@
         <v>-0.08172790717785906</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>0.01771513285779913</v>
+        <v>0.01771512373404903</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>-0.04885672809777236</v>
+        <v>-0.04885674191753085</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>-0.03472746718044786</v>
+        <v>-0.03472745837305419</v>
       </c>
       <c r="O100" s="5" t="n">
-        <v>-0.04543229647865241</v>
+        <v>-0.04543232791200534</v>
       </c>
       <c r="P100" s="5" t="n">
-        <v>-0.02234255296321283</v>
+        <v>-0.02234256399043874</v>
       </c>
     </row>
     <row r="101">
@@ -6157,19 +6157,19 @@
         <v>-0.1102888239570935</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>-0.04009746686702147</v>
+        <v>-0.04009743458060271</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>-0.002973592000739989</v>
+        <v>-0.002973595971094078</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>0.01761300352529043</v>
+        <v>0.01761301374592632</v>
       </c>
       <c r="O101" s="5" t="n">
-        <v>0.279704851008017</v>
+        <v>0.2797047898598549</v>
       </c>
       <c r="P101" s="5" t="n">
-        <v>0.08503676849811796</v>
+        <v>0.08503675053178879</v>
       </c>
     </row>
     <row r="102">
@@ -6216,10 +6216,10 @@
         <v>-0.1026218901219315</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>-0.01243421496495895</v>
+        <v>-0.01243419166714305</v>
       </c>
       <c r="N102" s="5" t="n">
-        <v>0.03421630675980797</v>
+        <v>0.0342162424706039</v>
       </c>
       <c r="O102" s="5" t="n">
         <v>0.1080823579463663</v>
@@ -6269,13 +6269,13 @@
         <v>-0.1205794227535397</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>-0.120942639268754</v>
+        <v>-0.1209426786369199</v>
       </c>
       <c r="M103" s="5" t="n">
         <v>0.01961408770241291</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>0.007562972122973799</v>
+        <v>0.007563126124074171</v>
       </c>
       <c r="O103" s="5" t="n">
         <v>0.5968733521584325</v>
@@ -6331,13 +6331,13 @@
         <v>0.00804670435819177</v>
       </c>
       <c r="N104" s="5" t="n">
-        <v>0.02729336632121515</v>
+        <v>0.0272933020220536</v>
       </c>
       <c r="O104" s="5" t="n">
-        <v>0.4171284561684774</v>
+        <v>0.4171287008858935</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.1232327033215768</v>
+        <v>0.123232767976875</v>
       </c>
     </row>
     <row r="105">
@@ -6381,19 +6381,19 @@
         <v>-0.06738336892756569</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>-0.07951847251300698</v>
+        <v>-0.07951845220285209</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>-0.1141130277120911</v>
+        <v>-0.1141130269165899</v>
       </c>
       <c r="N105" s="5" t="n">
-        <v>-0.03238443470219207</v>
+        <v>-0.03238438264288121</v>
       </c>
       <c r="O105" s="5" t="n">
-        <v>1.467250095850388</v>
+        <v>1.467249968944113</v>
       </c>
       <c r="P105" s="5" t="n">
-        <v>0.3493427020246786</v>
+        <v>0.3493426777126274</v>
       </c>
     </row>
     <row r="106">
@@ -6440,16 +6440,16 @@
         <v>0.05593092081670414</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>-0.1307402524792322</v>
+        <v>-0.1307402542472501</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>-0.1899355892614637</v>
+        <v>-0.1899356166035869</v>
       </c>
       <c r="O106" s="5" t="n">
-        <v>-0.01203206015785102</v>
+        <v>-0.01203203703975181</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>-0.005701099534310083</v>
+        <v>-0.005701094020938047</v>
       </c>
     </row>
     <row r="107">
@@ -6493,19 +6493,19 @@
         <v>-0.03633292353640456</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>-0.08709705242388169</v>
+        <v>-0.08709703877861359</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>-0.09944618443682263</v>
+        <v>-0.09944615826036921</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>-0.1749119167347507</v>
+        <v>-0.1749119225860023</v>
       </c>
       <c r="O107" s="5" t="n">
-        <v>0.6308373584734607</v>
+        <v>0.6308373456782711</v>
       </c>
       <c r="P107" s="5" t="n">
-        <v>0.1601740705803735</v>
+        <v>0.1601740737780592</v>
       </c>
     </row>
     <row r="108">
@@ -6549,19 +6549,19 @@
         <v>-0.1309159540425154</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>-0.03676150012959691</v>
+        <v>-0.03676148251165803</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>-0.1323063053641665</v>
+        <v>-0.132306303368124</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>-0.05093527152018374</v>
+        <v>-0.05093528061169753</v>
       </c>
       <c r="O108" s="5" t="n">
-        <v>0.988363979479745</v>
+        <v>0.988363995576429</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.2250290530682598</v>
+        <v>0.2250290546771774</v>
       </c>
     </row>
     <row r="109">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>PHM (26), DHI (25), LEN (14)</t>
+          <t>PHM (26), DHI (25), LEN (13)</t>
         </is>
       </c>
       <c r="G109" s="5" t="n">
@@ -6611,13 +6611,13 @@
         <v>-0.1330505892674483</v>
       </c>
       <c r="N109" s="5" t="n">
-        <v>-0.1542629366508359</v>
+        <v>-0.1542629467712481</v>
       </c>
       <c r="O109" s="5" t="n">
-        <v>0.2763047980164489</v>
+        <v>0.2763048042522727</v>
       </c>
       <c r="P109" s="5" t="n">
-        <v>0.07687875455202584</v>
+        <v>0.07687876286904333</v>
       </c>
     </row>
     <row r="110">
@@ -6720,7 +6720,7 @@
         <v>-0.2178538125420192</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>-0.229346870132649</v>
+        <v>-0.2293468365078948</v>
       </c>
       <c r="N111" s="5" t="n">
         <v>-0.02598179058634414</v>
@@ -6779,13 +6779,13 @@
         <v>-0.1931291022187065</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>-0.1613534141959103</v>
+        <v>-0.1613534407353724</v>
       </c>
       <c r="O112" s="5" t="n">
-        <v>0.1942023440452195</v>
+        <v>0.1942024453696709</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.06076638953016189</v>
+        <v>0.06076642033940693</v>
       </c>
     </row>
     <row r="113">
@@ -6835,13 +6835,13 @@
         <v>0.05125999333385511</v>
       </c>
       <c r="N113" s="5" t="n">
-        <v>0.3164362376064787</v>
+        <v>0.3164363098947274</v>
       </c>
       <c r="O113" s="5" t="n">
-        <v>0.1710160008503071</v>
+        <v>0.1710159756945132</v>
       </c>
       <c r="P113" s="5" t="n">
-        <v>0.05008943804382859</v>
+        <v>0.05008943431239721</v>
       </c>
     </row>
     <row r="114">
@@ -6894,10 +6894,10 @@
         <v>-0.2296221184598516</v>
       </c>
       <c r="O114" s="5" t="n">
-        <v>-0.05891139245590832</v>
+        <v>-0.05891131730138016</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>-0.04466202826566862</v>
+        <v>-0.04466198912015018</v>
       </c>
     </row>
     <row r="115">
@@ -6944,16 +6944,16 @@
         <v>-0.1548117049192659</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>-0.1732271110390871</v>
+        <v>-0.1732270796853811</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>-0.1721162755264391</v>
+        <v>-0.1721163131745015</v>
       </c>
       <c r="O115" s="5" t="n">
-        <v>0.8182292853896583</v>
+        <v>0.8182294044235284</v>
       </c>
       <c r="P115" s="5" t="n">
-        <v>0.2027962502438709</v>
+        <v>0.2027962720171251</v>
       </c>
     </row>
     <row r="116">
@@ -7000,16 +7000,16 @@
         <v>-0.1434602855159185</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>-0.2000784415100312</v>
+        <v>-0.2000784172711559</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>-0.1653625986629771</v>
+        <v>-0.165362588004053</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>1.170811971700827</v>
+        <v>1.170811925503028</v>
       </c>
       <c r="P116" s="5" t="n">
-        <v>0.1405332724383908</v>
+        <v>0.1405332689130136</v>
       </c>
     </row>
     <row r="117">
@@ -7112,16 +7112,16 @@
         <v>-0.1640624241152955</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>-0.2028286403704559</v>
+        <v>-0.202828625363975</v>
       </c>
       <c r="N118" s="5" t="n">
-        <v>-0.1754900933855182</v>
+        <v>-0.1754901053193829</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>0.4796306551525513</v>
+        <v>0.4796306336150107</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>0.1375209932542415</v>
+        <v>0.1375209916228729</v>
       </c>
     </row>
     <row r="119">
@@ -7336,16 +7336,16 @@
         <v>-0.213030447972736</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>-0.2436928278329458</v>
+        <v>-0.243692770980184</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>-0.1621972442598184</v>
+        <v>-0.1621971047294526</v>
       </c>
       <c r="O122" s="5" t="n">
-        <v>-0.262967279355988</v>
+        <v>-0.2629672253640812</v>
       </c>
       <c r="P122" s="5" t="n">
-        <v>-0.09670642130342155</v>
+        <v>-0.09670639924626356</v>
       </c>
     </row>
     <row r="123">
@@ -7392,16 +7392,16 @@
         <v>-0.1940683627916402</v>
       </c>
       <c r="M123" s="5" t="n">
-        <v>-0.2364124229686014</v>
+        <v>-0.2364124768254914</v>
       </c>
       <c r="N123" s="5" t="n">
         <v>-0.2661362225919138</v>
       </c>
       <c r="O123" s="5" t="n">
-        <v>3.173022768863329</v>
+        <v>3.173022634911134</v>
       </c>
       <c r="P123" s="5" t="n">
-        <v>0.4911255842858882</v>
+        <v>0.4911255440384755</v>
       </c>
     </row>
     <row r="124">
@@ -7507,7 +7507,7 @@
         <v>-0.3164325678503705</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>-0.3742031237945634</v>
+        <v>-0.3742030934728306</v>
       </c>
       <c r="O125" s="5" t="n">
         <v>-0.5314011568035422</v>
@@ -7560,16 +7560,16 @@
         <v>-0.3208493523596181</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>-0.3095883791686962</v>
+        <v>-0.309588393623302</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>-0.3048273328714556</v>
+        <v>-0.3048273455347706</v>
       </c>
       <c r="O126" s="5" t="n">
-        <v>-0.18075193108573</v>
+        <v>-0.1807518804037886</v>
       </c>
       <c r="P126" s="5" t="n">
-        <v>-0.06435242838116255</v>
+        <v>-0.06435240945532957</v>
       </c>
     </row>
     <row r="127">
@@ -7822,16 +7822,16 @@
         <v>1.40514324680368</v>
       </c>
       <c r="M3" t="n">
-        <v>3.234773339803067</v>
+        <v>3.234773616884959</v>
       </c>
       <c r="N3" t="n">
-        <v>2.026426244833331</v>
+        <v>2.02642596179978</v>
       </c>
       <c r="O3" t="n">
-        <v>6.821896497412916</v>
+        <v>6.821896024760498</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9850465167621418</v>
+        <v>0.9850464767787843</v>
       </c>
     </row>
     <row r="4">
@@ -8170,16 +8170,16 @@
         <v>0.6430665238277082</v>
       </c>
       <c r="M9" t="n">
-        <v>2.012354351695175</v>
+        <v>2.012354626804496</v>
       </c>
       <c r="N9" t="n">
-        <v>1.849585952063173</v>
+        <v>1.849585705880981</v>
       </c>
       <c r="O9" t="n">
-        <v>4.369529065489929</v>
+        <v>4.369529502544418</v>
       </c>
       <c r="P9" t="n">
-        <v>0.751104507154092</v>
+        <v>0.751104554664656</v>
       </c>
     </row>
     <row r="10">
@@ -8341,10 +8341,10 @@
         <v>0.2843895194780068</v>
       </c>
       <c r="L12" t="n">
-        <v>1.07651794862532</v>
+        <v>1.076517801538726</v>
       </c>
       <c r="M12" t="n">
-        <v>1.275214385256118</v>
+        <v>1.275214208674146</v>
       </c>
       <c r="N12" t="n">
         <v>0.9592767009556327</v>
@@ -8457,19 +8457,19 @@
         <v>0.444132994829352</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9074925319932203</v>
+        <v>0.9074926579535458</v>
       </c>
       <c r="M14" t="n">
         <v>1.592216235560947</v>
       </c>
       <c r="N14" t="n">
-        <v>1.331471656886119</v>
+        <v>1.331471468708358</v>
       </c>
       <c r="O14" t="n">
-        <v>2.20297709872032</v>
+        <v>2.202977453873549</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4740694463714439</v>
+        <v>0.4740695008541422</v>
       </c>
     </row>
     <row r="15">
@@ -8582,10 +8582,10 @@
         <v>1.312880662968547</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4266846936081914</v>
+        <v>0.4266848455265437</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1257518447131787</v>
+        <v>0.1257518846711689</v>
       </c>
     </row>
     <row r="17">
@@ -8753,13 +8753,13 @@
         <v>1.142324759184983</v>
       </c>
       <c r="N19" t="n">
-        <v>1.342722008050643</v>
+        <v>1.342722223622939</v>
       </c>
       <c r="O19" t="n">
-        <v>2.41428784275576</v>
+        <v>2.414288071695765</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5057979812162365</v>
+        <v>0.5057980148725856</v>
       </c>
     </row>
     <row r="20">
@@ -8811,13 +8811,13 @@
         <v>0.4904777835583778</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7183764194855227</v>
+        <v>0.7183762832234541</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7026039858757813</v>
+        <v>0.7026038521036455</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1940922562252538</v>
+        <v>0.194092224952318</v>
       </c>
     </row>
     <row r="21">
@@ -8869,13 +8869,13 @@
         <v>0.5809426535467295</v>
       </c>
       <c r="N21" t="n">
-        <v>2.148358890458941</v>
+        <v>2.148359107155406</v>
       </c>
       <c r="O21" t="n">
-        <v>9.863820578249065</v>
+        <v>9.86382186833475</v>
       </c>
       <c r="P21" t="n">
-        <v>1.214764369708611</v>
+        <v>1.214764457376839</v>
       </c>
     </row>
     <row r="22">
@@ -9037,7 +9037,7 @@
         <v>0.3369589403728732</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6787444086332901</v>
+        <v>0.6787442515539097</v>
       </c>
       <c r="M24" t="n">
         <v>0.9671314679880041</v>
@@ -9159,13 +9159,13 @@
         <v>1.138747755160901</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4123466722646407</v>
+        <v>0.4123465244653033</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1643686864778015</v>
+        <v>-0.164368531260311</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.05809977213716389</v>
+        <v>-0.05809971381823054</v>
       </c>
     </row>
     <row r="27">
@@ -9211,7 +9211,7 @@
         <v>-0.1444688160547735</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01447771023821209</v>
+        <v>0.01447778946636769</v>
       </c>
       <c r="M27" t="n">
         <v>0.4188075385077319</v>
@@ -9278,10 +9278,10 @@
         <v>1.048497392765467</v>
       </c>
       <c r="O28" t="n">
-        <v>2.867725187741058</v>
+        <v>2.867725560838151</v>
       </c>
       <c r="P28" t="n">
-        <v>0.5697067876764761</v>
+        <v>0.5697068381499881</v>
       </c>
     </row>
     <row r="29">
@@ -9394,10 +9394,10 @@
         <v>1.300264906988621</v>
       </c>
       <c r="O30" t="n">
-        <v>1.732913842868849</v>
+        <v>1.732913246380332</v>
       </c>
       <c r="P30" t="n">
-        <v>0.3981120543154275</v>
+        <v>0.3981119525976402</v>
       </c>
     </row>
     <row r="31">
@@ -9449,13 +9449,13 @@
         <v>0.5025719912209448</v>
       </c>
       <c r="N31" t="n">
-        <v>0.7716251504570795</v>
+        <v>0.7716249898100873</v>
       </c>
       <c r="O31" t="n">
-        <v>0.3824033319884963</v>
+        <v>0.3824034298019374</v>
       </c>
       <c r="P31" t="n">
-        <v>0.113982215073327</v>
+        <v>0.113982241346998</v>
       </c>
     </row>
     <row r="32">
@@ -9620,10 +9620,10 @@
         <v>0.680906545539945</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7691534985638295</v>
+        <v>0.7691536825335918</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2149537795928651</v>
+        <v>0.2149538663559358</v>
       </c>
       <c r="O34" t="n">
         <v>0.4209608679939267</v>
@@ -9742,10 +9742,10 @@
         <v>0.8887699130687463</v>
       </c>
       <c r="O36" t="n">
-        <v>1.427678619831078</v>
+        <v>1.427678769553975</v>
       </c>
       <c r="P36" t="n">
-        <v>0.3439931787595576</v>
+        <v>0.343993206389045</v>
       </c>
     </row>
     <row r="37">
@@ -9794,10 +9794,10 @@
         <v>0.5852715694257489</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3633798783770912</v>
+        <v>0.3633800346649059</v>
       </c>
       <c r="N37" t="n">
-        <v>0.2536294042350815</v>
+        <v>0.2536296685123054</v>
       </c>
       <c r="O37" t="n">
         <v>0.8057298404308741</v>
@@ -9910,10 +9910,10 @@
         <v>0.4428987934314057</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6108096616364662</v>
+        <v>0.61080954816606</v>
       </c>
       <c r="N39" t="n">
-        <v>0.1220771764673554</v>
+        <v>0.1220772865882382</v>
       </c>
       <c r="O39" t="n">
         <v>0.08963827749372189</v>
@@ -9965,7 +9965,7 @@
         <v>0.123962708716175</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1811269517516612</v>
+        <v>0.1811270891621317</v>
       </c>
       <c r="M40" t="n">
         <v>0.4573792490049924</v>
@@ -10197,19 +10197,19 @@
         <v>0.2411305219512101</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2617730333881498</v>
+        <v>0.2617729310411816</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3504776183931915</v>
+        <v>0.3504777356363082</v>
       </c>
       <c r="N44" t="n">
         <v>0.5718334915713499</v>
       </c>
       <c r="O44" t="n">
-        <v>1.931496110105246</v>
+        <v>1.931495833881416</v>
       </c>
       <c r="P44" t="n">
-        <v>0.431187191224885</v>
+        <v>0.4311871462730918</v>
       </c>
     </row>
     <row r="45">
@@ -10264,10 +10264,10 @@
         <v>0.8091369795324712</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9139080234000971</v>
+        <v>0.9139082290501166</v>
       </c>
       <c r="P45" t="n">
-        <v>0.2415770827114214</v>
+        <v>0.2415771271807026</v>
       </c>
     </row>
     <row r="46">
@@ -10432,16 +10432,16 @@
         <v>0.238680548448756</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3864548999866069</v>
+        <v>0.3864550279592076</v>
       </c>
       <c r="N48" t="n">
-        <v>0.5456533586111887</v>
+        <v>0.5456531995626728</v>
       </c>
       <c r="O48" t="n">
-        <v>0.8000550531585342</v>
+        <v>0.8000545138753032</v>
       </c>
       <c r="P48" t="n">
-        <v>0.2164528006338284</v>
+        <v>0.2164526791537176</v>
       </c>
     </row>
     <row r="49">
@@ -10493,13 +10493,13 @@
         <v>0.3473066588625053</v>
       </c>
       <c r="N49" t="n">
-        <v>0.5897971880615889</v>
+        <v>0.5897973587714112</v>
       </c>
       <c r="O49" t="n">
-        <v>0.889838672269549</v>
+        <v>0.8898387928826574</v>
       </c>
       <c r="P49" t="n">
-        <v>0.2363504102323803</v>
+        <v>0.2363504365344602</v>
       </c>
     </row>
     <row r="50">
@@ -10551,13 +10551,13 @@
         <v>0.5374143125676958</v>
       </c>
       <c r="N50" t="n">
-        <v>0.217790374037625</v>
+        <v>0.2177902573452437</v>
       </c>
       <c r="O50" t="n">
-        <v>0.7420502686806452</v>
+        <v>0.742050388076396</v>
       </c>
       <c r="P50" t="n">
-        <v>0.2032436016502024</v>
+        <v>0.2032436291393001</v>
       </c>
     </row>
     <row r="51">
@@ -10670,10 +10670,10 @@
         <v>0.5678946563248979</v>
       </c>
       <c r="O52" t="n">
-        <v>0.42119828001643</v>
+        <v>0.4211983757775972</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1243069390548428</v>
+        <v>0.1243069643069943</v>
       </c>
     </row>
     <row r="53">
@@ -10728,10 +10728,10 @@
         <v>0.6684267649783866</v>
       </c>
       <c r="O53" t="n">
-        <v>0.8950893999759162</v>
+        <v>0.8950895389560554</v>
       </c>
       <c r="P53" t="n">
-        <v>0.2374943767334812</v>
+        <v>0.2374944069848484</v>
       </c>
     </row>
     <row r="54">
@@ -10780,10 +10780,10 @@
         <v>0.2250403002733652</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3495526253506569</v>
+        <v>0.3495524726712202</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6282311970168726</v>
+        <v>0.6282313081396598</v>
       </c>
       <c r="O54" t="n">
         <v>0.9030978781706631</v>
@@ -10841,7 +10841,7 @@
         <v>0.3455458237909594</v>
       </c>
       <c r="N55" t="n">
-        <v>0.6668762597240592</v>
+        <v>0.6668764101398412</v>
       </c>
       <c r="O55" t="n">
         <v>0.5019467522107437</v>
@@ -10902,10 +10902,10 @@
         <v>0.4012624413720669</v>
       </c>
       <c r="O56" t="n">
-        <v>0.875032482405496</v>
+        <v>0.8750320356655139</v>
       </c>
       <c r="P56" t="n">
-        <v>0.2331131578797279</v>
+        <v>0.2331130599470255</v>
       </c>
     </row>
     <row r="57">
@@ -10954,10 +10954,10 @@
         <v>0.08241122776280729</v>
       </c>
       <c r="M57" t="n">
-        <v>0.4218455186517018</v>
+        <v>0.421845641336446</v>
       </c>
       <c r="N57" t="n">
-        <v>0.570209496932548</v>
+        <v>0.5702093473086878</v>
       </c>
       <c r="O57" t="n">
         <v>0.06719698471523206</v>
@@ -11015,7 +11015,7 @@
         <v>0.2644306026894276</v>
       </c>
       <c r="N58" t="n">
-        <v>0.5808135627798252</v>
+        <v>0.5808136811723759</v>
       </c>
       <c r="O58" t="n">
         <v>1.347459456501757</v>
@@ -11067,7 +11067,7 @@
         <v>0.001069922939858081</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2643095564233615</v>
+        <v>0.2643096770745808</v>
       </c>
       <c r="M59" t="n">
         <v>0.451024376866247</v>
@@ -11076,10 +11076,10 @@
         <v>0.6725263808962161</v>
       </c>
       <c r="O59" t="n">
-        <v>1.023668448349192</v>
+        <v>1.023668139246002</v>
       </c>
       <c r="P59" t="n">
-        <v>0.2648716348885956</v>
+        <v>0.2648715704880795</v>
       </c>
     </row>
     <row r="60">
@@ -11131,13 +11131,13 @@
         <v>0.3115869842577823</v>
       </c>
       <c r="N60" t="n">
-        <v>0.6425126033274875</v>
+        <v>0.642512502962056</v>
       </c>
       <c r="O60" t="n">
-        <v>0.2094875329433852</v>
+        <v>0.2094877506289459</v>
       </c>
       <c r="P60" t="n">
-        <v>0.06545177859748907</v>
+        <v>0.06545184251807457</v>
       </c>
     </row>
     <row r="61">
@@ -11247,13 +11247,13 @@
         <v>0.2533371433196721</v>
       </c>
       <c r="N62" t="n">
-        <v>0.3813111390541188</v>
+        <v>0.3813109898735587</v>
       </c>
       <c r="O62" t="n">
-        <v>0.04932575314110466</v>
+        <v>0.04932558096224016</v>
       </c>
       <c r="P62" t="n">
-        <v>0.01617875402440383</v>
+        <v>0.01617869844442366</v>
       </c>
     </row>
     <row r="63">
@@ -11305,13 +11305,13 @@
         <v>0.2764902337602628</v>
       </c>
       <c r="N63" t="n">
-        <v>0.4284570742686031</v>
+        <v>0.4284572459838198</v>
       </c>
       <c r="O63" t="n">
-        <v>0.4279494070633276</v>
+        <v>0.4279490638770822</v>
       </c>
       <c r="P63" t="n">
-        <v>0.1260843949521075</v>
+        <v>0.1260843047395961</v>
       </c>
     </row>
     <row r="64">
@@ -11366,10 +11366,10 @@
         <v>0.2671923351563348</v>
       </c>
       <c r="O64" t="n">
-        <v>0.6480807023974811</v>
+        <v>0.6480803492444187</v>
       </c>
       <c r="P64" t="n">
-        <v>0.1812073972987094</v>
+        <v>0.1812073129284397</v>
       </c>
     </row>
     <row r="65">
@@ -11421,13 +11421,13 @@
         <v>0.50444827559105</v>
       </c>
       <c r="N65" t="n">
-        <v>0.5960450393287295</v>
+        <v>0.5960449088587361</v>
       </c>
       <c r="O65" t="n">
-        <v>0.5505076984237534</v>
+        <v>0.5505075752925255</v>
       </c>
       <c r="P65" t="n">
-        <v>0.1574208697291974</v>
+        <v>0.1574208390909198</v>
       </c>
     </row>
     <row r="66">
@@ -11534,16 +11534,16 @@
         <v>0.4659019709380896</v>
       </c>
       <c r="M67" t="n">
-        <v>0.3362525221422001</v>
+        <v>0.3362526174100455</v>
       </c>
       <c r="N67" t="n">
         <v>0.2944945731435598</v>
       </c>
       <c r="O67" t="n">
-        <v>1.274470504673233</v>
+        <v>1.274470918693111</v>
       </c>
       <c r="P67" t="n">
-        <v>0.3151040132606815</v>
+        <v>0.3151040930564213</v>
       </c>
     </row>
     <row r="68">
@@ -11656,10 +11656,10 @@
         <v>1.173754936442394</v>
       </c>
       <c r="O69" t="n">
-        <v>2.776791287833003</v>
+        <v>2.776790592986687</v>
       </c>
       <c r="P69" t="n">
-        <v>0.557307332788002</v>
+        <v>0.5573072372845931</v>
       </c>
     </row>
     <row r="70">
@@ -11714,10 +11714,10 @@
         <v>0.456261448564095</v>
       </c>
       <c r="O70" t="n">
-        <v>0.3802007757880603</v>
+        <v>0.3802009205887791</v>
       </c>
       <c r="P70" t="n">
-        <v>0.1133902718904423</v>
+        <v>0.1133903108267353</v>
       </c>
     </row>
     <row r="71">
@@ -11882,16 +11882,16 @@
         <v>0.2467029529002489</v>
       </c>
       <c r="M73" t="n">
-        <v>0.1599197676276252</v>
+        <v>0.1599198965810742</v>
       </c>
       <c r="N73" t="n">
-        <v>0.3839024213279485</v>
+        <v>0.3839023295458615</v>
       </c>
       <c r="O73" t="n">
-        <v>1.28376518394091</v>
+        <v>1.28376543388908</v>
       </c>
       <c r="P73" t="n">
-        <v>0.316892980140038</v>
+        <v>0.3168930281827733</v>
       </c>
     </row>
     <row r="74">
@@ -11940,16 +11940,16 @@
         <v>-0.04123557554111268</v>
       </c>
       <c r="M74" t="n">
-        <v>0.3743721295047646</v>
+        <v>0.374372236842434</v>
       </c>
       <c r="N74" t="n">
         <v>0.4988477822192559</v>
       </c>
       <c r="O74" t="n">
-        <v>-0.09703110616694566</v>
+        <v>-0.09703092083550213</v>
       </c>
       <c r="P74" t="n">
-        <v>-0.03345013786147077</v>
+        <v>-0.03345007173439807</v>
       </c>
     </row>
     <row r="75">
@@ -11998,16 +11998,16 @@
         <v>0.2805947090509675</v>
       </c>
       <c r="M75" t="n">
-        <v>0.4127626514494558</v>
+        <v>0.4127628060394097</v>
       </c>
       <c r="N75" t="n">
-        <v>0.4919326974832623</v>
+        <v>0.4919325250816893</v>
       </c>
       <c r="O75" t="n">
-        <v>1.580184099304629</v>
+        <v>1.580183583667583</v>
       </c>
       <c r="P75" t="n">
-        <v>0.371566591837045</v>
+        <v>0.371566500470103</v>
       </c>
     </row>
     <row r="76">
@@ -12062,10 +12062,10 @@
         <v>0.5468442664086013</v>
       </c>
       <c r="O76" t="n">
-        <v>1.307591102674167</v>
+        <v>1.307590918494529</v>
       </c>
       <c r="P76" t="n">
-        <v>0.3214567447287631</v>
+        <v>0.3214567095715479</v>
       </c>
     </row>
     <row r="77">
@@ -12111,19 +12111,19 @@
         <v>0.04489694813493106</v>
       </c>
       <c r="L77" t="n">
-        <v>0.2690865766080559</v>
+        <v>0.2690866766630766</v>
       </c>
       <c r="M77" t="n">
-        <v>0.3604853102307921</v>
+        <v>0.3604851952450405</v>
       </c>
       <c r="N77" t="n">
         <v>0.4008902646321539</v>
       </c>
       <c r="O77" t="n">
-        <v>1.035909364388896</v>
+        <v>1.035909235640091</v>
       </c>
       <c r="P77" t="n">
-        <v>0.2674168596867585</v>
+        <v>0.267416832970047</v>
       </c>
     </row>
     <row r="78">
@@ -12175,13 +12175,13 @@
         <v>-0.03637364179104874</v>
       </c>
       <c r="N78" t="n">
-        <v>0.122569567874165</v>
+        <v>0.1225694799199444</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.07251532318168563</v>
+        <v>-0.0725153832220955</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.02478078939227502</v>
+        <v>-0.02478081043577174</v>
       </c>
     </row>
     <row r="79">
@@ -12230,16 +12230,16 @@
         <v>0.1559160741635857</v>
       </c>
       <c r="M79" t="n">
-        <v>0.4032708000312244</v>
+        <v>0.4032706555182837</v>
       </c>
       <c r="N79" t="n">
         <v>0.4755649814637242</v>
       </c>
       <c r="O79" t="n">
-        <v>0.8539889536845122</v>
+        <v>0.8539892059385639</v>
       </c>
       <c r="P79" t="n">
-        <v>0.2284827069734279</v>
+        <v>0.2284827626892805</v>
       </c>
     </row>
     <row r="80">
@@ -12352,10 +12352,10 @@
         <v>0.4144451279772254</v>
       </c>
       <c r="O81" t="n">
-        <v>2.411636184863279</v>
+        <v>2.411635620513107</v>
       </c>
       <c r="P81" t="n">
-        <v>0.5054080614244951</v>
+        <v>0.5054079784166852</v>
       </c>
     </row>
     <row r="82">
@@ -12410,10 +12410,10 @@
         <v>-0.03970916484663201</v>
       </c>
       <c r="O82" t="n">
-        <v>0.2551859443788558</v>
+        <v>0.2551861429671016</v>
       </c>
       <c r="P82" t="n">
-        <v>0.07870499340829951</v>
+        <v>0.07870505029711383</v>
       </c>
     </row>
     <row r="83">
@@ -12462,10 +12462,10 @@
         <v>0.2247249623685301</v>
       </c>
       <c r="M83" t="n">
-        <v>0.3083880296372361</v>
+        <v>0.3083881185900161</v>
       </c>
       <c r="N83" t="n">
-        <v>0.3523384020465519</v>
+        <v>0.3523383070173454</v>
       </c>
       <c r="O83" t="n">
         <v>2.02544353172809</v>
@@ -12523,13 +12523,13 @@
         <v>0.4447422208402874</v>
       </c>
       <c r="N84" t="n">
-        <v>0.568714480730822</v>
+        <v>0.5687143305255442</v>
       </c>
       <c r="O84" t="n">
-        <v>1.499798401447451</v>
+        <v>1.499798020024055</v>
       </c>
       <c r="P84" t="n">
-        <v>0.3571723258059587</v>
+        <v>0.3571722567794187</v>
       </c>
     </row>
     <row r="85">
@@ -12578,16 +12578,16 @@
         <v>0.2307704921756666</v>
       </c>
       <c r="M85" t="n">
-        <v>0.3383323597928081</v>
+        <v>0.338332261988177</v>
       </c>
       <c r="N85" t="n">
-        <v>0.2493178114518173</v>
+        <v>0.2493177262247928</v>
       </c>
       <c r="O85" t="n">
-        <v>0.2762465568261152</v>
+        <v>0.2762463789446923</v>
       </c>
       <c r="P85" t="n">
-        <v>0.08470471462894547</v>
+        <v>0.0847046642340783</v>
       </c>
     </row>
     <row r="86">
@@ -12639,13 +12639,13 @@
         <v>0.1095214754173728</v>
       </c>
       <c r="N86" t="n">
-        <v>-0.01234345340380683</v>
+        <v>-0.01234334128220449</v>
       </c>
       <c r="O86" t="n">
-        <v>0.6477580958504756</v>
+        <v>0.6477582518898881</v>
       </c>
       <c r="P86" t="n">
-        <v>0.1811303197409595</v>
+        <v>0.181130357024522</v>
       </c>
     </row>
     <row r="87">
@@ -12697,13 +12697,13 @@
         <v>0.3086816577031604</v>
       </c>
       <c r="N87" t="n">
-        <v>0.4962959715320521</v>
+        <v>0.4962961371946035</v>
       </c>
       <c r="O87" t="n">
-        <v>0.4381509801467816</v>
+        <v>0.4381514392598351</v>
       </c>
       <c r="P87" t="n">
-        <v>0.1287596958868498</v>
+        <v>0.1287598160013259</v>
       </c>
     </row>
     <row r="88">
@@ -12758,10 +12758,10 @@
         <v>0.3013894060837796</v>
       </c>
       <c r="O88" t="n">
-        <v>0.8683290103832344</v>
+        <v>0.8683288767442874</v>
       </c>
       <c r="P88" t="n">
-        <v>0.2316418927032007</v>
+        <v>0.2316418633373289</v>
       </c>
     </row>
     <row r="89">
@@ -12807,13 +12807,13 @@
         <v>0.1967442633160408</v>
       </c>
       <c r="L89" t="n">
-        <v>-0.08242167513329124</v>
+        <v>-0.08242176923771161</v>
       </c>
       <c r="M89" t="n">
-        <v>0.2703472479128557</v>
+        <v>0.2703471577269541</v>
       </c>
       <c r="N89" t="n">
-        <v>0.4111312495312711</v>
+        <v>0.4111311382483378</v>
       </c>
       <c r="O89" t="n">
         <v>-0.1567399306860341</v>
@@ -12868,16 +12868,16 @@
         <v>0.149386717553925</v>
       </c>
       <c r="M90" t="n">
-        <v>0.05379730427693308</v>
+        <v>0.05379736788322109</v>
       </c>
       <c r="N90" t="n">
         <v>0.6327474019888542</v>
       </c>
       <c r="O90" t="n">
-        <v>1.052589675346219</v>
+        <v>1.052589434028013</v>
       </c>
       <c r="P90" t="n">
-        <v>0.2708687868514903</v>
+        <v>0.2708687370471234</v>
       </c>
     </row>
     <row r="91">
@@ -12926,16 +12926,16 @@
         <v>0.1957734841184917</v>
       </c>
       <c r="M91" t="n">
-        <v>0.1714386182207497</v>
+        <v>0.1714387037704987</v>
       </c>
       <c r="N91" t="n">
         <v>0.5177427908690886</v>
       </c>
       <c r="O91" t="n">
-        <v>1.795587352350411</v>
+        <v>1.795587595960804</v>
       </c>
       <c r="P91" t="n">
-        <v>0.4087189464996575</v>
+        <v>0.4087189874187347</v>
       </c>
     </row>
     <row r="92">
@@ -12990,10 +12990,10 @@
         <v>0.2697662740076607</v>
       </c>
       <c r="O92" t="n">
-        <v>2.587458918524339</v>
+        <v>2.587458525908715</v>
       </c>
       <c r="P92" t="n">
-        <v>0.5308370999128968</v>
+        <v>0.5308370440673713</v>
       </c>
     </row>
     <row r="93">
@@ -13048,10 +13048,10 @@
         <v>0.2863426397634905</v>
       </c>
       <c r="O93" t="n">
-        <v>0.1861888348942111</v>
+        <v>0.1861889260223433</v>
       </c>
       <c r="P93" t="n">
-        <v>0.05856600768392584</v>
+        <v>0.0585660347917909</v>
       </c>
     </row>
     <row r="94">
@@ -13161,13 +13161,13 @@
         <v>0.2093778044457451</v>
       </c>
       <c r="N95" t="n">
-        <v>0.4826304513836519</v>
+        <v>0.4826303276315846</v>
       </c>
       <c r="O95" t="n">
-        <v>1.027200023007731</v>
+        <v>1.027200717074539</v>
       </c>
       <c r="P95" t="n">
-        <v>0.2656069978763225</v>
+        <v>0.2656071423145785</v>
       </c>
     </row>
     <row r="96">
@@ -13222,10 +13222,10 @@
         <v>0.448443273596427</v>
       </c>
       <c r="O96" t="n">
-        <v>0.3024100692662786</v>
+        <v>0.3024098522540133</v>
       </c>
       <c r="P96" t="n">
-        <v>0.0920669109225638</v>
+        <v>0.09206685026785077</v>
       </c>
     </row>
     <row r="97">
@@ -13280,10 +13280,10 @@
         <v>0.4969318346268636</v>
       </c>
       <c r="O97" t="n">
-        <v>2.017450450400853</v>
+        <v>2.017450850687267</v>
       </c>
       <c r="P97" t="n">
-        <v>0.4450405994907987</v>
+        <v>0.4450406633891242</v>
       </c>
     </row>
     <row r="98">
@@ -13338,10 +13338,10 @@
         <v>0.4980945333113551</v>
       </c>
       <c r="O98" t="n">
-        <v>1.189387997252867</v>
+        <v>1.189388553605312</v>
       </c>
       <c r="P98" t="n">
-        <v>0.298496881484102</v>
+        <v>0.2984969914725026</v>
       </c>
     </row>
     <row r="99">
@@ -13448,10 +13448,10 @@
         <v>0.2723711134598625</v>
       </c>
       <c r="M100" t="n">
-        <v>0.344430859538704</v>
+        <v>0.3444310199678648</v>
       </c>
       <c r="N100" t="n">
-        <v>0.2828997949477532</v>
+        <v>0.2829000871085099</v>
       </c>
       <c r="O100" t="n">
         <v>1.071574602269854</v>
@@ -13509,13 +13509,13 @@
         <v>0.2095820932869641</v>
       </c>
       <c r="N101" t="n">
-        <v>0.4026807780889734</v>
+        <v>0.4026805939170299</v>
       </c>
       <c r="O101" t="n">
-        <v>0.5963884907556334</v>
+        <v>0.5963883714796558</v>
       </c>
       <c r="P101" t="n">
-        <v>0.1687264225785452</v>
+        <v>0.1687263934709708</v>
       </c>
     </row>
     <row r="102">
@@ -13567,13 +13567,13 @@
         <v>0.2799306894298186</v>
       </c>
       <c r="N102" t="n">
-        <v>0.3421970788611051</v>
+        <v>0.3421967791925722</v>
       </c>
       <c r="O102" t="n">
-        <v>0.8102980805388478</v>
+        <v>0.8102979442536096</v>
       </c>
       <c r="P102" t="n">
-        <v>0.2187558041520166</v>
+        <v>0.2187557735680239</v>
       </c>
     </row>
     <row r="103">
@@ -13677,19 +13677,19 @@
         <v>0.07733368596609425</v>
       </c>
       <c r="L104" t="n">
-        <v>0.07822301446396129</v>
+        <v>0.07822310828315659</v>
       </c>
       <c r="M104" t="n">
-        <v>0.2381996765894465</v>
+        <v>0.2381995528649199</v>
       </c>
       <c r="N104" t="n">
-        <v>0.4424308549008416</v>
+        <v>0.4424310228061896</v>
       </c>
       <c r="O104" t="n">
-        <v>0.6817334702438196</v>
+        <v>0.6817333561246028</v>
       </c>
       <c r="P104" t="n">
-        <v>0.1891931234897954</v>
+        <v>0.1891930965910045</v>
       </c>
     </row>
     <row r="105">
@@ -13796,16 +13796,16 @@
         <v>0.09407408055439026</v>
       </c>
       <c r="M106" t="n">
-        <v>0.239740335946599</v>
+        <v>0.2397404486970367</v>
       </c>
       <c r="N106" t="n">
-        <v>0.8375547094769729</v>
+        <v>0.8375544617705701</v>
       </c>
       <c r="O106" t="n">
-        <v>2.243468295346107</v>
+        <v>2.243467523597339</v>
       </c>
       <c r="P106" t="n">
-        <v>0.4802550533384653</v>
+        <v>0.4802549359348096</v>
       </c>
     </row>
     <row r="107">
@@ -13857,7 +13857,7 @@
         <v>0.3248508762494247</v>
       </c>
       <c r="N107" t="n">
-        <v>0.06283402106248848</v>
+        <v>0.06283412702938862</v>
       </c>
       <c r="O107" t="n">
         <v>-0.1446680432104441</v>
@@ -13915,7 +13915,7 @@
         <v>0.2325082348045533</v>
       </c>
       <c r="N108" t="n">
-        <v>0.1640353000745765</v>
+        <v>0.1640351968527887</v>
       </c>
       <c r="O108" t="n">
         <v>0.7875906639579939</v>
@@ -13973,13 +13973,13 @@
         <v>0.3276007147973528</v>
       </c>
       <c r="N109" t="n">
-        <v>0.3974741864657965</v>
+        <v>0.3974739863354644</v>
       </c>
       <c r="O109" t="n">
-        <v>0.5771759281594782</v>
+        <v>0.5771755457956305</v>
       </c>
       <c r="P109" t="n">
-        <v>0.1640189394381273</v>
+        <v>0.1640188453715137</v>
       </c>
     </row>
     <row r="110">
@@ -14025,19 +14025,19 @@
         <v>0.105641026747801</v>
       </c>
       <c r="L110" t="n">
-        <v>0.373887786470557</v>
+        <v>0.3738878785838973</v>
       </c>
       <c r="M110" t="n">
         <v>0.1747468868782929</v>
       </c>
       <c r="N110" t="n">
-        <v>0.1036035070511876</v>
+        <v>0.1036033881801457</v>
       </c>
       <c r="O110" t="n">
-        <v>-0.2283945499080292</v>
+        <v>-0.2283946080166426</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.08279778361897061</v>
+        <v>-0.08279780664341063</v>
       </c>
     </row>
     <row r="111">
@@ -14089,7 +14089,7 @@
         <v>-0.1310702408828472</v>
       </c>
       <c r="N111" t="n">
-        <v>0.4493128060022002</v>
+        <v>0.4493130873505962</v>
       </c>
       <c r="O111" t="n">
         <v>2.09718329871097</v>
@@ -14147,13 +14147,13 @@
         <v>0.251188794588119</v>
       </c>
       <c r="N112" t="n">
-        <v>0.2459517518251384</v>
+        <v>0.2459516574218308</v>
       </c>
       <c r="O112" t="n">
-        <v>0.2501351678864212</v>
+        <v>0.250134882771534</v>
       </c>
       <c r="P112" t="n">
-        <v>0.07725617166760901</v>
+        <v>0.07725608977198606</v>
       </c>
     </row>
     <row r="113">
@@ -14205,13 +14205,13 @@
         <v>0.2224015774892825</v>
       </c>
       <c r="N113" t="n">
-        <v>0.2931542714526421</v>
+        <v>0.2931541883397903</v>
       </c>
       <c r="O113" t="n">
-        <v>0.6227083916706562</v>
+        <v>0.6227086534157584</v>
       </c>
       <c r="P113" t="n">
-        <v>0.1751144338032766</v>
+        <v>0.1751144969857996</v>
       </c>
     </row>
     <row r="114">
@@ -14266,10 +14266,10 @@
         <v>0.3907937369132117</v>
       </c>
       <c r="O114" t="n">
-        <v>1.043080011564663</v>
+        <v>1.043079341090071</v>
       </c>
       <c r="P114" t="n">
-        <v>0.2689030997437094</v>
+        <v>0.2689029609390001</v>
       </c>
     </row>
     <row r="115">
@@ -14379,7 +14379,7 @@
         <v>0.1638526031280501</v>
       </c>
       <c r="N116" t="n">
-        <v>0.05014564012307066</v>
+        <v>0.05014552218859625</v>
       </c>
       <c r="O116" t="n">
         <v>0.4272401276685667</v>
@@ -14431,13 +14431,13 @@
         <v>0.1084827289767809</v>
       </c>
       <c r="L117" t="n">
-        <v>0.2206246895282007</v>
+        <v>0.2206245539701406</v>
       </c>
       <c r="M117" t="n">
-        <v>0.1427578795504012</v>
+        <v>0.1427579983649403</v>
       </c>
       <c r="N117" t="n">
-        <v>0.2663103207401372</v>
+        <v>0.2663104666354823</v>
       </c>
       <c r="O117" t="n">
         <v>1.008417008672742</v>
@@ -14489,7 +14489,7 @@
         <v>0.1712357310589463</v>
       </c>
       <c r="L118" t="n">
-        <v>0.1143333999304368</v>
+        <v>0.1143334931217925</v>
       </c>
       <c r="M118" t="n">
         <v>0.0869179274598213</v>
@@ -14498,10 +14498,10 @@
         <v>0.2489920835522452</v>
       </c>
       <c r="O118" t="n">
-        <v>0.0590374141479395</v>
+        <v>0.05903749831999616</v>
       </c>
       <c r="P118" t="n">
-        <v>0.01930409219681128</v>
+        <v>0.01930411920149755</v>
       </c>
     </row>
     <row r="119">
@@ -14550,16 +14550,16 @@
         <v>0.2449849526558583</v>
       </c>
       <c r="M119" t="n">
-        <v>0.07347532275556801</v>
+        <v>0.07347521107027966</v>
       </c>
       <c r="N119" t="n">
-        <v>0.3298936131407795</v>
+        <v>0.3298936988476657</v>
       </c>
       <c r="O119" t="n">
-        <v>0.5385170771524006</v>
+        <v>0.5385171918585137</v>
       </c>
       <c r="P119" t="n">
-        <v>0.1544295646231215</v>
+        <v>0.154429593313113</v>
       </c>
     </row>
     <row r="120">
@@ -14611,13 +14611,13 @@
         <v>0.04868699910109675</v>
       </c>
       <c r="N120" t="n">
-        <v>0.08712845872589647</v>
+        <v>0.08712838168239712</v>
       </c>
       <c r="O120" t="n">
-        <v>0.2679311694101842</v>
+        <v>0.2679312742112485</v>
       </c>
       <c r="P120" t="n">
-        <v>0.08234378092530514</v>
+        <v>0.08234381074574015</v>
       </c>
     </row>
     <row r="121">
@@ -14730,10 +14730,10 @@
         <v>0.3531993308705275</v>
       </c>
       <c r="O122" t="n">
-        <v>1.043626597665508</v>
+        <v>1.043626796551213</v>
       </c>
       <c r="P122" t="n">
-        <v>0.2690162463904395</v>
+        <v>0.2690162875573181</v>
       </c>
     </row>
     <row r="123">
@@ -14782,10 +14782,10 @@
         <v>0.1520849649264222</v>
       </c>
       <c r="M123" t="n">
-        <v>0.2300231776537998</v>
+        <v>0.2300232890695177</v>
       </c>
       <c r="N123" t="n">
-        <v>0.2452877303909224</v>
+        <v>0.2452876161927344</v>
       </c>
       <c r="O123" t="n">
         <v>-0.01301411984104883</v>
@@ -14800,56 +14800,56 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hilton Worldwide</t>
+          <t>Fastenal</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Hotels, Resorts &amp; Cruise Lines</t>
+          <t>Trading Companies &amp; Distributors</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>349.63</v>
+        <v>51.45</v>
       </c>
       <c r="G124" t="n">
-        <v>0.01444947359501159</v>
+        <v>0.003119513444260313</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.03483780570652173</v>
+        <v>-0.01484455798270612</v>
       </c>
       <c r="I124" t="n">
-        <v>0.06594513683784298</v>
+        <v>-0.005561341015559051</v>
       </c>
       <c r="J124" t="n">
-        <v>0.09163858566060679</v>
+        <v>0.02417924966369611</v>
       </c>
       <c r="K124" t="n">
-        <v>0.08485312072880857</v>
+        <v>0.0750688890784208</v>
       </c>
       <c r="L124" t="n">
-        <v>0.08223601555093474</v>
+        <v>0.1637102758258902</v>
       </c>
       <c r="M124" t="n">
-        <v>0.1815904304248184</v>
+        <v>0.2049707769788403</v>
       </c>
       <c r="N124" t="n">
-        <v>0.3427208862935109</v>
+        <v>0.2625707962373314</v>
       </c>
       <c r="O124" t="n">
-        <v>1.36115162002211</v>
+        <v>0.9174248154465807</v>
       </c>
       <c r="P124" t="n">
-        <v>0.3316025719639504</v>
+        <v>0.242337080352014</v>
       </c>
     </row>
     <row r="125">
@@ -14858,56 +14858,56 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Hilton Worldwide</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Hotels, Resorts &amp; Cruise Lines</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>186.72</v>
+        <v>349.63</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.001497319675384357</v>
+        <v>0.01444947359501159</v>
       </c>
       <c r="H125" t="n">
-        <v>0.01296587297730811</v>
+        <v>-0.03483780570652173</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.04451948126987915</v>
+        <v>0.06594513683784298</v>
       </c>
       <c r="J125" t="n">
-        <v>-0.08881513327575419</v>
+        <v>0.09163858566060679</v>
       </c>
       <c r="K125" t="n">
-        <v>0.1002297674498061</v>
+        <v>0.08485312072880857</v>
       </c>
       <c r="L125" t="n">
-        <v>0.1296509698410655</v>
+        <v>0.08223601555093474</v>
       </c>
       <c r="M125" t="n">
-        <v>0.2435565022362283</v>
+        <v>0.1815904304248184</v>
       </c>
       <c r="N125" t="n">
-        <v>0.1910441802131364</v>
+        <v>0.3427208862935109</v>
       </c>
       <c r="O125" t="n">
-        <v>3.239060074541942</v>
+        <v>1.36115162002211</v>
       </c>
       <c r="P125" t="n">
-        <v>0.6184148588804004</v>
+        <v>0.3316025719639504</v>
       </c>
     </row>
     <row r="126">
@@ -14916,56 +14916,56 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Agricultural &amp; Farm Machinery</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>640.67</v>
+        <v>186.72</v>
       </c>
       <c r="G126" t="n">
-        <v>0.001704189923368737</v>
+        <v>-0.001497319675384357</v>
       </c>
       <c r="H126" t="n">
-        <v>0.006488209736035033</v>
+        <v>0.01296587297730811</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.01492976705888405</v>
+        <v>-0.04451948126987915</v>
       </c>
       <c r="J126" t="n">
-        <v>-0.06872373539060905</v>
+        <v>-0.08881513327575419</v>
       </c>
       <c r="K126" t="n">
-        <v>0.003686491238487521</v>
+        <v>0.1002297674498061</v>
       </c>
       <c r="L126" t="n">
-        <v>0.1418851509111323</v>
+        <v>0.1296509698410655</v>
       </c>
       <c r="M126" t="n">
-        <v>0.2299699524533283</v>
+        <v>0.2435565022362283</v>
       </c>
       <c r="N126" t="n">
-        <v>0.3840113218311731</v>
+        <v>0.1910441802131364</v>
       </c>
       <c r="O126" t="n">
-        <v>0.8465481289224408</v>
+        <v>3.239060074541942</v>
       </c>
       <c r="P126" t="n">
-        <v>0.2268370336199923</v>
+        <v>0.6184148588804004</v>
       </c>
     </row>
     <row r="127">
@@ -15075,13 +15075,13 @@
         <v>0.2648083890214989</v>
       </c>
       <c r="N128" t="n">
-        <v>0.5312292336617364</v>
+        <v>0.5312293700059498</v>
       </c>
       <c r="O128" t="n">
-        <v>4.253873769089679</v>
+        <v>4.253872966514998</v>
       </c>
       <c r="P128" t="n">
-        <v>0.7384406879696959</v>
+        <v>0.7384405994490719</v>
       </c>
     </row>
     <row r="129">
@@ -15090,17 +15090,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>W. W. Grainger</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
+          <t>Agricultural &amp; Farm Machinery</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -15109,37 +15109,37 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1340.76</v>
+        <v>640.67</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.001459694486016794</v>
+        <v>0.001704189923368737</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.008218235031246079</v>
+        <v>0.006488209736035033</v>
       </c>
       <c r="I129" t="n">
-        <v>0.007620518769932083</v>
+        <v>-0.01492976705888405</v>
       </c>
       <c r="J129" t="n">
-        <v>0.06774767046720531</v>
+        <v>-0.06872373539060905</v>
       </c>
       <c r="K129" t="n">
-        <v>-0.03968951828698219</v>
+        <v>0.003686491238487521</v>
       </c>
       <c r="L129" t="n">
-        <v>0.1602869494172845</v>
+        <v>0.1418851509111323</v>
       </c>
       <c r="M129" t="n">
-        <v>0.2603996830957469</v>
+        <v>0.2299699524533283</v>
       </c>
       <c r="N129" t="n">
-        <v>0.4030794661696564</v>
+        <v>0.3840112305891419</v>
       </c>
       <c r="O129" t="n">
-        <v>0.9452369217047658</v>
+        <v>0.8465479665034104</v>
       </c>
       <c r="P129" t="n">
-        <v>0.2483149394411306</v>
+        <v>0.2268369976498696</v>
       </c>
     </row>
     <row r="130">
@@ -15148,56 +15148,56 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>W. W. Grainger</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>529.6900000000001</v>
+        <v>1340.76</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01662087146151214</v>
+        <v>-0.001459694486016794</v>
       </c>
       <c r="H130" t="n">
-        <v>0.009856597875475881</v>
+        <v>-0.008218235031246079</v>
       </c>
       <c r="I130" t="n">
-        <v>0.06256770800683298</v>
+        <v>0.007620518769932083</v>
       </c>
       <c r="J130" t="n">
-        <v>0.003828187307736153</v>
+        <v>0.06774767046720531</v>
       </c>
       <c r="K130" t="n">
-        <v>0.08014026921233919</v>
+        <v>-0.03968951828698219</v>
       </c>
       <c r="L130" t="n">
-        <v>0.2314362403003427</v>
+        <v>0.1602868268457065</v>
       </c>
       <c r="M130" t="n">
-        <v>0.1083467564656928</v>
+        <v>0.2603995384600379</v>
       </c>
       <c r="N130" t="n">
-        <v>0.2540305974853037</v>
+        <v>0.403079645404979</v>
       </c>
       <c r="O130" t="n">
-        <v>0.4909085911432196</v>
+        <v>0.9452369217047658</v>
       </c>
       <c r="P130" t="n">
-        <v>0.1423968732605669</v>
+        <v>0.2483149394411306</v>
       </c>
     </row>
     <row r="131">
@@ -15206,56 +15206,56 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Allegion</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>180.66</v>
+        <v>529.6900000000001</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0006092528855843327</v>
+        <v>0.01662087146151214</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1362264381264739</v>
+        <v>0.009856597875475881</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1846557617187501</v>
+        <v>0.06256770800683298</v>
       </c>
       <c r="J131" t="n">
-        <v>0.1626978889488582</v>
+        <v>0.003828187307736153</v>
       </c>
       <c r="K131" t="n">
-        <v>0.1244912963462994</v>
+        <v>0.08014026921233919</v>
       </c>
       <c r="L131" t="n">
-        <v>0.320536114016579</v>
+        <v>0.2314362403003427</v>
       </c>
       <c r="M131" t="n">
-        <v>0.1081759388632555</v>
+        <v>0.1083467564656928</v>
       </c>
       <c r="N131" t="n">
-        <v>0.0807795918669143</v>
+        <v>0.2540305974853037</v>
       </c>
       <c r="O131" t="n">
-        <v>0.9251338620036622</v>
+        <v>0.4909085911432196</v>
       </c>
       <c r="P131" t="n">
-        <v>0.2439998014054847</v>
+        <v>0.1423968732605669</v>
       </c>
     </row>
     <row r="132">
@@ -15264,17 +15264,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fastenal</t>
+          <t>Allegion</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Trading Companies &amp; Distributors</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -15283,37 +15283,37 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>51.45</v>
+        <v>180.66</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.001939834638236104</v>
+        <v>0.0006092528855843327</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.01981331457937419</v>
+        <v>0.1362264381264739</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.01057690840501047</v>
+        <v>0.1846557617187501</v>
       </c>
       <c r="J132" t="n">
-        <v>0.0190136473075635</v>
+        <v>0.1626978889488582</v>
       </c>
       <c r="K132" t="n">
-        <v>0.0696466194405545</v>
+        <v>0.1244912963462994</v>
       </c>
       <c r="L132" t="n">
-        <v>0.1578409109639278</v>
+        <v>0.320535966731561</v>
       </c>
       <c r="M132" t="n">
-        <v>0.1988934379088407</v>
+        <v>0.1081759388632555</v>
       </c>
       <c r="N132" t="n">
-        <v>0.2562028893960444</v>
+        <v>0.0807794932089192</v>
       </c>
       <c r="O132" t="n">
-        <v>0.907753794079196</v>
+        <v>0.925133548978067</v>
       </c>
       <c r="P132" t="n">
-        <v>0.2402448775135979</v>
+        <v>0.2439997339809441</v>
       </c>
     </row>
     <row r="133">
@@ -15365,13 +15365,13 @@
         <v>0.1676401334138145</v>
       </c>
       <c r="N133" t="n">
-        <v>0.4129513761183934</v>
+        <v>0.4129514746153242</v>
       </c>
       <c r="O133" t="n">
-        <v>0.2167617383680964</v>
+        <v>0.2167620305406521</v>
       </c>
       <c r="P133" t="n">
-        <v>0.06758348839591122</v>
+        <v>0.06758357384637681</v>
       </c>
     </row>
     <row r="134">
@@ -15417,7 +15417,7 @@
         <v>-0.03829064730567278</v>
       </c>
       <c r="L134" t="n">
-        <v>0.09896416732397117</v>
+        <v>0.09896409472557077</v>
       </c>
       <c r="M134" t="n">
         <v>0.2801496011300884</v>
@@ -15426,10 +15426,10 @@
         <v>0.4279319042047089</v>
       </c>
       <c r="O134" t="n">
-        <v>0.6569499303182254</v>
+        <v>0.656949600246217</v>
       </c>
       <c r="P134" t="n">
-        <v>0.1833225163206325</v>
+        <v>0.183322437746207</v>
       </c>
     </row>
     <row r="135">
@@ -15478,7 +15478,7 @@
         <v>0.2309685584202126</v>
       </c>
       <c r="M135" t="n">
-        <v>0.2169666833007098</v>
+        <v>0.2169664362833568</v>
       </c>
       <c r="N135" t="n">
         <v>0.03176444380236476</v>
@@ -15542,10 +15542,10 @@
         <v>0.4074828960072634</v>
       </c>
       <c r="O136" t="n">
-        <v>0.8381313497672789</v>
+        <v>0.8381311192805314</v>
       </c>
       <c r="P136" t="n">
-        <v>0.2249701727608584</v>
+        <v>0.2249701215604183</v>
       </c>
     </row>
     <row r="137">
@@ -15600,10 +15600,10 @@
         <v>0.1165821732393897</v>
       </c>
       <c r="O137" t="n">
-        <v>1.876607219811835</v>
+        <v>1.876607451481292</v>
       </c>
       <c r="P137" t="n">
-        <v>0.4221984098034088</v>
+        <v>0.4221984479826364</v>
       </c>
     </row>
     <row r="138">
@@ -15658,10 +15658,10 @@
         <v>0.3385399268573546</v>
       </c>
       <c r="O138" t="n">
-        <v>1.371657282423322</v>
+        <v>1.371657122584617</v>
       </c>
       <c r="P138" t="n">
-        <v>0.3335745856886048</v>
+        <v>0.3335745557296894</v>
       </c>
     </row>
     <row r="139">
@@ -15707,19 +15707,19 @@
         <v>-0.02195603755509323</v>
       </c>
       <c r="L139" t="n">
-        <v>-0.02387900355523831</v>
+        <v>-0.02387909902283036</v>
       </c>
       <c r="M139" t="n">
         <v>0.2154341803213806</v>
       </c>
       <c r="N139" t="n">
-        <v>0.5403590670839842</v>
+        <v>0.540359304818756</v>
       </c>
       <c r="O139" t="n">
-        <v>0.754112894969601</v>
+        <v>0.7541125866765699</v>
       </c>
       <c r="P139" t="n">
-        <v>0.2060144565117725</v>
+        <v>0.2060143858576593</v>
       </c>
     </row>
     <row r="140">
@@ -15771,13 +15771,13 @@
         <v>0.1149410940105529</v>
       </c>
       <c r="N140" t="n">
-        <v>0.1876364849970589</v>
+        <v>0.1876366179159439</v>
       </c>
       <c r="O140" t="n">
-        <v>3.179587015443841</v>
+        <v>3.179587838551062</v>
       </c>
       <c r="P140" t="n">
-        <v>0.6108105193836535</v>
+        <v>0.6108106251253356</v>
       </c>
     </row>
     <row r="141">
@@ -15823,7 +15823,7 @@
         <v>-0.04634671634780929</v>
       </c>
       <c r="L141" t="n">
-        <v>0.121994963117475</v>
+        <v>0.1219950923918247</v>
       </c>
       <c r="M141" t="n">
         <v>0.2656824067112662</v>
@@ -15887,13 +15887,13 @@
         <v>0.2320826818264237</v>
       </c>
       <c r="N142" t="n">
-        <v>-0.02465102992719848</v>
+        <v>-0.02465109580915092</v>
       </c>
       <c r="O142" t="n">
-        <v>-0.05345734567347282</v>
+        <v>-0.05345722157773569</v>
       </c>
       <c r="P142" t="n">
-        <v>-0.01814641580543075</v>
+        <v>-0.01814637289704957</v>
       </c>
     </row>
     <row r="143">
@@ -15942,16 +15942,16 @@
         <v>0.1528672470725816</v>
       </c>
       <c r="M143" t="n">
-        <v>0.1655225087422623</v>
+        <v>0.1655225950593793</v>
       </c>
       <c r="N143" t="n">
         <v>0.1985504664752629</v>
       </c>
       <c r="O143" t="n">
-        <v>1.172584145139935</v>
+        <v>1.172583995178789</v>
       </c>
       <c r="P143" t="n">
-        <v>0.2951662989906301</v>
+        <v>0.2951662691913046</v>
       </c>
     </row>
     <row r="144">
@@ -16006,10 +16006,10 @@
         <v>0.2158148336150241</v>
       </c>
       <c r="O144" t="n">
-        <v>1.309211684289143</v>
+        <v>1.309211877010284</v>
       </c>
       <c r="P144" t="n">
-        <v>0.3217660178027415</v>
+        <v>0.32176605457319</v>
       </c>
     </row>
     <row r="145">
@@ -16061,7 +16061,7 @@
         <v>0.3059580032016347</v>
       </c>
       <c r="N145" t="n">
-        <v>0.4216242137187292</v>
+        <v>0.421624085140321</v>
       </c>
       <c r="O145" t="n">
         <v>0.6080479360961177</v>
@@ -16122,10 +16122,10 @@
         <v>0.0005514690657373311</v>
       </c>
       <c r="O146" t="n">
-        <v>0.1066881440511589</v>
+        <v>0.1066880736460485</v>
       </c>
       <c r="P146" t="n">
-        <v>0.03436802233570857</v>
+        <v>0.03436800040095456</v>
       </c>
     </row>
     <row r="147">
@@ -16174,16 +16174,16 @@
         <v>-0.03780607903659128</v>
       </c>
       <c r="M147" t="n">
-        <v>0.2616479569262962</v>
+        <v>0.2616478768845742</v>
       </c>
       <c r="N147" t="n">
         <v>0.3817235320634571</v>
       </c>
       <c r="O147" t="n">
-        <v>2.693541113654379</v>
+        <v>2.693541456655859</v>
       </c>
       <c r="P147" t="n">
-        <v>0.5457798646466732</v>
+        <v>0.5457799124963967</v>
       </c>
     </row>
     <row r="148">
@@ -16290,16 +16290,16 @@
         <v>0.2061381656609704</v>
       </c>
       <c r="M149" t="n">
-        <v>0.1763470149455655</v>
+        <v>0.1763468765569276</v>
       </c>
       <c r="N149" t="n">
-        <v>0.08535191784976282</v>
+        <v>0.08535180004287435</v>
       </c>
       <c r="O149" t="n">
-        <v>0.7065913644521311</v>
+        <v>0.7065912188195216</v>
       </c>
       <c r="P149" t="n">
-        <v>0.1950236894639448</v>
+        <v>0.1950236554713467</v>
       </c>
     </row>
     <row r="150">
@@ -16406,10 +16406,10 @@
         <v>0.1828119131480528</v>
       </c>
       <c r="M151" t="n">
-        <v>0.2514852223681248</v>
+        <v>0.2514853236160104</v>
       </c>
       <c r="N151" t="n">
-        <v>0.2002817370239771</v>
+        <v>0.2002816438915678</v>
       </c>
       <c r="O151" t="n">
         <v>2.2649488368932</v>
@@ -16470,10 +16470,10 @@
         <v>0.3705511456105939</v>
       </c>
       <c r="O152" t="n">
-        <v>-0.03307831428323282</v>
+        <v>-0.03307841401767087</v>
       </c>
       <c r="P152" t="n">
-        <v>-0.01114996440647675</v>
+        <v>-0.01114999840523356</v>
       </c>
     </row>
     <row r="153">
@@ -16580,7 +16580,7 @@
         <v>0.1181224476945699</v>
       </c>
       <c r="M154" t="n">
-        <v>0.2031620012943331</v>
+        <v>0.2031620926847457</v>
       </c>
       <c r="N154" t="n">
         <v>0.1108318087181619</v>
@@ -16638,16 +16638,16 @@
         <v>0.03178761367349647</v>
       </c>
       <c r="M155" t="n">
-        <v>0.1342468859444608</v>
+        <v>0.134246753786962</v>
       </c>
       <c r="N155" t="n">
         <v>0.3289100116110659</v>
       </c>
       <c r="O155" t="n">
-        <v>1.440183865115448</v>
+        <v>1.440184018034575</v>
       </c>
       <c r="P155" t="n">
-        <v>0.3462969142895251</v>
+        <v>0.3462969424123437</v>
       </c>
     </row>
     <row r="156">
@@ -16812,16 +16812,16 @@
         <v>0.1671204173277068</v>
       </c>
       <c r="M158" t="n">
-        <v>0.2863874159071982</v>
+        <v>0.2863873149874168</v>
       </c>
       <c r="N158" t="n">
         <v>0.3363390238277058</v>
       </c>
       <c r="O158" t="n">
-        <v>1.157131330052819</v>
+        <v>1.15713118816147</v>
       </c>
       <c r="P158" t="n">
-        <v>0.2920883047515017</v>
+        <v>0.2920882764212598</v>
       </c>
     </row>
     <row r="159">
@@ -16870,16 +16870,16 @@
         <v>0.085830464894324</v>
       </c>
       <c r="M159" t="n">
-        <v>0.1558602201185191</v>
+        <v>0.1558603174261084</v>
       </c>
       <c r="N159" t="n">
-        <v>0.2592762509649935</v>
+        <v>0.2592761354660456</v>
       </c>
       <c r="O159" t="n">
-        <v>0.2050919372686164</v>
+        <v>0.2050918314952406</v>
       </c>
       <c r="P159" t="n">
-        <v>0.06415950121369107</v>
+        <v>0.06415947007920741</v>
       </c>
     </row>
     <row r="160">
@@ -17099,19 +17099,19 @@
         <v>-0.03777817922381033</v>
       </c>
       <c r="L163" t="n">
-        <v>0.06227469066505176</v>
+        <v>0.06227461959671587</v>
       </c>
       <c r="M163" t="n">
         <v>0.1447500423746195</v>
       </c>
       <c r="N163" t="n">
-        <v>0.4774675906122459</v>
+        <v>0.4774677280919135</v>
       </c>
       <c r="O163" t="n">
-        <v>0.3674599878704929</v>
+        <v>0.367459870101293</v>
       </c>
       <c r="P163" t="n">
-        <v>0.1099537323112476</v>
+        <v>0.1099537004472155</v>
       </c>
     </row>
     <row r="164">
@@ -17166,10 +17166,10 @@
         <v>0.2395096573858151</v>
       </c>
       <c r="O164" t="n">
-        <v>0.2026325870609171</v>
+        <v>0.2026327307404223</v>
       </c>
       <c r="P164" t="n">
-        <v>0.0634350963824637</v>
+        <v>0.06343513873228424</v>
       </c>
     </row>
     <row r="165">
@@ -17224,10 +17224,10 @@
         <v>0.2913783150483</v>
       </c>
       <c r="O165" t="n">
-        <v>0.05831169298445316</v>
+        <v>0.05831160463559648</v>
       </c>
       <c r="P165" t="n">
-        <v>0.01907120788864369</v>
+        <v>0.01907117953096815</v>
       </c>
     </row>
     <row r="166">
@@ -17282,10 +17282,10 @@
         <v>0.2322235445259966</v>
       </c>
       <c r="O166" t="n">
-        <v>0.6735763050674455</v>
+        <v>0.6735759103714125</v>
       </c>
       <c r="P166" t="n">
-        <v>0.1872672989066253</v>
+        <v>0.187267205571626</v>
       </c>
     </row>
     <row r="167">
@@ -17340,10 +17340,10 @@
         <v>0.4318827836536179</v>
       </c>
       <c r="O167" t="n">
-        <v>1.75412762877478</v>
+        <v>1.754127218606651</v>
       </c>
       <c r="P167" t="n">
-        <v>0.4017202711710437</v>
+        <v>0.4017202015856689</v>
       </c>
     </row>
     <row r="168">
@@ -17398,10 +17398,10 @@
         <v>0.638557886456244</v>
       </c>
       <c r="O168" t="n">
-        <v>3.455764789613897</v>
+        <v>3.455765386386386</v>
       </c>
       <c r="P168" t="n">
-        <v>0.6455361179873043</v>
+        <v>0.6455361914509847</v>
       </c>
     </row>
     <row r="169">
@@ -17508,7 +17508,7 @@
         <v>0.04016860507793307</v>
       </c>
       <c r="M170" t="n">
-        <v>0.2182106783236442</v>
+        <v>0.2182107666273911</v>
       </c>
       <c r="N170" t="n">
         <v>0.3098883324820827</v>
@@ -17572,10 +17572,10 @@
         <v>0.1362007073821665</v>
       </c>
       <c r="O171" t="n">
-        <v>-0.1737384553607282</v>
+        <v>-0.1737383530045441</v>
       </c>
       <c r="P171" t="n">
-        <v>-0.06163345982380941</v>
+        <v>-0.06163342107594361</v>
       </c>
     </row>
     <row r="172">
@@ -17798,16 +17798,16 @@
         <v>0.1540205342618644</v>
       </c>
       <c r="M175" t="n">
-        <v>0.07816451465519014</v>
+        <v>0.0781643106362877</v>
       </c>
       <c r="N175" t="n">
-        <v>0.4231522571470301</v>
+        <v>0.423152168279495</v>
       </c>
       <c r="O175" t="n">
-        <v>1.074406032113663</v>
+        <v>1.074405843302389</v>
       </c>
       <c r="P175" t="n">
-        <v>0.2753554886469631</v>
+        <v>0.2753554499529147</v>
       </c>
     </row>
     <row r="176">
@@ -17911,19 +17911,19 @@
         <v>0.2006504327723559</v>
       </c>
       <c r="L177" t="n">
-        <v>0.1588559013425226</v>
+        <v>0.1588559832538092</v>
       </c>
       <c r="M177" t="n">
         <v>-0.02135317964661332</v>
       </c>
       <c r="N177" t="n">
-        <v>-0.01462850882691735</v>
+        <v>-0.0146285680491538</v>
       </c>
       <c r="O177" t="n">
-        <v>0.9135707237752027</v>
+        <v>0.9135709471190179</v>
       </c>
       <c r="P177" t="n">
-        <v>0.2415041415385002</v>
+        <v>0.2415041898395214</v>
       </c>
     </row>
     <row r="178">
@@ -17972,16 +17972,16 @@
         <v>0.08278284936475755</v>
       </c>
       <c r="M178" t="n">
-        <v>0.1814338494248471</v>
+        <v>0.1814337296048691</v>
       </c>
       <c r="N178" t="n">
         <v>0.3017721564818767</v>
       </c>
       <c r="O178" t="n">
-        <v>0.7612010432021772</v>
+        <v>0.7612013094759511</v>
       </c>
       <c r="P178" t="n">
-        <v>0.2076367239450114</v>
+        <v>0.2076367848053682</v>
       </c>
     </row>
     <row r="179">
@@ -18030,16 +18030,16 @@
         <v>0.0763681328359751</v>
       </c>
       <c r="M179" t="n">
-        <v>0.2036513055859315</v>
+        <v>0.2036511748126326</v>
       </c>
       <c r="N179" t="n">
         <v>0.2269940546038141</v>
       </c>
       <c r="O179" t="n">
-        <v>0.9522404308608317</v>
+        <v>0.9522406028711077</v>
       </c>
       <c r="P179" t="n">
-        <v>0.2498112634212146</v>
+        <v>0.249811300127823</v>
       </c>
     </row>
     <row r="180">
@@ -18088,16 +18088,16 @@
         <v>0.1307885430194464</v>
       </c>
       <c r="M180" t="n">
-        <v>0.1634611591848307</v>
+        <v>0.1634612423233632</v>
       </c>
       <c r="N180" t="n">
         <v>0.2356107543557771</v>
       </c>
       <c r="O180" t="n">
-        <v>0.7856365055106911</v>
+        <v>0.7856367013431622</v>
       </c>
       <c r="P180" t="n">
-        <v>0.2131961367298549</v>
+        <v>0.2131961810806486</v>
       </c>
     </row>
     <row r="181">
@@ -18317,19 +18317,19 @@
         <v>-0.09006644247753337</v>
       </c>
       <c r="L184" t="n">
-        <v>0.01484774394007893</v>
+        <v>0.01484767500741224</v>
       </c>
       <c r="M184" t="n">
-        <v>0.2328254985815519</v>
+        <v>0.2328253968568306</v>
       </c>
       <c r="N184" t="n">
         <v>0.4304749073478433</v>
       </c>
       <c r="O184" t="n">
-        <v>1.081665204317315</v>
+        <v>1.08166534933305</v>
       </c>
       <c r="P184" t="n">
-        <v>0.2768414155009442</v>
+        <v>0.2768414451506196</v>
       </c>
     </row>
     <row r="185">
@@ -18436,16 +18436,16 @@
         <v>0.03962198107967474</v>
       </c>
       <c r="M186" t="n">
-        <v>0.1613020608052804</v>
+        <v>0.1613021805164425</v>
       </c>
       <c r="N186" t="n">
-        <v>0.3785131280490917</v>
+        <v>0.3785130437086253</v>
       </c>
       <c r="O186" t="n">
-        <v>1.945440792999007</v>
+        <v>1.94544098552299</v>
       </c>
       <c r="P186" t="n">
-        <v>0.4334529159948051</v>
+        <v>0.4334529472265831</v>
       </c>
     </row>
     <row r="187">
@@ -18491,7 +18491,7 @@
         <v>-0.007153028974608122</v>
       </c>
       <c r="L187" t="n">
-        <v>0.2280044965233126</v>
+        <v>0.2280046046487794</v>
       </c>
       <c r="M187" t="n">
         <v>0.1336171430266739</v>
@@ -18558,10 +18558,10 @@
         <v>0.2829434658133574</v>
       </c>
       <c r="O188" t="n">
-        <v>1.961292606503207</v>
+        <v>1.961293195447854</v>
       </c>
       <c r="P188" t="n">
-        <v>0.4360198420776893</v>
+        <v>0.4360199372766733</v>
       </c>
     </row>
     <row r="189">
@@ -18668,10 +18668,10 @@
         <v>-0.02454809807669778</v>
       </c>
       <c r="O190" t="n">
-        <v>0.1474330749671118</v>
+        <v>0.1474333039364164</v>
       </c>
       <c r="P190" t="n">
-        <v>0.04690945346365383</v>
+        <v>0.04690952310028251</v>
       </c>
     </row>
     <row r="191">
@@ -18720,16 +18720,16 @@
         <v>0.2217844685350177</v>
       </c>
       <c r="M191" t="n">
-        <v>0.07955462749825526</v>
+        <v>0.07955472486562942</v>
       </c>
       <c r="N191" t="n">
-        <v>0.1601435963623263</v>
+        <v>0.1601434839153906</v>
       </c>
       <c r="O191" t="n">
-        <v>0.2428561312046267</v>
+        <v>0.2428562602569819</v>
       </c>
       <c r="P191" t="n">
-        <v>0.07516129001010241</v>
+        <v>0.07516132722333735</v>
       </c>
     </row>
     <row r="192">
@@ -18778,16 +18778,16 @@
         <v>0.1282324721668617</v>
       </c>
       <c r="M192" t="n">
-        <v>0.08230072277903755</v>
+        <v>0.08230079935900148</v>
       </c>
       <c r="N192" t="n">
-        <v>0.08485393435656174</v>
+        <v>0.08485385741486917</v>
       </c>
       <c r="O192" t="n">
-        <v>0.6540296157564303</v>
+        <v>0.6540292580426312</v>
       </c>
       <c r="P192" t="n">
-        <v>0.1826269197368977</v>
+        <v>0.1826268344820763</v>
       </c>
     </row>
     <row r="193">
@@ -18839,13 +18839,13 @@
         <v>0.1519707351592863</v>
       </c>
       <c r="N193" t="n">
-        <v>0.2087385508383595</v>
+        <v>0.2087384265625662</v>
       </c>
       <c r="O193" t="n">
-        <v>0.9770169006187919</v>
+        <v>0.9770172330813007</v>
       </c>
       <c r="P193" t="n">
-        <v>0.2550762958687551</v>
+        <v>0.2550763662215159</v>
       </c>
     </row>
     <row r="194">
@@ -18894,16 +18894,16 @@
         <v>0.06747687779097178</v>
       </c>
       <c r="M194" t="n">
-        <v>0.11249573285256</v>
+        <v>0.1124958298080614</v>
       </c>
       <c r="N194" t="n">
-        <v>0.1886897977427646</v>
+        <v>0.1886899084338947</v>
       </c>
       <c r="O194" t="n">
-        <v>2.70053047760378</v>
+        <v>2.700529941222487</v>
       </c>
       <c r="P194" t="n">
-        <v>0.5467542872936817</v>
+        <v>0.5467542125611435</v>
       </c>
     </row>
     <row r="195">
@@ -19010,16 +19010,16 @@
         <v>0.2000410366349037</v>
       </c>
       <c r="M196" t="n">
-        <v>0.1130239393761034</v>
+        <v>0.1130240646357263</v>
       </c>
       <c r="N196" t="n">
-        <v>-0.0365878938236267</v>
+        <v>-0.03658779997535466</v>
       </c>
       <c r="O196" t="n">
-        <v>0.4277533247288308</v>
+        <v>0.4277532216716227</v>
       </c>
       <c r="P196" t="n">
-        <v>0.1260328489231224</v>
+        <v>0.1260328218302527</v>
       </c>
     </row>
     <row r="197">
@@ -19065,10 +19065,10 @@
         <v>-0.01051279502559199</v>
       </c>
       <c r="L197" t="n">
-        <v>0.02833177870617898</v>
+        <v>0.02833189505790301</v>
       </c>
       <c r="M197" t="n">
-        <v>0.04865204524216415</v>
+        <v>0.04865192424671783</v>
       </c>
       <c r="N197" t="n">
         <v>0.3727143974177323</v>
@@ -19184,16 +19184,16 @@
         <v>0.07320298245451173</v>
       </c>
       <c r="M199" t="n">
-        <v>0.1041872920051616</v>
+        <v>0.1041872018696677</v>
       </c>
       <c r="N199" t="n">
-        <v>0.2388337517843009</v>
+        <v>0.2388336383259655</v>
       </c>
       <c r="O199" t="n">
-        <v>0.2093644400114869</v>
+        <v>0.2093643318868308</v>
       </c>
       <c r="P199" t="n">
-        <v>0.0654156327012434</v>
+        <v>0.06541560094966137</v>
       </c>
     </row>
     <row r="200">
@@ -19248,10 +19248,10 @@
         <v>0.2611017932401221</v>
       </c>
       <c r="O200" t="n">
-        <v>0.5114918509266935</v>
+        <v>0.5114919893080911</v>
       </c>
       <c r="P200" t="n">
-        <v>0.1476301166577032</v>
+        <v>0.1476301516806409</v>
       </c>
     </row>
     <row r="201">
@@ -19358,10 +19358,10 @@
         <v>0.07462348281632769</v>
       </c>
       <c r="M202" t="n">
-        <v>0.1694696825110018</v>
+        <v>0.1694695474027406</v>
       </c>
       <c r="N202" t="n">
-        <v>0.2952010396215283</v>
+        <v>0.2952011224821944</v>
       </c>
       <c r="O202" t="n">
         <v>0.2190057014912774</v>
@@ -19416,16 +19416,16 @@
         <v>0.05865908565215694</v>
       </c>
       <c r="M203" t="n">
-        <v>0.1120167911397603</v>
+        <v>0.1120167084909114</v>
       </c>
       <c r="N203" t="n">
-        <v>0.1967126666290209</v>
+        <v>0.1967125709109596</v>
       </c>
       <c r="O203" t="n">
-        <v>0.4453346782798067</v>
+        <v>0.4453348179009018</v>
       </c>
       <c r="P203" t="n">
-        <v>0.1306359951971763</v>
+        <v>0.1306360316041144</v>
       </c>
     </row>
     <row r="204">
@@ -19480,10 +19480,10 @@
         <v>0.1974512331546052</v>
       </c>
       <c r="O204" t="n">
-        <v>0.5073999957135857</v>
+        <v>0.5073996951861683</v>
       </c>
       <c r="P204" t="n">
-        <v>0.1465935733659882</v>
+        <v>0.1465934971679366</v>
       </c>
     </row>
     <row r="205">
@@ -19538,10 +19538,10 @@
         <v>0.07394926948227964</v>
       </c>
       <c r="O205" t="n">
-        <v>4.333908223137986</v>
+        <v>4.33390671143349</v>
       </c>
       <c r="P205" t="n">
-        <v>0.7472237037799725</v>
+        <v>0.7472235387173787</v>
       </c>
     </row>
     <row r="206">
@@ -19587,19 +19587,19 @@
         <v>0.004685773318881647</v>
       </c>
       <c r="L206" t="n">
-        <v>0.03531678551331496</v>
+        <v>0.03531686349369334</v>
       </c>
       <c r="M206" t="n">
         <v>0.1508377563625227</v>
       </c>
       <c r="N206" t="n">
-        <v>0.2012605372861245</v>
+        <v>0.2012604323045271</v>
       </c>
       <c r="O206" t="n">
-        <v>0.6107136462409279</v>
+        <v>0.6107134574959434</v>
       </c>
       <c r="P206" t="n">
-        <v>0.1722118643418693</v>
+        <v>0.1722118185548938</v>
       </c>
     </row>
     <row r="207">
@@ -19651,7 +19651,7 @@
         <v>-0.04185878573549662</v>
       </c>
       <c r="N207" t="n">
-        <v>-0.04316838169284809</v>
+        <v>-0.04316828956787522</v>
       </c>
       <c r="O207" t="n">
         <v>0.207965571224981</v>
@@ -19712,10 +19712,10 @@
         <v>0.05032157263263448</v>
       </c>
       <c r="O208" t="n">
-        <v>0.5060590884629703</v>
+        <v>0.5060591797538576</v>
       </c>
       <c r="P208" t="n">
-        <v>0.146253488506219</v>
+        <v>0.1462535116665533</v>
       </c>
     </row>
     <row r="209">
@@ -19767,13 +19767,13 @@
         <v>0.0974986910512774</v>
       </c>
       <c r="N209" t="n">
-        <v>0.07586433172098106</v>
+        <v>0.07586422012105754</v>
       </c>
       <c r="O209" t="n">
-        <v>0.1641589224264979</v>
+        <v>0.1641590530957826</v>
       </c>
       <c r="P209" t="n">
-        <v>0.05197178164877436</v>
+        <v>0.05197182100777487</v>
       </c>
     </row>
     <row r="210">
@@ -19822,16 +19822,16 @@
         <v>0.03686422524559152</v>
       </c>
       <c r="M210" t="n">
-        <v>0.135529843041855</v>
+        <v>0.1355297652869174</v>
       </c>
       <c r="N210" t="n">
-        <v>0.3066595300282493</v>
+        <v>0.3066594270712804</v>
       </c>
       <c r="O210" t="n">
-        <v>0.4009429264088076</v>
+        <v>0.4009431631107689</v>
       </c>
       <c r="P210" t="n">
-        <v>0.1189400384187269</v>
+        <v>0.1189401014370655</v>
       </c>
     </row>
     <row r="211">
@@ -19944,10 +19944,10 @@
         <v>0.2350336183783261</v>
       </c>
       <c r="O212" t="n">
-        <v>1.562624533490716</v>
+        <v>1.562624315121781</v>
       </c>
       <c r="P212" t="n">
-        <v>0.3684480861267139</v>
+        <v>0.3684480472568552</v>
       </c>
     </row>
     <row r="213">
@@ -19999,13 +19999,13 @@
         <v>0.008784525981321956</v>
       </c>
       <c r="N213" t="n">
-        <v>0.2840302500406593</v>
+        <v>0.2840303290237118</v>
       </c>
       <c r="O213" t="n">
-        <v>0.188544911278161</v>
+        <v>0.1885447759324439</v>
       </c>
       <c r="P213" t="n">
-        <v>0.05926640569664121</v>
+        <v>0.05926636548860342</v>
       </c>
     </row>
     <row r="214">
@@ -20057,13 +20057,13 @@
         <v>0.06226397990980326</v>
       </c>
       <c r="N214" t="n">
-        <v>0.1341594498678016</v>
+        <v>0.1341593628889484</v>
       </c>
       <c r="O214" t="n">
-        <v>0.612517287655687</v>
+        <v>0.6125176393005907</v>
       </c>
       <c r="P214" t="n">
-        <v>0.1726492400764357</v>
+        <v>0.1726493253170927</v>
       </c>
     </row>
     <row r="215">
@@ -20112,16 +20112,16 @@
         <v>0.2043248503621546</v>
       </c>
       <c r="M215" t="n">
-        <v>0.04584933506433275</v>
+        <v>0.04584941624174976</v>
       </c>
       <c r="N215" t="n">
         <v>0.008279003394678019</v>
       </c>
       <c r="O215" t="n">
-        <v>0.5329954286156373</v>
+        <v>0.5329949053770406</v>
       </c>
       <c r="P215" t="n">
-        <v>0.153046848893921</v>
+        <v>0.1530467177087758</v>
       </c>
     </row>
     <row r="216">
@@ -20173,7 +20173,7 @@
         <v>0.1950992026231724</v>
       </c>
       <c r="N216" t="n">
-        <v>0.3577543743711096</v>
+        <v>0.357754471059432</v>
       </c>
       <c r="O216" t="n">
         <v>1.387637733125239</v>
@@ -20286,16 +20286,16 @@
         <v>0.07924407548527279</v>
       </c>
       <c r="M218" t="n">
-        <v>0.102581093377736</v>
+        <v>0.1025811801080663</v>
       </c>
       <c r="N218" t="n">
-        <v>0.3068175408484202</v>
+        <v>0.3068176626855992</v>
       </c>
       <c r="O218" t="n">
-        <v>1.600091784269126</v>
+        <v>1.600091301958132</v>
       </c>
       <c r="P218" t="n">
-        <v>0.3750850476133532</v>
+        <v>0.3750849625883192</v>
       </c>
     </row>
     <row r="219">
@@ -20405,7 +20405,7 @@
         <v>0.05864368371827866</v>
       </c>
       <c r="N220" t="n">
-        <v>0.1541124960542477</v>
+        <v>0.1541125818543856</v>
       </c>
       <c r="O220" t="n">
         <v>0.05247076771026959</v>
@@ -20466,10 +20466,10 @@
         <v>0.0512684020539147</v>
       </c>
       <c r="O221" t="n">
-        <v>1.069800186067785</v>
+        <v>1.069800637719267</v>
       </c>
       <c r="P221" t="n">
-        <v>0.2744108899250817</v>
+        <v>0.2744109826215539</v>
       </c>
     </row>
     <row r="222">
@@ -20573,13 +20573,13 @@
         <v>0.0668873283297593</v>
       </c>
       <c r="N223" t="n">
-        <v>0.04655176669226369</v>
+        <v>0.04655185764466907</v>
       </c>
       <c r="O223" t="n">
-        <v>0.1877079705037688</v>
+        <v>0.1877076190783347</v>
       </c>
       <c r="P223" t="n">
-        <v>0.05901771184921478</v>
+        <v>0.05901760739991557</v>
       </c>
     </row>
     <row r="224">
@@ -20683,10 +20683,10 @@
         <v>-0.07264306151448319</v>
       </c>
       <c r="L225" t="n">
-        <v>0.04213917255605648</v>
+        <v>0.04213910092180018</v>
       </c>
       <c r="M225" t="n">
-        <v>0.282768555561685</v>
+        <v>0.282768664095731</v>
       </c>
       <c r="N225" t="n">
         <v>0.1490815478826484</v>
@@ -20805,13 +20805,13 @@
         <v>0.1028693514535695</v>
       </c>
       <c r="N227" t="n">
-        <v>0.07487830554615238</v>
+        <v>0.07487821386937532</v>
       </c>
       <c r="O227" t="n">
-        <v>0.09555124881252586</v>
+        <v>0.09555105833835364</v>
       </c>
       <c r="P227" t="n">
-        <v>0.03088661172190599</v>
+        <v>0.03088655197807522</v>
       </c>
     </row>
     <row r="228">
@@ -20866,10 +20866,10 @@
         <v>0.1018346794502931</v>
       </c>
       <c r="O228" t="n">
-        <v>0.9156102680981226</v>
+        <v>0.9156104595864032</v>
       </c>
       <c r="P228" t="n">
-        <v>0.2419450630796036</v>
+        <v>0.24194510446205</v>
       </c>
     </row>
     <row r="229">
@@ -20915,19 +20915,19 @@
         <v>-0.05516672875565731</v>
       </c>
       <c r="L229" t="n">
-        <v>0.1127871500743451</v>
+        <v>0.1127872352228882</v>
       </c>
       <c r="M229" t="n">
-        <v>0.08002174188632027</v>
+        <v>0.08002182209438047</v>
       </c>
       <c r="N229" t="n">
-        <v>0.2424629989026712</v>
+        <v>0.2424628927527015</v>
       </c>
       <c r="O229" t="n">
-        <v>0.7794107012787173</v>
+        <v>0.7794103746934726</v>
       </c>
       <c r="P229" t="n">
-        <v>0.2117845174173345</v>
+        <v>0.211784443282123</v>
       </c>
     </row>
     <row r="230">
@@ -20976,16 +20976,16 @@
         <v>0.06826298414515253</v>
       </c>
       <c r="M230" t="n">
-        <v>0.1230802876989465</v>
+        <v>0.1230803565381167</v>
       </c>
       <c r="N230" t="n">
-        <v>0.06522959009260632</v>
+        <v>0.06522971395243626</v>
       </c>
       <c r="O230" t="n">
-        <v>0.2921074522487574</v>
+        <v>0.2921076344877513</v>
       </c>
       <c r="P230" t="n">
-        <v>0.08917971341231734</v>
+        <v>0.08917976461832855</v>
       </c>
     </row>
     <row r="231">
@@ -21034,16 +21034,16 @@
         <v>0.002264688756225208</v>
       </c>
       <c r="M231" t="n">
-        <v>0.1365748888928477</v>
+        <v>0.136574966472125</v>
       </c>
       <c r="N231" t="n">
         <v>0.1633843097751215</v>
       </c>
       <c r="O231" t="n">
-        <v>0.4251035253610924</v>
+        <v>0.4251037692951749</v>
       </c>
       <c r="P231" t="n">
-        <v>0.1253358076669131</v>
+        <v>0.1253358718745858</v>
       </c>
     </row>
     <row r="232">
@@ -21089,7 +21089,7 @@
         <v>-0.09798358601275692</v>
       </c>
       <c r="L232" t="n">
-        <v>0.06460972301494761</v>
+        <v>0.0646098048849475</v>
       </c>
       <c r="M232" t="n">
         <v>0.188183875238086</v>
@@ -21098,10 +21098,10 @@
         <v>0.2503617279704504</v>
       </c>
       <c r="O232" t="n">
-        <v>1.340775500745705</v>
+        <v>1.340775698640087</v>
       </c>
       <c r="P232" t="n">
-        <v>0.3277610398796285</v>
+        <v>0.3277610772969208</v>
       </c>
     </row>
     <row r="233">
@@ -21156,10 +21156,10 @@
         <v>-0.01153449521633776</v>
       </c>
       <c r="O233" t="n">
-        <v>-0.1600611201224243</v>
+        <v>-0.1600613133905024</v>
       </c>
       <c r="P233" t="n">
-        <v>-0.05648408909760361</v>
+        <v>-0.05648416146458379</v>
       </c>
     </row>
     <row r="234">
@@ -21260,16 +21260,16 @@
         <v>0.1010903325308616</v>
       </c>
       <c r="M235" t="n">
-        <v>0.06235357401767394</v>
+        <v>0.062353642439128</v>
       </c>
       <c r="N235" t="n">
-        <v>0.2027404074473738</v>
+        <v>0.2027403197477204</v>
       </c>
       <c r="O235" t="n">
-        <v>0.4817090884592063</v>
+        <v>0.4817088222580661</v>
       </c>
       <c r="P235" t="n">
-        <v>0.140042341830217</v>
+        <v>0.1400422735575733</v>
       </c>
     </row>
     <row r="236">
@@ -21324,10 +21324,10 @@
         <v>0.2320264456945578</v>
       </c>
       <c r="O236" t="n">
-        <v>2.00117905555888</v>
+        <v>2.001179554368781</v>
       </c>
       <c r="P236" t="n">
-        <v>0.4424384891570521</v>
+        <v>0.4424385690703736</v>
       </c>
     </row>
     <row r="237">
@@ -21437,13 +21437,13 @@
         <v>0.1336352106224437</v>
       </c>
       <c r="N238" t="n">
-        <v>-0.036759353262522</v>
+        <v>-0.03675942670167587</v>
       </c>
       <c r="O238" t="n">
-        <v>-0.03900245740651309</v>
+        <v>-0.03900238430898628</v>
       </c>
       <c r="P238" t="n">
-        <v>-0.01317360082890207</v>
+        <v>-0.01317357580817646</v>
       </c>
     </row>
     <row r="239">
@@ -21553,13 +21553,13 @@
         <v>0.1446683501808295</v>
       </c>
       <c r="N240" t="n">
-        <v>0.1325479038122173</v>
+        <v>0.1325477884458179</v>
       </c>
       <c r="O240" t="n">
-        <v>1.664815691092565</v>
+        <v>1.6648163297981</v>
       </c>
       <c r="P240" t="n">
-        <v>0.3864016257415295</v>
+        <v>0.3864017365062029</v>
       </c>
     </row>
     <row r="241">
@@ -21608,10 +21608,10 @@
         <v>0.1946451732346219</v>
       </c>
       <c r="M241" t="n">
-        <v>0.1237452084182993</v>
+        <v>0.1237453199278515</v>
       </c>
       <c r="N241" t="n">
-        <v>0.05490495989596855</v>
+        <v>0.05490505816191282</v>
       </c>
       <c r="O241" t="n">
         <v>1.564200212207405</v>
@@ -21672,10 +21672,10 @@
         <v>-0.01501365381299091</v>
       </c>
       <c r="O242" t="n">
-        <v>0.1743931453021037</v>
+        <v>0.174393064490691</v>
       </c>
       <c r="P242" t="n">
-        <v>0.05504545084007395</v>
+        <v>0.05504542664042211</v>
       </c>
     </row>
     <row r="243">
@@ -21721,19 +21721,19 @@
         <v>-0.008248032830833085</v>
       </c>
       <c r="L243" t="n">
-        <v>0.04571794425263631</v>
+        <v>0.04571804327865681</v>
       </c>
       <c r="M243" t="n">
-        <v>0.1270378465676161</v>
+        <v>0.127037731541324</v>
       </c>
       <c r="N243" t="n">
         <v>0.1223957200466894</v>
       </c>
       <c r="O243" t="n">
-        <v>0.970536042736166</v>
+        <v>0.9705358669199635</v>
       </c>
       <c r="P243" t="n">
-        <v>0.2537033729710723</v>
+        <v>0.2537033356848772</v>
       </c>
     </row>
     <row r="244">
@@ -21779,19 +21779,19 @@
         <v>0.07461801478394858</v>
       </c>
       <c r="L244" t="n">
-        <v>0.09865398047883445</v>
+        <v>0.09865408240456452</v>
       </c>
       <c r="M244" t="n">
-        <v>-0.005672668052402741</v>
+        <v>-0.005672584565045158</v>
       </c>
       <c r="N244" t="n">
-        <v>0.03159080261839553</v>
+        <v>0.0315907127562447</v>
       </c>
       <c r="O244" t="n">
-        <v>0.1232603242332877</v>
+        <v>0.1232607504033307</v>
       </c>
       <c r="P244" t="n">
-        <v>0.0395055354811642</v>
+        <v>0.03950566694551338</v>
       </c>
     </row>
     <row r="245">
@@ -21840,16 +21840,16 @@
         <v>0.1003597501184872</v>
       </c>
       <c r="M245" t="n">
-        <v>-0.1171537565245783</v>
+        <v>-0.1171538507860189</v>
       </c>
       <c r="N245" t="n">
-        <v>0.2617161535883943</v>
+        <v>0.2617160573258648</v>
       </c>
       <c r="O245" t="n">
-        <v>0.1273140220492639</v>
+        <v>0.1273142525886533</v>
       </c>
       <c r="P245" t="n">
-        <v>0.04075451350867421</v>
+        <v>0.04075458445456537</v>
       </c>
     </row>
     <row r="246">
@@ -21901,13 +21901,13 @@
         <v>-0.05198016369944503</v>
       </c>
       <c r="N246" t="n">
-        <v>-0.0001532166370608046</v>
+        <v>-0.0001532824982609649</v>
       </c>
       <c r="O246" t="n">
-        <v>1.103667643975139</v>
+        <v>1.103667352422514</v>
       </c>
       <c r="P246" t="n">
-        <v>0.2813242406774059</v>
+        <v>0.2813241814834131</v>
       </c>
     </row>
     <row r="247">
@@ -21962,10 +21962,10 @@
         <v>-0.01767149107175381</v>
       </c>
       <c r="O247" t="n">
-        <v>0.5647789547785307</v>
+        <v>0.5647792420875128</v>
       </c>
       <c r="P247" t="n">
-        <v>0.1609610928004752</v>
+        <v>0.1609611638551394</v>
       </c>
     </row>
     <row r="248">
@@ -22017,13 +22017,13 @@
         <v>0.01348604251780072</v>
       </c>
       <c r="N248" t="n">
-        <v>0.09012510774405813</v>
+        <v>0.09012518837875261</v>
       </c>
       <c r="O248" t="n">
-        <v>0.3979802816556717</v>
+        <v>0.3979798838303248</v>
       </c>
       <c r="P248" t="n">
-        <v>0.1181507220862856</v>
+        <v>0.1181506160216659</v>
       </c>
     </row>
     <row r="249">
@@ -22075,7 +22075,7 @@
         <v>0.1352395635499826</v>
       </c>
       <c r="N249" t="n">
-        <v>0.1651233191043089</v>
+        <v>0.1651232340365756</v>
       </c>
       <c r="O249" t="n">
         <v>0.6964310031756757</v>
@@ -22136,10 +22136,10 @@
         <v>0.2220459113390876</v>
       </c>
       <c r="O250" t="n">
-        <v>3.284419009512112</v>
+        <v>3.28441942861391</v>
       </c>
       <c r="P250" t="n">
-        <v>0.6241668640665778</v>
+        <v>0.6241669170252351</v>
       </c>
     </row>
     <row r="251">
@@ -22194,10 +22194,10 @@
         <v>0.1608993396915717</v>
       </c>
       <c r="O251" t="n">
-        <v>1.28151126724946</v>
+        <v>1.281511100063986</v>
       </c>
       <c r="P251" t="n">
-        <v>0.316459610416032</v>
+        <v>0.3164595782600175</v>
       </c>
     </row>
     <row r="252">
@@ -22249,13 +22249,13 @@
         <v>0.05681897502083455</v>
       </c>
       <c r="N252" t="n">
-        <v>0.2894608718679357</v>
+        <v>0.2894607607138113</v>
       </c>
       <c r="O252" t="n">
-        <v>1.28349146651733</v>
+        <v>1.283491117932886</v>
       </c>
       <c r="P252" t="n">
-        <v>0.3168403665938035</v>
+        <v>0.3168402995867521</v>
       </c>
     </row>
     <row r="253">
@@ -22304,7 +22304,7 @@
         <v>0.07516806659461683</v>
       </c>
       <c r="M253" t="n">
-        <v>0.09969302690899773</v>
+        <v>0.09969295234608211</v>
       </c>
       <c r="N253" t="n">
         <v>0.06410479144887171</v>
@@ -22423,7 +22423,7 @@
         <v>0.1094283006798222</v>
       </c>
       <c r="N255" t="n">
-        <v>0.04410924681153716</v>
+        <v>0.04410935093388679</v>
       </c>
       <c r="O255" t="n">
         <v>0.4345774339308484</v>
@@ -22481,7 +22481,7 @@
         <v>0.02227151605523447</v>
       </c>
       <c r="N256" t="n">
-        <v>0.08753234954394062</v>
+        <v>0.08753227424781573</v>
       </c>
       <c r="O256" t="n">
         <v>0.1764369997106778</v>
@@ -22536,16 +22536,16 @@
         <v>0.1134426219809361</v>
       </c>
       <c r="M257" t="n">
-        <v>0.03380199763109304</v>
+        <v>0.03380189622403118</v>
       </c>
       <c r="N257" t="n">
         <v>0.0171165010296459</v>
       </c>
       <c r="O257" t="n">
-        <v>0.4585129112751767</v>
+        <v>0.45851301219677</v>
       </c>
       <c r="P257" t="n">
-        <v>0.1340618979811266</v>
+        <v>0.1340619241382097</v>
       </c>
     </row>
     <row r="258">
@@ -22652,7 +22652,7 @@
         <v>-0.024888521239259</v>
       </c>
       <c r="M259" t="n">
-        <v>0.1031905039337837</v>
+        <v>0.1031905787480385</v>
       </c>
       <c r="N259" t="n">
         <v>0.2499804826772234</v>
@@ -22716,10 +22716,10 @@
         <v>0.08335011008678128</v>
       </c>
       <c r="O260" t="n">
-        <v>0.4665638696188532</v>
+        <v>0.466563975468727</v>
       </c>
       <c r="P260" t="n">
-        <v>0.1361447356219814</v>
+        <v>0.1361447629558912</v>
       </c>
     </row>
     <row r="261">
@@ -22774,10 +22774,10 @@
         <v>0.1320256699324749</v>
       </c>
       <c r="O261" t="n">
-        <v>0.5704196600021947</v>
+        <v>0.5704194125893649</v>
       </c>
       <c r="P261" t="n">
-        <v>0.1623544282979914</v>
+        <v>0.1623543672566827</v>
       </c>
     </row>
     <row r="262">
@@ -22823,19 +22823,19 @@
         <v>0.01964128823102795</v>
       </c>
       <c r="L262" t="n">
-        <v>-0.04390285781422509</v>
+        <v>-0.04390292882007762</v>
       </c>
       <c r="M262" t="n">
-        <v>0.1406383233592354</v>
+        <v>0.1406384244208181</v>
       </c>
       <c r="N262" t="n">
         <v>0.05651525944503355</v>
       </c>
       <c r="O262" t="n">
-        <v>1.088220683663624</v>
+        <v>1.088220175581309</v>
       </c>
       <c r="P262" t="n">
-        <v>0.2781803334010007</v>
+        <v>0.2781802297368492</v>
       </c>
     </row>
     <row r="263">
@@ -22881,19 +22881,19 @@
         <v>-0.03379631236673741</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.03573464160203355</v>
+        <v>-0.03573470735907236</v>
       </c>
       <c r="M263" t="n">
-        <v>0.1384103528979854</v>
+        <v>0.1384104445510212</v>
       </c>
       <c r="N263" t="n">
-        <v>0.163616531199879</v>
+        <v>0.1636163396866246</v>
       </c>
       <c r="O263" t="n">
-        <v>1.602711412538695</v>
+        <v>1.602712131147541</v>
       </c>
       <c r="P263" t="n">
-        <v>0.3755466983139142</v>
+        <v>0.3755468249100899</v>
       </c>
     </row>
     <row r="264">
@@ -22942,16 +22942,16 @@
         <v>0.01810098742503685</v>
       </c>
       <c r="M264" t="n">
-        <v>0.0589796135999614</v>
+        <v>0.05897954805766403</v>
       </c>
       <c r="N264" t="n">
         <v>0.3098288195383545</v>
       </c>
       <c r="O264" t="n">
-        <v>2.219663688047024</v>
+        <v>2.219663385120383</v>
       </c>
       <c r="P264" t="n">
-        <v>0.4766248398039428</v>
+        <v>0.4766247934938246</v>
       </c>
     </row>
     <row r="265">
@@ -23000,16 +23000,16 @@
         <v>0.1351163504366337</v>
       </c>
       <c r="M265" t="n">
-        <v>0.004805962338410907</v>
+        <v>0.00480586857209242</v>
       </c>
       <c r="N265" t="n">
         <v>0.1138593786755586</v>
       </c>
       <c r="O265" t="n">
-        <v>0.3835115076817992</v>
+        <v>0.3835113299160884</v>
       </c>
       <c r="P265" t="n">
-        <v>0.1142798026789915</v>
+        <v>0.1142797549548373</v>
       </c>
     </row>
     <row r="266">
@@ -23064,10 +23064,10 @@
         <v>0.04700351911919509</v>
       </c>
       <c r="O266" t="n">
-        <v>1.228347699475127</v>
+        <v>1.228347550066657</v>
       </c>
       <c r="P266" t="n">
-        <v>0.3061538020208605</v>
+        <v>0.3061537728287607</v>
       </c>
     </row>
     <row r="267">
@@ -23116,16 +23116,16 @@
         <v>0.04124181122024684</v>
       </c>
       <c r="M267" t="n">
-        <v>0.08929353364788195</v>
+        <v>0.08929346806497418</v>
       </c>
       <c r="N267" t="n">
-        <v>0.1515327219116926</v>
+        <v>0.1515326486202311</v>
       </c>
       <c r="O267" t="n">
-        <v>0.3284816618374884</v>
+        <v>0.3284817593840581</v>
       </c>
       <c r="P267" t="n">
-        <v>0.09930580492550445</v>
+        <v>0.09930583183178654</v>
       </c>
     </row>
     <row r="268">
@@ -23238,10 +23238,10 @@
         <v>0.1692121424224373</v>
       </c>
       <c r="O269" t="n">
-        <v>0.6746727431170918</v>
+        <v>0.6746725373682243</v>
       </c>
       <c r="P269" t="n">
-        <v>0.1875265204030767</v>
+        <v>0.1875264717702423</v>
       </c>
     </row>
     <row r="270">
@@ -23269,37 +23269,37 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>32.01</v>
+        <v>32.02</v>
       </c>
       <c r="G270" t="n">
-        <v>-0.02274111630204434</v>
+        <v>-0.0225884585373477</v>
       </c>
       <c r="H270" t="n">
-        <v>-0.03801080036202942</v>
+        <v>-0.03786052787709338</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.01340528083400916</v>
+        <v>-0.01325116471697829</v>
       </c>
       <c r="J270" t="n">
-        <v>-0.006978978818373949</v>
+        <v>-0.006823858847689324</v>
       </c>
       <c r="K270" t="n">
-        <v>0.009472335658265996</v>
+        <v>0.009630025491385474</v>
       </c>
       <c r="L270" t="n">
-        <v>0.0654052903642437</v>
+        <v>0.06557171749305901</v>
       </c>
       <c r="M270" t="n">
-        <v>0.05291471876803855</v>
+        <v>0.05307919474269052</v>
       </c>
       <c r="N270" t="n">
-        <v>0.03399807665569954</v>
+        <v>0.03415959765869703</v>
       </c>
       <c r="O270" t="n">
-        <v>0.5595465675969857</v>
+        <v>0.5597900396885716</v>
       </c>
       <c r="P270" t="n">
-        <v>0.1596656209219611</v>
+        <v>0.1597259657102839</v>
       </c>
     </row>
     <row r="271">
@@ -23348,16 +23348,16 @@
         <v>0.1296987211403431</v>
       </c>
       <c r="M271" t="n">
-        <v>0.1310140874018964</v>
+        <v>0.1310139973699209</v>
       </c>
       <c r="N271" t="n">
-        <v>-0.05561652469103762</v>
+        <v>-0.05561646192025071</v>
       </c>
       <c r="O271" t="n">
-        <v>0.04961028756897568</v>
+        <v>0.04961036510740069</v>
       </c>
       <c r="P271" t="n">
-        <v>0.01627059449412926</v>
+        <v>0.01627061951929654</v>
       </c>
     </row>
     <row r="272">
@@ -23412,10 +23412,10 @@
         <v>0.1482672084652661</v>
       </c>
       <c r="O272" t="n">
-        <v>0.9064440197925645</v>
+        <v>0.9064438034957496</v>
       </c>
       <c r="P272" t="n">
-        <v>0.2399609812107724</v>
+        <v>0.2399609343172509</v>
       </c>
     </row>
     <row r="273">
@@ -23467,7 +23467,7 @@
         <v>-0.005159923812154577</v>
       </c>
       <c r="N273" t="n">
-        <v>0.03345427253278088</v>
+        <v>0.03345416477460228</v>
       </c>
       <c r="O273" t="n">
         <v>0.3196545820721082</v>
@@ -23525,7 +23525,7 @@
         <v>0.2421400173458199</v>
       </c>
       <c r="N274" t="n">
-        <v>0.1278858369558562</v>
+        <v>0.1278857290564224</v>
       </c>
       <c r="O274" t="n">
         <v>0.5193996593894399</v>
@@ -23580,16 +23580,16 @@
         <v>0.04130961619593077</v>
       </c>
       <c r="M275" t="n">
-        <v>0.1501350494486875</v>
+        <v>0.1501349219972334</v>
       </c>
       <c r="N275" t="n">
-        <v>0.188231229231012</v>
+        <v>0.1882313652655356</v>
       </c>
       <c r="O275" t="n">
-        <v>0.4504755755680214</v>
+        <v>0.4504752715081033</v>
       </c>
       <c r="P275" t="n">
-        <v>0.1319749251439044</v>
+        <v>0.1319748460461168</v>
       </c>
     </row>
     <row r="276">
@@ -23644,10 +23644,10 @@
         <v>0.2548078513364691</v>
       </c>
       <c r="O276" t="n">
-        <v>1.470999359291014</v>
+        <v>1.470999633959936</v>
       </c>
       <c r="P276" t="n">
-        <v>0.3519403938209513</v>
+        <v>0.3519404439135041</v>
       </c>
     </row>
     <row r="277">
@@ -23702,10 +23702,10 @@
         <v>0.06958080343008843</v>
       </c>
       <c r="O277" t="n">
-        <v>0.8831020601783872</v>
+        <v>0.8831025006558266</v>
       </c>
       <c r="P277" t="n">
-        <v>0.2348796093429264</v>
+        <v>0.2348797056267085</v>
       </c>
     </row>
     <row r="278">
@@ -23754,16 +23754,16 @@
         <v>0.02195335463127179</v>
       </c>
       <c r="M278" t="n">
-        <v>0.0491841272983029</v>
+        <v>0.04918420125340717</v>
       </c>
       <c r="N278" t="n">
         <v>0.2170513846363671</v>
       </c>
       <c r="O278" t="n">
-        <v>1.310630800915836</v>
+        <v>1.310631159611299</v>
       </c>
       <c r="P278" t="n">
-        <v>0.3220367243290618</v>
+        <v>0.3220367927387431</v>
       </c>
     </row>
     <row r="279">
@@ -23818,10 +23818,10 @@
         <v>-0.05451231971226345</v>
       </c>
       <c r="O279" t="n">
-        <v>1.002466625118903</v>
+        <v>1.002466763398153</v>
       </c>
       <c r="P279" t="n">
-        <v>0.260438795923863</v>
+        <v>0.2604388249368357</v>
       </c>
     </row>
     <row r="280">
@@ -23873,13 +23873,13 @@
         <v>0.2546860462862077</v>
       </c>
       <c r="N280" t="n">
-        <v>0.2761645000381536</v>
+        <v>0.2761643977478843</v>
       </c>
       <c r="O280" t="n">
-        <v>5.696351652215533</v>
+        <v>5.696350244005433</v>
       </c>
       <c r="P280" t="n">
-        <v>0.8848613858831289</v>
+        <v>0.8848612537574001</v>
       </c>
     </row>
     <row r="281">
@@ -23934,10 +23934,10 @@
         <v>0.04405896675027532</v>
       </c>
       <c r="O281" t="n">
-        <v>1.157855737522439</v>
+        <v>1.157855895131441</v>
       </c>
       <c r="P281" t="n">
-        <v>0.2922329248541764</v>
+        <v>0.2922329563155839</v>
       </c>
     </row>
     <row r="282">
@@ -23989,7 +23989,7 @@
         <v>-0.09447614052538988</v>
       </c>
       <c r="N282" t="n">
-        <v>-0.02940062791198372</v>
+        <v>-0.02940056392896839</v>
       </c>
       <c r="O282" t="n">
         <v>0.4207178542050123</v>
@@ -24050,10 +24050,10 @@
         <v>0.1251546838588877</v>
       </c>
       <c r="O283" t="n">
-        <v>0.5998446362706757</v>
+        <v>0.5998444276440209</v>
       </c>
       <c r="P283" t="n">
-        <v>0.1695692368680382</v>
+        <v>0.1695691860290749</v>
       </c>
     </row>
     <row r="284">
@@ -24105,13 +24105,13 @@
         <v>0.03990188551018647</v>
       </c>
       <c r="N284" t="n">
-        <v>0.03864088178111613</v>
+        <v>0.0386411025092761</v>
       </c>
       <c r="O284" t="n">
-        <v>2.726168192680376</v>
+        <v>2.726167482462401</v>
       </c>
       <c r="P284" t="n">
-        <v>0.5503181022711179</v>
+        <v>0.5503180037728039</v>
       </c>
     </row>
     <row r="285">
@@ -24273,13 +24273,13 @@
         <v>-0.09006408728533433</v>
       </c>
       <c r="L287" t="n">
-        <v>-0.05594153988732731</v>
+        <v>-0.0559416186236591</v>
       </c>
       <c r="M287" t="n">
         <v>0.1486449557458185</v>
       </c>
       <c r="N287" t="n">
-        <v>0.1712482892057849</v>
+        <v>0.1712485315906294</v>
       </c>
       <c r="O287" t="n">
         <v>0.5701053817764277</v>
@@ -24398,10 +24398,10 @@
         <v>-0.07999513509831968</v>
       </c>
       <c r="O289" t="n">
-        <v>0.1048672251672864</v>
+        <v>0.1048670530308571</v>
       </c>
       <c r="P289" t="n">
-        <v>0.03380040255872552</v>
+        <v>0.03380034887060956</v>
       </c>
     </row>
     <row r="290">
@@ -24453,13 +24453,13 @@
         <v>0.1014052186674292</v>
       </c>
       <c r="N290" t="n">
-        <v>-0.02180224468503877</v>
+        <v>-0.02180234367276057</v>
       </c>
       <c r="O290" t="n">
-        <v>0.03106926867334159</v>
+        <v>0.03106904871844351</v>
       </c>
       <c r="P290" t="n">
-        <v>0.01025098120873236</v>
+        <v>0.01025090937079542</v>
       </c>
     </row>
     <row r="291">
@@ -24511,7 +24511,7 @@
         <v>0.09172160600695745</v>
       </c>
       <c r="N291" t="n">
-        <v>0.1242308390531908</v>
+        <v>0.1242309140590578</v>
       </c>
       <c r="O291" t="n">
         <v>0.8471906299007683</v>
@@ -24569,13 +24569,13 @@
         <v>0.03611757970393703</v>
       </c>
       <c r="N292" t="n">
-        <v>0.2486065141300531</v>
+        <v>0.24860640609768</v>
       </c>
       <c r="O292" t="n">
-        <v>1.217750716894915</v>
+        <v>1.217751228128735</v>
       </c>
       <c r="P292" t="n">
-        <v>0.3040800250922704</v>
+        <v>0.3040801252973651</v>
       </c>
     </row>
     <row r="293">
@@ -24627,13 +24627,13 @@
         <v>0.115792612964043</v>
       </c>
       <c r="N293" t="n">
-        <v>0.3717588754880752</v>
+        <v>0.3717590364839456</v>
       </c>
       <c r="O293" t="n">
-        <v>2.110429663361973</v>
+        <v>2.110430077237704</v>
       </c>
       <c r="P293" t="n">
-        <v>0.4597331193179106</v>
+        <v>0.4597331840622438</v>
       </c>
     </row>
     <row r="294">
@@ -24679,13 +24679,13 @@
         <v>-0.02580429969477449</v>
       </c>
       <c r="L294" t="n">
-        <v>-0.07000686269850809</v>
+        <v>-0.07000678145788852</v>
       </c>
       <c r="M294" t="n">
         <v>-0.03121330705371794</v>
       </c>
       <c r="N294" t="n">
-        <v>0.2178371222884639</v>
+        <v>0.2178374009148312</v>
       </c>
       <c r="O294" t="n">
         <v>1.684632647311423</v>
@@ -24734,22 +24734,22 @@
         <v>-0.07212803137244128</v>
       </c>
       <c r="K295" t="n">
-        <v>-0.1745473970961984</v>
+        <v>-0.1745474671562466</v>
       </c>
       <c r="L295" t="n">
-        <v>0.1910928853097811</v>
+        <v>0.1910928123728601</v>
       </c>
       <c r="M295" t="n">
-        <v>0.1350933204793854</v>
+        <v>0.135093187999705</v>
       </c>
       <c r="N295" t="n">
-        <v>0.09919945442057565</v>
+        <v>0.09919933018695404</v>
       </c>
       <c r="O295" t="n">
-        <v>0.379318648887661</v>
+        <v>0.3793182576458372</v>
       </c>
       <c r="P295" t="n">
-        <v>0.1131530211846816</v>
+        <v>0.1131529159365674</v>
       </c>
     </row>
     <row r="296">
@@ -24853,7 +24853,7 @@
         <v>-0.04361373838746596</v>
       </c>
       <c r="L297" t="n">
-        <v>-0.06281785141895224</v>
+        <v>-0.06281779165150447</v>
       </c>
       <c r="M297" t="n">
         <v>0.1457054168438705</v>
@@ -24914,16 +24914,16 @@
         <v>0.009686961517533454</v>
       </c>
       <c r="M298" t="n">
-        <v>0.05990763418523581</v>
+        <v>0.05990772434348868</v>
       </c>
       <c r="N298" t="n">
         <v>0.1769270774004605</v>
       </c>
       <c r="O298" t="n">
-        <v>1.960630220603348</v>
+        <v>1.960630924060823</v>
       </c>
       <c r="P298" t="n">
-        <v>0.4359127638123985</v>
+        <v>0.4359128775385774</v>
       </c>
     </row>
     <row r="299">
@@ -24969,19 +24969,19 @@
         <v>0.1207930731517091</v>
       </c>
       <c r="L299" t="n">
-        <v>0.102443953982952</v>
+        <v>0.1024440272207254</v>
       </c>
       <c r="M299" t="n">
         <v>-0.1216401797091207</v>
       </c>
       <c r="N299" t="n">
-        <v>-0.1688169039988284</v>
+        <v>-0.1688168207370838</v>
       </c>
       <c r="O299" t="n">
-        <v>0.948853337360605</v>
+        <v>0.9488528796296634</v>
       </c>
       <c r="P299" t="n">
-        <v>0.2490880468051579</v>
+        <v>0.249087949013244</v>
       </c>
     </row>
     <row r="300">
@@ -25152,10 +25152,10 @@
         <v>-0.2122954357522833</v>
       </c>
       <c r="O302" t="n">
-        <v>0.1161468044240499</v>
+        <v>0.116146911838596</v>
       </c>
       <c r="P302" t="n">
-        <v>0.03730651776491989</v>
+        <v>0.03730655104065161</v>
       </c>
     </row>
     <row r="303">
@@ -25265,7 +25265,7 @@
         <v>0.07094832904133641</v>
       </c>
       <c r="N304" t="n">
-        <v>0.01402914893667573</v>
+        <v>0.01402903941603628</v>
       </c>
       <c r="O304" t="n">
         <v>0.7660386351935513</v>
@@ -25326,10 +25326,10 @@
         <v>0.07501842733463659</v>
       </c>
       <c r="O305" t="n">
-        <v>0.5703550960082775</v>
+        <v>0.5703552702138739</v>
       </c>
       <c r="P305" t="n">
-        <v>0.1623384989523475</v>
+        <v>0.1623385419332557</v>
       </c>
     </row>
     <row r="306">
@@ -25378,16 +25378,16 @@
         <v>0.04914162261284982</v>
       </c>
       <c r="M306" t="n">
-        <v>-0.02207482994120324</v>
+        <v>-0.02207474148003064</v>
       </c>
       <c r="N306" t="n">
         <v>0.1906624989660965</v>
       </c>
       <c r="O306" t="n">
-        <v>2.122682293530262</v>
+        <v>2.122682744520428</v>
       </c>
       <c r="P306" t="n">
-        <v>0.4616473389225673</v>
+        <v>0.4616474092881999</v>
       </c>
     </row>
     <row r="307">
@@ -25439,13 +25439,13 @@
         <v>0.06307202224709729</v>
       </c>
       <c r="N307" t="n">
-        <v>0.07631294293045321</v>
+        <v>0.0763128366757313</v>
       </c>
       <c r="O307" t="n">
-        <v>0.6821864258096451</v>
+        <v>0.6821865555841682</v>
       </c>
       <c r="P307" t="n">
-        <v>0.189299879068888</v>
+        <v>0.1892999096522641</v>
       </c>
     </row>
     <row r="308">
@@ -25491,19 +25491,19 @@
         <v>-0.07653458689211701</v>
       </c>
       <c r="L308" t="n">
-        <v>-0.01819456737101466</v>
+        <v>-0.01819450063513606</v>
       </c>
       <c r="M308" t="n">
-        <v>0.07371932059858333</v>
+        <v>0.07371940041460179</v>
       </c>
       <c r="N308" t="n">
-        <v>0.1228376403028741</v>
+        <v>0.1228377275884438</v>
       </c>
       <c r="O308" t="n">
-        <v>0.7693053721818264</v>
+        <v>0.7693052638180675</v>
       </c>
       <c r="P308" t="n">
-        <v>0.2094862405079871</v>
+        <v>0.2094862158157209</v>
       </c>
     </row>
     <row r="309">
@@ -25549,19 +25549,19 @@
         <v>-0.1010588040004399</v>
       </c>
       <c r="L309" t="n">
-        <v>0.123116114145323</v>
+        <v>0.1231162124259755</v>
       </c>
       <c r="M309" t="n">
         <v>-0.007498336431057906</v>
       </c>
       <c r="N309" t="n">
-        <v>0.1123681104102423</v>
+        <v>0.1123682068188419</v>
       </c>
       <c r="O309" t="n">
-        <v>1.626470801302004</v>
+        <v>1.626470532561089</v>
       </c>
       <c r="P309" t="n">
-        <v>0.3797196800402247</v>
+        <v>0.3797196329825101</v>
       </c>
     </row>
     <row r="310">
@@ -25607,13 +25607,13 @@
         <v>-0.01860213398897725</v>
       </c>
       <c r="L310" t="n">
-        <v>-0.003377137272038699</v>
+        <v>-0.003377237828696034</v>
       </c>
       <c r="M310" t="n">
         <v>0.03925175787470314</v>
       </c>
       <c r="N310" t="n">
-        <v>0.02536722411970738</v>
+        <v>0.02536711767893984</v>
       </c>
       <c r="O310" t="n">
         <v>1.851705187207294</v>
@@ -25668,16 +25668,16 @@
         <v>-0.07253860314677818</v>
       </c>
       <c r="M311" t="n">
-        <v>-0.04091863546415098</v>
+        <v>-0.04091854825671759</v>
       </c>
       <c r="N311" t="n">
-        <v>0.2022885640644285</v>
+        <v>0.2022884270204546</v>
       </c>
       <c r="O311" t="n">
-        <v>1.633215925704594</v>
+        <v>1.633215761359975</v>
       </c>
       <c r="P311" t="n">
-        <v>0.3808997712806046</v>
+        <v>0.3808997425523046</v>
       </c>
     </row>
     <row r="312">
@@ -25726,7 +25726,7 @@
         <v>-0.04825933643579616</v>
       </c>
       <c r="M312" t="n">
-        <v>0.001373890964570856</v>
+        <v>0.001373823850153055</v>
       </c>
       <c r="N312" t="n">
         <v>0.1988278670786727</v>
@@ -25781,7 +25781,7 @@
         <v>-0.05540685555546376</v>
       </c>
       <c r="L313" t="n">
-        <v>-0.0009894351025629966</v>
+        <v>-0.0009893674649423811</v>
       </c>
       <c r="M313" t="n">
         <v>-0.01542248521341794</v>
@@ -25790,10 +25790,10 @@
         <v>0.1208434574084682</v>
       </c>
       <c r="O313" t="n">
-        <v>0.4606079911687018</v>
+        <v>0.460607702003929</v>
       </c>
       <c r="P313" t="n">
-        <v>0.1346046456718404</v>
+        <v>0.1346045707971495</v>
       </c>
     </row>
     <row r="314">
@@ -25842,10 +25842,10 @@
         <v>0.007823103267130538</v>
       </c>
       <c r="M314" t="n">
-        <v>0.002031233948677214</v>
+        <v>0.002031167708571591</v>
       </c>
       <c r="N314" t="n">
-        <v>0.1909839487293397</v>
+        <v>0.1909840423066111</v>
       </c>
       <c r="O314" t="n">
         <v>2.411851231614689</v>
@@ -25900,16 +25900,16 @@
         <v>-0.06357539853302518</v>
       </c>
       <c r="M315" t="n">
-        <v>0.1240127423780431</v>
+        <v>0.1240126351408917</v>
       </c>
       <c r="N315" t="n">
-        <v>0.06238426647114403</v>
+        <v>0.06238417067102198</v>
       </c>
       <c r="O315" t="n">
-        <v>0.6084108750539601</v>
+        <v>0.6084110946360435</v>
       </c>
       <c r="P315" t="n">
-        <v>0.1716529768550081</v>
+        <v>0.1716530301734716</v>
       </c>
     </row>
     <row r="316">
@@ -25958,16 +25958,16 @@
         <v>0.1401210981014414</v>
       </c>
       <c r="M316" t="n">
-        <v>0.007329754906196362</v>
+        <v>0.007329842296044164</v>
       </c>
       <c r="N316" t="n">
-        <v>0.04061990840734531</v>
+        <v>0.04061981514596424</v>
       </c>
       <c r="O316" t="n">
-        <v>0.5765482604303576</v>
+        <v>0.5765481534011931</v>
       </c>
       <c r="P316" t="n">
-        <v>0.1638645043169211</v>
+        <v>0.1638644779793303</v>
       </c>
     </row>
     <row r="317">
@@ -26071,7 +26071,7 @@
         <v>-0.03546541452275254</v>
       </c>
       <c r="L318" t="n">
-        <v>-0.01616862605007541</v>
+        <v>-0.01616868581114161</v>
       </c>
       <c r="M318" t="n">
         <v>0.05459506653528745</v>
@@ -26080,10 +26080,10 @@
         <v>0.01796031174791679</v>
       </c>
       <c r="O318" t="n">
-        <v>0.5804657331680583</v>
+        <v>0.5804658873903807</v>
       </c>
       <c r="P318" t="n">
-        <v>0.1648277132708471</v>
+        <v>0.1648277511589256</v>
       </c>
     </row>
     <row r="319">
@@ -26132,16 +26132,16 @@
         <v>-0.1398544226304288</v>
       </c>
       <c r="M319" t="n">
-        <v>0.02320880820613325</v>
+        <v>0.02320872174107613</v>
       </c>
       <c r="N319" t="n">
-        <v>-0.02028309153602625</v>
+        <v>-0.02028317080683706</v>
       </c>
       <c r="O319" t="n">
-        <v>-0.03628495183227876</v>
+        <v>-0.0362846450222587</v>
       </c>
       <c r="P319" t="n">
-        <v>-0.01224429479976608</v>
+        <v>-0.01224418997856191</v>
       </c>
     </row>
     <row r="320">
@@ -26254,10 +26254,10 @@
         <v>0.04025919396679822</v>
       </c>
       <c r="O321" t="n">
-        <v>0.1930576984189123</v>
+        <v>0.19305742368421</v>
       </c>
       <c r="P321" t="n">
-        <v>0.06060535566294467</v>
+        <v>0.06060527425164919</v>
       </c>
     </row>
     <row r="322">
@@ -26306,7 +26306,7 @@
         <v>-0.02814265990762266</v>
       </c>
       <c r="M322" t="n">
-        <v>0.07143660965396093</v>
+        <v>0.07143673590977206</v>
       </c>
       <c r="N322" t="n">
         <v>0.0521806056880576</v>
@@ -26361,13 +26361,13 @@
         <v>0.02461112926115794</v>
       </c>
       <c r="L323" t="n">
-        <v>0.004861008906114739</v>
+        <v>0.0048609101147985</v>
       </c>
       <c r="M323" t="n">
         <v>-0.08624947377295111</v>
       </c>
       <c r="N323" t="n">
-        <v>0.004877902506837728</v>
+        <v>0.004877803712199924</v>
       </c>
       <c r="O323" t="n">
         <v>0.5460040027320163</v>
@@ -26483,13 +26483,13 @@
         <v>-0.0691929637605081</v>
       </c>
       <c r="N325" t="n">
-        <v>-0.02627320471916139</v>
+        <v>-0.02627311550979861</v>
       </c>
       <c r="O325" t="n">
-        <v>0.7724641122871243</v>
+        <v>0.772463964491688</v>
       </c>
       <c r="P325" t="n">
-        <v>0.2102055776852003</v>
+        <v>0.2102055440478732</v>
       </c>
     </row>
     <row r="326">
@@ -26541,13 +26541,13 @@
         <v>0.1528115691187757</v>
       </c>
       <c r="N326" t="n">
-        <v>0.3746861705951363</v>
+        <v>0.3746860848881328</v>
       </c>
       <c r="O326" t="n">
-        <v>6.723759029155496</v>
+        <v>6.723758352750799</v>
       </c>
       <c r="P326" t="n">
-        <v>0.9767097541075447</v>
+        <v>0.9767096964043893</v>
       </c>
     </row>
     <row r="327">
@@ -26599,13 +26599,13 @@
         <v>-0.00283899721622527</v>
       </c>
       <c r="N327" t="n">
-        <v>-0.07016495043140225</v>
+        <v>-0.07016488270734522</v>
       </c>
       <c r="O327" t="n">
-        <v>0.5640440047419653</v>
+        <v>0.5640441005493702</v>
       </c>
       <c r="P327" t="n">
-        <v>0.1607793031158933</v>
+        <v>0.160779326817539</v>
       </c>
     </row>
     <row r="328">
@@ -26654,16 +26654,16 @@
         <v>0.03290418053114341</v>
       </c>
       <c r="M328" t="n">
-        <v>0.04784406725301293</v>
+        <v>0.04784395953923304</v>
       </c>
       <c r="N328" t="n">
         <v>0.05298329301370042</v>
       </c>
       <c r="O328" t="n">
-        <v>0.1685195173215046</v>
+        <v>0.1685192494171142</v>
       </c>
       <c r="P328" t="n">
-        <v>0.05328360346323668</v>
+        <v>0.05328352296841143</v>
       </c>
     </row>
     <row r="329">
@@ -26712,7 +26712,7 @@
         <v>-0.01372796809654031</v>
       </c>
       <c r="M329" t="n">
-        <v>0.03891994457936288</v>
+        <v>0.03892005127569975</v>
       </c>
       <c r="N329" t="n">
         <v>-0.003034023220635507</v>
@@ -26773,13 +26773,13 @@
         <v>0.03022109614122037</v>
       </c>
       <c r="N330" t="n">
-        <v>-0.008168603974322619</v>
+        <v>-0.008168536053407505</v>
       </c>
       <c r="O330" t="n">
-        <v>0.5052233231910894</v>
+        <v>0.5052231667576375</v>
       </c>
       <c r="P330" t="n">
-        <v>0.1460414171185889</v>
+        <v>0.1460413774170113</v>
       </c>
     </row>
     <row r="331">
@@ -26892,10 +26892,10 @@
         <v>-0.001041321289781849</v>
       </c>
       <c r="O332" t="n">
-        <v>-0.1031171586905029</v>
+        <v>-0.1031172229934727</v>
       </c>
       <c r="P332" t="n">
-        <v>-0.03562656535768483</v>
+        <v>-0.03562658840494526</v>
       </c>
     </row>
     <row r="333">
@@ -26950,10 +26950,10 @@
         <v>0.3513886178345167</v>
       </c>
       <c r="O333" t="n">
-        <v>0.3845666217022479</v>
+        <v>0.3845664906824775</v>
       </c>
       <c r="P333" t="n">
-        <v>0.1145629935518639</v>
+        <v>0.1145629583953056</v>
       </c>
     </row>
     <row r="334">
@@ -27002,16 +27002,16 @@
         <v>0.1457806530719001</v>
       </c>
       <c r="M334" t="n">
-        <v>0.05489565962097953</v>
+        <v>0.05489558455442989</v>
       </c>
       <c r="N334" t="n">
-        <v>-0.2169180228455033</v>
+        <v>-0.2169181055771907</v>
       </c>
       <c r="O334" t="n">
-        <v>0.134761601013369</v>
+        <v>0.1347616878767581</v>
       </c>
       <c r="P334" t="n">
-        <v>0.04304139319950928</v>
+        <v>0.04304141981364795</v>
       </c>
     </row>
     <row r="335">
@@ -27060,16 +27060,16 @@
         <v>-0.03389096336118858</v>
       </c>
       <c r="M335" t="n">
-        <v>-0.007852209592253634</v>
+        <v>-0.00785213204113222</v>
       </c>
       <c r="N335" t="n">
-        <v>0.1390526891911064</v>
+        <v>0.1390524847572343</v>
       </c>
       <c r="O335" t="n">
-        <v>1.031673785174509</v>
+        <v>1.031673622577246</v>
       </c>
       <c r="P335" t="n">
-        <v>0.2665373228939021</v>
+        <v>0.2665372891064062</v>
       </c>
     </row>
     <row r="336">
@@ -27115,19 +27115,19 @@
         <v>-0.01222929073789636</v>
       </c>
       <c r="L336" t="n">
-        <v>0.04679105969637853</v>
+        <v>0.04679112976216127</v>
       </c>
       <c r="M336" t="n">
-        <v>-0.07000100616400329</v>
+        <v>-0.07000111677055165</v>
       </c>
       <c r="N336" t="n">
-        <v>-0.01905269787458885</v>
+        <v>-0.01905275940322171</v>
       </c>
       <c r="O336" t="n">
-        <v>0.6194146690598807</v>
+        <v>0.6194150044360207</v>
       </c>
       <c r="P336" t="n">
-        <v>0.174318825116327</v>
+        <v>0.1743189061823434</v>
       </c>
     </row>
     <row r="337">
@@ -27176,16 +27176,16 @@
         <v>-0.006101546166699112</v>
       </c>
       <c r="M337" t="n">
-        <v>0.09629504020619972</v>
+        <v>0.09629511035757066</v>
       </c>
       <c r="N337" t="n">
-        <v>0.06104940353981192</v>
+        <v>0.06104933782664146</v>
       </c>
       <c r="O337" t="n">
-        <v>0.4148567030406034</v>
+        <v>0.4148568198845415</v>
       </c>
       <c r="P337" t="n">
-        <v>0.1226321762176996</v>
+        <v>0.1226322071213619</v>
       </c>
     </row>
     <row r="338">
@@ -27237,13 +27237,13 @@
         <v>0.009374244083355965</v>
       </c>
       <c r="N338" t="n">
-        <v>0.03814080178606782</v>
+        <v>0.03814098921431719</v>
       </c>
       <c r="O338" t="n">
-        <v>0.9149593867005046</v>
+        <v>0.9149590678320791</v>
       </c>
       <c r="P338" t="n">
-        <v>0.2418043854544365</v>
+        <v>0.2418043165283044</v>
       </c>
     </row>
     <row r="339">
@@ -27292,16 +27292,16 @@
         <v>0.1732072323014957</v>
       </c>
       <c r="M339" t="n">
-        <v>-0.1086945975593511</v>
+        <v>-0.1086944976996442</v>
       </c>
       <c r="N339" t="n">
-        <v>-0.04454855713040351</v>
+        <v>-0.04454844237993871</v>
       </c>
       <c r="O339" t="n">
-        <v>0.05052164493203892</v>
+        <v>0.05052157557075132</v>
       </c>
       <c r="P339" t="n">
-        <v>0.01656464577710115</v>
+        <v>0.01656462340401488</v>
       </c>
     </row>
     <row r="340">
@@ -27347,19 +27347,19 @@
         <v>-0.05619348578169892</v>
       </c>
       <c r="L340" t="n">
-        <v>-0.04511287993784963</v>
+        <v>-0.04511295490070488</v>
       </c>
       <c r="M340" t="n">
-        <v>0.008140392428977572</v>
+        <v>0.00814030887173911</v>
       </c>
       <c r="N340" t="n">
         <v>0.04558404166559926</v>
       </c>
       <c r="O340" t="n">
-        <v>0.4960398885523354</v>
+        <v>0.4960395205434383</v>
       </c>
       <c r="P340" t="n">
-        <v>0.1437059778505625</v>
+        <v>0.1437058840709753</v>
       </c>
     </row>
     <row r="341">
@@ -27408,16 +27408,16 @@
         <v>0.07488842051871258</v>
       </c>
       <c r="M341" t="n">
-        <v>-0.05097683819389942</v>
+        <v>-0.05097690527096987</v>
       </c>
       <c r="N341" t="n">
         <v>-0.05848929328230423</v>
       </c>
       <c r="O341" t="n">
-        <v>1.19577321926839</v>
+        <v>1.19577339881016</v>
       </c>
       <c r="P341" t="n">
-        <v>0.2997579863623712</v>
+        <v>0.2997580217881368</v>
       </c>
     </row>
     <row r="342">
@@ -27466,16 +27466,16 @@
         <v>0.03842293856581325</v>
       </c>
       <c r="M342" t="n">
-        <v>-0.03388155660488312</v>
+        <v>-0.0338814714947836</v>
       </c>
       <c r="N342" t="n">
-        <v>-0.01617303048799523</v>
+        <v>-0.0161731187467351</v>
       </c>
       <c r="O342" t="n">
-        <v>1.321656068147506</v>
+        <v>1.321655822401743</v>
       </c>
       <c r="P342" t="n">
-        <v>0.3241361057927645</v>
+        <v>0.3241360590731184</v>
       </c>
     </row>
     <row r="343">
@@ -27640,10 +27640,10 @@
         <v>-0.07073251462678276</v>
       </c>
       <c r="M345" t="n">
-        <v>0.06965783785314672</v>
+        <v>0.06965795712229461</v>
       </c>
       <c r="N345" t="n">
-        <v>0.06522929919119203</v>
+        <v>0.06522941747480093</v>
       </c>
       <c r="O345" t="n">
         <v>0.4313787821218356</v>
@@ -27704,10 +27704,10 @@
         <v>-0.02696578424802432</v>
       </c>
       <c r="O346" t="n">
-        <v>0.3046459931298187</v>
+        <v>0.3046464282204666</v>
       </c>
       <c r="P346" t="n">
-        <v>0.09269149211007055</v>
+        <v>0.09269161357847366</v>
       </c>
     </row>
     <row r="347">
@@ -27762,10 +27762,10 @@
         <v>-0.04334058484927661</v>
       </c>
       <c r="O347" t="n">
-        <v>0.1238937555577859</v>
+        <v>0.1238939240510695</v>
       </c>
       <c r="P347" t="n">
-        <v>0.03970089881182171</v>
+        <v>0.03970095076887104</v>
       </c>
     </row>
     <row r="348">
@@ -27817,7 +27817,7 @@
         <v>0.0274980628160173</v>
       </c>
       <c r="N348" t="n">
-        <v>0.04296405112490875</v>
+        <v>0.0429638915276811</v>
       </c>
       <c r="O348" t="n">
         <v>0.3617637500897837</v>
@@ -27869,19 +27869,19 @@
         <v>-0.08931503564497234</v>
       </c>
       <c r="L349" t="n">
-        <v>-0.05447242489856075</v>
+        <v>-0.0544723199946745</v>
       </c>
       <c r="M349" t="n">
         <v>0.008580919250812613</v>
       </c>
       <c r="N349" t="n">
-        <v>0.07890516135721537</v>
+        <v>0.07890509306367144</v>
       </c>
       <c r="O349" t="n">
-        <v>0.9493683075748423</v>
+        <v>0.9493685305215109</v>
       </c>
       <c r="P349" t="n">
-        <v>0.2491980579037565</v>
+        <v>0.2491981055267964</v>
       </c>
     </row>
     <row r="350">
@@ -27933,13 +27933,13 @@
         <v>-0.0130983589528707</v>
       </c>
       <c r="N350" t="n">
-        <v>-0.1691723435522626</v>
+        <v>-0.1691723948614688</v>
       </c>
       <c r="O350" t="n">
-        <v>0.1774180109931311</v>
+        <v>0.1774182170868968</v>
       </c>
       <c r="P350" t="n">
-        <v>0.05595049549395692</v>
+        <v>0.05595055710470143</v>
       </c>
     </row>
     <row r="351">
@@ -28046,16 +28046,16 @@
         <v>-0.1922903533931279</v>
       </c>
       <c r="M352" t="n">
-        <v>0.04777909435341821</v>
+        <v>0.04777898370978062</v>
       </c>
       <c r="N352" t="n">
         <v>0.1224158076211681</v>
       </c>
       <c r="O352" t="n">
-        <v>2.049216615522762</v>
+        <v>2.049216849785725</v>
       </c>
       <c r="P352" t="n">
-        <v>0.4500937894977872</v>
+        <v>0.4500938266333645</v>
       </c>
     </row>
     <row r="353">
@@ -28107,13 +28107,13 @@
         <v>-0.08275577459332306</v>
       </c>
       <c r="N353" t="n">
-        <v>-0.2127034999688444</v>
+        <v>-0.212703576740974</v>
       </c>
       <c r="O353" t="n">
-        <v>-0.05090943309591889</v>
+        <v>-0.05090965623323029</v>
       </c>
       <c r="P353" t="n">
-        <v>-0.01726621748353341</v>
+        <v>-0.01726629449922223</v>
       </c>
     </row>
     <row r="354">
@@ -28165,13 +28165,13 @@
         <v>-0.2496321085156442</v>
       </c>
       <c r="N354" t="n">
-        <v>-0.2480876991826774</v>
+        <v>-0.2480877609799027</v>
       </c>
       <c r="O354" t="n">
-        <v>0.5953361381720943</v>
+        <v>0.5953364163605568</v>
       </c>
       <c r="P354" t="n">
-        <v>0.1684695547312074</v>
+        <v>0.1684696226489171</v>
       </c>
     </row>
     <row r="355">
@@ -28223,13 +28223,13 @@
         <v>-0.02065434023602786</v>
       </c>
       <c r="N355" t="n">
-        <v>0.3235589825547154</v>
+        <v>0.3235590667345842</v>
       </c>
       <c r="O355" t="n">
-        <v>2.550682873766013</v>
+        <v>2.550683176677281</v>
       </c>
       <c r="P355" t="n">
-        <v>0.5255881094608725</v>
+        <v>0.5255881528438717</v>
       </c>
     </row>
     <row r="356">
@@ -28281,13 +28281,13 @@
         <v>-0.01018286906841126</v>
       </c>
       <c r="N356" t="n">
-        <v>0.02427640677321419</v>
+        <v>0.02427647214128403</v>
       </c>
       <c r="O356" t="n">
-        <v>0.6417575511207794</v>
+        <v>0.641757383182656</v>
       </c>
       <c r="P356" t="n">
-        <v>0.1796948246341825</v>
+        <v>0.1796947844098629</v>
       </c>
     </row>
     <row r="357">
@@ -28391,7 +28391,7 @@
         <v>-0.09495409000497401</v>
       </c>
       <c r="L358" t="n">
-        <v>-0.04428706833791929</v>
+        <v>-0.04428701112452349</v>
       </c>
       <c r="M358" t="n">
         <v>0.03717547519703301</v>
@@ -28400,10 +28400,10 @@
         <v>0.03675962231709717</v>
       </c>
       <c r="O358" t="n">
-        <v>0.2726915292902719</v>
+        <v>0.2726913263730031</v>
       </c>
       <c r="P358" t="n">
-        <v>0.08369661757998825</v>
+        <v>0.08369655998531211</v>
       </c>
     </row>
     <row r="359">
@@ -28458,10 +28458,10 @@
         <v>0.05481453347614407</v>
       </c>
       <c r="O359" t="n">
-        <v>0.3333947319606581</v>
+        <v>0.3333951031534343</v>
       </c>
       <c r="P359" t="n">
-        <v>0.1006593105222751</v>
+        <v>0.1006594126567586</v>
       </c>
     </row>
     <row r="360">
@@ -28510,7 +28510,7 @@
         <v>-0.08524769555064982</v>
       </c>
       <c r="M360" t="n">
-        <v>-0.02088527891939063</v>
+        <v>-0.0208851747011074</v>
       </c>
       <c r="N360" t="n">
         <v>-0.01852866466238934</v>
@@ -28571,7 +28571,7 @@
         <v>-0.02433013897625413</v>
       </c>
       <c r="N361" t="n">
-        <v>0.1599392474070984</v>
+        <v>0.1599393413060999</v>
       </c>
       <c r="O361" t="n">
         <v>0.6725043120519063</v>
@@ -28632,10 +28632,10 @@
         <v>-0.0729304719269076</v>
       </c>
       <c r="O362" t="n">
-        <v>0.161416746426438</v>
+        <v>0.1614170835851683</v>
       </c>
       <c r="P362" t="n">
-        <v>0.05114515919802964</v>
+        <v>0.05114526091366689</v>
       </c>
     </row>
     <row r="363">
@@ -28684,16 +28684,16 @@
         <v>-0.02885742682156434</v>
       </c>
       <c r="M363" t="n">
-        <v>0.05537410848165436</v>
+        <v>0.05537402906361999</v>
       </c>
       <c r="N363" t="n">
-        <v>-0.007866423531627253</v>
+        <v>-0.00786635334625263</v>
       </c>
       <c r="O363" t="n">
-        <v>0.04854573916595761</v>
+        <v>0.04854566077228273</v>
       </c>
       <c r="P363" t="n">
-        <v>0.01592690020018095</v>
+        <v>0.0159268748818624</v>
       </c>
     </row>
     <row r="364">
@@ -28742,16 +28742,16 @@
         <v>-0.03332196132499365</v>
       </c>
       <c r="M364" t="n">
-        <v>-0.05267931898232892</v>
+        <v>-0.05267942800690895</v>
       </c>
       <c r="N364" t="n">
-        <v>0.04914152131814742</v>
+        <v>0.04914145445781037</v>
       </c>
       <c r="O364" t="n">
-        <v>0.8812935507817428</v>
+        <v>0.8812937657694473</v>
       </c>
       <c r="P364" t="n">
-        <v>0.2344841613657913</v>
+        <v>0.2344842083899796</v>
       </c>
     </row>
     <row r="365">
@@ -28855,13 +28855,13 @@
         <v>-0.09909490851509573</v>
       </c>
       <c r="L366" t="n">
-        <v>-0.0261993488744432</v>
+        <v>-0.02619924465574519</v>
       </c>
       <c r="M366" t="n">
-        <v>-0.01994086266575557</v>
+        <v>-0.01994096822833491</v>
       </c>
       <c r="N366" t="n">
-        <v>0.03097718291905682</v>
+        <v>0.03097729973540675</v>
       </c>
       <c r="O366" t="n">
         <v>0.2473118043729852</v>
@@ -28971,13 +28971,13 @@
         <v>-0.02166949206591484</v>
       </c>
       <c r="L368" t="n">
-        <v>0.1183877438975942</v>
+        <v>0.1183878209673714</v>
       </c>
       <c r="M368" t="n">
         <v>-0.1447949868915887</v>
       </c>
       <c r="N368" t="n">
-        <v>-0.1456865245398573</v>
+        <v>-0.1456864345975902</v>
       </c>
       <c r="O368" t="n">
         <v>0.3480962987218061</v>
@@ -29032,16 +29032,16 @@
         <v>-0.07436674719556347</v>
       </c>
       <c r="M369" t="n">
-        <v>-0.002179891928789424</v>
+        <v>-0.002179802213788551</v>
       </c>
       <c r="N369" t="n">
-        <v>-0.05756401899365171</v>
+        <v>-0.05756409902574999</v>
       </c>
       <c r="O369" t="n">
-        <v>0.334236781317478</v>
+        <v>0.3342370219296971</v>
       </c>
       <c r="P369" t="n">
-        <v>0.1008909534646252</v>
+        <v>0.1008910196417343</v>
       </c>
     </row>
     <row r="370">
@@ -29090,16 +29090,16 @@
         <v>-0.09949350079833141</v>
       </c>
       <c r="M370" t="n">
-        <v>-0.07298007889287594</v>
+        <v>-0.07298013572256479</v>
       </c>
       <c r="N370" t="n">
         <v>-0.05216497812651333</v>
       </c>
       <c r="O370" t="n">
-        <v>0.5965040880271408</v>
+        <v>0.5965045936871787</v>
       </c>
       <c r="P370" t="n">
-        <v>0.1687546317363873</v>
+        <v>0.1687547551294211</v>
       </c>
     </row>
     <row r="371">
@@ -29206,16 +29206,16 @@
         <v>-0.1448137936536031</v>
       </c>
       <c r="M372" t="n">
-        <v>0.09154043850310245</v>
+        <v>0.09154032996758077</v>
       </c>
       <c r="N372" t="n">
         <v>0.2629191823658066</v>
       </c>
       <c r="O372" t="n">
-        <v>1.530319860170518</v>
+        <v>1.530320443405051</v>
       </c>
       <c r="P372" t="n">
-        <v>0.3626734931864568</v>
+        <v>0.3626735978844424</v>
       </c>
     </row>
     <row r="373">
@@ -29261,19 +29261,19 @@
         <v>0.03707377247382326</v>
       </c>
       <c r="L373" t="n">
-        <v>0.06201700245476394</v>
+        <v>0.06201690250073999</v>
       </c>
       <c r="M373" t="n">
-        <v>-0.1489119766329176</v>
+        <v>-0.1489119124401093</v>
       </c>
       <c r="N373" t="n">
         <v>-0.211518053663367</v>
       </c>
       <c r="O373" t="n">
-        <v>0.4145883401266199</v>
+        <v>0.4145886061310522</v>
       </c>
       <c r="P373" t="n">
-        <v>0.1225611933185187</v>
+        <v>0.1225612636820361</v>
       </c>
     </row>
     <row r="374">
@@ -29322,16 +29322,16 @@
         <v>-0.1671832296683968</v>
       </c>
       <c r="M374" t="n">
-        <v>-0.07098279786288442</v>
+        <v>-0.0709826987308021</v>
       </c>
       <c r="N374" t="n">
         <v>0.3013757181446322</v>
       </c>
       <c r="O374" t="n">
-        <v>1.623442891872965</v>
+        <v>1.623443089501633</v>
       </c>
       <c r="P374" t="n">
-        <v>0.3791892759387958</v>
+        <v>0.3791893105710638</v>
       </c>
     </row>
     <row r="375">
@@ -29377,7 +29377,7 @@
         <v>0.01104113888404812</v>
       </c>
       <c r="L375" t="n">
-        <v>-0.03477228180316694</v>
+        <v>-0.03477217893163753</v>
       </c>
       <c r="M375" t="n">
         <v>-0.1880861476849217</v>
@@ -29444,10 +29444,10 @@
         <v>-0.04972030571215025</v>
       </c>
       <c r="O376" t="n">
-        <v>3.334854541410571</v>
+        <v>3.334852911398641</v>
       </c>
       <c r="P376" t="n">
-        <v>0.6305151672351419</v>
+        <v>0.6305149628638471</v>
       </c>
     </row>
     <row r="377">
@@ -29502,10 +29502,10 @@
         <v>-7.239466051145449e-05</v>
       </c>
       <c r="O377" t="n">
-        <v>0.7034930303980433</v>
+        <v>0.7034928454540115</v>
       </c>
       <c r="P377" t="n">
-        <v>0.194300058795899</v>
+        <v>0.1943000155751613</v>
       </c>
     </row>
     <row r="378">
@@ -29560,10 +29560,10 @@
         <v>-0.0002308350015248761</v>
       </c>
       <c r="O378" t="n">
-        <v>0.7366356760272639</v>
+        <v>0.7366358221936955</v>
       </c>
       <c r="P378" t="n">
-        <v>0.2019956782972903</v>
+        <v>0.2019957120198526</v>
       </c>
     </row>
     <row r="379">
@@ -29615,13 +29615,13 @@
         <v>-0.009795984739367158</v>
       </c>
       <c r="N379" t="n">
-        <v>-0.06528346041972888</v>
+        <v>-0.06528356005744285</v>
       </c>
       <c r="O379" t="n">
-        <v>0.4456420867706703</v>
+        <v>0.4456418484369782</v>
       </c>
       <c r="P379" t="n">
-        <v>0.1307161479054644</v>
+        <v>0.1307160857675003</v>
       </c>
     </row>
     <row r="380">
@@ -29734,10 +29734,10 @@
         <v>0.06581518202889614</v>
       </c>
       <c r="O381" t="n">
-        <v>0.5256480166304509</v>
+        <v>0.5256482163739475</v>
       </c>
       <c r="P381" t="n">
-        <v>0.15120177245319</v>
+        <v>0.1512018226930565</v>
       </c>
     </row>
     <row r="382">
@@ -29844,16 +29844,16 @@
         <v>-0.08609425681287652</v>
       </c>
       <c r="M383" t="n">
-        <v>-0.08174171422422272</v>
+        <v>-0.08174179824965155</v>
       </c>
       <c r="N383" t="n">
-        <v>-0.1821468555798778</v>
+        <v>-0.1821467889250277</v>
       </c>
       <c r="O383" t="n">
-        <v>1.083901714535147</v>
+        <v>1.08390149816094</v>
       </c>
       <c r="P383" t="n">
-        <v>0.277298524995192</v>
+        <v>0.2772984807873387</v>
       </c>
     </row>
     <row r="384">
@@ -29960,10 +29960,10 @@
         <v>0.01233427542156385</v>
       </c>
       <c r="M385" t="n">
-        <v>-0.101354645427718</v>
+        <v>-0.1013547229419631</v>
       </c>
       <c r="N385" t="n">
-        <v>-0.1094368041044561</v>
+        <v>-0.1094367279782099</v>
       </c>
       <c r="O385" t="n">
         <v>1.327329516946998</v>
@@ -30076,10 +30076,10 @@
         <v>-0.03650994505043559</v>
       </c>
       <c r="M387" t="n">
-        <v>-0.1094962233327506</v>
+        <v>-0.1094961239228359</v>
       </c>
       <c r="N387" t="n">
-        <v>-0.06916639546182213</v>
+        <v>-0.06916650407991609</v>
       </c>
       <c r="O387" t="n">
         <v>-0.04912222773861663</v>
@@ -30140,10 +30140,10 @@
         <v>-0.02244521316825931</v>
       </c>
       <c r="O388" t="n">
-        <v>0.5091475853480882</v>
+        <v>0.5091474536707212</v>
       </c>
       <c r="P388" t="n">
-        <v>0.1470364996398013</v>
+        <v>0.1470364662790811</v>
       </c>
     </row>
     <row r="389">
@@ -30198,10 +30198,10 @@
         <v>-0.0421979771402492</v>
       </c>
       <c r="O389" t="n">
-        <v>0.3823185508232101</v>
+        <v>0.3823184439599858</v>
       </c>
       <c r="P389" t="n">
-        <v>0.1139594415361327</v>
+        <v>0.113959412830424</v>
       </c>
     </row>
     <row r="390">
@@ -30250,16 +30250,16 @@
         <v>-0.04187375911683133</v>
       </c>
       <c r="M390" t="n">
-        <v>-0.04303355727747771</v>
+        <v>-0.04303348705048005</v>
       </c>
       <c r="N390" t="n">
         <v>0.02187241453295186</v>
       </c>
       <c r="O390" t="n">
-        <v>0.3306129633295443</v>
+        <v>0.3306128275563274</v>
       </c>
       <c r="P390" t="n">
-        <v>0.09989336799131832</v>
+        <v>0.09989333058097438</v>
       </c>
     </row>
     <row r="391">
@@ -30308,16 +30308,16 @@
         <v>-0.1210767513731689</v>
       </c>
       <c r="M391" t="n">
-        <v>-0.1206935329619381</v>
+        <v>-0.1206936395170941</v>
       </c>
       <c r="N391" t="n">
-        <v>0.09909207823663491</v>
+        <v>0.09909216147665578</v>
       </c>
       <c r="O391" t="n">
-        <v>0.3469124472550342</v>
+        <v>0.3469125722644615</v>
       </c>
       <c r="P391" t="n">
-        <v>0.1043662403952239</v>
+        <v>0.1043662745613119</v>
       </c>
     </row>
     <row r="392">
@@ -30424,16 +30424,16 @@
         <v>-0.05042321555827989</v>
       </c>
       <c r="M393" t="n">
-        <v>-0.09699129964422148</v>
+        <v>-0.09699122808685823</v>
       </c>
       <c r="N393" t="n">
         <v>-0.05767177102037624</v>
       </c>
       <c r="O393" t="n">
-        <v>1.173938756409508</v>
+        <v>1.173938549044726</v>
       </c>
       <c r="P393" t="n">
-        <v>0.295435422798924</v>
+        <v>0.2954353816098316</v>
       </c>
     </row>
     <row r="394">
@@ -30488,10 +30488,10 @@
         <v>-0.08635051929176696</v>
       </c>
       <c r="O394" t="n">
-        <v>0.3957993135178559</v>
+        <v>0.3957992208494572</v>
       </c>
       <c r="P394" t="n">
-        <v>0.1175689493678975</v>
+        <v>0.1175689246357539</v>
       </c>
     </row>
     <row r="395">
@@ -30543,13 +30543,13 @@
         <v>0.00804670435819177</v>
       </c>
       <c r="N395" t="n">
-        <v>0.02729336632121515</v>
+        <v>0.0272933020220536</v>
       </c>
       <c r="O395" t="n">
-        <v>0.4171284561684774</v>
+        <v>0.4171287008858935</v>
       </c>
       <c r="P395" t="n">
-        <v>0.1232327033215768</v>
+        <v>0.123232767976875</v>
       </c>
     </row>
     <row r="396">
@@ -30595,7 +30595,7 @@
         <v>-0.1090880209989542</v>
       </c>
       <c r="L396" t="n">
-        <v>-0.08591142188484335</v>
+        <v>-0.08591136524008203</v>
       </c>
       <c r="M396" t="n">
         <v>-0.02135214600564983</v>
@@ -30656,16 +30656,16 @@
         <v>-0.1228050501221951</v>
       </c>
       <c r="M397" t="n">
-        <v>-0.1545847970126661</v>
+        <v>-0.1545848724649009</v>
       </c>
       <c r="N397" t="n">
-        <v>-0.4784249938248418</v>
+        <v>-0.478425051262342</v>
       </c>
       <c r="O397" t="n">
-        <v>0.4827195049719439</v>
+        <v>0.4827193889286598</v>
       </c>
       <c r="P397" t="n">
-        <v>0.1403014245958618</v>
+        <v>0.1403013948477481</v>
       </c>
     </row>
     <row r="398">
@@ -30720,10 +30720,10 @@
         <v>-0.00444761682732997</v>
       </c>
       <c r="O398" t="n">
-        <v>-0.3962298635000751</v>
+        <v>-0.3962299063538015</v>
       </c>
       <c r="P398" t="n">
-        <v>-0.1548044351669108</v>
+        <v>-0.1548044551633622</v>
       </c>
     </row>
     <row r="399">
@@ -30775,13 +30775,13 @@
         <v>0.007711740165146974</v>
       </c>
       <c r="N399" t="n">
-        <v>0.2814838573784406</v>
+        <v>0.2814840019549381</v>
       </c>
       <c r="O399" t="n">
-        <v>-0.04253462000163366</v>
+        <v>-0.04253453929345119</v>
       </c>
       <c r="P399" t="n">
-        <v>-0.01438411746420676</v>
+        <v>-0.0143840897705112</v>
       </c>
     </row>
     <row r="400">
@@ -30827,7 +30827,7 @@
         <v>-0.08569376257773942</v>
       </c>
       <c r="L400" t="n">
-        <v>-0.1479934573438443</v>
+        <v>-0.1479935257009518</v>
       </c>
       <c r="M400" t="n">
         <v>-0.05460969616243461</v>
@@ -30836,10 +30836,10 @@
         <v>-0.002651374702705267</v>
       </c>
       <c r="O400" t="n">
-        <v>0.5748775699484832</v>
+        <v>0.5748774531703791</v>
       </c>
       <c r="P400" t="n">
-        <v>0.1634532377841316</v>
+        <v>0.1634532090272154</v>
       </c>
     </row>
     <row r="401">
@@ -30943,7 +30943,7 @@
         <v>-0.07371768617529606</v>
       </c>
       <c r="L402" t="n">
-        <v>-0.08547314991681554</v>
+        <v>-0.08547323796586759</v>
       </c>
       <c r="M402" t="n">
         <v>-0.08706503069630933</v>
@@ -30952,10 +30952,10 @@
         <v>-0.07771880466427006</v>
       </c>
       <c r="O402" t="n">
-        <v>0.3301527889406228</v>
+        <v>0.330152695807356</v>
       </c>
       <c r="P402" t="n">
-        <v>0.09976655898644959</v>
+        <v>0.09976653331900853</v>
       </c>
     </row>
     <row r="403">
@@ -31004,16 +31004,16 @@
         <v>-0.04658881500699597</v>
       </c>
       <c r="M403" t="n">
-        <v>-0.163712496299571</v>
+        <v>-0.163712569523405</v>
       </c>
       <c r="N403" t="n">
         <v>-0.1846638507150099</v>
       </c>
       <c r="O403" t="n">
-        <v>0.01052921919426542</v>
+        <v>0.01052911227917863</v>
       </c>
       <c r="P403" t="n">
-        <v>0.003497493013067343</v>
+        <v>0.003497457622691824</v>
       </c>
     </row>
     <row r="404">
@@ -31056,22 +31056,22 @@
         <v>0.02093496261556926</v>
       </c>
       <c r="K404" t="n">
-        <v>-0.1328671283419691</v>
+        <v>-0.1328670263200838</v>
       </c>
       <c r="L404" t="n">
-        <v>-0.09138397053985592</v>
+        <v>-0.09138402654820343</v>
       </c>
       <c r="M404" t="n">
-        <v>-0.02621068181372255</v>
+        <v>-0.02621055315119947</v>
       </c>
       <c r="N404" t="n">
-        <v>0.002017105390884621</v>
+        <v>0.002017173505812098</v>
       </c>
       <c r="O404" t="n">
-        <v>0.3556333293787322</v>
+        <v>0.3556335787271112</v>
       </c>
       <c r="P404" t="n">
-        <v>0.1067446023929215</v>
+        <v>0.1067446702492634</v>
       </c>
     </row>
     <row r="405">
@@ -31120,16 +31120,16 @@
         <v>-0.02440198611813416</v>
       </c>
       <c r="M405" t="n">
-        <v>-0.002790461485818851</v>
+        <v>-0.002790536086355044</v>
       </c>
       <c r="N405" t="n">
         <v>-0.0177054432882422</v>
       </c>
       <c r="O405" t="n">
-        <v>1.170833395081743</v>
+        <v>1.170833571845068</v>
       </c>
       <c r="P405" t="n">
-        <v>0.2948183075854769</v>
+        <v>0.294818342729642</v>
       </c>
     </row>
     <row r="406">
@@ -31236,16 +31236,16 @@
         <v>0.08019858573360428</v>
       </c>
       <c r="M407" t="n">
-        <v>-0.1265538865464714</v>
+        <v>-0.1265538252132016</v>
       </c>
       <c r="N407" t="n">
         <v>-0.1741343744549412</v>
       </c>
       <c r="O407" t="n">
-        <v>-0.1332116268229758</v>
+        <v>-0.1332116872247894</v>
       </c>
       <c r="P407" t="n">
-        <v>-0.04653587034051831</v>
+        <v>-0.0465358924877789</v>
       </c>
     </row>
     <row r="408">
@@ -31294,10 +31294,10 @@
         <v>-0.1332957484024576</v>
       </c>
       <c r="M408" t="n">
-        <v>-0.07968092646438796</v>
+        <v>-0.07968102390838361</v>
       </c>
       <c r="N408" t="n">
-        <v>-0.08070791087815155</v>
+        <v>-0.0807078136514896</v>
       </c>
       <c r="O408" t="n">
         <v>-0.07405916023134351</v>
@@ -31352,16 +31352,16 @@
         <v>0.03166325589980401</v>
       </c>
       <c r="M409" t="n">
-        <v>-0.134926618411993</v>
+        <v>-0.1349266832812985</v>
       </c>
       <c r="N409" t="n">
-        <v>-0.2057368040679862</v>
+        <v>-0.2057368587522326</v>
       </c>
       <c r="O409" t="n">
-        <v>0.1091475065072738</v>
+        <v>0.1091476131452858</v>
       </c>
       <c r="P409" t="n">
-        <v>0.03513367127189815</v>
+        <v>0.0351337044459028</v>
       </c>
     </row>
     <row r="410">
@@ -31416,10 +31416,10 @@
         <v>-0.03844567361975237</v>
       </c>
       <c r="O410" t="n">
-        <v>0.05094296248009833</v>
+        <v>0.05094317599900933</v>
       </c>
       <c r="P410" t="n">
-        <v>0.01670052724828008</v>
+        <v>0.01670059610224661</v>
       </c>
     </row>
     <row r="411">
@@ -31590,10 +31590,10 @@
         <v>-0.03627961585248851</v>
       </c>
       <c r="O413" t="n">
-        <v>0.4317287395127547</v>
+        <v>0.4317286425682274</v>
       </c>
       <c r="P413" t="n">
-        <v>0.127076983381216</v>
+        <v>0.1270769579425173</v>
       </c>
     </row>
     <row r="414">
@@ -31648,10 +31648,10 @@
         <v>-0.1925561071489685</v>
       </c>
       <c r="O414" t="n">
-        <v>-0.004389667125749175</v>
+        <v>-0.004389781918705871</v>
       </c>
       <c r="P414" t="n">
-        <v>-0.001465368631611619</v>
+        <v>-0.001465407008321651</v>
       </c>
     </row>
     <row r="415">
@@ -31700,7 +31700,7 @@
         <v>-0.0702186720971546</v>
       </c>
       <c r="M415" t="n">
-        <v>-0.1143056017536591</v>
+        <v>-0.1143055224307411</v>
       </c>
       <c r="N415" t="n">
         <v>-0.04217010359253215</v>
@@ -31761,13 +31761,13 @@
         <v>-0.1355482191097555</v>
       </c>
       <c r="N416" t="n">
-        <v>-0.0734525705879292</v>
+        <v>-0.07345262832049637</v>
       </c>
       <c r="O416" t="n">
-        <v>0.4787851702195516</v>
+        <v>0.478785023159161</v>
       </c>
       <c r="P416" t="n">
-        <v>0.1392919503465617</v>
+        <v>0.1392919125802636</v>
       </c>
     </row>
     <row r="417">
@@ -31819,13 +31819,13 @@
         <v>-0.05490801858062289</v>
       </c>
       <c r="N417" t="n">
-        <v>-0.0274359924069566</v>
+        <v>-0.02743609669912617</v>
       </c>
       <c r="O417" t="n">
-        <v>0.6503172113315925</v>
+        <v>0.6503170611833735</v>
       </c>
       <c r="P417" t="n">
-        <v>0.1817414704165929</v>
+        <v>0.1817414345777491</v>
       </c>
     </row>
     <row r="418">
@@ -31935,13 +31935,13 @@
         <v>-0.06564470007476619</v>
       </c>
       <c r="N419" t="n">
-        <v>-0.09505885873204278</v>
+        <v>-0.09505893239325203</v>
       </c>
       <c r="O419" t="n">
-        <v>2.327595361812174</v>
+        <v>2.327595610812133</v>
       </c>
       <c r="P419" t="n">
-        <v>0.4929439507971805</v>
+        <v>0.4929439880355795</v>
       </c>
     </row>
     <row r="420">
@@ -31996,10 +31996,10 @@
         <v>-0.02783464213310438</v>
       </c>
       <c r="O420" t="n">
-        <v>0.6174246156530638</v>
+        <v>0.6174247982060552</v>
       </c>
       <c r="P420" t="n">
-        <v>0.173837598750791</v>
+        <v>0.1738376429130875</v>
       </c>
     </row>
     <row r="421">
@@ -32051,13 +32051,13 @@
         <v>-0.1098713833125466</v>
       </c>
       <c r="N421" t="n">
-        <v>0.07279854576835532</v>
+        <v>0.07279863287793442</v>
       </c>
       <c r="O421" t="n">
-        <v>0.04327536489603845</v>
+        <v>0.04327520013392272</v>
       </c>
       <c r="P421" t="n">
-        <v>0.01422190033086168</v>
+        <v>0.01422184693960293</v>
       </c>
     </row>
     <row r="422">
@@ -32106,10 +32106,10 @@
         <v>-0.2272656389148381</v>
       </c>
       <c r="M422" t="n">
-        <v>-0.06039592550467721</v>
+        <v>-0.06039600667426004</v>
       </c>
       <c r="N422" t="n">
-        <v>0.09497474749508528</v>
+        <v>0.09497485772813397</v>
       </c>
       <c r="O422" t="n">
         <v>0.6962246785995359</v>
@@ -32164,16 +32164,16 @@
         <v>-0.08202561183921442</v>
       </c>
       <c r="M423" t="n">
-        <v>-0.08536405546369941</v>
+        <v>-0.08536411013125911</v>
       </c>
       <c r="N423" t="n">
         <v>-0.06259360568246564</v>
       </c>
       <c r="O423" t="n">
-        <v>0.1330512550066805</v>
+        <v>0.1330511711124172</v>
       </c>
       <c r="P423" t="n">
-        <v>0.04251709549352989</v>
+        <v>0.04251706976324177</v>
       </c>
     </row>
     <row r="424">
@@ -32228,10 +32228,10 @@
         <v>-0.01949124252301304</v>
       </c>
       <c r="O424" t="n">
-        <v>0.04379203792220943</v>
+        <v>0.04379214405397769</v>
       </c>
       <c r="P424" t="n">
-        <v>0.01438930088308665</v>
+        <v>0.01438933526379427</v>
       </c>
     </row>
     <row r="425">
@@ -32286,10 +32286,10 @@
         <v>0.1086516473491663</v>
       </c>
       <c r="O425" t="n">
-        <v>0.1079460456202497</v>
+        <v>0.1079461252175742</v>
       </c>
       <c r="P425" t="n">
-        <v>0.03475977391895668</v>
+        <v>0.03475979869877555</v>
       </c>
     </row>
     <row r="426">
@@ -32335,13 +32335,13 @@
         <v>-0.09996356358992142</v>
       </c>
       <c r="L426" t="n">
-        <v>-0.1149071186239405</v>
+        <v>-0.1149071916139414</v>
       </c>
       <c r="M426" t="n">
         <v>-0.1280271736781438</v>
       </c>
       <c r="N426" t="n">
-        <v>-0.06403005545968676</v>
+        <v>-0.06402997383725062</v>
       </c>
       <c r="O426" t="n">
         <v>-0.0274094875328752</v>
@@ -32399,13 +32399,13 @@
         <v>-0.134573710402781</v>
       </c>
       <c r="N427" t="n">
-        <v>-0.246817456206806</v>
+        <v>-0.2468173349054135</v>
       </c>
       <c r="O427" t="n">
-        <v>3.572595865838699</v>
+        <v>3.572595306981535</v>
       </c>
       <c r="P427" t="n">
-        <v>0.6597943164422613</v>
+        <v>0.6597942488229038</v>
       </c>
     </row>
     <row r="428">
@@ -32460,10 +32460,10 @@
         <v>-0.04214742001148042</v>
       </c>
       <c r="O428" t="n">
-        <v>0.8456303161841074</v>
+        <v>0.84563016978711</v>
       </c>
       <c r="P428" t="n">
-        <v>0.2266337365872031</v>
+        <v>0.2266337041546518</v>
       </c>
     </row>
     <row r="429">
@@ -32515,13 +32515,13 @@
         <v>-0.1053431729891168</v>
       </c>
       <c r="N429" t="n">
-        <v>-0.04743702398868588</v>
+        <v>-0.04743709640218774</v>
       </c>
       <c r="O429" t="n">
-        <v>0.4489338720738996</v>
+        <v>0.4489335369856382</v>
       </c>
       <c r="P429" t="n">
-        <v>0.1315737260698564</v>
+        <v>0.1315736388385689</v>
       </c>
     </row>
     <row r="430">
@@ -32573,13 +32573,13 @@
         <v>-0.1774849427300533</v>
       </c>
       <c r="N430" t="n">
-        <v>-0.1969903745326115</v>
+        <v>-0.1969902904796332</v>
       </c>
       <c r="O430" t="n">
-        <v>0.4245346441938003</v>
+        <v>0.4245347764535312</v>
       </c>
       <c r="P430" t="n">
-        <v>0.1251860483595422</v>
+        <v>0.1251860831818612</v>
       </c>
     </row>
     <row r="431">
@@ -32689,7 +32689,7 @@
         <v>-0.09975611729363654</v>
       </c>
       <c r="N432" t="n">
-        <v>-0.32582757224217</v>
+        <v>-0.3258276259871216</v>
       </c>
       <c r="O432" t="n">
         <v>1.374937909599185</v>
@@ -32744,16 +32744,16 @@
         <v>-0.0486985760759171</v>
       </c>
       <c r="M433" t="n">
-        <v>-0.1431567479208493</v>
+        <v>-0.1431568216228379</v>
       </c>
       <c r="N433" t="n">
         <v>-0.1823796344775673</v>
       </c>
       <c r="O433" t="n">
-        <v>0.1955708006980335</v>
+        <v>0.1955705854603733</v>
       </c>
       <c r="P433" t="n">
-        <v>0.06134953325530645</v>
+        <v>0.06134946956399845</v>
       </c>
     </row>
     <row r="434">
@@ -32802,7 +32802,7 @@
         <v>-0.006164486875264386</v>
       </c>
       <c r="M434" t="n">
-        <v>-0.1268210830154541</v>
+        <v>-0.1268210124554504</v>
       </c>
       <c r="N434" t="n">
         <v>-0.08014400235634034</v>
@@ -32866,10 +32866,10 @@
         <v>-0.2647200327588511</v>
       </c>
       <c r="O435" t="n">
-        <v>-0.4136899930127547</v>
+        <v>-0.4136900723675497</v>
       </c>
       <c r="P435" t="n">
-        <v>-0.1630315212860934</v>
+        <v>-0.1630315590462454</v>
       </c>
     </row>
     <row r="436">
@@ -32918,16 +32918,16 @@
         <v>-0.1493101386055748</v>
       </c>
       <c r="M436" t="n">
-        <v>-0.1119068647083408</v>
+        <v>-0.1119068007481406</v>
       </c>
       <c r="N436" t="n">
-        <v>-0.1709819402697094</v>
+        <v>-0.1709818845356381</v>
       </c>
       <c r="O436" t="n">
-        <v>0.02791158858709042</v>
+        <v>0.02791141721732404</v>
       </c>
       <c r="P436" t="n">
-        <v>0.009218618788248145</v>
+        <v>0.00921856270379795</v>
       </c>
     </row>
     <row r="437">
@@ -32936,56 +32936,56 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>KKR &amp; Co.</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Homebuilding</t>
+          <t>Asset Management &amp; Custody Banks</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>83.45</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="G437" t="n">
-        <v>-0.01336018985988718</v>
+        <v>0.0121845383909116</v>
       </c>
       <c r="H437" t="n">
-        <v>0.07400257690911127</v>
+        <v>0.03527315090758543</v>
       </c>
       <c r="I437" t="n">
-        <v>0.1349108980502036</v>
+        <v>0.08691591792090447</v>
       </c>
       <c r="J437" t="n">
-        <v>0.02392433003516348</v>
+        <v>-0.002144969464010438</v>
       </c>
       <c r="K437" t="n">
-        <v>-0.0417283439235987</v>
+        <v>-0.09198522359575501</v>
       </c>
       <c r="L437" t="n">
-        <v>-0.0847772468290271</v>
+        <v>-0.07889821929250718</v>
       </c>
       <c r="M437" t="n">
-        <v>-0.2298905832112123</v>
+        <v>-0.1986821524497253</v>
       </c>
       <c r="N437" t="n">
-        <v>-0.3345778766187788</v>
+        <v>-0.2229959806486483</v>
       </c>
       <c r="O437" t="n">
-        <v>-0.1252165573196494</v>
+        <v>0.7546576357341304</v>
       </c>
       <c r="P437" t="n">
-        <v>-0.0436133216480693</v>
+        <v>0.206139286417478</v>
       </c>
     </row>
     <row r="438">
@@ -32994,56 +32994,56 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>KKR &amp; Co.</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Asset Management &amp; Custody Banks</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F438" t="n">
-        <v>93.04000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="G438" t="n">
-        <v>0.0121845383909116</v>
+        <v>0.008477479065901905</v>
       </c>
       <c r="H438" t="n">
-        <v>0.03527315090758543</v>
+        <v>0.03928984595493601</v>
       </c>
       <c r="I438" t="n">
-        <v>0.08691591792090447</v>
+        <v>0.0368435291856406</v>
       </c>
       <c r="J438" t="n">
-        <v>-0.002144969464010438</v>
+        <v>0.08205105682171854</v>
       </c>
       <c r="K438" t="n">
-        <v>-0.09198522359575501</v>
+        <v>-0.1115449978191183</v>
       </c>
       <c r="L438" t="n">
-        <v>-0.07889821929250718</v>
+        <v>-0.07733115439269733</v>
       </c>
       <c r="M438" t="n">
-        <v>-0.1986821524497253</v>
+        <v>-0.1704657829557757</v>
       </c>
       <c r="N438" t="n">
-        <v>-0.2229959806486483</v>
+        <v>-0.2080107015313001</v>
       </c>
       <c r="O438" t="n">
-        <v>0.7546578882014745</v>
+        <v>-0.1702549195506166</v>
       </c>
       <c r="P438" t="n">
-        <v>0.2061393442655661</v>
+        <v>-0.06031658448599075</v>
       </c>
     </row>
     <row r="439">
@@ -33147,19 +33147,19 @@
         <v>-0.06448025488099685</v>
       </c>
       <c r="L440" t="n">
-        <v>-0.2203261361889705</v>
+        <v>-0.2203262026194261</v>
       </c>
       <c r="M440" t="n">
-        <v>-0.3355401173777527</v>
+        <v>-0.3355400691298013</v>
       </c>
       <c r="N440" t="n">
-        <v>-0.050942254990056</v>
+        <v>-0.05094235341984321</v>
       </c>
       <c r="O440" t="n">
-        <v>0.3938586268344981</v>
+        <v>0.3938584145204629</v>
       </c>
       <c r="P440" t="n">
-        <v>0.1170507619018331</v>
+        <v>0.1170507051850418</v>
       </c>
     </row>
     <row r="441">
@@ -33211,13 +33211,13 @@
         <v>-0.1607477278211715</v>
       </c>
       <c r="N441" t="n">
-        <v>0.05823286761890634</v>
+        <v>0.05823295103845516</v>
       </c>
       <c r="O441" t="n">
-        <v>0.3725283788803282</v>
+        <v>0.3725282385511663</v>
       </c>
       <c r="P441" t="n">
-        <v>0.1113233624902645</v>
+        <v>0.1113233246158609</v>
       </c>
     </row>
     <row r="442">
@@ -33269,7 +33269,7 @@
         <v>-0.1094167803409927</v>
       </c>
       <c r="N442" t="n">
-        <v>-0.1561223449598373</v>
+        <v>-0.156122279342481</v>
       </c>
       <c r="O442" t="n">
         <v>0.6236413225404374</v>
@@ -33324,7 +33324,7 @@
         <v>0.04035488932757225</v>
       </c>
       <c r="M443" t="n">
-        <v>-0.1384432886560155</v>
+        <v>-0.1384433707782059</v>
       </c>
       <c r="N443" t="n">
         <v>-0.2321623091252798</v>
@@ -33342,17 +33342,17 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Home Improvement Retail</t>
+          <t>Homebuilding</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -33361,37 +33361,37 @@
         </is>
       </c>
       <c r="F444" t="n">
-        <v>198.4</v>
+        <v>83.45</v>
       </c>
       <c r="G444" t="n">
-        <v>0.001110108128135057</v>
+        <v>-0.01336018985988718</v>
       </c>
       <c r="H444" t="n">
-        <v>0.00936099084627906</v>
+        <v>0.07400257690911127</v>
       </c>
       <c r="I444" t="n">
-        <v>0.06025752604440804</v>
+        <v>0.1349108980502036</v>
       </c>
       <c r="J444" t="n">
-        <v>0.06392993532225666</v>
+        <v>0.02392433003516348</v>
       </c>
       <c r="K444" t="n">
-        <v>-0.08514898550039385</v>
+        <v>-0.0417283439235987</v>
       </c>
       <c r="L444" t="n">
-        <v>-0.1640687603186768</v>
+        <v>-0.0847772468290271</v>
       </c>
       <c r="M444" t="n">
-        <v>-0.2507783299123119</v>
+        <v>-0.2298905832112123</v>
       </c>
       <c r="N444" t="n">
-        <v>-0.1692471060664387</v>
+        <v>-0.3345779171004276</v>
       </c>
       <c r="O444" t="n">
-        <v>0.1478043985122897</v>
+        <v>-0.1252163474323226</v>
       </c>
       <c r="P444" t="n">
-        <v>0.04702237223624173</v>
+        <v>-0.04361324515926168</v>
       </c>
     </row>
     <row r="445">
@@ -33400,56 +33400,56 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Home Improvement Retail</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F445" t="n">
-        <v>86.84</v>
+        <v>198.4</v>
       </c>
       <c r="G445" t="n">
-        <v>-0.005952429817168703</v>
+        <v>0.001110108128135057</v>
       </c>
       <c r="H445" t="n">
-        <v>0.0244190135283382</v>
+        <v>0.00936099084627906</v>
       </c>
       <c r="I445" t="n">
-        <v>0.02200770966603049</v>
+        <v>0.06025752604440804</v>
       </c>
       <c r="J445" t="n">
-        <v>0.06656838971795231</v>
+        <v>0.06392993532225666</v>
       </c>
       <c r="K445" t="n">
-        <v>-0.1242575961510793</v>
+        <v>-0.08514898550039385</v>
       </c>
       <c r="L445" t="n">
-        <v>-0.09053331956890054</v>
+        <v>-0.1640687603186768</v>
       </c>
       <c r="M445" t="n">
-        <v>-0.182335274453022</v>
+        <v>-0.2507783299123119</v>
       </c>
       <c r="N445" t="n">
-        <v>-0.2193429535540863</v>
+        <v>-0.1692471591453629</v>
       </c>
       <c r="O445" t="n">
-        <v>-0.1821275233255097</v>
+        <v>0.1478046011611924</v>
       </c>
       <c r="P445" t="n">
-        <v>-0.06482002695191935</v>
+        <v>0.04702243385473182</v>
       </c>
     </row>
     <row r="446">
@@ -33559,7 +33559,7 @@
         <v>-0.223250298958832</v>
       </c>
       <c r="N447" t="n">
-        <v>-0.2307340181733876</v>
+        <v>-0.2307340765330248</v>
       </c>
       <c r="O447" t="n">
         <v>-0.04545994541267051</v>
@@ -33678,10 +33678,10 @@
         <v>-0.2770329470895678</v>
       </c>
       <c r="O449" t="n">
-        <v>-0.2053647564630012</v>
+        <v>-0.2053647041665998</v>
       </c>
       <c r="P449" t="n">
-        <v>-0.07376197190773415</v>
+        <v>-0.073761951588594</v>
       </c>
     </row>
     <row r="450">
@@ -33733,7 +33733,7 @@
         <v>-0.2093653315167229</v>
       </c>
       <c r="N450" t="n">
-        <v>-0.1718633245820026</v>
+        <v>-0.171863263938537</v>
       </c>
       <c r="O450" t="n">
         <v>-0.3461087635792576</v>
@@ -33791,13 +33791,13 @@
         <v>-0.1088826869794413</v>
       </c>
       <c r="N451" t="n">
-        <v>-0.003868056617357563</v>
+        <v>-0.003868124672791295</v>
       </c>
       <c r="O451" t="n">
-        <v>3.304189680801618</v>
+        <v>3.304189998453875</v>
       </c>
       <c r="P451" t="n">
-        <v>0.6266612981960789</v>
+        <v>0.6266613382123312</v>
       </c>
     </row>
     <row r="452">
@@ -33843,19 +33843,19 @@
         <v>-0.1420097404769928</v>
       </c>
       <c r="L452" t="n">
-        <v>-0.1907180278074031</v>
+        <v>-0.1907179511138627</v>
       </c>
       <c r="M452" t="n">
         <v>-0.2677341071758245</v>
       </c>
       <c r="N452" t="n">
-        <v>-0.07810572508885993</v>
+        <v>-0.07810582461134286</v>
       </c>
       <c r="O452" t="n">
-        <v>0.6150750230568487</v>
+        <v>0.6150751757833703</v>
       </c>
       <c r="P452" t="n">
-        <v>0.1732689217121031</v>
+        <v>0.1732689586947556</v>
       </c>
     </row>
     <row r="453">
@@ -33965,13 +33965,13 @@
         <v>-0.2123008608294868</v>
       </c>
       <c r="N454" t="n">
-        <v>-0.168554850808162</v>
+        <v>-0.1685549335408337</v>
       </c>
       <c r="O454" t="n">
-        <v>0.3000268458505968</v>
+        <v>0.300027048112735</v>
       </c>
       <c r="P454" t="n">
-        <v>0.09140039566843905</v>
+        <v>0.09140045226956928</v>
       </c>
     </row>
     <row r="455">
@@ -34200,10 +34200,10 @@
         <v>-0.02707723306304854</v>
       </c>
       <c r="O458" t="n">
-        <v>3.567287889278731</v>
+        <v>3.567288296958651</v>
       </c>
       <c r="P458" t="n">
-        <v>0.6591518250439279</v>
+        <v>0.6591518744096843</v>
       </c>
     </row>
     <row r="459">
@@ -34255,7 +34255,7 @@
         <v>-0.4154817583263128</v>
       </c>
       <c r="N459" t="n">
-        <v>-0.4166331500402728</v>
+        <v>-0.4166331911097368</v>
       </c>
       <c r="O459" t="n">
         <v>-0.108338852610811</v>
@@ -34356,13 +34356,13 @@
         <v>-0.3833213198851526</v>
       </c>
       <c r="N461" t="n">
-        <v>-0.5097924095777584</v>
+        <v>-0.5097923648872992</v>
       </c>
       <c r="O461" t="n">
-        <v>-0.297175403397097</v>
+        <v>-0.2971753574647485</v>
       </c>
       <c r="P461" t="n">
-        <v>-0.1109033292892884</v>
+        <v>-0.1109033099206354</v>
       </c>
     </row>
     <row r="462">
@@ -34429,56 +34429,56 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Take-Two Interactive</t>
+          <t>Deckers Brands</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Interactive Home Entertainment</t>
+          <t>Footwear</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F463" t="n">
-        <v>195.29</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="G463" t="n">
-        <v>-0.02975956642235522</v>
+        <v>0.002483200223103443</v>
       </c>
       <c r="H463" t="n">
-        <v>-0.05272608742184648</v>
+        <v>-0.05556205542979709</v>
       </c>
       <c r="I463" t="n">
-        <v>-0.02951847422115383</v>
+        <v>-0.02511472879400023</v>
       </c>
       <c r="J463" t="n">
-        <v>-0.03489010429666672</v>
+        <v>0.03037260381419093</v>
       </c>
       <c r="K463" t="n">
-        <v>-0.2113318910546349</v>
+        <v>-0.2230562039415309</v>
       </c>
       <c r="L463" t="n">
-        <v>-0.08318859057167127</v>
+        <v>-0.2395931660226805</v>
       </c>
       <c r="M463" t="n">
-        <v>-0.1969323169340563</v>
+        <v>-0.1729154313448688</v>
       </c>
       <c r="N463" t="n">
-        <v>-0.2237151186530487</v>
+        <v>-0.07841573677343761</v>
       </c>
       <c r="O463" t="n">
-        <v>0.4527263551753211</v>
+        <v>-0.1594982763475007</v>
       </c>
       <c r="P463" t="n">
-        <v>0.1325601376516412</v>
+        <v>-0.05627338587686137</v>
       </c>
     </row>
     <row r="464">
@@ -34487,56 +34487,56 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Deckers Brands</t>
+          <t>Take-Two Interactive</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>Interactive Home Entertainment</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F464" t="n">
-        <v>80.73999999999999</v>
+        <v>195.29</v>
       </c>
       <c r="G464" t="n">
-        <v>0.002483200223103443</v>
+        <v>-0.02975956642235522</v>
       </c>
       <c r="H464" t="n">
-        <v>-0.05556205542979709</v>
+        <v>-0.05272608742184648</v>
       </c>
       <c r="I464" t="n">
-        <v>-0.02511472879400023</v>
+        <v>-0.02951847422115383</v>
       </c>
       <c r="J464" t="n">
-        <v>0.03037260381419093</v>
+        <v>-0.03489010429666672</v>
       </c>
       <c r="K464" t="n">
-        <v>-0.2230562039415309</v>
+        <v>-0.2113318910546349</v>
       </c>
       <c r="L464" t="n">
-        <v>-0.2395931660226805</v>
+        <v>-0.08318859057167127</v>
       </c>
       <c r="M464" t="n">
-        <v>-0.1729154313448688</v>
+        <v>-0.1969323169340563</v>
       </c>
       <c r="N464" t="n">
-        <v>-0.07841573677343761</v>
+        <v>-0.2237151186530487</v>
       </c>
       <c r="O464" t="n">
-        <v>-0.1594982763475007</v>
+        <v>0.4527263551753211</v>
       </c>
       <c r="P464" t="n">
-        <v>-0.05627338587686137</v>
+        <v>0.1325601376516412</v>
       </c>
     </row>
     <row r="465">
@@ -34640,13 +34640,13 @@
         <v>-0.2573563802044342</v>
       </c>
       <c r="L466" t="n">
-        <v>-0.1855712446948155</v>
+        <v>-0.1855713409026609</v>
       </c>
       <c r="M466" t="n">
-        <v>-0.1104756514119568</v>
+        <v>-0.1104755940280575</v>
       </c>
       <c r="N466" t="n">
-        <v>-0.1735717717841188</v>
+        <v>-0.1735718213159753</v>
       </c>
       <c r="O466" t="n">
         <v>-0.150247765781792</v>
@@ -34707,10 +34707,10 @@
         <v>-0.3278103769335343</v>
       </c>
       <c r="O467" t="n">
-        <v>-0.4880498091888062</v>
+        <v>-0.4880496588797499</v>
       </c>
       <c r="P467" t="n">
-        <v>-0.2000259431271348</v>
+        <v>-0.200025864836098</v>
       </c>
     </row>
     <row r="468">
@@ -34759,16 +34759,16 @@
         <v>-0.213030447972736</v>
       </c>
       <c r="M468" t="n">
-        <v>-0.2436928278329458</v>
+        <v>-0.243692770980184</v>
       </c>
       <c r="N468" t="n">
-        <v>-0.1621972442598184</v>
+        <v>-0.1621971047294526</v>
       </c>
       <c r="O468" t="n">
-        <v>-0.262967279355988</v>
+        <v>-0.2629672253640812</v>
       </c>
       <c r="P468" t="n">
-        <v>-0.09670642130342155</v>
+        <v>-0.09670639924626356</v>
       </c>
     </row>
     <row r="469">
@@ -34893,56 +34893,56 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>T-Mobile US</t>
+          <t>Norwegian Cruise Line Holdings</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Wireless Telecommunication Services</t>
+          <t>Hotels, Resorts &amp; Cruise Lines</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F471" t="n">
-        <v>148.08</v>
+        <v>16.06</v>
       </c>
       <c r="G471" t="n">
-        <v>0.008513246505562844</v>
+        <v>0.01968250577411945</v>
       </c>
       <c r="H471" t="n">
-        <v>-0.03687803687118907</v>
+        <v>0.03014748612920792</v>
       </c>
       <c r="I471" t="n">
-        <v>-0.06153743499735276</v>
+        <v>0.08002687219513449</v>
       </c>
       <c r="J471" t="n">
-        <v>-0.1103634452027036</v>
+        <v>0.122292033194263</v>
       </c>
       <c r="K471" t="n">
-        <v>-0.1834276016195858</v>
+        <v>-0.2431668244289122</v>
       </c>
       <c r="L471" t="n">
-        <v>-0.1980358819813629</v>
+        <v>-0.09724572009858601</v>
       </c>
       <c r="M471" t="n">
-        <v>-0.1921463161367354</v>
+        <v>-0.2275132872193518</v>
       </c>
       <c r="N471" t="n">
-        <v>-0.3126587577023868</v>
+        <v>-0.2814318034975226</v>
       </c>
       <c r="O471" t="n">
-        <v>0.1124391556001494</v>
+        <v>0.2020957993000916</v>
       </c>
       <c r="P471" t="n">
-        <v>0.03615665865395767</v>
+        <v>0.0632768535681727</v>
       </c>
     </row>
     <row r="472">
@@ -34951,56 +34951,56 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Hotels, Resorts &amp; Cruise Lines</t>
+          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>16.06</v>
+        <v>64.37</v>
       </c>
       <c r="G472" t="n">
-        <v>0.01968250577411945</v>
+        <v>0.03339222668940756</v>
       </c>
       <c r="H472" t="n">
-        <v>0.03014748612920792</v>
+        <v>0.2237046199169552</v>
       </c>
       <c r="I472" t="n">
-        <v>0.08002687219513449</v>
+        <v>0.2413169035847746</v>
       </c>
       <c r="J472" t="n">
-        <v>0.122292033194263</v>
+        <v>0.2197817894353493</v>
       </c>
       <c r="K472" t="n">
-        <v>-0.2431668244289122</v>
+        <v>-0.03122612039997452</v>
       </c>
       <c r="L472" t="n">
-        <v>-0.09724572009858601</v>
+        <v>-0.2159349002668967</v>
       </c>
       <c r="M472" t="n">
-        <v>-0.2275132872193518</v>
+        <v>-0.3803755169929735</v>
       </c>
       <c r="N472" t="n">
-        <v>-0.2814318034975226</v>
+        <v>-0.3999355776236294</v>
       </c>
       <c r="O472" t="n">
-        <v>0.2020957993000916</v>
+        <v>0.1572484521291626</v>
       </c>
       <c r="P472" t="n">
-        <v>0.0632768535681727</v>
+        <v>0.0498861409809308</v>
       </c>
     </row>
     <row r="473">
@@ -35009,56 +35009,56 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>T-Mobile US</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Industrial Machinery &amp; Supplies &amp; Components</t>
+          <t>Wireless Telecommunication Services</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>64.37</v>
+        <v>148.08</v>
       </c>
       <c r="G473" t="n">
-        <v>0.03339222668940756</v>
+        <v>0.008513246505562844</v>
       </c>
       <c r="H473" t="n">
-        <v>0.2237046199169552</v>
+        <v>-0.03687803687118907</v>
       </c>
       <c r="I473" t="n">
-        <v>0.2413169035847746</v>
+        <v>-0.06153743499735276</v>
       </c>
       <c r="J473" t="n">
-        <v>0.2197817894353493</v>
+        <v>-0.1103634452027036</v>
       </c>
       <c r="K473" t="n">
-        <v>-0.03122612039997452</v>
+        <v>-0.1834276016195858</v>
       </c>
       <c r="L473" t="n">
-        <v>-0.2159349731305179</v>
+        <v>-0.1980358819813629</v>
       </c>
       <c r="M473" t="n">
-        <v>-0.3803755624984486</v>
+        <v>-0.192146248887227</v>
       </c>
       <c r="N473" t="n">
-        <v>-0.3999355349457989</v>
+        <v>-0.3126587577023868</v>
       </c>
       <c r="O473" t="n">
-        <v>0.1572484521291626</v>
+        <v>0.1124391556001494</v>
       </c>
       <c r="P473" t="n">
-        <v>0.0498861409809308</v>
+        <v>0.03615665865395767</v>
       </c>
     </row>
     <row r="474">
@@ -35168,13 +35168,13 @@
         <v>-0.2998204503260554</v>
       </c>
       <c r="N475" t="n">
-        <v>0.01152065636158439</v>
+        <v>0.01152071753869222</v>
       </c>
       <c r="O475" t="n">
-        <v>0.6799161929610966</v>
+        <v>0.6799158554838123</v>
       </c>
       <c r="P475" t="n">
-        <v>0.1887646226644566</v>
+        <v>0.1887645430610643</v>
       </c>
     </row>
     <row r="476">
@@ -35220,7 +35220,7 @@
         <v>-0.1402735039936595</v>
       </c>
       <c r="L476" t="n">
-        <v>-0.4781433745812004</v>
+        <v>-0.4781434174389965</v>
       </c>
       <c r="M476" t="n">
         <v>-0.4695566740721832</v>
@@ -35345,10 +35345,10 @@
         <v>-0.2711048441468539</v>
       </c>
       <c r="O478" t="n">
-        <v>0.3787200724555708</v>
+        <v>0.3787199744261089</v>
       </c>
       <c r="P478" t="n">
-        <v>0.1129919746244101</v>
+        <v>0.1129919482458364</v>
       </c>
     </row>
     <row r="479">
@@ -35394,19 +35394,19 @@
         <v>-0.03272536519877989</v>
       </c>
       <c r="L479" t="n">
-        <v>-0.2544333314451901</v>
+        <v>-0.2544332632188496</v>
       </c>
       <c r="M479" t="n">
-        <v>-0.3047692566574151</v>
+        <v>-0.3047691973325112</v>
       </c>
       <c r="N479" t="n">
-        <v>-0.5117751653955243</v>
+        <v>-0.5117751946517822</v>
       </c>
       <c r="O479" t="n">
-        <v>-0.2357189472190221</v>
+        <v>-0.2357188038301884</v>
       </c>
       <c r="P479" t="n">
-        <v>-0.08570916913220128</v>
+        <v>-0.08570911195468034</v>
       </c>
     </row>
     <row r="480">
@@ -35455,16 +35455,16 @@
         <v>-0.2380040586145195</v>
       </c>
       <c r="M480" t="n">
-        <v>-0.2853992705547774</v>
+        <v>-0.2853992255353346</v>
       </c>
       <c r="N480" t="n">
-        <v>-0.2703851582466789</v>
+        <v>-0.2703851113156014</v>
       </c>
       <c r="O480" t="n">
-        <v>0.7398715838654606</v>
+        <v>0.7398713169907005</v>
       </c>
       <c r="P480" t="n">
-        <v>0.2027417825732449</v>
+        <v>0.2027417210780089</v>
       </c>
     </row>
     <row r="481">
@@ -35623,7 +35623,7 @@
         <v>-0.1947785360053061</v>
       </c>
       <c r="M483" t="n">
-        <v>-0.3308264331315526</v>
+        <v>-0.3308263865359208</v>
       </c>
       <c r="N483" t="n">
         <v>-0.3531916001991132</v>
@@ -35803,10 +35803,10 @@
         <v>-0.430892669828163</v>
       </c>
       <c r="O486" t="n">
-        <v>-0.5934850921088441</v>
+        <v>-0.5934850581710018</v>
       </c>
       <c r="P486" t="n">
-        <v>-0.2592150356025862</v>
+        <v>-0.2592150149878091</v>
       </c>
     </row>
     <row r="487">
@@ -36136,10 +36136,10 @@
         <v>-0.4055362292646754</v>
       </c>
       <c r="O492" t="n">
-        <v>0.03862585587180356</v>
+        <v>0.03862576259105999</v>
       </c>
       <c r="P492" t="n">
-        <v>0.01271298052662773</v>
+        <v>0.01271295020880525</v>
       </c>
     </row>
     <row r="493">
@@ -36365,13 +36365,13 @@
         <v>-0.4607587599290658</v>
       </c>
       <c r="N496" t="n">
-        <v>-0.3936369407479862</v>
+        <v>-0.3936369826158411</v>
       </c>
       <c r="O496" t="n">
-        <v>-0.03358369468292011</v>
+        <v>-0.03358348197980032</v>
       </c>
       <c r="P496" t="n">
-        <v>-0.01132227498967808</v>
+        <v>-0.01132220245543647</v>
       </c>
     </row>
     <row r="497">
@@ -36478,16 +36478,16 @@
         <v>-0.3244565803271475</v>
       </c>
       <c r="M498" t="n">
-        <v>-0.3630475755022545</v>
+        <v>-0.363047618866072</v>
       </c>
       <c r="N498" t="n">
-        <v>-0.4038197667064612</v>
+        <v>-0.4038198046964062</v>
       </c>
       <c r="O498" t="n">
-        <v>-0.1566352628668772</v>
+        <v>-0.156635110821053</v>
       </c>
       <c r="P498" t="n">
-        <v>-0.05520305693254535</v>
+        <v>-0.05520300015504642</v>
       </c>
     </row>
     <row r="499">
@@ -36600,10 +36600,10 @@
         <v>-0.3284187315630038</v>
       </c>
       <c r="O500" t="n">
-        <v>-0.04516814231232291</v>
+        <v>-0.04516805866935913</v>
       </c>
       <c r="P500" t="n">
-        <v>-0.01528859745790312</v>
+        <v>-0.01528856870443651</v>
       </c>
     </row>
     <row r="501">
@@ -36652,16 +36652,16 @@
         <v>-0.3694707624143804</v>
       </c>
       <c r="M501" t="n">
-        <v>-0.3687257381334086</v>
+        <v>-0.3687256754259967</v>
       </c>
       <c r="N501" t="n">
         <v>-0.4317649005968188</v>
       </c>
       <c r="O501" t="n">
-        <v>1.460021571068639</v>
+        <v>1.460021809136379</v>
       </c>
       <c r="P501" t="n">
-        <v>0.3499353551246678</v>
+        <v>0.3499353986711762</v>
       </c>
     </row>
     <row r="502">
